--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -46,99 +46,99 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>پناهگاه حيات وحش دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع توت سياه</t>
+  </si>
+  <si>
+    <t>پارک ملي قطرويه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع دره باغ</t>
   </si>
   <si>
-    <t>پناهگاه حيات وحش دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع مل بلند</t>
   </si>
   <si>
-    <t>پارک ملي قطرويه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه دراء</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مزايجان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده برم فیروز</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوهستان</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع بصيران</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوهستان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دالان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بناب</t>
   </si>
   <si>
     <t>پارک ملی بمو</t>
   </si>
   <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مهارلو</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع شیکوه</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه دراء</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
     <t>منطقه حفاظت شده ماله گاله</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع بناب</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دالان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع کوه هوا و</t>
   </si>
   <si>
@@ -151,16 +151,16 @@
     <t>منطقه حفاظت شده مارگون</t>
   </si>
   <si>
+    <t>مناطق ممنوعه شکار</t>
+  </si>
+  <si>
     <t>مناطق حفاظت‌شده</t>
   </si>
   <si>
-    <t>مناطق ممنوعه شکار</t>
-  </si>
-  <si>
-    <t>1405-06-22</t>
-  </si>
-  <si>
-    <t>2026-09-13</t>
+    <t>1405-06-23</t>
+  </si>
+  <si>
+    <t>2026-09-14</t>
   </si>
   <si>
     <t>بسیار شدید</t>
@@ -628,16 +628,16 @@
         <v>47</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>87.98999999999999</v>
+        <v>89.94</v>
       </c>
       <c r="G2">
-        <v>100.43</v>
+        <v>96.73999999999999</v>
       </c>
       <c r="H2">
-        <v>110.04</v>
+        <v>103.84</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -657,16 +657,16 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>93.86</v>
+        <v>91.04000000000001</v>
       </c>
       <c r="G3">
-        <v>100</v>
+        <v>94.45</v>
       </c>
       <c r="H3">
-        <v>103.5</v>
+        <v>97.3</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -689,13 +689,13 @@
         <v>4</v>
       </c>
       <c r="F4">
-        <v>89.62</v>
+        <v>92.81999999999999</v>
       </c>
       <c r="G4">
-        <v>92.44</v>
+        <v>92.81999999999999</v>
       </c>
       <c r="H4">
-        <v>93.68000000000001</v>
+        <v>92.81999999999999</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -715,16 +715,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F5">
-        <v>81.02</v>
+        <v>84.04000000000001</v>
       </c>
       <c r="G5">
-        <v>89.79000000000001</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="H5">
-        <v>93.66</v>
+        <v>97.18000000000001</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -744,16 +744,16 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F6">
-        <v>88.15000000000001</v>
+        <v>67.28</v>
       </c>
       <c r="G6">
-        <v>88.15000000000001</v>
+        <v>89.14</v>
       </c>
       <c r="H6">
-        <v>88.15000000000001</v>
+        <v>103.84</v>
       </c>
       <c r="I6" t="s">
         <v>48</v>
@@ -764,7 +764,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
         <v>46</v>
@@ -773,16 +773,16 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>80.31</v>
+        <v>81.72</v>
       </c>
       <c r="G7">
-        <v>88.11</v>
+        <v>84.48</v>
       </c>
       <c r="H7">
-        <v>93.8</v>
+        <v>88.08</v>
       </c>
       <c r="I7" t="s">
         <v>48</v>
@@ -793,7 +793,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
         <v>46</v>
@@ -802,16 +802,16 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="F8">
-        <v>57.88</v>
+        <v>75.42</v>
       </c>
       <c r="G8">
-        <v>87.33</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="H8">
-        <v>106.66</v>
+        <v>89.09</v>
       </c>
       <c r="I8" t="s">
         <v>48</v>
@@ -822,7 +822,7 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
         <v>46</v>
@@ -831,16 +831,16 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="F9">
-        <v>79.98999999999999</v>
+        <v>76.27</v>
       </c>
       <c r="G9">
-        <v>82.76000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="H9">
-        <v>84.92</v>
+        <v>88.78</v>
       </c>
       <c r="I9" t="s">
         <v>48</v>
@@ -851,7 +851,7 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
         <v>46</v>
@@ -860,16 +860,16 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F10">
-        <v>72.64</v>
+        <v>77.36</v>
       </c>
       <c r="G10">
-        <v>79.23999999999999</v>
+        <v>80.73</v>
       </c>
       <c r="H10">
-        <v>88.19</v>
+        <v>85.06</v>
       </c>
       <c r="I10" t="s">
         <v>48</v>
@@ -880,7 +880,7 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
         <v>46</v>
@@ -889,16 +889,16 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F11">
-        <v>73.44</v>
+        <v>75.13</v>
       </c>
       <c r="G11">
-        <v>78.31</v>
+        <v>80.09</v>
       </c>
       <c r="H11">
-        <v>85.14</v>
+        <v>88.12</v>
       </c>
       <c r="I11" t="s">
         <v>48</v>
@@ -909,7 +909,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
         <v>46</v>
@@ -918,16 +918,16 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="F12">
-        <v>72.54000000000001</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="G12">
-        <v>77.92</v>
+        <v>79.86</v>
       </c>
       <c r="H12">
-        <v>83.29000000000001</v>
+        <v>97.61</v>
       </c>
       <c r="I12" t="s">
         <v>48</v>
@@ -938,7 +938,7 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s">
         <v>46</v>
@@ -947,16 +947,16 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>5</v>
+        <v>117</v>
       </c>
       <c r="F13">
-        <v>72.03</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="G13">
-        <v>77.5</v>
+        <v>79.23</v>
       </c>
       <c r="H13">
-        <v>80.26000000000001</v>
+        <v>97.61</v>
       </c>
       <c r="I13" t="s">
         <v>48</v>
@@ -976,16 +976,16 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="F14">
-        <v>65.11</v>
+        <v>72.16</v>
       </c>
       <c r="G14">
-        <v>77.03</v>
+        <v>78.89</v>
       </c>
       <c r="H14">
-        <v>97.58</v>
+        <v>85.34999999999999</v>
       </c>
       <c r="I14" t="s">
         <v>48</v>
@@ -996,7 +996,7 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
         <v>46</v>
@@ -1005,16 +1005,16 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F15">
-        <v>76.64</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="G15">
-        <v>76.64</v>
+        <v>78.7</v>
       </c>
       <c r="H15">
-        <v>76.64</v>
+        <v>83.91</v>
       </c>
       <c r="I15" t="s">
         <v>48</v>
@@ -1025,7 +1025,7 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
         <v>46</v>
@@ -1037,13 +1037,13 @@
         <v>12</v>
       </c>
       <c r="F16">
-        <v>72.83</v>
+        <v>74.08</v>
       </c>
       <c r="G16">
-        <v>76.31</v>
+        <v>77.8</v>
       </c>
       <c r="H16">
-        <v>82.67</v>
+        <v>83.2</v>
       </c>
       <c r="I16" t="s">
         <v>48</v>
@@ -1054,7 +1054,7 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C17" t="s">
         <v>46</v>
@@ -1063,16 +1063,16 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="F17">
-        <v>62.55</v>
+        <v>72.02</v>
       </c>
       <c r="G17">
-        <v>76.22</v>
+        <v>77.61</v>
       </c>
       <c r="H17">
-        <v>97.58</v>
+        <v>82.88</v>
       </c>
       <c r="I17" t="s">
         <v>48</v>
@@ -1092,16 +1092,16 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F18">
-        <v>66.59</v>
+        <v>74.76000000000001</v>
       </c>
       <c r="G18">
-        <v>75.93000000000001</v>
+        <v>77.56999999999999</v>
       </c>
       <c r="H18">
-        <v>86.64</v>
+        <v>82.83</v>
       </c>
       <c r="I18" t="s">
         <v>48</v>
@@ -1112,7 +1112,7 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
         <v>46</v>
@@ -1121,16 +1121,16 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F19">
-        <v>57.45</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="G19">
-        <v>75.91</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="H19">
-        <v>87.26000000000001</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="I19" t="s">
         <v>48</v>
@@ -1141,7 +1141,7 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C20" t="s">
         <v>46</v>
@@ -1150,16 +1150,16 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F20">
-        <v>67.22</v>
+        <v>66.33</v>
       </c>
       <c r="G20">
-        <v>74.91</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="H20">
-        <v>79.97</v>
+        <v>94.58</v>
       </c>
       <c r="I20" t="s">
         <v>48</v>
@@ -1170,7 +1170,7 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C21" t="s">
         <v>46</v>
@@ -1179,16 +1179,16 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F21">
-        <v>70.13</v>
+        <v>70.94</v>
       </c>
       <c r="G21">
-        <v>74.73</v>
+        <v>76.22</v>
       </c>
       <c r="H21">
-        <v>82</v>
+        <v>80.75</v>
       </c>
       <c r="I21" t="s">
         <v>48</v>
@@ -1199,7 +1199,7 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C22" t="s">
         <v>46</v>
@@ -1208,16 +1208,16 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="F22">
-        <v>67.95</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="G22">
-        <v>73.88</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="H22">
-        <v>83.95</v>
+        <v>77.44</v>
       </c>
       <c r="I22" t="s">
         <v>48</v>
@@ -1237,16 +1237,16 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F23">
-        <v>70.09</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="G23">
-        <v>73.27</v>
+        <v>75.87</v>
       </c>
       <c r="H23">
-        <v>77.05</v>
+        <v>84.67</v>
       </c>
       <c r="I23" t="s">
         <v>48</v>
@@ -1266,16 +1266,16 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F24">
-        <v>63.46</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="G24">
-        <v>72.68000000000001</v>
+        <v>75.08</v>
       </c>
       <c r="H24">
-        <v>82.36</v>
+        <v>83.11</v>
       </c>
       <c r="I24" t="s">
         <v>48</v>
@@ -1295,16 +1295,16 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="F25">
-        <v>71.45</v>
+        <v>67.94</v>
       </c>
       <c r="G25">
-        <v>72.54000000000001</v>
+        <v>73.66</v>
       </c>
       <c r="H25">
-        <v>73.62</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="I25" t="s">
         <v>48</v>
@@ -1315,7 +1315,7 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C26" t="s">
         <v>46</v>
@@ -1327,13 +1327,13 @@
         <v>13</v>
       </c>
       <c r="F26">
-        <v>69.48999999999999</v>
+        <v>70.12</v>
       </c>
       <c r="G26">
-        <v>72.53</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="H26">
-        <v>74.93000000000001</v>
+        <v>78.17</v>
       </c>
       <c r="I26" t="s">
         <v>48</v>
@@ -1353,16 +1353,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="F27">
-        <v>64.08</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="G27">
-        <v>72.36</v>
+        <v>72.81</v>
       </c>
       <c r="H27">
-        <v>75.58</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="I27" t="s">
         <v>48</v>
@@ -1373,7 +1373,7 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C28" t="s">
         <v>46</v>
@@ -1385,13 +1385,13 @@
         <v>20</v>
       </c>
       <c r="F28">
-        <v>65.14</v>
+        <v>65</v>
       </c>
       <c r="G28">
-        <v>71.93000000000001</v>
+        <v>72.73999999999999</v>
       </c>
       <c r="H28">
-        <v>82.09</v>
+        <v>84.39</v>
       </c>
       <c r="I28" t="s">
         <v>48</v>
@@ -1402,7 +1402,7 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C29" t="s">
         <v>46</v>
@@ -1411,16 +1411,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F29">
-        <v>64.83</v>
+        <v>69.61</v>
       </c>
       <c r="G29">
-        <v>71.64</v>
+        <v>72.37</v>
       </c>
       <c r="H29">
-        <v>78.48</v>
+        <v>75.14</v>
       </c>
       <c r="I29" t="s">
         <v>48</v>
@@ -1431,7 +1431,7 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C30" t="s">
         <v>46</v>
@@ -1440,16 +1440,16 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F30">
-        <v>66.58</v>
+        <v>61.31</v>
       </c>
       <c r="G30">
         <v>70.91</v>
       </c>
       <c r="H30">
-        <v>76.23</v>
+        <v>77.84</v>
       </c>
       <c r="I30" t="s">
         <v>48</v>
@@ -1460,7 +1460,7 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C31" t="s">
         <v>46</v>
@@ -1469,19 +1469,19 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F31">
-        <v>67.91</v>
+        <v>65.98</v>
       </c>
       <c r="G31">
-        <v>69.81999999999999</v>
+        <v>70.83</v>
       </c>
       <c r="H31">
-        <v>71.43000000000001</v>
+        <v>73.39</v>
       </c>
       <c r="I31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -1498,16 +1498,16 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F32">
-        <v>61.23</v>
+        <v>65.09</v>
       </c>
       <c r="G32">
-        <v>67.09</v>
+        <v>69.42</v>
       </c>
       <c r="H32">
-        <v>72.62</v>
+        <v>74.89</v>
       </c>
       <c r="I32" t="s">
         <v>49</v>
@@ -1518,7 +1518,7 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C33" t="s">
         <v>46</v>
@@ -1530,13 +1530,13 @@
         <v>37</v>
       </c>
       <c r="F33">
-        <v>55.11</v>
+        <v>55.18</v>
       </c>
       <c r="G33">
-        <v>62.76</v>
+        <v>64.42</v>
       </c>
       <c r="H33">
-        <v>74.62</v>
+        <v>78.63</v>
       </c>
       <c r="I33" t="s">
         <v>49</v>
@@ -1547,7 +1547,7 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C34" t="s">
         <v>46</v>
@@ -1559,13 +1559,13 @@
         <v>9</v>
       </c>
       <c r="F34">
-        <v>51.79</v>
+        <v>52.46</v>
       </c>
       <c r="G34">
-        <v>57.6</v>
+        <v>56.83</v>
       </c>
       <c r="H34">
-        <v>62.94</v>
+        <v>64.94</v>
       </c>
       <c r="I34" t="s">
         <v>49</v>
@@ -1576,7 +1576,7 @@
         <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C35" t="s">
         <v>46</v>
@@ -1596,7 +1596,7 @@
         <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C36" t="s">
         <v>46</v>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -46,121 +46,121 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع کوه دراء</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دالان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
     <t>پناهگاه حيات وحش دره باغ</t>
   </si>
   <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوهستان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مزايجان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بناب</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بصيران</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه هوا و</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع شیکوه</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>پارک ملي قطرويه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده برم فیروز</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده هرمود</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع توت سياه</t>
   </si>
   <si>
-    <t>پارک ملي قطرويه</t>
+    <t>منطقه شکار ممن.ع آق جلو</t>
   </si>
   <si>
     <t>منطقه حفاظت شده بهرام گور</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع مل بلند</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه دراء</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوهستان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بصيران</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دالان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بناب</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع مهارلو</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع شیکوه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه هوا و</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده هرمود</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع چاه نفت</t>
   </si>
   <si>
     <t>منطقه حفاظت شده مارگون</t>
   </si>
   <si>
+    <t>مناطق حفاظت‌شده</t>
+  </si>
+  <si>
     <t>مناطق ممنوعه شکار</t>
   </si>
   <si>
-    <t>مناطق حفاظت‌شده</t>
-  </si>
-  <si>
-    <t>1405-06-23</t>
-  </si>
-  <si>
-    <t>2026-09-14</t>
+    <t>1405-06-24</t>
+  </si>
+  <si>
+    <t>2026-09-15</t>
   </si>
   <si>
     <t>بسیار شدید</t>
@@ -628,16 +628,16 @@
         <v>47</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="F2">
-        <v>89.94</v>
+        <v>72.47</v>
       </c>
       <c r="G2">
-        <v>96.73999999999999</v>
+        <v>75.18000000000001</v>
       </c>
       <c r="H2">
-        <v>103.84</v>
+        <v>79.53</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -648,7 +648,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C3" t="s">
         <v>46</v>
@@ -657,16 +657,16 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>91.04000000000001</v>
+        <v>74.12</v>
       </c>
       <c r="G3">
-        <v>94.45</v>
+        <v>74.97</v>
       </c>
       <c r="H3">
-        <v>97.3</v>
+        <v>76.38</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -686,16 +686,16 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F4">
-        <v>92.81999999999999</v>
+        <v>62.06</v>
       </c>
       <c r="G4">
-        <v>92.81999999999999</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="H4">
-        <v>92.81999999999999</v>
+        <v>80.15000000000001</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -706,7 +706,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
         <v>46</v>
@@ -715,16 +715,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>84.04000000000001</v>
+        <v>65.23</v>
       </c>
       <c r="G5">
-        <v>91.18000000000001</v>
+        <v>71.14</v>
       </c>
       <c r="H5">
-        <v>97.18000000000001</v>
+        <v>80.15000000000001</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -744,16 +744,16 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F6">
-        <v>67.28</v>
+        <v>63.48</v>
       </c>
       <c r="G6">
-        <v>89.14</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="H6">
-        <v>103.84</v>
+        <v>77.13</v>
       </c>
       <c r="I6" t="s">
         <v>48</v>
@@ -773,19 +773,19 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>81.72</v>
+        <v>69.2</v>
       </c>
       <c r="G7">
-        <v>84.48</v>
+        <v>69.2</v>
       </c>
       <c r="H7">
-        <v>88.08</v>
+        <v>69.2</v>
       </c>
       <c r="I7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -793,7 +793,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C8" t="s">
         <v>46</v>
@@ -802,19 +802,19 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F8">
-        <v>75.42</v>
+        <v>62.35</v>
       </c>
       <c r="G8">
-        <v>84.31999999999999</v>
+        <v>69</v>
       </c>
       <c r="H8">
-        <v>89.09</v>
+        <v>77.61</v>
       </c>
       <c r="I8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -831,19 +831,19 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F9">
-        <v>76.27</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="G9">
-        <v>81.5</v>
+        <v>68.69</v>
       </c>
       <c r="H9">
-        <v>88.78</v>
+        <v>71.51000000000001</v>
       </c>
       <c r="I9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -851,7 +851,7 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
         <v>46</v>
@@ -860,19 +860,19 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F10">
-        <v>77.36</v>
+        <v>60.82</v>
       </c>
       <c r="G10">
-        <v>80.73</v>
+        <v>68.42</v>
       </c>
       <c r="H10">
-        <v>85.06</v>
+        <v>77.89</v>
       </c>
       <c r="I10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -889,19 +889,19 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="F11">
-        <v>75.13</v>
+        <v>67.03</v>
       </c>
       <c r="G11">
-        <v>80.09</v>
+        <v>67.70999999999999</v>
       </c>
       <c r="H11">
-        <v>88.12</v>
+        <v>68.86</v>
       </c>
       <c r="I11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -918,19 +918,19 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="F12">
-        <v>64.93000000000001</v>
+        <v>62.24</v>
       </c>
       <c r="G12">
-        <v>79.86</v>
+        <v>67.45999999999999</v>
       </c>
       <c r="H12">
-        <v>97.61</v>
+        <v>72.23999999999999</v>
       </c>
       <c r="I12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -947,19 +947,19 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>117</v>
+        <v>27</v>
       </c>
       <c r="F13">
-        <v>64.93000000000001</v>
+        <v>54.98</v>
       </c>
       <c r="G13">
-        <v>79.23</v>
+        <v>67.36</v>
       </c>
       <c r="H13">
-        <v>97.61</v>
+        <v>85.42</v>
       </c>
       <c r="I13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -967,7 +967,7 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
         <v>46</v>
@@ -976,19 +976,19 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="F14">
-        <v>72.16</v>
+        <v>58.04</v>
       </c>
       <c r="G14">
-        <v>78.89</v>
+        <v>67.33</v>
       </c>
       <c r="H14">
-        <v>85.34999999999999</v>
+        <v>78.36</v>
       </c>
       <c r="I14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -996,7 +996,7 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s">
         <v>46</v>
@@ -1005,19 +1005,19 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F15">
-        <v>70.56999999999999</v>
+        <v>58.27</v>
       </c>
       <c r="G15">
-        <v>78.7</v>
+        <v>66.66</v>
       </c>
       <c r="H15">
-        <v>83.91</v>
+        <v>75.98</v>
       </c>
       <c r="I15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1025,7 +1025,7 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
         <v>46</v>
@@ -1034,19 +1034,19 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F16">
-        <v>74.08</v>
+        <v>59.67</v>
       </c>
       <c r="G16">
-        <v>77.8</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="H16">
-        <v>83.2</v>
+        <v>73.17</v>
       </c>
       <c r="I16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1054,7 +1054,7 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
         <v>46</v>
@@ -1063,19 +1063,19 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F17">
-        <v>72.02</v>
+        <v>62.56</v>
       </c>
       <c r="G17">
-        <v>77.61</v>
+        <v>65.73</v>
       </c>
       <c r="H17">
-        <v>82.88</v>
+        <v>70.04000000000001</v>
       </c>
       <c r="I17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1083,7 +1083,7 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C18" t="s">
         <v>46</v>
@@ -1092,19 +1092,19 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="F18">
-        <v>74.76000000000001</v>
+        <v>56.07</v>
       </c>
       <c r="G18">
-        <v>77.56999999999999</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="H18">
-        <v>82.83</v>
+        <v>74.03</v>
       </c>
       <c r="I18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1112,7 +1112,7 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C19" t="s">
         <v>46</v>
@@ -1121,19 +1121,19 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="F19">
-        <v>77.40000000000001</v>
+        <v>60.4</v>
       </c>
       <c r="G19">
-        <v>77.40000000000001</v>
+        <v>65.08</v>
       </c>
       <c r="H19">
-        <v>77.40000000000001</v>
+        <v>71.92</v>
       </c>
       <c r="I19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1150,19 +1150,19 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F20">
-        <v>66.33</v>
+        <v>59.96</v>
       </c>
       <c r="G20">
-        <v>77.09999999999999</v>
+        <v>64.81999999999999</v>
       </c>
       <c r="H20">
-        <v>94.58</v>
+        <v>69.14</v>
       </c>
       <c r="I20" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1170,7 +1170,7 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C21" t="s">
         <v>46</v>
@@ -1179,19 +1179,19 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F21">
-        <v>70.94</v>
+        <v>58.92</v>
       </c>
       <c r="G21">
-        <v>76.22</v>
+        <v>63.41</v>
       </c>
       <c r="H21">
-        <v>80.75</v>
+        <v>67.01000000000001</v>
       </c>
       <c r="I21" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -1208,19 +1208,19 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="F22">
-        <v>74.04000000000001</v>
+        <v>53.69</v>
       </c>
       <c r="G22">
-        <v>76.09999999999999</v>
+        <v>63.38</v>
       </c>
       <c r="H22">
-        <v>77.44</v>
+        <v>78.31999999999999</v>
       </c>
       <c r="I22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1228,7 +1228,7 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C23" t="s">
         <v>46</v>
@@ -1237,19 +1237,19 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F23">
-        <v>68.90000000000001</v>
+        <v>54.53</v>
       </c>
       <c r="G23">
-        <v>75.87</v>
+        <v>63.23</v>
       </c>
       <c r="H23">
-        <v>84.67</v>
+        <v>68.28</v>
       </c>
       <c r="I23" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -1257,7 +1257,7 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C24" t="s">
         <v>46</v>
@@ -1266,19 +1266,19 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>19</v>
+        <v>117</v>
       </c>
       <c r="F24">
-        <v>64.73999999999999</v>
+        <v>53.69</v>
       </c>
       <c r="G24">
-        <v>75.08</v>
+        <v>62.79</v>
       </c>
       <c r="H24">
-        <v>83.11</v>
+        <v>78.31999999999999</v>
       </c>
       <c r="I24" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -1286,7 +1286,7 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C25" t="s">
         <v>46</v>
@@ -1295,19 +1295,19 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F25">
-        <v>67.94</v>
+        <v>62.48</v>
       </c>
       <c r="G25">
-        <v>73.66</v>
+        <v>62.48</v>
       </c>
       <c r="H25">
-        <v>82.90000000000001</v>
+        <v>62.48</v>
       </c>
       <c r="I25" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -1324,19 +1324,19 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F26">
-        <v>70.12</v>
+        <v>56.9</v>
       </c>
       <c r="G26">
-        <v>73.06999999999999</v>
+        <v>61.64</v>
       </c>
       <c r="H26">
-        <v>78.17</v>
+        <v>67.45999999999999</v>
       </c>
       <c r="I26" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -1353,19 +1353,19 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>62</v>
+        <v>16</v>
       </c>
       <c r="F27">
-        <v>64.20999999999999</v>
+        <v>52.5</v>
       </c>
       <c r="G27">
-        <v>72.81</v>
+        <v>61.51</v>
       </c>
       <c r="H27">
-        <v>88.59999999999999</v>
+        <v>71.61</v>
       </c>
       <c r="I27" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -1382,19 +1382,19 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F28">
-        <v>65</v>
+        <v>59.51</v>
       </c>
       <c r="G28">
-        <v>72.73999999999999</v>
+        <v>60.98</v>
       </c>
       <c r="H28">
-        <v>84.39</v>
+        <v>62.52</v>
       </c>
       <c r="I28" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -1402,7 +1402,7 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C29" t="s">
         <v>46</v>
@@ -1411,19 +1411,19 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F29">
-        <v>69.61</v>
+        <v>55.27</v>
       </c>
       <c r="G29">
-        <v>72.37</v>
+        <v>60.33</v>
       </c>
       <c r="H29">
-        <v>75.14</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="I29" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -1431,7 +1431,7 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C30" t="s">
         <v>46</v>
@@ -1440,19 +1440,19 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F30">
-        <v>61.31</v>
+        <v>56.62</v>
       </c>
       <c r="G30">
-        <v>70.91</v>
+        <v>59.87</v>
       </c>
       <c r="H30">
-        <v>77.84</v>
+        <v>63.59</v>
       </c>
       <c r="I30" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -1460,7 +1460,7 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C31" t="s">
         <v>46</v>
@@ -1469,19 +1469,19 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F31">
-        <v>65.98</v>
+        <v>55.62</v>
       </c>
       <c r="G31">
-        <v>70.83</v>
+        <v>59.46</v>
       </c>
       <c r="H31">
-        <v>73.39</v>
+        <v>63.3</v>
       </c>
       <c r="I31" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -1489,7 +1489,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C32" t="s">
         <v>46</v>
@@ -1498,16 +1498,16 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F32">
-        <v>65.09</v>
+        <v>54.39</v>
       </c>
       <c r="G32">
-        <v>69.42</v>
+        <v>59.4</v>
       </c>
       <c r="H32">
-        <v>74.89</v>
+        <v>77.03</v>
       </c>
       <c r="I32" t="s">
         <v>49</v>
@@ -1518,7 +1518,7 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C33" t="s">
         <v>46</v>
@@ -1527,16 +1527,16 @@
         <v>47</v>
       </c>
       <c r="E33">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="F33">
-        <v>55.18</v>
+        <v>54.22</v>
       </c>
       <c r="G33">
-        <v>64.42</v>
+        <v>59.37</v>
       </c>
       <c r="H33">
-        <v>78.63</v>
+        <v>64.61</v>
       </c>
       <c r="I33" t="s">
         <v>49</v>
@@ -1556,16 +1556,16 @@
         <v>47</v>
       </c>
       <c r="E34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F34">
-        <v>52.46</v>
+        <v>53.91</v>
       </c>
       <c r="G34">
-        <v>56.83</v>
+        <v>56.99</v>
       </c>
       <c r="H34">
-        <v>64.94</v>
+        <v>63.97</v>
       </c>
       <c r="I34" t="s">
         <v>49</v>
@@ -1576,7 +1576,7 @@
         <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C35" t="s">
         <v>46</v>
@@ -1596,7 +1596,7 @@
         <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C36" t="s">
         <v>46</v>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -49,102 +49,102 @@
     <t>منطقه شکار ممنوع کوه دراء</t>
   </si>
   <si>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع دالان</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
   </si>
   <si>
     <t>پناهگاه حيات وحش دره باغ</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
+    <t>منطقه شکار ممنوع بناب</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده برم فیروز</t>
+  </si>
+  <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بصيران</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع توت سياه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع شیکوه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>پارک ملي قطرويه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه هوا و</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مزايجان</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده هرمود</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مهارلو</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع کوهستان</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بناب</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بصيران</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه هوا و</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع شیکوه</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>پارک ملي قطرويه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده هرمود</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع چاه نفت</t>
   </si>
   <si>
@@ -157,10 +157,10 @@
     <t>مناطق ممنوعه شکار</t>
   </si>
   <si>
-    <t>1405-06-24</t>
-  </si>
-  <si>
-    <t>2026-09-15</t>
+    <t>1405-06-25</t>
+  </si>
+  <si>
+    <t>2026-09-16</t>
   </si>
   <si>
     <t>بسیار شدید</t>
@@ -631,13 +631,13 @@
         <v>33</v>
       </c>
       <c r="F2">
-        <v>72.47</v>
+        <v>65.95999999999999</v>
       </c>
       <c r="G2">
-        <v>75.18000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="H2">
-        <v>79.53</v>
+        <v>83.03</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -648,7 +648,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s">
         <v>46</v>
@@ -657,16 +657,16 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>74.12</v>
+        <v>70.68000000000001</v>
       </c>
       <c r="G3">
-        <v>74.97</v>
+        <v>71.72</v>
       </c>
       <c r="H3">
-        <v>76.38</v>
+        <v>72.63</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -689,13 +689,13 @@
         <v>12</v>
       </c>
       <c r="F4">
-        <v>62.06</v>
+        <v>63.55</v>
       </c>
       <c r="G4">
-        <v>71.79000000000001</v>
+        <v>70.29000000000001</v>
       </c>
       <c r="H4">
-        <v>80.15000000000001</v>
+        <v>77.01000000000001</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -706,7 +706,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
         <v>46</v>
@@ -715,16 +715,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F5">
-        <v>65.23</v>
+        <v>56.82</v>
       </c>
       <c r="G5">
-        <v>71.14</v>
+        <v>70.09</v>
       </c>
       <c r="H5">
-        <v>80.15000000000001</v>
+        <v>86.66</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -735,7 +735,7 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
         <v>46</v>
@@ -744,19 +744,19 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>63.48</v>
+        <v>69.23999999999999</v>
       </c>
       <c r="G6">
-        <v>70.09999999999999</v>
+        <v>69.97</v>
       </c>
       <c r="H6">
-        <v>77.13</v>
+        <v>70.53</v>
       </c>
       <c r="I6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -773,16 +773,16 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="F7">
-        <v>69.2</v>
+        <v>63.64</v>
       </c>
       <c r="G7">
-        <v>69.2</v>
+        <v>69.95999999999999</v>
       </c>
       <c r="H7">
-        <v>69.2</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="I7" t="s">
         <v>49</v>
@@ -802,16 +802,16 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F8">
-        <v>62.35</v>
+        <v>62.92</v>
       </c>
       <c r="G8">
-        <v>69</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="H8">
-        <v>77.61</v>
+        <v>76.39</v>
       </c>
       <c r="I8" t="s">
         <v>49</v>
@@ -822,7 +822,7 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s">
         <v>46</v>
@@ -831,16 +831,16 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F9">
-        <v>64.56999999999999</v>
+        <v>61.61</v>
       </c>
       <c r="G9">
-        <v>68.69</v>
+        <v>69</v>
       </c>
       <c r="H9">
-        <v>71.51000000000001</v>
+        <v>76.45</v>
       </c>
       <c r="I9" t="s">
         <v>49</v>
@@ -860,16 +860,16 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F10">
-        <v>60.82</v>
+        <v>65.27</v>
       </c>
       <c r="G10">
-        <v>68.42</v>
+        <v>68.27</v>
       </c>
       <c r="H10">
-        <v>77.89</v>
+        <v>72.5</v>
       </c>
       <c r="I10" t="s">
         <v>49</v>
@@ -880,7 +880,7 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s">
         <v>46</v>
@@ -889,16 +889,16 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="F11">
-        <v>67.03</v>
+        <v>53.83</v>
       </c>
       <c r="G11">
-        <v>67.70999999999999</v>
+        <v>67.63</v>
       </c>
       <c r="H11">
-        <v>68.86</v>
+        <v>74.73</v>
       </c>
       <c r="I11" t="s">
         <v>49</v>
@@ -909,7 +909,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
         <v>46</v>
@@ -918,16 +918,16 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F12">
-        <v>62.24</v>
+        <v>60.9</v>
       </c>
       <c r="G12">
-        <v>67.45999999999999</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="H12">
-        <v>72.23999999999999</v>
+        <v>75.56</v>
       </c>
       <c r="I12" t="s">
         <v>49</v>
@@ -947,16 +947,16 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F13">
-        <v>54.98</v>
+        <v>60.19</v>
       </c>
       <c r="G13">
-        <v>67.36</v>
+        <v>67.06</v>
       </c>
       <c r="H13">
-        <v>85.42</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="I13" t="s">
         <v>49</v>
@@ -967,7 +967,7 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
         <v>46</v>
@@ -976,16 +976,16 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="F14">
-        <v>58.04</v>
+        <v>60.67</v>
       </c>
       <c r="G14">
-        <v>67.33</v>
+        <v>67.03</v>
       </c>
       <c r="H14">
-        <v>78.36</v>
+        <v>71.78</v>
       </c>
       <c r="I14" t="s">
         <v>49</v>
@@ -996,7 +996,7 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
         <v>46</v>
@@ -1005,16 +1005,16 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F15">
-        <v>58.27</v>
+        <v>61.68</v>
       </c>
       <c r="G15">
-        <v>66.66</v>
+        <v>66.44</v>
       </c>
       <c r="H15">
-        <v>75.98</v>
+        <v>69.19</v>
       </c>
       <c r="I15" t="s">
         <v>49</v>
@@ -1025,7 +1025,7 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
         <v>46</v>
@@ -1037,13 +1037,13 @@
         <v>20</v>
       </c>
       <c r="F16">
-        <v>59.67</v>
+        <v>58.62</v>
       </c>
       <c r="G16">
-        <v>66.65000000000001</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="H16">
-        <v>73.17</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="I16" t="s">
         <v>49</v>
@@ -1054,7 +1054,7 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C17" t="s">
         <v>46</v>
@@ -1063,16 +1063,16 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F17">
-        <v>62.56</v>
+        <v>59.82</v>
       </c>
       <c r="G17">
-        <v>65.73</v>
+        <v>65.5</v>
       </c>
       <c r="H17">
-        <v>70.04000000000001</v>
+        <v>74.18000000000001</v>
       </c>
       <c r="I17" t="s">
         <v>49</v>
@@ -1092,16 +1092,16 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="F18">
-        <v>56.07</v>
+        <v>56.33</v>
       </c>
       <c r="G18">
-        <v>65.56999999999999</v>
+        <v>65.3</v>
       </c>
       <c r="H18">
-        <v>74.03</v>
+        <v>92.43000000000001</v>
       </c>
       <c r="I18" t="s">
         <v>49</v>
@@ -1121,16 +1121,16 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F19">
-        <v>60.4</v>
+        <v>57.61</v>
       </c>
       <c r="G19">
-        <v>65.08</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="H19">
-        <v>71.92</v>
+        <v>67.68000000000001</v>
       </c>
       <c r="I19" t="s">
         <v>49</v>
@@ -1141,7 +1141,7 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C20" t="s">
         <v>46</v>
@@ -1150,16 +1150,16 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F20">
-        <v>59.96</v>
+        <v>58.72</v>
       </c>
       <c r="G20">
-        <v>64.81999999999999</v>
+        <v>64.02</v>
       </c>
       <c r="H20">
-        <v>69.14</v>
+        <v>70.34</v>
       </c>
       <c r="I20" t="s">
         <v>49</v>
@@ -1182,13 +1182,13 @@
         <v>3</v>
       </c>
       <c r="F21">
-        <v>58.92</v>
+        <v>56.52</v>
       </c>
       <c r="G21">
-        <v>63.41</v>
+        <v>63.65</v>
       </c>
       <c r="H21">
-        <v>67.01000000000001</v>
+        <v>67.73</v>
       </c>
       <c r="I21" t="s">
         <v>49</v>
@@ -1208,16 +1208,16 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="F22">
-        <v>53.69</v>
+        <v>55.39</v>
       </c>
       <c r="G22">
-        <v>63.38</v>
+        <v>62.78</v>
       </c>
       <c r="H22">
-        <v>78.31999999999999</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="I22" t="s">
         <v>49</v>
@@ -1228,7 +1228,7 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C23" t="s">
         <v>46</v>
@@ -1237,16 +1237,16 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="F23">
-        <v>54.53</v>
+        <v>54.37</v>
       </c>
       <c r="G23">
-        <v>63.23</v>
+        <v>62.67</v>
       </c>
       <c r="H23">
-        <v>68.28</v>
+        <v>75.63</v>
       </c>
       <c r="I23" t="s">
         <v>49</v>
@@ -1266,16 +1266,16 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>117</v>
+        <v>4</v>
       </c>
       <c r="F24">
-        <v>53.69</v>
+        <v>62.58</v>
       </c>
       <c r="G24">
-        <v>62.79</v>
+        <v>62.58</v>
       </c>
       <c r="H24">
-        <v>78.31999999999999</v>
+        <v>62.58</v>
       </c>
       <c r="I24" t="s">
         <v>49</v>
@@ -1286,7 +1286,7 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C25" t="s">
         <v>46</v>
@@ -1295,16 +1295,16 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="F25">
-        <v>62.48</v>
+        <v>54.59</v>
       </c>
       <c r="G25">
-        <v>62.48</v>
+        <v>62.21</v>
       </c>
       <c r="H25">
-        <v>62.48</v>
+        <v>73.42</v>
       </c>
       <c r="I25" t="s">
         <v>49</v>
@@ -1315,7 +1315,7 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s">
         <v>46</v>
@@ -1324,16 +1324,16 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F26">
-        <v>56.9</v>
+        <v>59.53</v>
       </c>
       <c r="G26">
-        <v>61.64</v>
+        <v>62.17</v>
       </c>
       <c r="H26">
-        <v>67.45999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="I26" t="s">
         <v>49</v>
@@ -1353,16 +1353,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>16</v>
+        <v>117</v>
       </c>
       <c r="F27">
-        <v>52.5</v>
+        <v>54.37</v>
       </c>
       <c r="G27">
-        <v>61.51</v>
+        <v>62.13</v>
       </c>
       <c r="H27">
-        <v>71.61</v>
+        <v>75.63</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1385,13 +1385,13 @@
         <v>9</v>
       </c>
       <c r="F28">
-        <v>59.51</v>
+        <v>57.11</v>
       </c>
       <c r="G28">
-        <v>60.98</v>
+        <v>61.16</v>
       </c>
       <c r="H28">
-        <v>62.52</v>
+        <v>67.97</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
@@ -1402,7 +1402,7 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C29" t="s">
         <v>46</v>
@@ -1411,16 +1411,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F29">
-        <v>55.27</v>
+        <v>54.69</v>
       </c>
       <c r="G29">
-        <v>60.33</v>
+        <v>60.32</v>
       </c>
       <c r="H29">
-        <v>66.59999999999999</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="I29" t="s">
         <v>49</v>
@@ -1440,16 +1440,16 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F30">
-        <v>56.62</v>
+        <v>55.97</v>
       </c>
       <c r="G30">
-        <v>59.87</v>
+        <v>59.94</v>
       </c>
       <c r="H30">
-        <v>63.59</v>
+        <v>64.19</v>
       </c>
       <c r="I30" t="s">
         <v>49</v>
@@ -1469,16 +1469,16 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F31">
-        <v>55.62</v>
+        <v>54.91</v>
       </c>
       <c r="G31">
-        <v>59.46</v>
+        <v>59.47</v>
       </c>
       <c r="H31">
-        <v>63.3</v>
+        <v>64.41</v>
       </c>
       <c r="I31" t="s">
         <v>49</v>
@@ -1489,7 +1489,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C32" t="s">
         <v>46</v>
@@ -1498,16 +1498,16 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="F32">
-        <v>54.39</v>
+        <v>54.81</v>
       </c>
       <c r="G32">
-        <v>59.4</v>
+        <v>58.66</v>
       </c>
       <c r="H32">
-        <v>77.03</v>
+        <v>62.51</v>
       </c>
       <c r="I32" t="s">
         <v>49</v>
@@ -1527,16 +1527,16 @@
         <v>47</v>
       </c>
       <c r="E33">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F33">
-        <v>54.22</v>
+        <v>54.55</v>
       </c>
       <c r="G33">
-        <v>59.37</v>
+        <v>57.73</v>
       </c>
       <c r="H33">
-        <v>64.61</v>
+        <v>65.61</v>
       </c>
       <c r="I33" t="s">
         <v>49</v>
@@ -1556,16 +1556,16 @@
         <v>47</v>
       </c>
       <c r="E34">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F34">
-        <v>53.91</v>
+        <v>56.08</v>
       </c>
       <c r="G34">
-        <v>56.99</v>
+        <v>56.08</v>
       </c>
       <c r="H34">
-        <v>63.97</v>
+        <v>56.08</v>
       </c>
       <c r="I34" t="s">
         <v>49</v>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -46,121 +46,121 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده برم فیروز</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع کوه دراء</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دالان</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع روشن کوه</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بناب</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بصيران</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مزايجان</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع دره باغ</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع دالان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع توت سياه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده هرمود</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوهستان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه هوا و</t>
+  </si>
+  <si>
+    <t>پارک ملي قطرويه</t>
   </si>
   <si>
     <t>پناهگاه حيات وحش دره باغ</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع بناب</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بصيران</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مهارلو</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع شیکوه</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>پارک ملي قطرويه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه هوا و</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده هرمود</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوهستان</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع چاه نفت</t>
   </si>
   <si>
     <t>منطقه حفاظت شده مارگون</t>
   </si>
   <si>
+    <t>مناطق ممنوعه شکار</t>
+  </si>
+  <si>
     <t>مناطق حفاظت‌شده</t>
   </si>
   <si>
-    <t>مناطق ممنوعه شکار</t>
-  </si>
-  <si>
-    <t>1405-06-25</t>
-  </si>
-  <si>
-    <t>2026-09-16</t>
+    <t>1405-06-26</t>
+  </si>
+  <si>
+    <t>2026-09-17</t>
   </si>
   <si>
     <t>بسیار شدید</t>
@@ -628,16 +628,16 @@
         <v>47</v>
       </c>
       <c r="E2">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>65.95999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="G2">
-        <v>73.33</v>
+        <v>75.06999999999999</v>
       </c>
       <c r="H2">
-        <v>83.03</v>
+        <v>78.09</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -648,7 +648,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C3" t="s">
         <v>46</v>
@@ -657,16 +657,16 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>70.68000000000001</v>
+        <v>70.77</v>
       </c>
       <c r="G3">
-        <v>71.72</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="H3">
-        <v>72.63</v>
+        <v>78.09</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -677,7 +677,7 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C4" t="s">
         <v>46</v>
@@ -686,16 +686,16 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>63.55</v>
+        <v>71.45999999999999</v>
       </c>
       <c r="G4">
-        <v>70.29000000000001</v>
+        <v>74.77</v>
       </c>
       <c r="H4">
-        <v>77.01000000000001</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -715,16 +715,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>56.82</v>
+        <v>73.36</v>
       </c>
       <c r="G5">
-        <v>70.09</v>
+        <v>73.87</v>
       </c>
       <c r="H5">
-        <v>86.66</v>
+        <v>74.61</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -735,7 +735,7 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s">
         <v>46</v>
@@ -744,19 +744,19 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F6">
-        <v>69.23999999999999</v>
+        <v>67.28</v>
       </c>
       <c r="G6">
-        <v>69.97</v>
+        <v>72.88</v>
       </c>
       <c r="H6">
-        <v>70.53</v>
+        <v>77.2</v>
       </c>
       <c r="I6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -764,7 +764,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
         <v>46</v>
@@ -773,19 +773,19 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F7">
-        <v>63.64</v>
+        <v>64.53</v>
       </c>
       <c r="G7">
-        <v>69.95999999999999</v>
+        <v>72.62</v>
       </c>
       <c r="H7">
-        <v>76.98999999999999</v>
+        <v>82.92</v>
       </c>
       <c r="I7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -793,7 +793,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
         <v>46</v>
@@ -802,19 +802,19 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F8">
-        <v>62.92</v>
+        <v>70.48</v>
       </c>
       <c r="G8">
-        <v>69.43000000000001</v>
+        <v>71.01000000000001</v>
       </c>
       <c r="H8">
-        <v>76.39</v>
+        <v>71.2</v>
       </c>
       <c r="I8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -831,19 +831,19 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F9">
-        <v>61.61</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="G9">
-        <v>69</v>
+        <v>70.89</v>
       </c>
       <c r="H9">
-        <v>76.45</v>
+        <v>77.09</v>
       </c>
       <c r="I9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -860,19 +860,19 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F10">
-        <v>65.27</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="G10">
-        <v>68.27</v>
+        <v>70.87</v>
       </c>
       <c r="H10">
-        <v>72.5</v>
+        <v>77.48</v>
       </c>
       <c r="I10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -889,19 +889,19 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="F11">
-        <v>53.83</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="G11">
-        <v>67.63</v>
+        <v>70.25</v>
       </c>
       <c r="H11">
-        <v>74.73</v>
+        <v>72.67</v>
       </c>
       <c r="I11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -909,7 +909,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
         <v>46</v>
@@ -918,16 +918,16 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="F12">
-        <v>60.9</v>
+        <v>65.45</v>
       </c>
       <c r="G12">
-        <v>67.54000000000001</v>
+        <v>69.88</v>
       </c>
       <c r="H12">
-        <v>75.56</v>
+        <v>76.12</v>
       </c>
       <c r="I12" t="s">
         <v>49</v>
@@ -938,7 +938,7 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
         <v>46</v>
@@ -947,16 +947,16 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="F13">
-        <v>60.19</v>
+        <v>60.91</v>
       </c>
       <c r="G13">
-        <v>67.06</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="H13">
-        <v>73.54000000000001</v>
+        <v>76.03</v>
       </c>
       <c r="I13" t="s">
         <v>49</v>
@@ -967,7 +967,7 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
         <v>46</v>
@@ -976,16 +976,16 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F14">
-        <v>60.67</v>
+        <v>60.98</v>
       </c>
       <c r="G14">
-        <v>67.03</v>
+        <v>68.39</v>
       </c>
       <c r="H14">
-        <v>71.78</v>
+        <v>72.09</v>
       </c>
       <c r="I14" t="s">
         <v>49</v>
@@ -1005,16 +1005,16 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F15">
-        <v>61.68</v>
+        <v>63.93</v>
       </c>
       <c r="G15">
-        <v>66.44</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="H15">
-        <v>69.19</v>
+        <v>70.84</v>
       </c>
       <c r="I15" t="s">
         <v>49</v>
@@ -1034,16 +1034,16 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F16">
-        <v>58.62</v>
+        <v>67.06</v>
       </c>
       <c r="G16">
-        <v>65.70999999999999</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="H16">
-        <v>69.31999999999999</v>
+        <v>68.84999999999999</v>
       </c>
       <c r="I16" t="s">
         <v>49</v>
@@ -1054,7 +1054,7 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
         <v>46</v>
@@ -1066,13 +1066,13 @@
         <v>20</v>
       </c>
       <c r="F17">
-        <v>59.82</v>
+        <v>61.91</v>
       </c>
       <c r="G17">
-        <v>65.5</v>
+        <v>67.16</v>
       </c>
       <c r="H17">
-        <v>74.18000000000001</v>
+        <v>71.29000000000001</v>
       </c>
       <c r="I17" t="s">
         <v>49</v>
@@ -1083,7 +1083,7 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
         <v>46</v>
@@ -1092,16 +1092,16 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F18">
-        <v>56.33</v>
+        <v>58.63</v>
       </c>
       <c r="G18">
-        <v>65.3</v>
+        <v>66.36</v>
       </c>
       <c r="H18">
-        <v>92.43000000000001</v>
+        <v>73.47</v>
       </c>
       <c r="I18" t="s">
         <v>49</v>
@@ -1121,16 +1121,16 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F19">
-        <v>57.61</v>
+        <v>61.8</v>
       </c>
       <c r="G19">
-        <v>64.56999999999999</v>
+        <v>66.19</v>
       </c>
       <c r="H19">
-        <v>67.68000000000001</v>
+        <v>74.55</v>
       </c>
       <c r="I19" t="s">
         <v>49</v>
@@ -1141,7 +1141,7 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C20" t="s">
         <v>46</v>
@@ -1150,16 +1150,16 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="F20">
-        <v>58.72</v>
+        <v>55.56</v>
       </c>
       <c r="G20">
-        <v>64.02</v>
+        <v>64.72</v>
       </c>
       <c r="H20">
-        <v>70.34</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="I20" t="s">
         <v>49</v>
@@ -1179,16 +1179,16 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="F21">
-        <v>56.52</v>
+        <v>59.05</v>
       </c>
       <c r="G21">
-        <v>63.65</v>
+        <v>64.48999999999999</v>
       </c>
       <c r="H21">
-        <v>67.73</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="I21" t="s">
         <v>49</v>
@@ -1208,16 +1208,16 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F22">
-        <v>55.39</v>
+        <v>58.94</v>
       </c>
       <c r="G22">
-        <v>62.78</v>
+        <v>64.17</v>
       </c>
       <c r="H22">
-        <v>70.43000000000001</v>
+        <v>69.06</v>
       </c>
       <c r="I22" t="s">
         <v>49</v>
@@ -1237,16 +1237,16 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="F23">
-        <v>54.37</v>
+        <v>56.36</v>
       </c>
       <c r="G23">
-        <v>62.67</v>
+        <v>64.15000000000001</v>
       </c>
       <c r="H23">
-        <v>75.63</v>
+        <v>77.06</v>
       </c>
       <c r="I23" t="s">
         <v>49</v>
@@ -1257,7 +1257,7 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C24" t="s">
         <v>46</v>
@@ -1266,16 +1266,16 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>4</v>
+        <v>65</v>
       </c>
       <c r="F24">
-        <v>62.58</v>
+        <v>56.42</v>
       </c>
       <c r="G24">
-        <v>62.58</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="H24">
-        <v>62.58</v>
+        <v>77.87</v>
       </c>
       <c r="I24" t="s">
         <v>49</v>
@@ -1295,16 +1295,16 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>37</v>
+        <v>117</v>
       </c>
       <c r="F25">
-        <v>54.59</v>
+        <v>52.41</v>
       </c>
       <c r="G25">
-        <v>62.21</v>
+        <v>63.28</v>
       </c>
       <c r="H25">
-        <v>73.42</v>
+        <v>77.87</v>
       </c>
       <c r="I25" t="s">
         <v>49</v>
@@ -1315,7 +1315,7 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C26" t="s">
         <v>46</v>
@@ -1324,16 +1324,16 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F26">
-        <v>59.53</v>
+        <v>58.31</v>
       </c>
       <c r="G26">
-        <v>62.17</v>
+        <v>61.89</v>
       </c>
       <c r="H26">
-        <v>66.7</v>
+        <v>63.5</v>
       </c>
       <c r="I26" t="s">
         <v>49</v>
@@ -1344,7 +1344,7 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
         <v>46</v>
@@ -1353,16 +1353,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>117</v>
+        <v>9</v>
       </c>
       <c r="F27">
-        <v>54.37</v>
+        <v>57.41</v>
       </c>
       <c r="G27">
-        <v>62.13</v>
+        <v>60.26</v>
       </c>
       <c r="H27">
-        <v>75.63</v>
+        <v>65.5</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1382,16 +1382,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F28">
-        <v>57.11</v>
+        <v>60.03</v>
       </c>
       <c r="G28">
-        <v>61.16</v>
+        <v>60.03</v>
       </c>
       <c r="H28">
-        <v>67.97</v>
+        <v>60.03</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
@@ -1411,16 +1411,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="F29">
-        <v>54.69</v>
+        <v>52.41</v>
       </c>
       <c r="G29">
-        <v>60.32</v>
+        <v>59.91</v>
       </c>
       <c r="H29">
-        <v>67.34999999999999</v>
+        <v>68.72</v>
       </c>
       <c r="I29" t="s">
         <v>49</v>
@@ -1440,16 +1440,16 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F30">
-        <v>55.97</v>
+        <v>59.05</v>
       </c>
       <c r="G30">
-        <v>59.94</v>
+        <v>59.05</v>
       </c>
       <c r="H30">
-        <v>64.19</v>
+        <v>59.05</v>
       </c>
       <c r="I30" t="s">
         <v>49</v>
@@ -1469,16 +1469,16 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F31">
-        <v>54.91</v>
+        <v>56.36</v>
       </c>
       <c r="G31">
-        <v>59.47</v>
+        <v>58.27</v>
       </c>
       <c r="H31">
-        <v>64.41</v>
+        <v>59.28</v>
       </c>
       <c r="I31" t="s">
         <v>49</v>
@@ -1489,7 +1489,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C32" t="s">
         <v>46</v>
@@ -1498,16 +1498,16 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F32">
-        <v>54.81</v>
+        <v>53.55</v>
       </c>
       <c r="G32">
-        <v>58.66</v>
+        <v>57.96</v>
       </c>
       <c r="H32">
-        <v>62.51</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="I32" t="s">
         <v>49</v>
@@ -1518,7 +1518,7 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C33" t="s">
         <v>46</v>
@@ -1530,13 +1530,13 @@
         <v>10</v>
       </c>
       <c r="F33">
-        <v>54.55</v>
+        <v>54.5</v>
       </c>
       <c r="G33">
-        <v>57.73</v>
+        <v>57.09</v>
       </c>
       <c r="H33">
-        <v>65.61</v>
+        <v>61.8</v>
       </c>
       <c r="I33" t="s">
         <v>49</v>
@@ -1547,7 +1547,7 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C34" t="s">
         <v>46</v>
@@ -1556,16 +1556,16 @@
         <v>47</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F34">
-        <v>56.08</v>
+        <v>51.63</v>
       </c>
       <c r="G34">
-        <v>56.08</v>
+        <v>56.69</v>
       </c>
       <c r="H34">
-        <v>56.08</v>
+        <v>59.34</v>
       </c>
       <c r="I34" t="s">
         <v>49</v>
@@ -1576,7 +1576,7 @@
         <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C35" t="s">
         <v>46</v>
@@ -1596,7 +1596,7 @@
         <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C36" t="s">
         <v>46</v>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -46,121 +46,121 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه دراء</t>
+  </si>
+  <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
     <t>منطقه حفاظت شده تنگ بستانک</t>
   </si>
   <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
     <t>منطقه حفاظت شده برم فیروز</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه دراء</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع پادنا</t>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع دالان</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
     <t>منطقه شکار ممن.ع آق جلو</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع بناب</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
+    <t>پارک ملي قطرويه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوهستان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع توت سياه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مزايجان</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع بصيران</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
+    <t>پناهگاه حيات وحش دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه هوا و</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع شیکوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مهارلو</t>
   </si>
   <si>
     <t>منطقه حفاظت شده هرمود</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوهستان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه هوا و</t>
-  </si>
-  <si>
-    <t>پارک ملي قطرويه</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع شیکوه</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع چاه نفت</t>
   </si>
   <si>
     <t>منطقه حفاظت شده مارگون</t>
   </si>
   <si>
+    <t>مناطق حفاظت‌شده</t>
+  </si>
+  <si>
     <t>مناطق ممنوعه شکار</t>
   </si>
   <si>
-    <t>مناطق حفاظت‌شده</t>
-  </si>
-  <si>
-    <t>1405-06-26</t>
-  </si>
-  <si>
-    <t>2026-09-17</t>
+    <t>1405-06-27</t>
+  </si>
+  <si>
+    <t>2026-09-18</t>
   </si>
   <si>
     <t>بسیار شدید</t>
@@ -628,16 +628,16 @@
         <v>47</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>68.7</v>
+        <v>72.28</v>
       </c>
       <c r="G2">
-        <v>75.06999999999999</v>
+        <v>84.06999999999999</v>
       </c>
       <c r="H2">
-        <v>78.09</v>
+        <v>89.95999999999999</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -648,7 +648,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s">
         <v>46</v>
@@ -657,16 +657,16 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F3">
-        <v>70.77</v>
+        <v>68.69</v>
       </c>
       <c r="G3">
-        <v>74.98999999999999</v>
+        <v>79.43000000000001</v>
       </c>
       <c r="H3">
-        <v>78.09</v>
+        <v>85.95999999999999</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -686,16 +686,16 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>71.45999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="G4">
-        <v>74.77</v>
+        <v>75.44</v>
       </c>
       <c r="H4">
-        <v>78.56999999999999</v>
+        <v>77.66</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -715,16 +715,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="F5">
-        <v>73.36</v>
+        <v>69.78</v>
       </c>
       <c r="G5">
-        <v>73.87</v>
+        <v>75.34</v>
       </c>
       <c r="H5">
-        <v>74.61</v>
+        <v>81.47</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -744,16 +744,16 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="F6">
-        <v>67.28</v>
+        <v>67.68000000000001</v>
       </c>
       <c r="G6">
-        <v>72.88</v>
+        <v>74.93000000000001</v>
       </c>
       <c r="H6">
-        <v>77.2</v>
+        <v>80.88</v>
       </c>
       <c r="I6" t="s">
         <v>48</v>
@@ -764,7 +764,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
         <v>46</v>
@@ -776,13 +776,13 @@
         <v>20</v>
       </c>
       <c r="F7">
-        <v>64.53</v>
+        <v>68.69</v>
       </c>
       <c r="G7">
-        <v>72.62</v>
+        <v>74.78</v>
       </c>
       <c r="H7">
-        <v>82.92</v>
+        <v>79.03</v>
       </c>
       <c r="I7" t="s">
         <v>48</v>
@@ -802,16 +802,16 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F8">
-        <v>70.48</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="G8">
-        <v>71.01000000000001</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="H8">
-        <v>71.2</v>
+        <v>78.98999999999999</v>
       </c>
       <c r="I8" t="s">
         <v>48</v>
@@ -831,16 +831,16 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F9">
-        <v>64.56999999999999</v>
+        <v>63.76</v>
       </c>
       <c r="G9">
-        <v>70.89</v>
+        <v>73.19</v>
       </c>
       <c r="H9">
-        <v>77.09</v>
+        <v>79.34999999999999</v>
       </c>
       <c r="I9" t="s">
         <v>48</v>
@@ -851,7 +851,7 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
         <v>46</v>
@@ -860,16 +860,16 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F10">
-        <v>64.56999999999999</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="G10">
-        <v>70.87</v>
+        <v>73.08</v>
       </c>
       <c r="H10">
-        <v>77.48</v>
+        <v>80.31</v>
       </c>
       <c r="I10" t="s">
         <v>48</v>
@@ -880,7 +880,7 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
         <v>46</v>
@@ -889,16 +889,16 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F11">
-        <v>64.20999999999999</v>
+        <v>67.68000000000001</v>
       </c>
       <c r="G11">
-        <v>70.25</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="H11">
-        <v>72.67</v>
+        <v>77.34</v>
       </c>
       <c r="I11" t="s">
         <v>48</v>
@@ -918,19 +918,19 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F12">
-        <v>65.45</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="G12">
-        <v>69.88</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="H12">
-        <v>76.12</v>
+        <v>75.20999999999999</v>
       </c>
       <c r="I12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -947,19 +947,19 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>62</v>
+        <v>16</v>
       </c>
       <c r="F13">
-        <v>60.91</v>
+        <v>68.25</v>
       </c>
       <c r="G13">
-        <v>69.34999999999999</v>
+        <v>71.84</v>
       </c>
       <c r="H13">
-        <v>76.03</v>
+        <v>74.14</v>
       </c>
       <c r="I13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -976,19 +976,19 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F14">
-        <v>60.98</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="G14">
-        <v>68.39</v>
+        <v>71.7</v>
       </c>
       <c r="H14">
-        <v>72.09</v>
+        <v>76.15000000000001</v>
       </c>
       <c r="I14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -1005,19 +1005,19 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F15">
-        <v>63.93</v>
+        <v>66.29000000000001</v>
       </c>
       <c r="G15">
-        <v>68.31999999999999</v>
+        <v>71.45999999999999</v>
       </c>
       <c r="H15">
-        <v>70.84</v>
+        <v>85.45999999999999</v>
       </c>
       <c r="I15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1025,7 +1025,7 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
         <v>46</v>
@@ -1034,19 +1034,19 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="F16">
-        <v>67.06</v>
+        <v>63.52</v>
       </c>
       <c r="G16">
-        <v>67.95999999999999</v>
+        <v>71.19</v>
       </c>
       <c r="H16">
-        <v>68.84999999999999</v>
+        <v>82.13</v>
       </c>
       <c r="I16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1054,7 +1054,7 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C17" t="s">
         <v>46</v>
@@ -1063,19 +1063,19 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F17">
-        <v>61.91</v>
+        <v>67.44</v>
       </c>
       <c r="G17">
-        <v>67.16</v>
+        <v>71.19</v>
       </c>
       <c r="H17">
-        <v>71.29000000000001</v>
+        <v>76.14</v>
       </c>
       <c r="I17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1083,7 +1083,7 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C18" t="s">
         <v>46</v>
@@ -1092,19 +1092,19 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F18">
-        <v>58.63</v>
+        <v>68.91</v>
       </c>
       <c r="G18">
-        <v>66.36</v>
+        <v>71.12</v>
       </c>
       <c r="H18">
-        <v>73.47</v>
+        <v>73.77</v>
       </c>
       <c r="I18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1121,19 +1121,19 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F19">
-        <v>61.8</v>
+        <v>68.43000000000001</v>
       </c>
       <c r="G19">
-        <v>66.19</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="H19">
-        <v>74.55</v>
+        <v>75.67</v>
       </c>
       <c r="I19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1141,7 +1141,7 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C20" t="s">
         <v>46</v>
@@ -1150,19 +1150,19 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="F20">
-        <v>55.56</v>
+        <v>69.03</v>
       </c>
       <c r="G20">
-        <v>64.72</v>
+        <v>70.09</v>
       </c>
       <c r="H20">
-        <v>77.20999999999999</v>
+        <v>71.16</v>
       </c>
       <c r="I20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1179,16 +1179,16 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F21">
-        <v>59.05</v>
+        <v>62.97</v>
       </c>
       <c r="G21">
-        <v>64.48999999999999</v>
+        <v>68.31</v>
       </c>
       <c r="H21">
-        <v>72.18000000000001</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="I21" t="s">
         <v>49</v>
@@ -1208,16 +1208,16 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F22">
-        <v>58.94</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="G22">
-        <v>64.17</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="H22">
-        <v>69.06</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="I22" t="s">
         <v>49</v>
@@ -1228,7 +1228,7 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C23" t="s">
         <v>46</v>
@@ -1240,13 +1240,13 @@
         <v>12</v>
       </c>
       <c r="F23">
-        <v>56.36</v>
+        <v>57.86</v>
       </c>
       <c r="G23">
-        <v>64.15000000000001</v>
+        <v>67.05</v>
       </c>
       <c r="H23">
-        <v>77.06</v>
+        <v>77.77</v>
       </c>
       <c r="I23" t="s">
         <v>49</v>
@@ -1257,7 +1257,7 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C24" t="s">
         <v>46</v>
@@ -1266,16 +1266,16 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="F24">
-        <v>56.42</v>
+        <v>57.82</v>
       </c>
       <c r="G24">
-        <v>64.09999999999999</v>
+        <v>66.89</v>
       </c>
       <c r="H24">
-        <v>77.87</v>
+        <v>77.64</v>
       </c>
       <c r="I24" t="s">
         <v>49</v>
@@ -1286,7 +1286,7 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C25" t="s">
         <v>46</v>
@@ -1295,16 +1295,16 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>117</v>
+        <v>65</v>
       </c>
       <c r="F25">
-        <v>52.41</v>
+        <v>57.82</v>
       </c>
       <c r="G25">
-        <v>63.28</v>
+        <v>66.31</v>
       </c>
       <c r="H25">
-        <v>77.87</v>
+        <v>77.64</v>
       </c>
       <c r="I25" t="s">
         <v>49</v>
@@ -1315,7 +1315,7 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s">
         <v>46</v>
@@ -1324,16 +1324,16 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F26">
-        <v>58.31</v>
+        <v>66.05</v>
       </c>
       <c r="G26">
-        <v>61.89</v>
+        <v>66.05</v>
       </c>
       <c r="H26">
-        <v>63.5</v>
+        <v>66.05</v>
       </c>
       <c r="I26" t="s">
         <v>49</v>
@@ -1353,16 +1353,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F27">
-        <v>57.41</v>
+        <v>59.8</v>
       </c>
       <c r="G27">
-        <v>60.26</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="H27">
-        <v>65.5</v>
+        <v>69.81999999999999</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1373,7 +1373,7 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C28" t="s">
         <v>46</v>
@@ -1382,16 +1382,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F28">
-        <v>60.03</v>
+        <v>59.4</v>
       </c>
       <c r="G28">
-        <v>60.03</v>
+        <v>64.3</v>
       </c>
       <c r="H28">
-        <v>60.03</v>
+        <v>70.23</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
@@ -1402,7 +1402,7 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C29" t="s">
         <v>46</v>
@@ -1411,16 +1411,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="F29">
-        <v>52.41</v>
+        <v>53.31</v>
       </c>
       <c r="G29">
-        <v>59.91</v>
+        <v>63.85</v>
       </c>
       <c r="H29">
-        <v>68.72</v>
+        <v>87.97</v>
       </c>
       <c r="I29" t="s">
         <v>49</v>
@@ -1431,7 +1431,7 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C30" t="s">
         <v>46</v>
@@ -1440,16 +1440,16 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F30">
-        <v>59.05</v>
+        <v>57.91</v>
       </c>
       <c r="G30">
-        <v>59.05</v>
+        <v>62.18</v>
       </c>
       <c r="H30">
-        <v>59.05</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="I30" t="s">
         <v>49</v>
@@ -1469,16 +1469,16 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="F31">
-        <v>56.36</v>
+        <v>57.76</v>
       </c>
       <c r="G31">
-        <v>58.27</v>
+        <v>62.01</v>
       </c>
       <c r="H31">
-        <v>59.28</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="I31" t="s">
         <v>49</v>
@@ -1489,7 +1489,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C32" t="s">
         <v>46</v>
@@ -1498,16 +1498,16 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F32">
-        <v>53.55</v>
+        <v>57.7</v>
       </c>
       <c r="G32">
-        <v>57.96</v>
+        <v>59.66</v>
       </c>
       <c r="H32">
-        <v>65.84999999999999</v>
+        <v>61.62</v>
       </c>
       <c r="I32" t="s">
         <v>49</v>
@@ -1518,7 +1518,7 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C33" t="s">
         <v>46</v>
@@ -1530,13 +1530,13 @@
         <v>10</v>
       </c>
       <c r="F33">
-        <v>54.5</v>
+        <v>57.17</v>
       </c>
       <c r="G33">
-        <v>57.09</v>
+        <v>59.62</v>
       </c>
       <c r="H33">
-        <v>61.8</v>
+        <v>63.7</v>
       </c>
       <c r="I33" t="s">
         <v>49</v>
@@ -1556,16 +1556,16 @@
         <v>47</v>
       </c>
       <c r="E34">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F34">
-        <v>51.63</v>
+        <v>56.8</v>
       </c>
       <c r="G34">
-        <v>56.69</v>
+        <v>58.32</v>
       </c>
       <c r="H34">
-        <v>59.34</v>
+        <v>61.57</v>
       </c>
       <c r="I34" t="s">
         <v>49</v>
@@ -1576,7 +1576,7 @@
         <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C35" t="s">
         <v>46</v>
@@ -1596,7 +1596,7 @@
         <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C36" t="s">
         <v>46</v>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -46,121 +46,121 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>پناهگاه حيات وحش دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه دراء</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بصيران</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بناب</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دالان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
+  </si>
+  <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع توت سياه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده برم فیروز</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع شیکوه</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع مل بلند</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه دراء</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
+    <t>منطقه شکار ممنوع مزايجان</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوهستان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده هرمود</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه هوا و</t>
+  </si>
+  <si>
+    <t>پارک ملي قطرويه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مهارلو</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع خرمنکوه</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دالان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بناب</t>
-  </si>
-  <si>
-    <t>پارک ملي قطرويه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوهستان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بصيران</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه هوا و</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع شیکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده هرمود</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع چاه نفت</t>
   </si>
   <si>
     <t>منطقه حفاظت شده مارگون</t>
   </si>
   <si>
+    <t>مناطق ممنوعه شکار</t>
+  </si>
+  <si>
     <t>مناطق حفاظت‌شده</t>
   </si>
   <si>
-    <t>مناطق ممنوعه شکار</t>
-  </si>
-  <si>
-    <t>1405-06-27</t>
-  </si>
-  <si>
-    <t>2026-09-18</t>
+    <t>1405-06-28</t>
+  </si>
+  <si>
+    <t>2026-09-19</t>
   </si>
   <si>
     <t>بسیار شدید</t>
@@ -628,16 +628,16 @@
         <v>47</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>72.28</v>
+        <v>74.61</v>
       </c>
       <c r="G2">
-        <v>84.06999999999999</v>
+        <v>78.17</v>
       </c>
       <c r="H2">
-        <v>89.95999999999999</v>
+        <v>83.62</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -657,16 +657,16 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F3">
-        <v>68.69</v>
+        <v>72.94</v>
       </c>
       <c r="G3">
-        <v>79.43000000000001</v>
+        <v>77.58</v>
       </c>
       <c r="H3">
-        <v>85.95999999999999</v>
+        <v>84.23999999999999</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -686,16 +686,16 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F4">
-        <v>73.40000000000001</v>
+        <v>66.87</v>
       </c>
       <c r="G4">
-        <v>75.44</v>
+        <v>76.20999999999999</v>
       </c>
       <c r="H4">
-        <v>77.66</v>
+        <v>83.62</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -706,7 +706,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
         <v>46</v>
@@ -715,16 +715,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F5">
-        <v>69.78</v>
+        <v>51.87</v>
       </c>
       <c r="G5">
-        <v>75.34</v>
+        <v>74.55</v>
       </c>
       <c r="H5">
-        <v>81.47</v>
+        <v>83.83</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -735,7 +735,7 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
         <v>46</v>
@@ -744,16 +744,16 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F6">
-        <v>67.68000000000001</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="G6">
-        <v>74.93000000000001</v>
+        <v>72.84</v>
       </c>
       <c r="H6">
-        <v>80.88</v>
+        <v>79.22</v>
       </c>
       <c r="I6" t="s">
         <v>48</v>
@@ -764,7 +764,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
         <v>46</v>
@@ -776,13 +776,13 @@
         <v>20</v>
       </c>
       <c r="F7">
-        <v>68.69</v>
+        <v>65.53</v>
       </c>
       <c r="G7">
-        <v>74.78</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="H7">
-        <v>79.03</v>
+        <v>77.11</v>
       </c>
       <c r="I7" t="s">
         <v>48</v>
@@ -802,16 +802,16 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F8">
-        <v>67.40000000000001</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="G8">
-        <v>74.06999999999999</v>
+        <v>70.87</v>
       </c>
       <c r="H8">
-        <v>78.98999999999999</v>
+        <v>80.73</v>
       </c>
       <c r="I8" t="s">
         <v>48</v>
@@ -831,16 +831,16 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F9">
-        <v>63.76</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="G9">
-        <v>73.19</v>
+        <v>70.48</v>
       </c>
       <c r="H9">
-        <v>79.34999999999999</v>
+        <v>75.73999999999999</v>
       </c>
       <c r="I9" t="s">
         <v>48</v>
@@ -851,7 +851,7 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
         <v>46</v>
@@ -863,13 +863,13 @@
         <v>20</v>
       </c>
       <c r="F10">
-        <v>65.68000000000001</v>
+        <v>61.38</v>
       </c>
       <c r="G10">
-        <v>73.08</v>
+        <v>70.36</v>
       </c>
       <c r="H10">
-        <v>80.31</v>
+        <v>74.22</v>
       </c>
       <c r="I10" t="s">
         <v>48</v>
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="F11">
-        <v>67.68000000000001</v>
+        <v>69.09</v>
       </c>
       <c r="G11">
-        <v>73.06999999999999</v>
+        <v>70.04000000000001</v>
       </c>
       <c r="H11">
-        <v>77.34</v>
+        <v>72.17</v>
       </c>
       <c r="I11" t="s">
         <v>48</v>
@@ -909,7 +909,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
         <v>46</v>
@@ -918,19 +918,19 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F12">
-        <v>66.81999999999999</v>
+        <v>62.08</v>
       </c>
       <c r="G12">
-        <v>72.06999999999999</v>
+        <v>69.89</v>
       </c>
       <c r="H12">
-        <v>75.20999999999999</v>
+        <v>78.92</v>
       </c>
       <c r="I12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -938,7 +938,7 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s">
         <v>46</v>
@@ -947,19 +947,19 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F13">
-        <v>68.25</v>
+        <v>65.61</v>
       </c>
       <c r="G13">
-        <v>71.84</v>
+        <v>69.64</v>
       </c>
       <c r="H13">
-        <v>74.14</v>
+        <v>80.66</v>
       </c>
       <c r="I13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -976,19 +976,19 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="F14">
-        <v>64.23999999999999</v>
+        <v>68.37</v>
       </c>
       <c r="G14">
-        <v>71.7</v>
+        <v>69.23</v>
       </c>
       <c r="H14">
-        <v>76.15000000000001</v>
+        <v>70.59</v>
       </c>
       <c r="I14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -1005,19 +1005,19 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="F15">
-        <v>66.29000000000001</v>
+        <v>54.61</v>
       </c>
       <c r="G15">
-        <v>71.45999999999999</v>
+        <v>69.19</v>
       </c>
       <c r="H15">
-        <v>85.45999999999999</v>
+        <v>78.20999999999999</v>
       </c>
       <c r="I15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1034,19 +1034,19 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>62</v>
+        <v>5</v>
       </c>
       <c r="F16">
-        <v>63.52</v>
+        <v>64.8</v>
       </c>
       <c r="G16">
-        <v>71.19</v>
+        <v>68.34</v>
       </c>
       <c r="H16">
-        <v>82.13</v>
+        <v>72.17</v>
       </c>
       <c r="I16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1063,19 +1063,19 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F17">
-        <v>67.44</v>
+        <v>57.36</v>
       </c>
       <c r="G17">
-        <v>71.19</v>
+        <v>68.23999999999999</v>
       </c>
       <c r="H17">
-        <v>76.14</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="I17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1092,19 +1092,19 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F18">
-        <v>68.91</v>
+        <v>58.18</v>
       </c>
       <c r="G18">
-        <v>71.12</v>
+        <v>67.37</v>
       </c>
       <c r="H18">
-        <v>73.77</v>
+        <v>72.25</v>
       </c>
       <c r="I18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1112,7 +1112,7 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
         <v>46</v>
@@ -1121,19 +1121,19 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F19">
-        <v>68.43000000000001</v>
+        <v>59.99</v>
       </c>
       <c r="G19">
-        <v>70.65000000000001</v>
+        <v>66.45999999999999</v>
       </c>
       <c r="H19">
-        <v>75.67</v>
+        <v>73.87</v>
       </c>
       <c r="I19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1150,19 +1150,19 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F20">
-        <v>69.03</v>
+        <v>59.03</v>
       </c>
       <c r="G20">
-        <v>70.09</v>
+        <v>65.98</v>
       </c>
       <c r="H20">
-        <v>71.16</v>
+        <v>74.86</v>
       </c>
       <c r="I20" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1170,7 +1170,7 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C21" t="s">
         <v>46</v>
@@ -1179,16 +1179,16 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F21">
-        <v>62.97</v>
+        <v>63.78</v>
       </c>
       <c r="G21">
-        <v>68.31</v>
+        <v>65.72</v>
       </c>
       <c r="H21">
-        <v>73.18000000000001</v>
+        <v>67.66</v>
       </c>
       <c r="I21" t="s">
         <v>49</v>
@@ -1199,7 +1199,7 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C22" t="s">
         <v>46</v>
@@ -1208,16 +1208,16 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F22">
-        <v>67.56999999999999</v>
+        <v>54.13</v>
       </c>
       <c r="G22">
-        <v>67.56999999999999</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="H22">
-        <v>67.56999999999999</v>
+        <v>75.11</v>
       </c>
       <c r="I22" t="s">
         <v>49</v>
@@ -1228,7 +1228,7 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C23" t="s">
         <v>46</v>
@@ -1237,16 +1237,16 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F23">
-        <v>57.86</v>
+        <v>53.74</v>
       </c>
       <c r="G23">
-        <v>67.05</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="H23">
-        <v>77.77</v>
+        <v>71.47</v>
       </c>
       <c r="I23" t="s">
         <v>49</v>
@@ -1266,16 +1266,16 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>117</v>
+        <v>3</v>
       </c>
       <c r="F24">
-        <v>57.82</v>
+        <v>59.96</v>
       </c>
       <c r="G24">
-        <v>66.89</v>
+        <v>64.02</v>
       </c>
       <c r="H24">
-        <v>77.64</v>
+        <v>67.92</v>
       </c>
       <c r="I24" t="s">
         <v>49</v>
@@ -1295,16 +1295,16 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>65</v>
+        <v>6</v>
       </c>
       <c r="F25">
-        <v>57.82</v>
+        <v>58.23</v>
       </c>
       <c r="G25">
-        <v>66.31</v>
+        <v>63.99</v>
       </c>
       <c r="H25">
-        <v>77.64</v>
+        <v>69.81999999999999</v>
       </c>
       <c r="I25" t="s">
         <v>49</v>
@@ -1315,7 +1315,7 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C26" t="s">
         <v>46</v>
@@ -1324,16 +1324,16 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F26">
-        <v>66.05</v>
+        <v>56.28</v>
       </c>
       <c r="G26">
-        <v>66.05</v>
+        <v>62.92</v>
       </c>
       <c r="H26">
-        <v>66.05</v>
+        <v>67.64</v>
       </c>
       <c r="I26" t="s">
         <v>49</v>
@@ -1353,16 +1353,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>4</v>
+        <v>65</v>
       </c>
       <c r="F27">
-        <v>59.8</v>
+        <v>55.88</v>
       </c>
       <c r="G27">
-        <v>65.04000000000001</v>
+        <v>62.72</v>
       </c>
       <c r="H27">
-        <v>69.81999999999999</v>
+        <v>81.44</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1382,16 +1382,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>15</v>
+        <v>117</v>
       </c>
       <c r="F28">
-        <v>59.4</v>
+        <v>53.94</v>
       </c>
       <c r="G28">
-        <v>64.3</v>
+        <v>62.21</v>
       </c>
       <c r="H28">
-        <v>70.23</v>
+        <v>81.44</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
@@ -1402,7 +1402,7 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C29" t="s">
         <v>46</v>
@@ -1411,16 +1411,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="F29">
-        <v>53.31</v>
+        <v>61.28</v>
       </c>
       <c r="G29">
-        <v>63.85</v>
+        <v>61.28</v>
       </c>
       <c r="H29">
-        <v>87.97</v>
+        <v>61.28</v>
       </c>
       <c r="I29" t="s">
         <v>49</v>
@@ -1431,7 +1431,7 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C30" t="s">
         <v>46</v>
@@ -1440,16 +1440,16 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F30">
-        <v>57.91</v>
+        <v>57.1</v>
       </c>
       <c r="G30">
-        <v>62.18</v>
+        <v>61.05</v>
       </c>
       <c r="H30">
-        <v>64.79000000000001</v>
+        <v>64.84</v>
       </c>
       <c r="I30" t="s">
         <v>49</v>
@@ -1460,7 +1460,7 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C31" t="s">
         <v>46</v>
@@ -1472,13 +1472,13 @@
         <v>37</v>
       </c>
       <c r="F31">
-        <v>57.76</v>
+        <v>56.53</v>
       </c>
       <c r="G31">
-        <v>62.01</v>
+        <v>60.53</v>
       </c>
       <c r="H31">
-        <v>66.04000000000001</v>
+        <v>67.03</v>
       </c>
       <c r="I31" t="s">
         <v>49</v>
@@ -1498,16 +1498,16 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F32">
-        <v>57.7</v>
+        <v>59.87</v>
       </c>
       <c r="G32">
-        <v>59.66</v>
+        <v>59.87</v>
       </c>
       <c r="H32">
-        <v>61.62</v>
+        <v>59.87</v>
       </c>
       <c r="I32" t="s">
         <v>49</v>
@@ -1518,7 +1518,7 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C33" t="s">
         <v>46</v>
@@ -1530,13 +1530,13 @@
         <v>10</v>
       </c>
       <c r="F33">
-        <v>57.17</v>
+        <v>54.76</v>
       </c>
       <c r="G33">
-        <v>59.62</v>
+        <v>57.8</v>
       </c>
       <c r="H33">
-        <v>63.7</v>
+        <v>62.57</v>
       </c>
       <c r="I33" t="s">
         <v>49</v>
@@ -1556,16 +1556,16 @@
         <v>47</v>
       </c>
       <c r="E34">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F34">
-        <v>56.8</v>
+        <v>53.13</v>
       </c>
       <c r="G34">
-        <v>58.32</v>
+        <v>55.86</v>
       </c>
       <c r="H34">
-        <v>61.57</v>
+        <v>60.26</v>
       </c>
       <c r="I34" t="s">
         <v>49</v>
@@ -1576,7 +1576,7 @@
         <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C35" t="s">
         <v>46</v>
@@ -1596,7 +1596,7 @@
         <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C36" t="s">
         <v>46</v>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -49,96 +49,96 @@
     <t>پناهگاه حيات وحش دره باغ</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده برم فیروز</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع توت سياه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بصيران</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بناب</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>پارک ملي قطرويه</t>
+  </si>
+  <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع کوه دراء</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بصيران</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بناب</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع دالان</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع شیکوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
   </si>
   <si>
     <t>منطقه حفاظت شده بهرام گور</t>
   </si>
   <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع شیکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
+    <t>منطقه حفاظت شده هرمود</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع مزايجان</t>
   </si>
   <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع کوهستان</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده هرمود</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع کوه هوا و</t>
   </si>
   <si>
-    <t>پارک ملي قطرويه</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع مهارلو</t>
   </si>
   <si>
@@ -157,10 +157,10 @@
     <t>مناطق حفاظت‌شده</t>
   </si>
   <si>
-    <t>1405-06-28</t>
-  </si>
-  <si>
-    <t>2026-09-19</t>
+    <t>1405-06-29</t>
+  </si>
+  <si>
+    <t>2026-09-20</t>
   </si>
   <si>
     <t>بسیار شدید</t>
@@ -631,13 +631,13 @@
         <v>3</v>
       </c>
       <c r="F2">
-        <v>74.61</v>
+        <v>71.8</v>
       </c>
       <c r="G2">
-        <v>78.17</v>
+        <v>76.45</v>
       </c>
       <c r="H2">
-        <v>83.62</v>
+        <v>81.81</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -657,16 +657,16 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>72.94</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="G3">
-        <v>77.58</v>
+        <v>75.79000000000001</v>
       </c>
       <c r="H3">
-        <v>84.23999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -677,7 +677,7 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C4" t="s">
         <v>46</v>
@@ -686,16 +686,16 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>66.87</v>
+        <v>64.06</v>
       </c>
       <c r="G4">
-        <v>76.20999999999999</v>
+        <v>73.44</v>
       </c>
       <c r="H4">
-        <v>83.62</v>
+        <v>80.05</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -706,7 +706,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
         <v>46</v>
@@ -715,16 +715,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>51.87</v>
+        <v>65.09</v>
       </c>
       <c r="G5">
-        <v>74.55</v>
+        <v>72.84</v>
       </c>
       <c r="H5">
-        <v>83.83</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -735,7 +735,7 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s">
         <v>46</v>
@@ -747,13 +747,13 @@
         <v>20</v>
       </c>
       <c r="F6">
-        <v>64.20999999999999</v>
+        <v>65.92</v>
       </c>
       <c r="G6">
-        <v>72.84</v>
+        <v>72.52</v>
       </c>
       <c r="H6">
-        <v>79.22</v>
+        <v>79.98</v>
       </c>
       <c r="I6" t="s">
         <v>48</v>
@@ -773,16 +773,16 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F7">
-        <v>65.53</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="G7">
-        <v>71.73999999999999</v>
+        <v>72.27</v>
       </c>
       <c r="H7">
-        <v>77.11</v>
+        <v>81.37</v>
       </c>
       <c r="I7" t="s">
         <v>48</v>
@@ -802,19 +802,19 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F8">
-        <v>64.18000000000001</v>
+        <v>62.97</v>
       </c>
       <c r="G8">
-        <v>70.87</v>
+        <v>69.55</v>
       </c>
       <c r="H8">
-        <v>80.73</v>
+        <v>76.54000000000001</v>
       </c>
       <c r="I8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -831,19 +831,19 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F9">
-        <v>65.06999999999999</v>
+        <v>61.65</v>
       </c>
       <c r="G9">
-        <v>70.48</v>
+        <v>69.39</v>
       </c>
       <c r="H9">
-        <v>75.73999999999999</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="I9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -851,7 +851,7 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
         <v>46</v>
@@ -863,16 +863,16 @@
         <v>20</v>
       </c>
       <c r="F10">
-        <v>61.38</v>
+        <v>62.07</v>
       </c>
       <c r="G10">
-        <v>70.36</v>
+        <v>69.09</v>
       </c>
       <c r="H10">
-        <v>74.22</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="I10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -889,19 +889,19 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F11">
-        <v>69.09</v>
+        <v>64.98</v>
       </c>
       <c r="G11">
-        <v>70.04000000000001</v>
+        <v>68.73</v>
       </c>
       <c r="H11">
-        <v>72.17</v>
+        <v>72.33</v>
       </c>
       <c r="I11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -909,7 +909,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
         <v>46</v>
@@ -918,16 +918,16 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F12">
-        <v>62.08</v>
+        <v>66.64</v>
       </c>
       <c r="G12">
-        <v>69.89</v>
+        <v>68.16</v>
       </c>
       <c r="H12">
-        <v>78.92</v>
+        <v>70.67</v>
       </c>
       <c r="I12" t="s">
         <v>49</v>
@@ -938,7 +938,7 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
         <v>46</v>
@@ -947,16 +947,16 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="F13">
-        <v>65.61</v>
+        <v>59.42</v>
       </c>
       <c r="G13">
-        <v>69.64</v>
+        <v>68.13</v>
       </c>
       <c r="H13">
-        <v>80.66</v>
+        <v>77.02</v>
       </c>
       <c r="I13" t="s">
         <v>49</v>
@@ -967,7 +967,7 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
         <v>46</v>
@@ -976,16 +976,16 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="F14">
-        <v>68.37</v>
+        <v>58</v>
       </c>
       <c r="G14">
-        <v>69.23</v>
+        <v>68.05</v>
       </c>
       <c r="H14">
-        <v>70.59</v>
+        <v>94.67</v>
       </c>
       <c r="I14" t="s">
         <v>49</v>
@@ -1005,16 +1005,16 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="F15">
-        <v>54.61</v>
+        <v>62.09</v>
       </c>
       <c r="G15">
-        <v>69.19</v>
+        <v>67.94</v>
       </c>
       <c r="H15">
-        <v>78.20999999999999</v>
+        <v>72.92</v>
       </c>
       <c r="I15" t="s">
         <v>49</v>
@@ -1034,16 +1034,16 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F16">
-        <v>64.8</v>
+        <v>58.76</v>
       </c>
       <c r="G16">
-        <v>68.34</v>
+        <v>67.37</v>
       </c>
       <c r="H16">
-        <v>72.17</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="I16" t="s">
         <v>49</v>
@@ -1054,7 +1054,7 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
         <v>46</v>
@@ -1063,16 +1063,16 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F17">
-        <v>57.36</v>
+        <v>59.57</v>
       </c>
       <c r="G17">
-        <v>68.23999999999999</v>
+        <v>67.08</v>
       </c>
       <c r="H17">
-        <v>77.18000000000001</v>
+        <v>74.42</v>
       </c>
       <c r="I17" t="s">
         <v>49</v>
@@ -1092,16 +1092,16 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F18">
-        <v>58.18</v>
+        <v>61.28</v>
       </c>
       <c r="G18">
-        <v>67.37</v>
+        <v>67.05</v>
       </c>
       <c r="H18">
-        <v>72.25</v>
+        <v>73.61</v>
       </c>
       <c r="I18" t="s">
         <v>49</v>
@@ -1112,7 +1112,7 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C19" t="s">
         <v>46</v>
@@ -1124,13 +1124,13 @@
         <v>4</v>
       </c>
       <c r="F19">
-        <v>59.99</v>
+        <v>66.17</v>
       </c>
       <c r="G19">
-        <v>66.45999999999999</v>
+        <v>66.17</v>
       </c>
       <c r="H19">
-        <v>73.87</v>
+        <v>66.17</v>
       </c>
       <c r="I19" t="s">
         <v>49</v>
@@ -1150,16 +1150,16 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F20">
-        <v>59.03</v>
+        <v>59.56</v>
       </c>
       <c r="G20">
-        <v>65.98</v>
+        <v>65.95999999999999</v>
       </c>
       <c r="H20">
-        <v>74.86</v>
+        <v>69.31</v>
       </c>
       <c r="I20" t="s">
         <v>49</v>
@@ -1179,16 +1179,16 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F21">
-        <v>63.78</v>
+        <v>57.15</v>
       </c>
       <c r="G21">
-        <v>65.72</v>
+        <v>65.84</v>
       </c>
       <c r="H21">
-        <v>67.66</v>
+        <v>70</v>
       </c>
       <c r="I21" t="s">
         <v>49</v>
@@ -1199,7 +1199,7 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C22" t="s">
         <v>46</v>
@@ -1208,16 +1208,16 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="F22">
-        <v>54.13</v>
+        <v>60.42</v>
       </c>
       <c r="G22">
-        <v>65.26000000000001</v>
+        <v>65.17</v>
       </c>
       <c r="H22">
-        <v>75.11</v>
+        <v>73.62</v>
       </c>
       <c r="I22" t="s">
         <v>49</v>
@@ -1237,16 +1237,16 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F23">
-        <v>53.74</v>
+        <v>63.67</v>
       </c>
       <c r="G23">
-        <v>64.18000000000001</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="H23">
-        <v>71.47</v>
+        <v>65.52</v>
       </c>
       <c r="I23" t="s">
         <v>49</v>
@@ -1257,7 +1257,7 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C24" t="s">
         <v>46</v>
@@ -1266,16 +1266,16 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>117</v>
       </c>
       <c r="F24">
-        <v>59.96</v>
+        <v>54.51</v>
       </c>
       <c r="G24">
-        <v>64.02</v>
+        <v>63.87</v>
       </c>
       <c r="H24">
-        <v>67.92</v>
+        <v>84.12</v>
       </c>
       <c r="I24" t="s">
         <v>49</v>
@@ -1286,7 +1286,7 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C25" t="s">
         <v>46</v>
@@ -1295,16 +1295,16 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>6</v>
+        <v>65</v>
       </c>
       <c r="F25">
-        <v>58.23</v>
+        <v>55.86</v>
       </c>
       <c r="G25">
-        <v>63.99</v>
+        <v>63.72</v>
       </c>
       <c r="H25">
-        <v>69.81999999999999</v>
+        <v>84.12</v>
       </c>
       <c r="I25" t="s">
         <v>49</v>
@@ -1324,16 +1324,16 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="F26">
-        <v>56.28</v>
+        <v>59.73</v>
       </c>
       <c r="G26">
-        <v>62.92</v>
+        <v>63.68</v>
       </c>
       <c r="H26">
-        <v>67.64</v>
+        <v>67.69</v>
       </c>
       <c r="I26" t="s">
         <v>49</v>
@@ -1344,7 +1344,7 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
         <v>46</v>
@@ -1353,16 +1353,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="F27">
-        <v>55.88</v>
+        <v>62.39</v>
       </c>
       <c r="G27">
-        <v>62.72</v>
+        <v>62.98</v>
       </c>
       <c r="H27">
-        <v>81.44</v>
+        <v>63.57</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1382,16 +1382,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="F28">
-        <v>53.94</v>
+        <v>55.57</v>
       </c>
       <c r="G28">
-        <v>62.21</v>
+        <v>62.98</v>
       </c>
       <c r="H28">
-        <v>81.44</v>
+        <v>67.39</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
@@ -1402,7 +1402,7 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C29" t="s">
         <v>46</v>
@@ -1411,16 +1411,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F29">
-        <v>61.28</v>
+        <v>58.61</v>
       </c>
       <c r="G29">
-        <v>61.28</v>
+        <v>62.87</v>
       </c>
       <c r="H29">
-        <v>61.28</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="I29" t="s">
         <v>49</v>
@@ -1431,7 +1431,7 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C30" t="s">
         <v>46</v>
@@ -1440,16 +1440,16 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F30">
-        <v>57.1</v>
+        <v>55.32</v>
       </c>
       <c r="G30">
-        <v>61.05</v>
+        <v>61.46</v>
       </c>
       <c r="H30">
-        <v>64.84</v>
+        <v>70.14</v>
       </c>
       <c r="I30" t="s">
         <v>49</v>
@@ -1469,16 +1469,16 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="F31">
-        <v>56.53</v>
+        <v>60.6</v>
       </c>
       <c r="G31">
-        <v>60.53</v>
+        <v>60.6</v>
       </c>
       <c r="H31">
-        <v>67.03</v>
+        <v>60.6</v>
       </c>
       <c r="I31" t="s">
         <v>49</v>
@@ -1489,7 +1489,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C32" t="s">
         <v>46</v>
@@ -1498,16 +1498,16 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="F32">
-        <v>59.87</v>
+        <v>54.43</v>
       </c>
       <c r="G32">
-        <v>59.87</v>
+        <v>60.49</v>
       </c>
       <c r="H32">
-        <v>59.87</v>
+        <v>72.12</v>
       </c>
       <c r="I32" t="s">
         <v>49</v>
@@ -1530,13 +1530,13 @@
         <v>10</v>
       </c>
       <c r="F33">
-        <v>54.76</v>
+        <v>57.05</v>
       </c>
       <c r="G33">
-        <v>57.8</v>
+        <v>58.07</v>
       </c>
       <c r="H33">
-        <v>62.57</v>
+        <v>61.92</v>
       </c>
       <c r="I33" t="s">
         <v>49</v>
@@ -1559,13 +1559,13 @@
         <v>12</v>
       </c>
       <c r="F34">
-        <v>53.13</v>
+        <v>52.17</v>
       </c>
       <c r="G34">
-        <v>55.86</v>
+        <v>55.94</v>
       </c>
       <c r="H34">
-        <v>60.26</v>
+        <v>61.49</v>
       </c>
       <c r="I34" t="s">
         <v>49</v>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -46,105 +46,105 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده برم فیروز</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه دراء</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع شیکوه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بناب</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بصيران</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
     <t>پناهگاه حيات وحش دره باغ</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
+    <t>منطقه شکار ممنوع مهارلو</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع توت سياه</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بصيران</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بناب</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
+    <t>منطقه شکار ممنوع دالان</t>
   </si>
   <si>
     <t>پارک ملي قطرويه</t>
   </si>
   <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه دراء</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دالان</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع شیکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
+    <t>منطقه شکار ممنوع مزايجان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوهستان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه هوا و</t>
   </si>
   <si>
     <t>منطقه حفاظت شده هرمود</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوهستان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه هوا و</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع چاه نفت</t>
   </si>
   <si>
@@ -157,10 +157,10 @@
     <t>مناطق حفاظت‌شده</t>
   </si>
   <si>
-    <t>1405-06-29</t>
-  </si>
-  <si>
-    <t>2026-09-20</t>
+    <t>1405-06-30</t>
+  </si>
+  <si>
+    <t>2026-09-21</t>
   </si>
   <si>
     <t>بسیار شدید</t>
@@ -628,16 +628,16 @@
         <v>47</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="F2">
-        <v>71.8</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="G2">
-        <v>76.45</v>
+        <v>78.01000000000001</v>
       </c>
       <c r="H2">
-        <v>81.81</v>
+        <v>88.94</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -648,7 +648,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C3" t="s">
         <v>46</v>
@@ -657,16 +657,16 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>65.20999999999999</v>
+        <v>63.81</v>
       </c>
       <c r="G3">
-        <v>75.79000000000001</v>
+        <v>77.86</v>
       </c>
       <c r="H3">
-        <v>88.7</v>
+        <v>82.73</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -677,7 +677,7 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C4" t="s">
         <v>46</v>
@@ -686,16 +686,16 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F4">
-        <v>64.06</v>
+        <v>64.91</v>
       </c>
       <c r="G4">
-        <v>73.44</v>
+        <v>76.45999999999999</v>
       </c>
       <c r="H4">
-        <v>80.05</v>
+        <v>97.39</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -706,7 +706,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
         <v>46</v>
@@ -715,16 +715,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F5">
-        <v>65.09</v>
+        <v>65.41</v>
       </c>
       <c r="G5">
-        <v>72.84</v>
+        <v>75.95999999999999</v>
       </c>
       <c r="H5">
-        <v>81.51000000000001</v>
+        <v>85.18000000000001</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -735,7 +735,7 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
         <v>46</v>
@@ -744,16 +744,16 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>65.92</v>
+        <v>67.59</v>
       </c>
       <c r="G6">
-        <v>72.52</v>
+        <v>73.81999999999999</v>
       </c>
       <c r="H6">
-        <v>79.98</v>
+        <v>82.73</v>
       </c>
       <c r="I6" t="s">
         <v>48</v>
@@ -773,16 +773,16 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F7">
-        <v>64.23999999999999</v>
+        <v>65.41</v>
       </c>
       <c r="G7">
-        <v>72.27</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="H7">
-        <v>81.37</v>
+        <v>79.77</v>
       </c>
       <c r="I7" t="s">
         <v>48</v>
@@ -802,19 +802,19 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F8">
-        <v>62.97</v>
+        <v>63.39</v>
       </c>
       <c r="G8">
-        <v>69.55</v>
+        <v>71.67</v>
       </c>
       <c r="H8">
-        <v>76.54000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="I8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -831,19 +831,19 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F9">
-        <v>61.65</v>
+        <v>68.22</v>
       </c>
       <c r="G9">
-        <v>69.39</v>
+        <v>71.16</v>
       </c>
       <c r="H9">
-        <v>80.68000000000001</v>
+        <v>72.86</v>
       </c>
       <c r="I9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -860,19 +860,19 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F10">
-        <v>62.07</v>
+        <v>66.33</v>
       </c>
       <c r="G10">
-        <v>69.09</v>
+        <v>71.14</v>
       </c>
       <c r="H10">
-        <v>77.51000000000001</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="I10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -889,19 +889,19 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F11">
-        <v>64.98</v>
+        <v>64.05</v>
       </c>
       <c r="G11">
-        <v>68.73</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="H11">
-        <v>72.33</v>
+        <v>77.68000000000001</v>
       </c>
       <c r="I11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -909,7 +909,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
         <v>46</v>
@@ -918,16 +918,16 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F12">
-        <v>66.64</v>
+        <v>67.34</v>
       </c>
       <c r="G12">
-        <v>68.16</v>
+        <v>69.7</v>
       </c>
       <c r="H12">
-        <v>70.67</v>
+        <v>72.05</v>
       </c>
       <c r="I12" t="s">
         <v>49</v>
@@ -950,13 +950,13 @@
         <v>62</v>
       </c>
       <c r="F13">
-        <v>59.42</v>
+        <v>61.17</v>
       </c>
       <c r="G13">
-        <v>68.13</v>
+        <v>69.67</v>
       </c>
       <c r="H13">
-        <v>77.02</v>
+        <v>78.08</v>
       </c>
       <c r="I13" t="s">
         <v>49</v>
@@ -967,7 +967,7 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
         <v>46</v>
@@ -976,16 +976,16 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F14">
-        <v>58</v>
+        <v>60.65</v>
       </c>
       <c r="G14">
-        <v>68.05</v>
+        <v>67.92</v>
       </c>
       <c r="H14">
-        <v>94.67</v>
+        <v>75.23999999999999</v>
       </c>
       <c r="I14" t="s">
         <v>49</v>
@@ -1005,16 +1005,16 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F15">
-        <v>62.09</v>
+        <v>66.19</v>
       </c>
       <c r="G15">
-        <v>67.94</v>
+        <v>67.52</v>
       </c>
       <c r="H15">
-        <v>72.92</v>
+        <v>69.31</v>
       </c>
       <c r="I15" t="s">
         <v>49</v>
@@ -1034,16 +1034,16 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F16">
-        <v>58.76</v>
+        <v>60.44</v>
       </c>
       <c r="G16">
         <v>67.37</v>
       </c>
       <c r="H16">
-        <v>73.54000000000001</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="I16" t="s">
         <v>49</v>
@@ -1066,13 +1066,13 @@
         <v>20</v>
       </c>
       <c r="F17">
-        <v>59.57</v>
+        <v>62.23</v>
       </c>
       <c r="G17">
-        <v>67.08</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="H17">
-        <v>74.42</v>
+        <v>72.13</v>
       </c>
       <c r="I17" t="s">
         <v>49</v>
@@ -1083,7 +1083,7 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
         <v>46</v>
@@ -1092,16 +1092,16 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F18">
-        <v>61.28</v>
+        <v>50.47</v>
       </c>
       <c r="G18">
-        <v>67.05</v>
+        <v>67.09</v>
       </c>
       <c r="H18">
-        <v>73.61</v>
+        <v>85.78</v>
       </c>
       <c r="I18" t="s">
         <v>49</v>
@@ -1112,7 +1112,7 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
         <v>46</v>
@@ -1121,16 +1121,16 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F19">
-        <v>66.17</v>
+        <v>52.2</v>
       </c>
       <c r="G19">
-        <v>66.17</v>
+        <v>66.72</v>
       </c>
       <c r="H19">
-        <v>66.17</v>
+        <v>83.44</v>
       </c>
       <c r="I19" t="s">
         <v>49</v>
@@ -1150,16 +1150,16 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="F20">
-        <v>59.56</v>
+        <v>63.33</v>
       </c>
       <c r="G20">
-        <v>65.95999999999999</v>
+        <v>66.42</v>
       </c>
       <c r="H20">
-        <v>69.31</v>
+        <v>70.95</v>
       </c>
       <c r="I20" t="s">
         <v>49</v>
@@ -1179,16 +1179,16 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F21">
-        <v>57.15</v>
+        <v>59.89</v>
       </c>
       <c r="G21">
-        <v>65.84</v>
+        <v>65.61</v>
       </c>
       <c r="H21">
-        <v>70</v>
+        <v>73.88</v>
       </c>
       <c r="I21" t="s">
         <v>49</v>
@@ -1199,7 +1199,7 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C22" t="s">
         <v>46</v>
@@ -1208,16 +1208,16 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="F22">
-        <v>60.42</v>
+        <v>56.07</v>
       </c>
       <c r="G22">
-        <v>65.17</v>
+        <v>65.52</v>
       </c>
       <c r="H22">
-        <v>73.62</v>
+        <v>77.7</v>
       </c>
       <c r="I22" t="s">
         <v>49</v>
@@ -1228,7 +1228,7 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C23" t="s">
         <v>46</v>
@@ -1237,16 +1237,16 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>8</v>
+        <v>117</v>
       </c>
       <c r="F23">
-        <v>63.67</v>
+        <v>55.65</v>
       </c>
       <c r="G23">
-        <v>64.93000000000001</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="H23">
-        <v>65.52</v>
+        <v>77.7</v>
       </c>
       <c r="I23" t="s">
         <v>49</v>
@@ -1266,16 +1266,16 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>117</v>
+        <v>19</v>
       </c>
       <c r="F24">
-        <v>54.51</v>
+        <v>58.75</v>
       </c>
       <c r="G24">
-        <v>63.87</v>
+        <v>64.28</v>
       </c>
       <c r="H24">
-        <v>84.12</v>
+        <v>72.03</v>
       </c>
       <c r="I24" t="s">
         <v>49</v>
@@ -1286,7 +1286,7 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C25" t="s">
         <v>46</v>
@@ -1295,16 +1295,16 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="F25">
-        <v>55.86</v>
+        <v>58.89</v>
       </c>
       <c r="G25">
-        <v>63.72</v>
+        <v>63.83</v>
       </c>
       <c r="H25">
-        <v>84.12</v>
+        <v>69.95999999999999</v>
       </c>
       <c r="I25" t="s">
         <v>49</v>
@@ -1315,7 +1315,7 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s">
         <v>46</v>
@@ -1327,13 +1327,13 @@
         <v>3</v>
       </c>
       <c r="F26">
-        <v>59.73</v>
+        <v>59.61</v>
       </c>
       <c r="G26">
-        <v>63.68</v>
+        <v>63.02</v>
       </c>
       <c r="H26">
-        <v>67.69</v>
+        <v>67.92</v>
       </c>
       <c r="I26" t="s">
         <v>49</v>
@@ -1353,16 +1353,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F27">
-        <v>62.39</v>
+        <v>58.95</v>
       </c>
       <c r="G27">
-        <v>62.98</v>
+        <v>62.64</v>
       </c>
       <c r="H27">
-        <v>63.57</v>
+        <v>68.17</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1373,7 +1373,7 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C28" t="s">
         <v>46</v>
@@ -1382,16 +1382,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F28">
-        <v>55.57</v>
+        <v>56.77</v>
       </c>
       <c r="G28">
-        <v>62.98</v>
+        <v>62.3</v>
       </c>
       <c r="H28">
-        <v>67.39</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
@@ -1402,7 +1402,7 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C29" t="s">
         <v>46</v>
@@ -1411,16 +1411,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F29">
-        <v>58.61</v>
+        <v>55.98</v>
       </c>
       <c r="G29">
-        <v>62.87</v>
+        <v>61.96</v>
       </c>
       <c r="H29">
-        <v>66.98999999999999</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I29" t="s">
         <v>49</v>
@@ -1431,7 +1431,7 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C30" t="s">
         <v>46</v>
@@ -1440,16 +1440,16 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F30">
-        <v>55.32</v>
+        <v>61.37</v>
       </c>
       <c r="G30">
-        <v>61.46</v>
+        <v>61.37</v>
       </c>
       <c r="H30">
-        <v>70.14</v>
+        <v>61.37</v>
       </c>
       <c r="I30" t="s">
         <v>49</v>
@@ -1469,16 +1469,16 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F31">
-        <v>60.6</v>
+        <v>56.98</v>
       </c>
       <c r="G31">
-        <v>60.6</v>
+        <v>58.24</v>
       </c>
       <c r="H31">
-        <v>60.6</v>
+        <v>61.01</v>
       </c>
       <c r="I31" t="s">
         <v>49</v>
@@ -1498,16 +1498,16 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="F32">
-        <v>54.43</v>
+        <v>57.12</v>
       </c>
       <c r="G32">
-        <v>60.49</v>
+        <v>57.12</v>
       </c>
       <c r="H32">
-        <v>72.12</v>
+        <v>57.12</v>
       </c>
       <c r="I32" t="s">
         <v>49</v>
@@ -1527,16 +1527,16 @@
         <v>47</v>
       </c>
       <c r="E33">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="F33">
-        <v>57.05</v>
+        <v>49.3</v>
       </c>
       <c r="G33">
-        <v>58.07</v>
+        <v>57.04</v>
       </c>
       <c r="H33">
-        <v>61.92</v>
+        <v>67.42</v>
       </c>
       <c r="I33" t="s">
         <v>49</v>
@@ -1547,7 +1547,7 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C34" t="s">
         <v>46</v>
@@ -1556,16 +1556,16 @@
         <v>47</v>
       </c>
       <c r="E34">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F34">
-        <v>52.17</v>
+        <v>50.16</v>
       </c>
       <c r="G34">
-        <v>55.94</v>
+        <v>53.1</v>
       </c>
       <c r="H34">
-        <v>61.49</v>
+        <v>56.24</v>
       </c>
       <c r="I34" t="s">
         <v>49</v>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="52">
   <si>
     <t>نام منطقه</t>
   </si>
@@ -46,96 +46,96 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>پناهگاه حيات وحش دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه دراء</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
     <t>منطقه حفاظت شده ارژن و پريشان</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع توت سياه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بصيران</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دالان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
     <t>منطقه حفاظت شده برم فیروز</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه دراء</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع کوه سياه</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع پادنا</t>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مزايجان</t>
+  </si>
+  <si>
+    <t>پارک ملي قطرويه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
   </si>
   <si>
     <t>منطقه شکار ممن.ع آق جلو</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بناب</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مهارلو</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع شیکوه</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بناب</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بصيران</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دالان</t>
-  </si>
-  <si>
-    <t>پارک ملي قطرويه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع کوهستان</t>
   </si>
   <si>
@@ -157,16 +157,19 @@
     <t>مناطق حفاظت‌شده</t>
   </si>
   <si>
-    <t>1405-06-30</t>
-  </si>
-  <si>
-    <t>2026-09-21</t>
+    <t>1405-06-31</t>
+  </si>
+  <si>
+    <t>2026-09-22</t>
   </si>
   <si>
     <t>بسیار شدید</t>
   </si>
   <si>
     <t>شدید</t>
+  </si>
+  <si>
+    <t>خیلی زیاد</t>
   </si>
   <si>
     <t>بدون داده</t>
@@ -628,16 +631,16 @@
         <v>47</v>
       </c>
       <c r="E2">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>69.15000000000001</v>
+        <v>74.25</v>
       </c>
       <c r="G2">
-        <v>78.01000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="H2">
-        <v>88.94</v>
+        <v>80.25</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -648,7 +651,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s">
         <v>46</v>
@@ -657,16 +660,16 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F3">
-        <v>63.81</v>
+        <v>65.66</v>
       </c>
       <c r="G3">
-        <v>77.86</v>
+        <v>75.31</v>
       </c>
       <c r="H3">
-        <v>82.73</v>
+        <v>83.63</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -686,16 +689,16 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F4">
-        <v>64.91</v>
+        <v>68.25</v>
       </c>
       <c r="G4">
-        <v>76.45999999999999</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="H4">
-        <v>97.39</v>
+        <v>80.25</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -706,7 +709,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
         <v>46</v>
@@ -715,16 +718,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F5">
-        <v>65.41</v>
+        <v>59.6</v>
       </c>
       <c r="G5">
-        <v>75.95999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="H5">
-        <v>85.18000000000001</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -735,7 +738,7 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s">
         <v>46</v>
@@ -744,19 +747,19 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>67.59</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="G6">
-        <v>73.81999999999999</v>
+        <v>69.76000000000001</v>
       </c>
       <c r="H6">
-        <v>82.73</v>
+        <v>74.19</v>
       </c>
       <c r="I6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -764,7 +767,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
         <v>46</v>
@@ -773,19 +776,19 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>65.41</v>
+        <v>68.37</v>
       </c>
       <c r="G7">
-        <v>73.79000000000001</v>
+        <v>69.73</v>
       </c>
       <c r="H7">
-        <v>79.77</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="I7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -793,7 +796,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C8" t="s">
         <v>46</v>
@@ -802,19 +805,19 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F8">
-        <v>63.39</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="G8">
-        <v>71.67</v>
+        <v>69.19</v>
       </c>
       <c r="H8">
-        <v>76.09999999999999</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="I8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -831,19 +834,19 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F9">
-        <v>68.22</v>
+        <v>63.1</v>
       </c>
       <c r="G9">
-        <v>71.16</v>
+        <v>67.94</v>
       </c>
       <c r="H9">
-        <v>72.86</v>
+        <v>73.61</v>
       </c>
       <c r="I9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -851,7 +854,7 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
         <v>46</v>
@@ -860,19 +863,19 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F10">
-        <v>66.33</v>
+        <v>61.59</v>
       </c>
       <c r="G10">
-        <v>71.14</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="H10">
-        <v>74.34999999999999</v>
+        <v>76.77</v>
       </c>
       <c r="I10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -889,19 +892,19 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F11">
-        <v>64.05</v>
+        <v>61.48</v>
       </c>
       <c r="G11">
-        <v>70.48999999999999</v>
+        <v>67.75</v>
       </c>
       <c r="H11">
-        <v>77.68000000000001</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="I11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -918,16 +921,16 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="F12">
-        <v>67.34</v>
+        <v>56.22</v>
       </c>
       <c r="G12">
-        <v>69.7</v>
+        <v>67.62</v>
       </c>
       <c r="H12">
-        <v>72.05</v>
+        <v>82.55</v>
       </c>
       <c r="I12" t="s">
         <v>49</v>
@@ -938,7 +941,7 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s">
         <v>46</v>
@@ -947,16 +950,16 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="F13">
-        <v>61.17</v>
+        <v>64.47</v>
       </c>
       <c r="G13">
-        <v>69.67</v>
+        <v>67.56</v>
       </c>
       <c r="H13">
-        <v>78.08</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="I13" t="s">
         <v>49</v>
@@ -967,7 +970,7 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
         <v>46</v>
@@ -976,16 +979,16 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F14">
-        <v>60.65</v>
+        <v>62.03</v>
       </c>
       <c r="G14">
-        <v>67.92</v>
+        <v>66.95</v>
       </c>
       <c r="H14">
-        <v>75.23999999999999</v>
+        <v>69.14</v>
       </c>
       <c r="I14" t="s">
         <v>49</v>
@@ -1005,16 +1008,16 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="F15">
-        <v>66.19</v>
+        <v>55.44</v>
       </c>
       <c r="G15">
-        <v>67.52</v>
+        <v>66.11</v>
       </c>
       <c r="H15">
-        <v>69.31</v>
+        <v>74.34</v>
       </c>
       <c r="I15" t="s">
         <v>49</v>
@@ -1025,7 +1028,7 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
         <v>46</v>
@@ -1034,16 +1037,16 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="F16">
-        <v>60.44</v>
+        <v>58.49</v>
       </c>
       <c r="G16">
-        <v>67.37</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="H16">
-        <v>76.40000000000001</v>
+        <v>72.91</v>
       </c>
       <c r="I16" t="s">
         <v>49</v>
@@ -1054,7 +1057,7 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C17" t="s">
         <v>46</v>
@@ -1063,16 +1066,16 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F17">
-        <v>62.23</v>
+        <v>57.17</v>
       </c>
       <c r="G17">
-        <v>67.18000000000001</v>
+        <v>64.63</v>
       </c>
       <c r="H17">
-        <v>72.13</v>
+        <v>69.12</v>
       </c>
       <c r="I17" t="s">
         <v>49</v>
@@ -1083,7 +1086,7 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C18" t="s">
         <v>46</v>
@@ -1092,16 +1095,16 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="F18">
-        <v>50.47</v>
+        <v>54.71</v>
       </c>
       <c r="G18">
-        <v>67.09</v>
+        <v>63.23</v>
       </c>
       <c r="H18">
-        <v>85.78</v>
+        <v>70.13</v>
       </c>
       <c r="I18" t="s">
         <v>49</v>
@@ -1112,7 +1115,7 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C19" t="s">
         <v>46</v>
@@ -1121,16 +1124,16 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F19">
-        <v>52.2</v>
+        <v>53.77</v>
       </c>
       <c r="G19">
-        <v>66.72</v>
+        <v>63.12</v>
       </c>
       <c r="H19">
-        <v>83.44</v>
+        <v>74.63</v>
       </c>
       <c r="I19" t="s">
         <v>49</v>
@@ -1150,16 +1153,16 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="F20">
-        <v>63.33</v>
+        <v>54.45</v>
       </c>
       <c r="G20">
-        <v>66.42</v>
+        <v>62.81</v>
       </c>
       <c r="H20">
-        <v>70.95</v>
+        <v>71.94</v>
       </c>
       <c r="I20" t="s">
         <v>49</v>
@@ -1179,16 +1182,16 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F21">
-        <v>59.89</v>
+        <v>54.58</v>
       </c>
       <c r="G21">
-        <v>65.61</v>
+        <v>62.09</v>
       </c>
       <c r="H21">
-        <v>73.88</v>
+        <v>67.22</v>
       </c>
       <c r="I21" t="s">
         <v>49</v>
@@ -1211,13 +1214,13 @@
         <v>65</v>
       </c>
       <c r="F22">
-        <v>56.07</v>
+        <v>54.5</v>
       </c>
       <c r="G22">
-        <v>65.52</v>
+        <v>61.77</v>
       </c>
       <c r="H22">
-        <v>77.7</v>
+        <v>75.37</v>
       </c>
       <c r="I22" t="s">
         <v>49</v>
@@ -1240,13 +1243,13 @@
         <v>117</v>
       </c>
       <c r="F23">
-        <v>55.65</v>
+        <v>54.09</v>
       </c>
       <c r="G23">
-        <v>65.18000000000001</v>
+        <v>61.46</v>
       </c>
       <c r="H23">
-        <v>77.7</v>
+        <v>75.37</v>
       </c>
       <c r="I23" t="s">
         <v>49</v>
@@ -1257,7 +1260,7 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C24" t="s">
         <v>46</v>
@@ -1266,16 +1269,16 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F24">
-        <v>58.75</v>
+        <v>57.17</v>
       </c>
       <c r="G24">
-        <v>64.28</v>
+        <v>60.7</v>
       </c>
       <c r="H24">
-        <v>72.03</v>
+        <v>64.88</v>
       </c>
       <c r="I24" t="s">
         <v>49</v>
@@ -1286,7 +1289,7 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C25" t="s">
         <v>46</v>
@@ -1295,16 +1298,16 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F25">
-        <v>58.89</v>
+        <v>59.75</v>
       </c>
       <c r="G25">
-        <v>63.83</v>
+        <v>59.75</v>
       </c>
       <c r="H25">
-        <v>69.95999999999999</v>
+        <v>59.75</v>
       </c>
       <c r="I25" t="s">
         <v>49</v>
@@ -1315,7 +1318,7 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C26" t="s">
         <v>46</v>
@@ -1324,16 +1327,16 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F26">
-        <v>59.61</v>
+        <v>54.09</v>
       </c>
       <c r="G26">
-        <v>63.02</v>
+        <v>59.68</v>
       </c>
       <c r="H26">
-        <v>67.92</v>
+        <v>64.02</v>
       </c>
       <c r="I26" t="s">
         <v>49</v>
@@ -1353,16 +1356,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F27">
-        <v>58.95</v>
+        <v>54.96</v>
       </c>
       <c r="G27">
-        <v>62.64</v>
+        <v>59.3</v>
       </c>
       <c r="H27">
-        <v>68.17</v>
+        <v>63.65</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1382,16 +1385,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F28">
-        <v>56.77</v>
+        <v>56.56</v>
       </c>
       <c r="G28">
-        <v>62.3</v>
+        <v>59.1</v>
       </c>
       <c r="H28">
-        <v>65.65000000000001</v>
+        <v>63.78</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
@@ -1411,16 +1414,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F29">
-        <v>55.98</v>
+        <v>56.09</v>
       </c>
       <c r="G29">
-        <v>61.96</v>
+        <v>58.56</v>
       </c>
       <c r="H29">
-        <v>64.90000000000001</v>
+        <v>61.93</v>
       </c>
       <c r="I29" t="s">
         <v>49</v>
@@ -1431,7 +1434,7 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C30" t="s">
         <v>46</v>
@@ -1440,16 +1443,16 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F30">
-        <v>61.37</v>
+        <v>55.36</v>
       </c>
       <c r="G30">
-        <v>61.37</v>
+        <v>57.81</v>
       </c>
       <c r="H30">
-        <v>61.37</v>
+        <v>62.34</v>
       </c>
       <c r="I30" t="s">
         <v>49</v>
@@ -1469,16 +1472,16 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="F31">
-        <v>56.98</v>
+        <v>52.78</v>
       </c>
       <c r="G31">
-        <v>58.24</v>
+        <v>57.5</v>
       </c>
       <c r="H31">
-        <v>61.01</v>
+        <v>62.39</v>
       </c>
       <c r="I31" t="s">
         <v>49</v>
@@ -1501,13 +1504,13 @@
         <v>2</v>
       </c>
       <c r="F32">
-        <v>57.12</v>
+        <v>53</v>
       </c>
       <c r="G32">
-        <v>57.12</v>
+        <v>53</v>
       </c>
       <c r="H32">
-        <v>57.12</v>
+        <v>53</v>
       </c>
       <c r="I32" t="s">
         <v>49</v>
@@ -1530,16 +1533,16 @@
         <v>37</v>
       </c>
       <c r="F33">
-        <v>49.3</v>
+        <v>45.22</v>
       </c>
       <c r="G33">
-        <v>57.04</v>
+        <v>49.24</v>
       </c>
       <c r="H33">
-        <v>67.42</v>
+        <v>55.1</v>
       </c>
       <c r="I33" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1559,16 +1562,16 @@
         <v>9</v>
       </c>
       <c r="F34">
-        <v>50.16</v>
+        <v>44.28</v>
       </c>
       <c r="G34">
-        <v>53.1</v>
+        <v>49.01</v>
       </c>
       <c r="H34">
-        <v>56.24</v>
+        <v>51.51</v>
       </c>
       <c r="I34" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -1588,7 +1591,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -1608,7 +1611,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="51">
   <si>
     <t>نام منطقه</t>
   </si>
@@ -49,96 +49,96 @@
     <t>پناهگاه حيات وحش دره باغ</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بصيران</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع کوه دراء</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
+    <t>منطقه شکار ممنوع توت سياه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
   </si>
   <si>
     <t>منطقه حفاظت شده ارژن و پريشان</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>پارک ملي قطرويه</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع کوه خم</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع دالان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوهستان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع پادنا</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بصيران</t>
+    <t>منطقه حفاظت شده برم فیروز</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع شیکوه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
   </si>
   <si>
     <t>منطقه حفاظت شده میانجنگل فسا</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع دالان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مهارلو</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع مزايجان</t>
   </si>
   <si>
-    <t>پارک ملي قطرويه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع بناب</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع شیکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوهستان</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع کوه هوا و</t>
   </si>
   <si>
@@ -157,19 +157,16 @@
     <t>مناطق حفاظت‌شده</t>
   </si>
   <si>
-    <t>1405-06-31</t>
-  </si>
-  <si>
-    <t>2026-09-22</t>
+    <t>1405-07-01</t>
+  </si>
+  <si>
+    <t>2026-09-23</t>
   </si>
   <si>
     <t>بسیار شدید</t>
   </si>
   <si>
     <t>شدید</t>
-  </si>
-  <si>
-    <t>خیلی زیاد</t>
   </si>
   <si>
     <t>بدون داده</t>
@@ -634,13 +631,13 @@
         <v>3</v>
       </c>
       <c r="F2">
-        <v>74.25</v>
+        <v>74.63</v>
       </c>
       <c r="G2">
-        <v>76.8</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="H2">
-        <v>80.25</v>
+        <v>78.54000000000001</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -660,16 +657,16 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>65.66</v>
+        <v>71.23</v>
       </c>
       <c r="G3">
-        <v>75.31</v>
+        <v>76.42</v>
       </c>
       <c r="H3">
-        <v>83.63</v>
+        <v>78.54000000000001</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -689,16 +686,16 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="F4">
-        <v>68.25</v>
+        <v>56.45</v>
       </c>
       <c r="G4">
-        <v>74.09999999999999</v>
+        <v>75.77</v>
       </c>
       <c r="H4">
-        <v>80.25</v>
+        <v>87.16</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -709,7 +706,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
         <v>46</v>
@@ -718,16 +715,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F5">
-        <v>59.6</v>
+        <v>67.87</v>
       </c>
       <c r="G5">
-        <v>70.09999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="H5">
-        <v>76.31999999999999</v>
+        <v>87.95</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -750,16 +747,16 @@
         <v>4</v>
       </c>
       <c r="F6">
-        <v>65.68000000000001</v>
+        <v>73.8</v>
       </c>
       <c r="G6">
-        <v>69.76000000000001</v>
+        <v>75.62</v>
       </c>
       <c r="H6">
-        <v>74.19</v>
+        <v>76.41</v>
       </c>
       <c r="I6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -776,19 +773,19 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F7">
-        <v>68.37</v>
+        <v>69.76000000000001</v>
       </c>
       <c r="G7">
-        <v>69.73</v>
+        <v>72.63</v>
       </c>
       <c r="H7">
-        <v>71.90000000000001</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="I7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -805,19 +802,19 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="F8">
-        <v>65.73999999999999</v>
+        <v>63.36</v>
       </c>
       <c r="G8">
-        <v>69.19</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="H8">
-        <v>74.06999999999999</v>
+        <v>82.41</v>
       </c>
       <c r="I8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -834,19 +831,19 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="F9">
-        <v>63.1</v>
+        <v>68.47</v>
       </c>
       <c r="G9">
-        <v>67.94</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="H9">
-        <v>73.61</v>
+        <v>73.72</v>
       </c>
       <c r="I9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -854,7 +851,7 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
         <v>46</v>
@@ -863,19 +860,19 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>20</v>
+        <v>117</v>
       </c>
       <c r="F10">
-        <v>61.59</v>
+        <v>59.76</v>
       </c>
       <c r="G10">
-        <v>67.81999999999999</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="H10">
-        <v>76.77</v>
+        <v>84.86</v>
       </c>
       <c r="I10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -892,19 +889,19 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F11">
-        <v>61.48</v>
+        <v>66.91</v>
       </c>
       <c r="G11">
-        <v>67.75</v>
+        <v>70.31999999999999</v>
       </c>
       <c r="H11">
-        <v>74.34999999999999</v>
+        <v>73.77</v>
       </c>
       <c r="I11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -912,7 +909,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
         <v>46</v>
@@ -921,19 +918,19 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="F12">
-        <v>56.22</v>
+        <v>59.85</v>
       </c>
       <c r="G12">
-        <v>67.62</v>
+        <v>70.31</v>
       </c>
       <c r="H12">
-        <v>82.55</v>
+        <v>79.20999999999999</v>
       </c>
       <c r="I12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -950,19 +947,19 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="F13">
-        <v>64.47</v>
+        <v>69.37</v>
       </c>
       <c r="G13">
-        <v>67.56</v>
+        <v>70.05</v>
       </c>
       <c r="H13">
-        <v>70.90000000000001</v>
+        <v>71.23999999999999</v>
       </c>
       <c r="I13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -979,16 +976,16 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F14">
-        <v>62.03</v>
+        <v>67.22</v>
       </c>
       <c r="G14">
-        <v>66.95</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="H14">
-        <v>69.14</v>
+        <v>71.64</v>
       </c>
       <c r="I14" t="s">
         <v>49</v>
@@ -999,7 +996,7 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s">
         <v>46</v>
@@ -1008,16 +1005,16 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="F15">
-        <v>55.44</v>
+        <v>59.46</v>
       </c>
       <c r="G15">
-        <v>66.11</v>
+        <v>69.39</v>
       </c>
       <c r="H15">
-        <v>74.34</v>
+        <v>75.78</v>
       </c>
       <c r="I15" t="s">
         <v>49</v>
@@ -1037,16 +1034,16 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F16">
-        <v>58.49</v>
+        <v>62.79</v>
       </c>
       <c r="G16">
-        <v>65.20999999999999</v>
+        <v>68.45</v>
       </c>
       <c r="H16">
-        <v>72.91</v>
+        <v>74.66</v>
       </c>
       <c r="I16" t="s">
         <v>49</v>
@@ -1069,13 +1066,13 @@
         <v>19</v>
       </c>
       <c r="F17">
-        <v>57.17</v>
+        <v>63.02</v>
       </c>
       <c r="G17">
-        <v>64.63</v>
+        <v>68.36</v>
       </c>
       <c r="H17">
-        <v>69.12</v>
+        <v>77.68000000000001</v>
       </c>
       <c r="I17" t="s">
         <v>49</v>
@@ -1095,16 +1092,16 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F18">
-        <v>54.71</v>
+        <v>67.67</v>
       </c>
       <c r="G18">
-        <v>63.23</v>
+        <v>67.67</v>
       </c>
       <c r="H18">
-        <v>70.13</v>
+        <v>67.67</v>
       </c>
       <c r="I18" t="s">
         <v>49</v>
@@ -1115,7 +1112,7 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
         <v>46</v>
@@ -1124,16 +1121,16 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F19">
-        <v>53.77</v>
+        <v>59.87</v>
       </c>
       <c r="G19">
-        <v>63.12</v>
+        <v>67.12</v>
       </c>
       <c r="H19">
-        <v>74.63</v>
+        <v>76.78</v>
       </c>
       <c r="I19" t="s">
         <v>49</v>
@@ -1144,7 +1141,7 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C20" t="s">
         <v>46</v>
@@ -1153,16 +1150,16 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F20">
-        <v>54.45</v>
+        <v>61.12</v>
       </c>
       <c r="G20">
-        <v>62.81</v>
+        <v>66.88</v>
       </c>
       <c r="H20">
-        <v>71.94</v>
+        <v>70.09</v>
       </c>
       <c r="I20" t="s">
         <v>49</v>
@@ -1182,16 +1179,16 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F21">
-        <v>54.58</v>
+        <v>66.83</v>
       </c>
       <c r="G21">
-        <v>62.09</v>
+        <v>66.83</v>
       </c>
       <c r="H21">
-        <v>67.22</v>
+        <v>66.83</v>
       </c>
       <c r="I21" t="s">
         <v>49</v>
@@ -1202,7 +1199,7 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C22" t="s">
         <v>46</v>
@@ -1211,16 +1208,16 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F22">
-        <v>54.5</v>
+        <v>52.52</v>
       </c>
       <c r="G22">
-        <v>61.77</v>
+        <v>66.66</v>
       </c>
       <c r="H22">
-        <v>75.37</v>
+        <v>77.88</v>
       </c>
       <c r="I22" t="s">
         <v>49</v>
@@ -1231,7 +1228,7 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C23" t="s">
         <v>46</v>
@@ -1240,16 +1237,16 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>117</v>
+        <v>20</v>
       </c>
       <c r="F23">
-        <v>54.09</v>
+        <v>61.14</v>
       </c>
       <c r="G23">
-        <v>61.46</v>
+        <v>66.58</v>
       </c>
       <c r="H23">
-        <v>75.37</v>
+        <v>74.54000000000001</v>
       </c>
       <c r="I23" t="s">
         <v>49</v>
@@ -1260,7 +1257,7 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C24" t="s">
         <v>46</v>
@@ -1269,16 +1266,16 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F24">
-        <v>57.17</v>
+        <v>57.05</v>
       </c>
       <c r="G24">
-        <v>60.7</v>
+        <v>65.7</v>
       </c>
       <c r="H24">
-        <v>64.88</v>
+        <v>71.42</v>
       </c>
       <c r="I24" t="s">
         <v>49</v>
@@ -1289,7 +1286,7 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C25" t="s">
         <v>46</v>
@@ -1298,16 +1295,16 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F25">
-        <v>59.75</v>
+        <v>53.28</v>
       </c>
       <c r="G25">
-        <v>59.75</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="H25">
-        <v>59.75</v>
+        <v>73.26000000000001</v>
       </c>
       <c r="I25" t="s">
         <v>49</v>
@@ -1327,16 +1324,16 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F26">
-        <v>54.09</v>
+        <v>57.55</v>
       </c>
       <c r="G26">
-        <v>59.68</v>
+        <v>63.41</v>
       </c>
       <c r="H26">
-        <v>64.02</v>
+        <v>70.39</v>
       </c>
       <c r="I26" t="s">
         <v>49</v>
@@ -1347,7 +1344,7 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
         <v>46</v>
@@ -1356,16 +1353,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F27">
-        <v>54.96</v>
+        <v>53.16</v>
       </c>
       <c r="G27">
-        <v>59.3</v>
+        <v>62.46</v>
       </c>
       <c r="H27">
-        <v>63.65</v>
+        <v>77.48</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1376,7 +1373,7 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C28" t="s">
         <v>46</v>
@@ -1385,16 +1382,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F28">
-        <v>56.56</v>
+        <v>58.16</v>
       </c>
       <c r="G28">
-        <v>59.1</v>
+        <v>61.45</v>
       </c>
       <c r="H28">
-        <v>63.78</v>
+        <v>67.86</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
@@ -1417,13 +1414,13 @@
         <v>20</v>
       </c>
       <c r="F29">
-        <v>56.09</v>
+        <v>56.1</v>
       </c>
       <c r="G29">
-        <v>58.56</v>
+        <v>58.4</v>
       </c>
       <c r="H29">
-        <v>61.93</v>
+        <v>61.72</v>
       </c>
       <c r="I29" t="s">
         <v>49</v>
@@ -1446,13 +1443,13 @@
         <v>10</v>
       </c>
       <c r="F30">
-        <v>55.36</v>
+        <v>55.73</v>
       </c>
       <c r="G30">
-        <v>57.81</v>
+        <v>58.04</v>
       </c>
       <c r="H30">
-        <v>62.34</v>
+        <v>62.37</v>
       </c>
       <c r="I30" t="s">
         <v>49</v>
@@ -1472,16 +1469,16 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="F31">
-        <v>52.78</v>
+        <v>50</v>
       </c>
       <c r="G31">
-        <v>57.5</v>
+        <v>53.73</v>
       </c>
       <c r="H31">
-        <v>62.39</v>
+        <v>55.83</v>
       </c>
       <c r="I31" t="s">
         <v>49</v>
@@ -1501,16 +1498,16 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="F32">
-        <v>53</v>
+        <v>49.98</v>
       </c>
       <c r="G32">
-        <v>53</v>
+        <v>53.67</v>
       </c>
       <c r="H32">
-        <v>53</v>
+        <v>58.11</v>
       </c>
       <c r="I32" t="s">
         <v>49</v>
@@ -1533,16 +1530,16 @@
         <v>37</v>
       </c>
       <c r="F33">
-        <v>45.22</v>
+        <v>43.7</v>
       </c>
       <c r="G33">
-        <v>49.24</v>
+        <v>51.34</v>
       </c>
       <c r="H33">
-        <v>55.1</v>
+        <v>58.09</v>
       </c>
       <c r="I33" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1562,16 +1559,16 @@
         <v>9</v>
       </c>
       <c r="F34">
-        <v>44.28</v>
+        <v>44.88</v>
       </c>
       <c r="G34">
-        <v>49.01</v>
+        <v>50.75</v>
       </c>
       <c r="H34">
-        <v>51.51</v>
+        <v>55.27</v>
       </c>
       <c r="I34" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -1591,7 +1588,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -1611,7 +1608,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -52,99 +52,99 @@
     <t>منطقه شکار ممنوع دره باغ</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع توت سياه</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع بصيران</t>
   </si>
   <si>
+    <t>پارک ملي قطرويه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع کوه دراء</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
+    <t>منطقه حفاظت شده بهرام گور</t>
   </si>
   <si>
     <t>منطقه حفاظت شده تنگ بستانک</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده برم فیروز</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوهستان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
   </si>
   <si>
     <t>منطقه شکار ممن.ع آق جلو</t>
   </si>
   <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بناب</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دالان</t>
   </si>
   <si>
     <t>پارک ملی بمو</t>
   </si>
   <si>
-    <t>پارک ملي قطرويه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دالان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوهستان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
+    <t>منطقه شکار ممنوع مهارلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع شیکوه</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع مزايجان</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع بناب</t>
+    <t>منطقه حفاظت شده هرمود</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع کوه هوا و</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده هرمود</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع چاه نفت</t>
   </si>
   <si>
@@ -157,10 +157,10 @@
     <t>مناطق حفاظت‌شده</t>
   </si>
   <si>
-    <t>1405-07-01</t>
-  </si>
-  <si>
-    <t>2026-09-23</t>
+    <t>1405-07-02</t>
+  </si>
+  <si>
+    <t>2026-09-24</t>
   </si>
   <si>
     <t>بسیار شدید</t>
@@ -631,13 +631,13 @@
         <v>3</v>
       </c>
       <c r="F2">
-        <v>74.63</v>
+        <v>80.98</v>
       </c>
       <c r="G2">
-        <v>76.98999999999999</v>
+        <v>82.25</v>
       </c>
       <c r="H2">
-        <v>78.54000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -660,13 +660,13 @@
         <v>12</v>
       </c>
       <c r="F3">
-        <v>71.23</v>
+        <v>71.26000000000001</v>
       </c>
       <c r="G3">
-        <v>76.42</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="H3">
-        <v>78.54000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -686,16 +686,16 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>56.45</v>
+        <v>75.2</v>
       </c>
       <c r="G4">
-        <v>75.77</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="H4">
-        <v>87.16</v>
+        <v>83.62</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -715,16 +715,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F5">
-        <v>67.87</v>
+        <v>58.63</v>
       </c>
       <c r="G5">
-        <v>75.7</v>
+        <v>76.55</v>
       </c>
       <c r="H5">
-        <v>87.95</v>
+        <v>84.28</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -735,7 +735,7 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
         <v>46</v>
@@ -747,13 +747,13 @@
         <v>4</v>
       </c>
       <c r="F6">
-        <v>73.8</v>
+        <v>72.81</v>
       </c>
       <c r="G6">
-        <v>75.62</v>
+        <v>72.81</v>
       </c>
       <c r="H6">
-        <v>76.41</v>
+        <v>72.81</v>
       </c>
       <c r="I6" t="s">
         <v>48</v>
@@ -773,16 +773,16 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F7">
-        <v>69.76000000000001</v>
+        <v>58.88</v>
       </c>
       <c r="G7">
-        <v>72.63</v>
+        <v>71.89</v>
       </c>
       <c r="H7">
-        <v>74.34999999999999</v>
+        <v>78.86</v>
       </c>
       <c r="I7" t="s">
         <v>48</v>
@@ -793,7 +793,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
         <v>46</v>
@@ -802,16 +802,16 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="F8">
-        <v>63.36</v>
+        <v>65.23999999999999</v>
       </c>
       <c r="G8">
-        <v>71.43000000000001</v>
+        <v>70.84</v>
       </c>
       <c r="H8">
-        <v>82.41</v>
+        <v>82.20999999999999</v>
       </c>
       <c r="I8" t="s">
         <v>48</v>
@@ -822,7 +822,7 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
         <v>46</v>
@@ -831,16 +831,16 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="F9">
-        <v>68.47</v>
+        <v>66.34</v>
       </c>
       <c r="G9">
-        <v>71.09999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="H9">
-        <v>73.72</v>
+        <v>73.17</v>
       </c>
       <c r="I9" t="s">
         <v>48</v>
@@ -860,19 +860,19 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>117</v>
+        <v>5</v>
       </c>
       <c r="F10">
-        <v>59.76</v>
+        <v>66.37</v>
       </c>
       <c r="G10">
-        <v>70.95999999999999</v>
+        <v>69.03</v>
       </c>
       <c r="H10">
-        <v>84.86</v>
+        <v>72.41</v>
       </c>
       <c r="I10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -889,19 +889,19 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F11">
-        <v>66.91</v>
+        <v>62.29</v>
       </c>
       <c r="G11">
-        <v>70.31999999999999</v>
+        <v>67.43000000000001</v>
       </c>
       <c r="H11">
-        <v>73.77</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="I11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -918,19 +918,19 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>65</v>
+        <v>8</v>
       </c>
       <c r="F12">
-        <v>59.85</v>
+        <v>58.49</v>
       </c>
       <c r="G12">
-        <v>70.31</v>
+        <v>66.83</v>
       </c>
       <c r="H12">
-        <v>79.20999999999999</v>
+        <v>75.67</v>
       </c>
       <c r="I12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -947,19 +947,19 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>117</v>
       </c>
       <c r="F13">
-        <v>69.37</v>
+        <v>54.86</v>
       </c>
       <c r="G13">
-        <v>70.05</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="H13">
-        <v>71.23999999999999</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="I13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -976,16 +976,16 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F14">
-        <v>67.22</v>
+        <v>62.37</v>
       </c>
       <c r="G14">
-        <v>69.70999999999999</v>
+        <v>65.98999999999999</v>
       </c>
       <c r="H14">
-        <v>71.64</v>
+        <v>69.63</v>
       </c>
       <c r="I14" t="s">
         <v>49</v>
@@ -996,7 +996,7 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
         <v>46</v>
@@ -1005,16 +1005,16 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="F15">
-        <v>59.46</v>
+        <v>54.36</v>
       </c>
       <c r="G15">
-        <v>69.39</v>
+        <v>65.73</v>
       </c>
       <c r="H15">
-        <v>75.78</v>
+        <v>75.11</v>
       </c>
       <c r="I15" t="s">
         <v>49</v>
@@ -1025,7 +1025,7 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
         <v>46</v>
@@ -1034,16 +1034,16 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="F16">
-        <v>62.79</v>
+        <v>54.86</v>
       </c>
       <c r="G16">
-        <v>68.45</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="H16">
-        <v>74.66</v>
+        <v>76.28</v>
       </c>
       <c r="I16" t="s">
         <v>49</v>
@@ -1063,16 +1063,16 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F17">
-        <v>63.02</v>
+        <v>55.57</v>
       </c>
       <c r="G17">
-        <v>68.36</v>
+        <v>65</v>
       </c>
       <c r="H17">
-        <v>77.68000000000001</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="I17" t="s">
         <v>49</v>
@@ -1083,7 +1083,7 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
         <v>46</v>
@@ -1092,16 +1092,16 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F18">
-        <v>67.67</v>
+        <v>64.87</v>
       </c>
       <c r="G18">
-        <v>67.67</v>
+        <v>64.87</v>
       </c>
       <c r="H18">
-        <v>67.67</v>
+        <v>64.87</v>
       </c>
       <c r="I18" t="s">
         <v>49</v>
@@ -1124,13 +1124,13 @@
         <v>18</v>
       </c>
       <c r="F19">
-        <v>59.87</v>
+        <v>54.42</v>
       </c>
       <c r="G19">
-        <v>67.12</v>
+        <v>64.83</v>
       </c>
       <c r="H19">
-        <v>76.78</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="I19" t="s">
         <v>49</v>
@@ -1141,7 +1141,7 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C20" t="s">
         <v>46</v>
@@ -1150,16 +1150,16 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F20">
-        <v>61.12</v>
+        <v>61.61</v>
       </c>
       <c r="G20">
-        <v>66.88</v>
+        <v>64.28</v>
       </c>
       <c r="H20">
-        <v>70.09</v>
+        <v>67.08</v>
       </c>
       <c r="I20" t="s">
         <v>49</v>
@@ -1179,16 +1179,16 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F21">
-        <v>66.83</v>
+        <v>55.72</v>
       </c>
       <c r="G21">
-        <v>66.83</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="H21">
-        <v>66.83</v>
+        <v>77.06999999999999</v>
       </c>
       <c r="I21" t="s">
         <v>49</v>
@@ -1208,16 +1208,16 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="F22">
-        <v>52.52</v>
+        <v>58.47</v>
       </c>
       <c r="G22">
-        <v>66.66</v>
+        <v>63.16</v>
       </c>
       <c r="H22">
-        <v>77.88</v>
+        <v>67.63</v>
       </c>
       <c r="I22" t="s">
         <v>49</v>
@@ -1237,16 +1237,16 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F23">
-        <v>61.14</v>
+        <v>61.31</v>
       </c>
       <c r="G23">
-        <v>66.58</v>
+        <v>63.16</v>
       </c>
       <c r="H23">
-        <v>74.54000000000001</v>
+        <v>65.02</v>
       </c>
       <c r="I23" t="s">
         <v>49</v>
@@ -1266,16 +1266,16 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F24">
-        <v>57.05</v>
+        <v>53.91</v>
       </c>
       <c r="G24">
-        <v>65.7</v>
+        <v>62.62</v>
       </c>
       <c r="H24">
-        <v>71.42</v>
+        <v>75.03</v>
       </c>
       <c r="I24" t="s">
         <v>49</v>
@@ -1301,10 +1301,10 @@
         <v>53.28</v>
       </c>
       <c r="G25">
-        <v>64.73999999999999</v>
+        <v>62.22</v>
       </c>
       <c r="H25">
-        <v>73.26000000000001</v>
+        <v>69.61</v>
       </c>
       <c r="I25" t="s">
         <v>49</v>
@@ -1324,16 +1324,16 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="F26">
-        <v>57.55</v>
+        <v>57.11</v>
       </c>
       <c r="G26">
-        <v>63.41</v>
+        <v>62.02</v>
       </c>
       <c r="H26">
-        <v>70.39</v>
+        <v>65.77</v>
       </c>
       <c r="I26" t="s">
         <v>49</v>
@@ -1344,7 +1344,7 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
         <v>46</v>
@@ -1353,16 +1353,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F27">
-        <v>53.16</v>
+        <v>55.41</v>
       </c>
       <c r="G27">
-        <v>62.46</v>
+        <v>61.33</v>
       </c>
       <c r="H27">
-        <v>77.48</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1382,16 +1382,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F28">
-        <v>58.16</v>
+        <v>55.34</v>
       </c>
       <c r="G28">
-        <v>61.45</v>
+        <v>60.57</v>
       </c>
       <c r="H28">
-        <v>67.86</v>
+        <v>69</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
@@ -1411,16 +1411,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F29">
-        <v>56.1</v>
+        <v>56.61</v>
       </c>
       <c r="G29">
-        <v>58.4</v>
+        <v>59.23</v>
       </c>
       <c r="H29">
-        <v>61.72</v>
+        <v>61.3</v>
       </c>
       <c r="I29" t="s">
         <v>49</v>
@@ -1440,16 +1440,16 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F30">
-        <v>55.73</v>
+        <v>56.15</v>
       </c>
       <c r="G30">
-        <v>58.04</v>
+        <v>58.76</v>
       </c>
       <c r="H30">
-        <v>62.37</v>
+        <v>62.85</v>
       </c>
       <c r="I30" t="s">
         <v>49</v>
@@ -1469,16 +1469,16 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="F31">
-        <v>50</v>
+        <v>55.54</v>
       </c>
       <c r="G31">
-        <v>53.73</v>
+        <v>57.95</v>
       </c>
       <c r="H31">
-        <v>55.83</v>
+        <v>60.66</v>
       </c>
       <c r="I31" t="s">
         <v>49</v>
@@ -1498,16 +1498,16 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F32">
-        <v>49.98</v>
+        <v>52.83</v>
       </c>
       <c r="G32">
-        <v>53.67</v>
+        <v>57.33</v>
       </c>
       <c r="H32">
-        <v>58.11</v>
+        <v>59.98</v>
       </c>
       <c r="I32" t="s">
         <v>49</v>
@@ -1518,7 +1518,7 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C33" t="s">
         <v>46</v>
@@ -1527,16 +1527,16 @@
         <v>47</v>
       </c>
       <c r="E33">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="F33">
-        <v>43.7</v>
+        <v>51.58</v>
       </c>
       <c r="G33">
-        <v>51.34</v>
+        <v>55.63</v>
       </c>
       <c r="H33">
-        <v>58.09</v>
+        <v>60.52</v>
       </c>
       <c r="I33" t="s">
         <v>49</v>
@@ -1547,7 +1547,7 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C34" t="s">
         <v>46</v>
@@ -1556,16 +1556,16 @@
         <v>47</v>
       </c>
       <c r="E34">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="F34">
-        <v>44.88</v>
+        <v>46.48</v>
       </c>
       <c r="G34">
-        <v>50.75</v>
+        <v>52.23</v>
       </c>
       <c r="H34">
-        <v>55.27</v>
+        <v>59.6</v>
       </c>
       <c r="I34" t="s">
         <v>49</v>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -55,37 +55,61 @@
     <t>منطقه شکار ممنوع توت سياه</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع کوهستان</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع بصيران</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع دالان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
     <t>پارک ملي قطرويه</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع کوه دراء</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع پادنا</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
     <t>منطقه حفاظت شده برم فیروز</t>
   </si>
   <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع شیکوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
     <t>پناهگاه حيات وحش بختگان</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
+    <t>منطقه حفاظت شده ماله گاله</t>
   </si>
   <si>
     <t>پارک ملي بختگان</t>
@@ -94,54 +118,30 @@
     <t>منطقه حفاظت شده میانجنگل فسا</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوهستان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
+    <t>پارک ملی بمو</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع خرمنکوه</t>
   </si>
   <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
+    <t>منطقه شکار ممنوع کوه گورم</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع کوه سياه</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع مهارلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مزايجان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده هرمود</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع بناب</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع دالان</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع شیکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده هرمود</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع کوه هوا و</t>
   </si>
   <si>
@@ -157,10 +157,10 @@
     <t>مناطق حفاظت‌شده</t>
   </si>
   <si>
-    <t>1405-07-02</t>
-  </si>
-  <si>
-    <t>2026-09-24</t>
+    <t>1405-07-03</t>
+  </si>
+  <si>
+    <t>2026-09-25</t>
   </si>
   <si>
     <t>بسیار شدید</t>
@@ -631,13 +631,13 @@
         <v>3</v>
       </c>
       <c r="F2">
-        <v>80.98</v>
+        <v>81.42</v>
       </c>
       <c r="G2">
-        <v>82.25</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="H2">
-        <v>84.2</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -660,13 +660,13 @@
         <v>12</v>
       </c>
       <c r="F3">
-        <v>71.26000000000001</v>
+        <v>71.13</v>
       </c>
       <c r="G3">
-        <v>80.09999999999999</v>
+        <v>84.29000000000001</v>
       </c>
       <c r="H3">
-        <v>84.2</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -689,13 +689,13 @@
         <v>4</v>
       </c>
       <c r="F4">
-        <v>75.2</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="G4">
-        <v>78.90000000000001</v>
+        <v>83.38</v>
       </c>
       <c r="H4">
-        <v>83.62</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -715,16 +715,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>58.63</v>
+        <v>81.03</v>
       </c>
       <c r="G5">
-        <v>76.55</v>
+        <v>81.03</v>
       </c>
       <c r="H5">
-        <v>84.28</v>
+        <v>81.03</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -735,7 +735,7 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s">
         <v>46</v>
@@ -744,16 +744,16 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="F6">
-        <v>72.81</v>
+        <v>54.68</v>
       </c>
       <c r="G6">
-        <v>72.81</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="H6">
-        <v>72.81</v>
+        <v>93.33</v>
       </c>
       <c r="I6" t="s">
         <v>48</v>
@@ -764,7 +764,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
         <v>46</v>
@@ -773,16 +773,16 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F7">
-        <v>58.88</v>
+        <v>71.06999999999999</v>
       </c>
       <c r="G7">
-        <v>71.89</v>
+        <v>75.66</v>
       </c>
       <c r="H7">
-        <v>78.86</v>
+        <v>77.55</v>
       </c>
       <c r="I7" t="s">
         <v>48</v>
@@ -793,7 +793,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C8" t="s">
         <v>46</v>
@@ -802,16 +802,16 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F8">
-        <v>65.23999999999999</v>
+        <v>63.42</v>
       </c>
       <c r="G8">
-        <v>70.84</v>
+        <v>74.34</v>
       </c>
       <c r="H8">
-        <v>82.20999999999999</v>
+        <v>79.81</v>
       </c>
       <c r="I8" t="s">
         <v>48</v>
@@ -831,16 +831,16 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F9">
-        <v>66.34</v>
+        <v>73.45999999999999</v>
       </c>
       <c r="G9">
-        <v>70.5</v>
+        <v>73.45999999999999</v>
       </c>
       <c r="H9">
-        <v>73.17</v>
+        <v>73.45999999999999</v>
       </c>
       <c r="I9" t="s">
         <v>48</v>
@@ -863,16 +863,16 @@
         <v>5</v>
       </c>
       <c r="F10">
-        <v>66.37</v>
+        <v>68.11</v>
       </c>
       <c r="G10">
-        <v>69.03</v>
+        <v>73.19</v>
       </c>
       <c r="H10">
-        <v>72.41</v>
+        <v>77.2</v>
       </c>
       <c r="I10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -880,7 +880,7 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s">
         <v>46</v>
@@ -889,19 +889,19 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F11">
-        <v>62.29</v>
+        <v>66.23</v>
       </c>
       <c r="G11">
-        <v>67.43000000000001</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="H11">
-        <v>71.79000000000001</v>
+        <v>80.34</v>
       </c>
       <c r="I11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -909,7 +909,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
         <v>46</v>
@@ -918,16 +918,16 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F12">
-        <v>58.49</v>
+        <v>64</v>
       </c>
       <c r="G12">
-        <v>66.83</v>
+        <v>69.44</v>
       </c>
       <c r="H12">
-        <v>75.67</v>
+        <v>78.27</v>
       </c>
       <c r="I12" t="s">
         <v>49</v>
@@ -947,16 +947,16 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>117</v>
+        <v>3</v>
       </c>
       <c r="F13">
-        <v>54.86</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="G13">
-        <v>66.18000000000001</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="H13">
-        <v>77.79000000000001</v>
+        <v>68.7</v>
       </c>
       <c r="I13" t="s">
         <v>49</v>
@@ -976,16 +976,16 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F14">
-        <v>62.37</v>
+        <v>65.08</v>
       </c>
       <c r="G14">
-        <v>65.98999999999999</v>
+        <v>68.02</v>
       </c>
       <c r="H14">
-        <v>69.63</v>
+        <v>71.44</v>
       </c>
       <c r="I14" t="s">
         <v>49</v>
@@ -1008,13 +1008,13 @@
         <v>62</v>
       </c>
       <c r="F15">
-        <v>54.36</v>
+        <v>57.51</v>
       </c>
       <c r="G15">
-        <v>65.73</v>
+        <v>67.98</v>
       </c>
       <c r="H15">
-        <v>75.11</v>
+        <v>75.31999999999999</v>
       </c>
       <c r="I15" t="s">
         <v>49</v>
@@ -1025,7 +1025,7 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
         <v>46</v>
@@ -1034,16 +1034,16 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="F16">
-        <v>54.86</v>
+        <v>57.37</v>
       </c>
       <c r="G16">
-        <v>65.48999999999999</v>
+        <v>67.11</v>
       </c>
       <c r="H16">
-        <v>76.28</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="I16" t="s">
         <v>49</v>
@@ -1063,16 +1063,16 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F17">
-        <v>55.57</v>
+        <v>58.35</v>
       </c>
       <c r="G17">
-        <v>65</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="H17">
-        <v>68.68000000000001</v>
+        <v>75.20999999999999</v>
       </c>
       <c r="I17" t="s">
         <v>49</v>
@@ -1095,13 +1095,13 @@
         <v>2</v>
       </c>
       <c r="F18">
-        <v>64.87</v>
+        <v>64.7</v>
       </c>
       <c r="G18">
-        <v>64.87</v>
+        <v>66.8</v>
       </c>
       <c r="H18">
-        <v>64.87</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="I18" t="s">
         <v>49</v>
@@ -1121,16 +1121,16 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="F19">
-        <v>54.42</v>
+        <v>63.03</v>
       </c>
       <c r="G19">
-        <v>64.83</v>
+        <v>66.73</v>
       </c>
       <c r="H19">
-        <v>78.34999999999999</v>
+        <v>70.12</v>
       </c>
       <c r="I19" t="s">
         <v>49</v>
@@ -1141,7 +1141,7 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C20" t="s">
         <v>46</v>
@@ -1150,16 +1150,16 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F20">
-        <v>61.61</v>
+        <v>58.69</v>
       </c>
       <c r="G20">
-        <v>64.28</v>
+        <v>65.36</v>
       </c>
       <c r="H20">
-        <v>67.08</v>
+        <v>76.23</v>
       </c>
       <c r="I20" t="s">
         <v>49</v>
@@ -1179,16 +1179,16 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F21">
-        <v>55.72</v>
+        <v>60.07</v>
       </c>
       <c r="G21">
-        <v>64.23999999999999</v>
+        <v>65.14</v>
       </c>
       <c r="H21">
-        <v>77.06999999999999</v>
+        <v>71.41</v>
       </c>
       <c r="I21" t="s">
         <v>49</v>
@@ -1199,7 +1199,7 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C22" t="s">
         <v>46</v>
@@ -1208,16 +1208,16 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>12</v>
+        <v>117</v>
       </c>
       <c r="F22">
-        <v>58.47</v>
+        <v>54.73</v>
       </c>
       <c r="G22">
-        <v>63.16</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="H22">
-        <v>67.63</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="I22" t="s">
         <v>49</v>
@@ -1228,7 +1228,7 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C23" t="s">
         <v>46</v>
@@ -1237,16 +1237,16 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F23">
-        <v>61.31</v>
+        <v>56.19</v>
       </c>
       <c r="G23">
-        <v>63.16</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="H23">
-        <v>65.02</v>
+        <v>79.44</v>
       </c>
       <c r="I23" t="s">
         <v>49</v>
@@ -1266,16 +1266,16 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="F24">
-        <v>53.91</v>
+        <v>54.73</v>
       </c>
       <c r="G24">
-        <v>62.62</v>
+        <v>64.61</v>
       </c>
       <c r="H24">
-        <v>75.03</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="I24" t="s">
         <v>49</v>
@@ -1286,7 +1286,7 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C25" t="s">
         <v>46</v>
@@ -1295,16 +1295,16 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F25">
-        <v>53.28</v>
+        <v>58.99</v>
       </c>
       <c r="G25">
-        <v>62.22</v>
+        <v>63.31</v>
       </c>
       <c r="H25">
-        <v>69.61</v>
+        <v>67.58</v>
       </c>
       <c r="I25" t="s">
         <v>49</v>
@@ -1315,7 +1315,7 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s">
         <v>46</v>
@@ -1324,16 +1324,16 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F26">
-        <v>57.11</v>
+        <v>58.69</v>
       </c>
       <c r="G26">
-        <v>62.02</v>
+        <v>63.26</v>
       </c>
       <c r="H26">
-        <v>65.77</v>
+        <v>70.08</v>
       </c>
       <c r="I26" t="s">
         <v>49</v>
@@ -1353,16 +1353,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F27">
-        <v>55.41</v>
+        <v>58.85</v>
       </c>
       <c r="G27">
-        <v>61.33</v>
+        <v>62.02</v>
       </c>
       <c r="H27">
-        <v>65.06999999999999</v>
+        <v>63.93</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1373,7 +1373,7 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C28" t="s">
         <v>46</v>
@@ -1382,16 +1382,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F28">
-        <v>55.34</v>
+        <v>57.66</v>
       </c>
       <c r="G28">
-        <v>60.57</v>
+        <v>60.99</v>
       </c>
       <c r="H28">
-        <v>69</v>
+        <v>65.72</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
@@ -1411,16 +1411,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F29">
-        <v>56.61</v>
+        <v>56.13</v>
       </c>
       <c r="G29">
-        <v>59.23</v>
+        <v>60.87</v>
       </c>
       <c r="H29">
-        <v>61.3</v>
+        <v>67.25</v>
       </c>
       <c r="I29" t="s">
         <v>49</v>
@@ -1440,16 +1440,16 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F30">
-        <v>56.15</v>
+        <v>55.78</v>
       </c>
       <c r="G30">
-        <v>58.76</v>
+        <v>59.53</v>
       </c>
       <c r="H30">
-        <v>62.85</v>
+        <v>61.34</v>
       </c>
       <c r="I30" t="s">
         <v>49</v>
@@ -1469,16 +1469,16 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="F31">
-        <v>55.54</v>
+        <v>53.86</v>
       </c>
       <c r="G31">
-        <v>57.95</v>
+        <v>58.54</v>
       </c>
       <c r="H31">
-        <v>60.66</v>
+        <v>62.99</v>
       </c>
       <c r="I31" t="s">
         <v>49</v>
@@ -1489,7 +1489,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C32" t="s">
         <v>46</v>
@@ -1498,16 +1498,16 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F32">
-        <v>52.83</v>
+        <v>53.33</v>
       </c>
       <c r="G32">
-        <v>57.33</v>
+        <v>57.13</v>
       </c>
       <c r="H32">
-        <v>59.98</v>
+        <v>63.77</v>
       </c>
       <c r="I32" t="s">
         <v>49</v>
@@ -1518,7 +1518,7 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C33" t="s">
         <v>46</v>
@@ -1527,16 +1527,16 @@
         <v>47</v>
       </c>
       <c r="E33">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F33">
-        <v>51.58</v>
+        <v>52.52</v>
       </c>
       <c r="G33">
-        <v>55.63</v>
+        <v>57.1</v>
       </c>
       <c r="H33">
-        <v>60.52</v>
+        <v>61.99</v>
       </c>
       <c r="I33" t="s">
         <v>49</v>
@@ -1559,13 +1559,13 @@
         <v>37</v>
       </c>
       <c r="F34">
-        <v>46.48</v>
+        <v>47.15</v>
       </c>
       <c r="G34">
-        <v>52.23</v>
+        <v>51.5</v>
       </c>
       <c r="H34">
-        <v>59.6</v>
+        <v>56.74</v>
       </c>
       <c r="I34" t="s">
         <v>49</v>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -46,102 +46,102 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
     <t>پناهگاه حيات وحش دره باغ</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع توت سياه</t>
   </si>
   <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع کوهستان</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع بصيران</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع شیکوه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع دالان</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه دراء</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده برم فیروز</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
   </si>
   <si>
     <t>پارک ملي قطرويه</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه دراء</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
     <t>منطقه شکار ممن.ع آق جلو</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع شیکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع مل بلند</t>
   </si>
   <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
     <t>منطقه حفاظت شده ماله گاله</t>
   </si>
   <si>
-    <t>پارک ملي بختگان</t>
+    <t>منطقه شکار ممنوع مزايجان</t>
   </si>
   <si>
     <t>منطقه حفاظت شده میانجنگل فسا</t>
   </si>
   <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع کوه گورم</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
+    <t>منطقه حفاظت شده هرمود</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بناب</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع مهارلو</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده هرمود</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بناب</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع کوه هوا و</t>
   </si>
   <si>
@@ -151,16 +151,16 @@
     <t>منطقه حفاظت شده مارگون</t>
   </si>
   <si>
+    <t>مناطق حفاظت‌شده</t>
+  </si>
+  <si>
     <t>مناطق ممنوعه شکار</t>
   </si>
   <si>
-    <t>مناطق حفاظت‌شده</t>
-  </si>
-  <si>
-    <t>1405-07-03</t>
-  </si>
-  <si>
-    <t>2026-09-25</t>
+    <t>1405-07-04</t>
+  </si>
+  <si>
+    <t>2026-09-26</t>
   </si>
   <si>
     <t>بسیار شدید</t>
@@ -628,16 +628,16 @@
         <v>47</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F2">
-        <v>81.42</v>
+        <v>76.28</v>
       </c>
       <c r="G2">
-        <v>86.15000000000001</v>
+        <v>86.31</v>
       </c>
       <c r="H2">
-        <v>91.65000000000001</v>
+        <v>96.54000000000001</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -657,16 +657,16 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>71.13</v>
+        <v>78.76000000000001</v>
       </c>
       <c r="G3">
-        <v>84.29000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="H3">
-        <v>91.65000000000001</v>
+        <v>95.14</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -677,7 +677,7 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C4" t="s">
         <v>46</v>
@@ -689,13 +689,13 @@
         <v>4</v>
       </c>
       <c r="F4">
-        <v>82.43000000000001</v>
+        <v>77.56</v>
       </c>
       <c r="G4">
-        <v>83.38</v>
+        <v>79.63</v>
       </c>
       <c r="H4">
-        <v>85.59999999999999</v>
+        <v>82.34</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -715,16 +715,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="F5">
-        <v>81.03</v>
+        <v>61.29</v>
       </c>
       <c r="G5">
-        <v>81.03</v>
+        <v>78.86</v>
       </c>
       <c r="H5">
-        <v>81.03</v>
+        <v>87.92</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -735,7 +735,7 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
         <v>46</v>
@@ -744,16 +744,16 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>54.68</v>
+        <v>76.06999999999999</v>
       </c>
       <c r="G6">
-        <v>78.79000000000001</v>
+        <v>76.06999999999999</v>
       </c>
       <c r="H6">
-        <v>93.33</v>
+        <v>76.06999999999999</v>
       </c>
       <c r="I6" t="s">
         <v>48</v>
@@ -764,7 +764,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
         <v>46</v>
@@ -773,16 +773,16 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F7">
-        <v>71.06999999999999</v>
+        <v>56.64</v>
       </c>
       <c r="G7">
-        <v>75.66</v>
+        <v>75.58</v>
       </c>
       <c r="H7">
-        <v>77.55</v>
+        <v>99.56</v>
       </c>
       <c r="I7" t="s">
         <v>48</v>
@@ -802,16 +802,16 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F8">
-        <v>63.42</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="G8">
-        <v>74.34</v>
+        <v>74.16</v>
       </c>
       <c r="H8">
-        <v>79.81</v>
+        <v>81.92</v>
       </c>
       <c r="I8" t="s">
         <v>48</v>
@@ -822,7 +822,7 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s">
         <v>46</v>
@@ -831,16 +831,16 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F9">
-        <v>73.45999999999999</v>
+        <v>70.61</v>
       </c>
       <c r="G9">
-        <v>73.45999999999999</v>
+        <v>73.81999999999999</v>
       </c>
       <c r="H9">
-        <v>73.45999999999999</v>
+        <v>77.72</v>
       </c>
       <c r="I9" t="s">
         <v>48</v>
@@ -860,16 +860,16 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F10">
-        <v>68.11</v>
+        <v>71.54000000000001</v>
       </c>
       <c r="G10">
-        <v>73.19</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="H10">
-        <v>77.2</v>
+        <v>76.66</v>
       </c>
       <c r="I10" t="s">
         <v>48</v>
@@ -880,7 +880,7 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
         <v>46</v>
@@ -889,16 +889,16 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="F11">
-        <v>66.23</v>
+        <v>57.98</v>
       </c>
       <c r="G11">
-        <v>70.59999999999999</v>
+        <v>70.98999999999999</v>
       </c>
       <c r="H11">
-        <v>80.34</v>
+        <v>85.66</v>
       </c>
       <c r="I11" t="s">
         <v>48</v>
@@ -918,19 +918,19 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="F12">
-        <v>64</v>
+        <v>57.98</v>
       </c>
       <c r="G12">
-        <v>69.44</v>
+        <v>70.04000000000001</v>
       </c>
       <c r="H12">
-        <v>78.27</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="I12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -938,7 +938,7 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
         <v>46</v>
@@ -947,16 +947,16 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="F13">
-        <v>67.54000000000001</v>
+        <v>62.21</v>
       </c>
       <c r="G13">
-        <v>68.18000000000001</v>
+        <v>69.23999999999999</v>
       </c>
       <c r="H13">
-        <v>68.7</v>
+        <v>86.45999999999999</v>
       </c>
       <c r="I13" t="s">
         <v>49</v>
@@ -967,7 +967,7 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
         <v>46</v>
@@ -976,16 +976,16 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F14">
-        <v>65.08</v>
+        <v>62.52</v>
       </c>
       <c r="G14">
-        <v>68.02</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="H14">
-        <v>71.44</v>
+        <v>75.31</v>
       </c>
       <c r="I14" t="s">
         <v>49</v>
@@ -996,7 +996,7 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s">
         <v>46</v>
@@ -1005,16 +1005,16 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="F15">
-        <v>57.51</v>
+        <v>64.3</v>
       </c>
       <c r="G15">
-        <v>67.98</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="H15">
-        <v>75.31999999999999</v>
+        <v>72.03</v>
       </c>
       <c r="I15" t="s">
         <v>49</v>
@@ -1025,7 +1025,7 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
         <v>46</v>
@@ -1034,16 +1034,16 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F16">
-        <v>57.37</v>
+        <v>60.56</v>
       </c>
       <c r="G16">
-        <v>67.11</v>
+        <v>68.23</v>
       </c>
       <c r="H16">
-        <v>76.93000000000001</v>
+        <v>83.93000000000001</v>
       </c>
       <c r="I16" t="s">
         <v>49</v>
@@ -1063,16 +1063,16 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F17">
-        <v>58.35</v>
+        <v>63.7</v>
       </c>
       <c r="G17">
-        <v>66.90000000000001</v>
+        <v>67.61</v>
       </c>
       <c r="H17">
-        <v>75.20999999999999</v>
+        <v>71.48</v>
       </c>
       <c r="I17" t="s">
         <v>49</v>
@@ -1092,16 +1092,16 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F18">
-        <v>64.7</v>
+        <v>60.95</v>
       </c>
       <c r="G18">
-        <v>66.8</v>
+        <v>67.5</v>
       </c>
       <c r="H18">
-        <v>68.90000000000001</v>
+        <v>75.92</v>
       </c>
       <c r="I18" t="s">
         <v>49</v>
@@ -1112,7 +1112,7 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C19" t="s">
         <v>46</v>
@@ -1121,16 +1121,16 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="F19">
-        <v>63.03</v>
+        <v>56.85</v>
       </c>
       <c r="G19">
-        <v>66.73</v>
+        <v>66.93000000000001</v>
       </c>
       <c r="H19">
-        <v>70.12</v>
+        <v>74.92</v>
       </c>
       <c r="I19" t="s">
         <v>49</v>
@@ -1150,16 +1150,16 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F20">
-        <v>58.69</v>
+        <v>63.41</v>
       </c>
       <c r="G20">
-        <v>65.36</v>
+        <v>66.91</v>
       </c>
       <c r="H20">
-        <v>76.23</v>
+        <v>73.34</v>
       </c>
       <c r="I20" t="s">
         <v>49</v>
@@ -1179,16 +1179,16 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F21">
-        <v>60.07</v>
+        <v>65.41</v>
       </c>
       <c r="G21">
-        <v>65.14</v>
+        <v>66.56</v>
       </c>
       <c r="H21">
-        <v>71.41</v>
+        <v>67.81</v>
       </c>
       <c r="I21" t="s">
         <v>49</v>
@@ -1199,7 +1199,7 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C22" t="s">
         <v>46</v>
@@ -1208,16 +1208,16 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>117</v>
+        <v>4</v>
       </c>
       <c r="F22">
-        <v>54.73</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="G22">
-        <v>64.90000000000001</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="H22">
-        <v>76.90000000000001</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="I22" t="s">
         <v>49</v>
@@ -1237,16 +1237,16 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="F23">
-        <v>56.19</v>
+        <v>62.38</v>
       </c>
       <c r="G23">
-        <v>64.68000000000001</v>
+        <v>65.14</v>
       </c>
       <c r="H23">
-        <v>79.44</v>
+        <v>67.89</v>
       </c>
       <c r="I23" t="s">
         <v>49</v>
@@ -1266,16 +1266,16 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>65</v>
+        <v>13</v>
       </c>
       <c r="F24">
-        <v>54.73</v>
+        <v>57.13</v>
       </c>
       <c r="G24">
-        <v>64.61</v>
+        <v>64.53</v>
       </c>
       <c r="H24">
-        <v>76.90000000000001</v>
+        <v>70.29000000000001</v>
       </c>
       <c r="I24" t="s">
         <v>49</v>
@@ -1295,16 +1295,16 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F25">
-        <v>58.99</v>
+        <v>60.32</v>
       </c>
       <c r="G25">
-        <v>63.31</v>
+        <v>64.31</v>
       </c>
       <c r="H25">
-        <v>67.58</v>
+        <v>67.79000000000001</v>
       </c>
       <c r="I25" t="s">
         <v>49</v>
@@ -1324,16 +1324,16 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F26">
-        <v>58.69</v>
+        <v>60.7</v>
       </c>
       <c r="G26">
-        <v>63.26</v>
+        <v>63.58</v>
       </c>
       <c r="H26">
-        <v>70.08</v>
+        <v>67</v>
       </c>
       <c r="I26" t="s">
         <v>49</v>
@@ -1353,16 +1353,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F27">
-        <v>58.85</v>
+        <v>54.09</v>
       </c>
       <c r="G27">
-        <v>62.02</v>
+        <v>62.27</v>
       </c>
       <c r="H27">
-        <v>63.93</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1373,7 +1373,7 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C28" t="s">
         <v>46</v>
@@ -1382,16 +1382,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F28">
-        <v>57.66</v>
+        <v>58.74</v>
       </c>
       <c r="G28">
-        <v>60.99</v>
+        <v>61.64</v>
       </c>
       <c r="H28">
-        <v>65.72</v>
+        <v>65.91</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
@@ -1411,16 +1411,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F29">
-        <v>56.13</v>
+        <v>56.08</v>
       </c>
       <c r="G29">
-        <v>60.87</v>
+        <v>61.14</v>
       </c>
       <c r="H29">
-        <v>67.25</v>
+        <v>67.06</v>
       </c>
       <c r="I29" t="s">
         <v>49</v>
@@ -1431,7 +1431,7 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C30" t="s">
         <v>46</v>
@@ -1440,16 +1440,16 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F30">
-        <v>55.78</v>
+        <v>56.74</v>
       </c>
       <c r="G30">
-        <v>59.53</v>
+        <v>61</v>
       </c>
       <c r="H30">
-        <v>61.34</v>
+        <v>65.72</v>
       </c>
       <c r="I30" t="s">
         <v>49</v>
@@ -1469,16 +1469,16 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F31">
-        <v>53.86</v>
+        <v>56.29</v>
       </c>
       <c r="G31">
-        <v>58.54</v>
+        <v>59.48</v>
       </c>
       <c r="H31">
-        <v>62.99</v>
+        <v>64.31</v>
       </c>
       <c r="I31" t="s">
         <v>49</v>
@@ -1498,16 +1498,16 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F32">
-        <v>53.33</v>
+        <v>53.21</v>
       </c>
       <c r="G32">
-        <v>57.13</v>
+        <v>57.71</v>
       </c>
       <c r="H32">
-        <v>63.77</v>
+        <v>62.13</v>
       </c>
       <c r="I32" t="s">
         <v>49</v>
@@ -1518,7 +1518,7 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C33" t="s">
         <v>46</v>
@@ -1527,16 +1527,16 @@
         <v>47</v>
       </c>
       <c r="E33">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F33">
-        <v>52.52</v>
+        <v>54.27</v>
       </c>
       <c r="G33">
-        <v>57.1</v>
+        <v>56.75</v>
       </c>
       <c r="H33">
-        <v>61.99</v>
+        <v>62.02</v>
       </c>
       <c r="I33" t="s">
         <v>49</v>
@@ -1547,7 +1547,7 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C34" t="s">
         <v>46</v>
@@ -1559,13 +1559,13 @@
         <v>37</v>
       </c>
       <c r="F34">
-        <v>47.15</v>
+        <v>50.71</v>
       </c>
       <c r="G34">
-        <v>51.5</v>
+        <v>55.42</v>
       </c>
       <c r="H34">
-        <v>56.74</v>
+        <v>60.95</v>
       </c>
       <c r="I34" t="s">
         <v>49</v>
@@ -1576,7 +1576,7 @@
         <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C35" t="s">
         <v>46</v>
@@ -1596,7 +1596,7 @@
         <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C36" t="s">
         <v>46</v>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -46,121 +46,121 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه دراء</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده برم فیروز</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دالان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>پارک ملي قطرويه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع دره باغ</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع بصيران</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
     <t>پناهگاه حيات وحش دره باغ</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع بناب</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه هوا و</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مهارلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع شیکوه</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع توت سياه</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده هرمود</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مزايجان</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع کوهستان</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع بصيران</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع شیکوه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دالان</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه دراء</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
-  </si>
-  <si>
-    <t>پارک ملي قطرويه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده هرمود</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بناب</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه هوا و</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع چاه نفت</t>
   </si>
   <si>
     <t>منطقه حفاظت شده مارگون</t>
   </si>
   <si>
+    <t>مناطق ممنوعه شکار</t>
+  </si>
+  <si>
     <t>مناطق حفاظت‌شده</t>
   </si>
   <si>
-    <t>مناطق ممنوعه شکار</t>
-  </si>
-  <si>
-    <t>1405-07-04</t>
-  </si>
-  <si>
-    <t>2026-09-26</t>
+    <t>1405-07-05</t>
+  </si>
+  <si>
+    <t>2026-09-27</t>
   </si>
   <si>
     <t>بسیار شدید</t>
@@ -628,16 +628,16 @@
         <v>47</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F2">
-        <v>76.28</v>
+        <v>67.63</v>
       </c>
       <c r="G2">
-        <v>86.31</v>
+        <v>76.22</v>
       </c>
       <c r="H2">
-        <v>96.54000000000001</v>
+        <v>85.51000000000001</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -648,7 +648,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C3" t="s">
         <v>46</v>
@@ -657,16 +657,16 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="F3">
-        <v>78.76000000000001</v>
+        <v>66.41</v>
       </c>
       <c r="G3">
-        <v>85.2</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="H3">
-        <v>95.14</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -677,7 +677,7 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C4" t="s">
         <v>46</v>
@@ -686,16 +686,16 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F4">
-        <v>77.56</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="G4">
-        <v>79.63</v>
+        <v>71.62</v>
       </c>
       <c r="H4">
-        <v>82.34</v>
+        <v>78.12</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -706,7 +706,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
         <v>46</v>
@@ -715,16 +715,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>61.29</v>
+        <v>60.51</v>
       </c>
       <c r="G5">
-        <v>78.86</v>
+        <v>70.91</v>
       </c>
       <c r="H5">
-        <v>87.92</v>
+        <v>74.56</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -735,7 +735,7 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s">
         <v>46</v>
@@ -744,16 +744,16 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>76.06999999999999</v>
+        <v>69.41</v>
       </c>
       <c r="G6">
-        <v>76.06999999999999</v>
+        <v>70.67</v>
       </c>
       <c r="H6">
-        <v>76.06999999999999</v>
+        <v>72.12</v>
       </c>
       <c r="I6" t="s">
         <v>48</v>
@@ -764,7 +764,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
         <v>46</v>
@@ -773,16 +773,16 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="F7">
-        <v>56.64</v>
+        <v>62.9</v>
       </c>
       <c r="G7">
-        <v>75.58</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="H7">
-        <v>99.56</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="I7" t="s">
         <v>48</v>
@@ -802,19 +802,19 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="F8">
-        <v>67.95999999999999</v>
+        <v>62.66</v>
       </c>
       <c r="G8">
-        <v>74.16</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="H8">
-        <v>81.92</v>
+        <v>73.93000000000001</v>
       </c>
       <c r="I8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -831,19 +831,19 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F9">
-        <v>70.61</v>
+        <v>62.9</v>
       </c>
       <c r="G9">
-        <v>73.81999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="H9">
-        <v>77.72</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="I9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -860,19 +860,19 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F10">
-        <v>71.54000000000001</v>
+        <v>68.26000000000001</v>
       </c>
       <c r="G10">
-        <v>72.84999999999999</v>
+        <v>68.26000000000001</v>
       </c>
       <c r="H10">
-        <v>76.66</v>
+        <v>68.26000000000001</v>
       </c>
       <c r="I10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -889,19 +889,19 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>117</v>
+        <v>20</v>
       </c>
       <c r="F11">
-        <v>57.98</v>
+        <v>63.98</v>
       </c>
       <c r="G11">
-        <v>70.98999999999999</v>
+        <v>67.97</v>
       </c>
       <c r="H11">
-        <v>85.66</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="I11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -918,19 +918,19 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="F12">
-        <v>57.98</v>
+        <v>56.65</v>
       </c>
       <c r="G12">
-        <v>70.04000000000001</v>
+        <v>67.83</v>
       </c>
       <c r="H12">
-        <v>81.84999999999999</v>
+        <v>76.98</v>
       </c>
       <c r="I12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -947,16 +947,16 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F13">
-        <v>62.21</v>
+        <v>54.06</v>
       </c>
       <c r="G13">
-        <v>69.23999999999999</v>
+        <v>67.42</v>
       </c>
       <c r="H13">
-        <v>86.45999999999999</v>
+        <v>74.67</v>
       </c>
       <c r="I13" t="s">
         <v>49</v>
@@ -967,7 +967,7 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
         <v>46</v>
@@ -976,16 +976,16 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F14">
-        <v>62.52</v>
+        <v>60.73</v>
       </c>
       <c r="G14">
-        <v>68.70999999999999</v>
+        <v>66.77</v>
       </c>
       <c r="H14">
-        <v>75.31</v>
+        <v>70.59</v>
       </c>
       <c r="I14" t="s">
         <v>49</v>
@@ -1005,16 +1005,16 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F15">
-        <v>64.3</v>
+        <v>62.79</v>
       </c>
       <c r="G15">
-        <v>68.65000000000001</v>
+        <v>66.55</v>
       </c>
       <c r="H15">
-        <v>72.03</v>
+        <v>72.34</v>
       </c>
       <c r="I15" t="s">
         <v>49</v>
@@ -1025,7 +1025,7 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
         <v>46</v>
@@ -1034,16 +1034,16 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F16">
-        <v>60.56</v>
+        <v>61.54</v>
       </c>
       <c r="G16">
-        <v>68.23</v>
+        <v>66.2</v>
       </c>
       <c r="H16">
-        <v>83.93000000000001</v>
+        <v>71.54000000000001</v>
       </c>
       <c r="I16" t="s">
         <v>49</v>
@@ -1054,7 +1054,7 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
         <v>46</v>
@@ -1063,16 +1063,16 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="F17">
-        <v>63.7</v>
+        <v>57.7</v>
       </c>
       <c r="G17">
-        <v>67.61</v>
+        <v>65.75</v>
       </c>
       <c r="H17">
-        <v>71.48</v>
+        <v>71.28</v>
       </c>
       <c r="I17" t="s">
         <v>49</v>
@@ -1083,7 +1083,7 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C18" t="s">
         <v>46</v>
@@ -1092,16 +1092,16 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="F18">
-        <v>60.95</v>
+        <v>56.46</v>
       </c>
       <c r="G18">
-        <v>67.5</v>
+        <v>65.06</v>
       </c>
       <c r="H18">
-        <v>75.92</v>
+        <v>79.67</v>
       </c>
       <c r="I18" t="s">
         <v>49</v>
@@ -1121,16 +1121,16 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>62</v>
+        <v>117</v>
       </c>
       <c r="F19">
-        <v>56.85</v>
+        <v>55.87</v>
       </c>
       <c r="G19">
-        <v>66.93000000000001</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="H19">
-        <v>74.92</v>
+        <v>79.67</v>
       </c>
       <c r="I19" t="s">
         <v>49</v>
@@ -1141,7 +1141,7 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C20" t="s">
         <v>46</v>
@@ -1150,16 +1150,16 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="F20">
-        <v>63.41</v>
+        <v>59.05</v>
       </c>
       <c r="G20">
-        <v>66.91</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="H20">
-        <v>73.34</v>
+        <v>72.48999999999999</v>
       </c>
       <c r="I20" t="s">
         <v>49</v>
@@ -1179,16 +1179,16 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="F21">
-        <v>65.41</v>
+        <v>56.65</v>
       </c>
       <c r="G21">
-        <v>66.56</v>
+        <v>64.16</v>
       </c>
       <c r="H21">
-        <v>67.81</v>
+        <v>70.77</v>
       </c>
       <c r="I21" t="s">
         <v>49</v>
@@ -1208,16 +1208,16 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F22">
-        <v>65.93000000000001</v>
+        <v>60.24</v>
       </c>
       <c r="G22">
-        <v>65.93000000000001</v>
+        <v>63.2</v>
       </c>
       <c r="H22">
-        <v>65.93000000000001</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="I22" t="s">
         <v>49</v>
@@ -1237,16 +1237,16 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="F23">
-        <v>62.38</v>
+        <v>56.6</v>
       </c>
       <c r="G23">
-        <v>65.14</v>
+        <v>63.19</v>
       </c>
       <c r="H23">
-        <v>67.89</v>
+        <v>74.11</v>
       </c>
       <c r="I23" t="s">
         <v>49</v>
@@ -1257,7 +1257,7 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C24" t="s">
         <v>46</v>
@@ -1266,16 +1266,16 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F24">
-        <v>57.13</v>
+        <v>58.95</v>
       </c>
       <c r="G24">
-        <v>64.53</v>
+        <v>62.9</v>
       </c>
       <c r="H24">
-        <v>70.29000000000001</v>
+        <v>68.09</v>
       </c>
       <c r="I24" t="s">
         <v>49</v>
@@ -1295,16 +1295,16 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F25">
-        <v>60.32</v>
+        <v>60.36</v>
       </c>
       <c r="G25">
-        <v>64.31</v>
+        <v>62.89</v>
       </c>
       <c r="H25">
-        <v>67.79000000000001</v>
+        <v>67.34</v>
       </c>
       <c r="I25" t="s">
         <v>49</v>
@@ -1315,7 +1315,7 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C26" t="s">
         <v>46</v>
@@ -1324,16 +1324,16 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F26">
-        <v>60.7</v>
+        <v>56.34</v>
       </c>
       <c r="G26">
-        <v>63.58</v>
+        <v>62.29</v>
       </c>
       <c r="H26">
-        <v>67</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="I26" t="s">
         <v>49</v>
@@ -1353,16 +1353,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F27">
-        <v>54.09</v>
+        <v>58.29</v>
       </c>
       <c r="G27">
-        <v>62.27</v>
+        <v>62.06</v>
       </c>
       <c r="H27">
-        <v>76.31999999999999</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1373,7 +1373,7 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C28" t="s">
         <v>46</v>
@@ -1382,16 +1382,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="F28">
-        <v>58.74</v>
+        <v>59.67</v>
       </c>
       <c r="G28">
-        <v>61.64</v>
+        <v>61.94</v>
       </c>
       <c r="H28">
-        <v>65.91</v>
+        <v>63.27</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
@@ -1411,16 +1411,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F29">
-        <v>56.08</v>
+        <v>56.84</v>
       </c>
       <c r="G29">
-        <v>61.14</v>
+        <v>60</v>
       </c>
       <c r="H29">
-        <v>67.06</v>
+        <v>63.13</v>
       </c>
       <c r="I29" t="s">
         <v>49</v>
@@ -1440,16 +1440,16 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F30">
-        <v>56.74</v>
+        <v>56.96</v>
       </c>
       <c r="G30">
-        <v>61</v>
+        <v>59.7</v>
       </c>
       <c r="H30">
-        <v>65.72</v>
+        <v>62.72</v>
       </c>
       <c r="I30" t="s">
         <v>49</v>
@@ -1469,16 +1469,16 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F31">
-        <v>56.29</v>
+        <v>56.84</v>
       </c>
       <c r="G31">
-        <v>59.48</v>
+        <v>57.43</v>
       </c>
       <c r="H31">
-        <v>64.31</v>
+        <v>58.03</v>
       </c>
       <c r="I31" t="s">
         <v>49</v>
@@ -1498,16 +1498,16 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F32">
-        <v>53.21</v>
+        <v>55.14</v>
       </c>
       <c r="G32">
-        <v>57.71</v>
+        <v>57.32</v>
       </c>
       <c r="H32">
-        <v>62.13</v>
+        <v>60.04</v>
       </c>
       <c r="I32" t="s">
         <v>49</v>
@@ -1518,7 +1518,7 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C33" t="s">
         <v>46</v>
@@ -1527,16 +1527,16 @@
         <v>47</v>
       </c>
       <c r="E33">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F33">
-        <v>54.27</v>
+        <v>53.14</v>
       </c>
       <c r="G33">
-        <v>56.75</v>
+        <v>57.09</v>
       </c>
       <c r="H33">
-        <v>62.02</v>
+        <v>60.81</v>
       </c>
       <c r="I33" t="s">
         <v>49</v>
@@ -1547,7 +1547,7 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C34" t="s">
         <v>46</v>
@@ -1556,16 +1556,16 @@
         <v>47</v>
       </c>
       <c r="E34">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="F34">
-        <v>50.71</v>
+        <v>53.64</v>
       </c>
       <c r="G34">
-        <v>55.42</v>
+        <v>53.64</v>
       </c>
       <c r="H34">
-        <v>60.95</v>
+        <v>53.64</v>
       </c>
       <c r="I34" t="s">
         <v>49</v>
@@ -1576,7 +1576,7 @@
         <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C35" t="s">
         <v>46</v>
@@ -1596,7 +1596,7 @@
         <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C36" t="s">
         <v>46</v>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -46,121 +46,121 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دالان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بصيران</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بناب</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
+  </si>
+  <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه دراء</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده برم فیروز</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع توت سياه</t>
+  </si>
+  <si>
     <t>منطقه حفاظت شده ارژن و پريشان</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه دراء</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دالان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
+    <t>منطقه شکار ممنوع مزايجان</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
   </si>
   <si>
     <t>پارک ملي قطرويه</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بصيران</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بناب</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
+    <t>منطقه شکار ممنوع شیکوه</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع کوه هوا و</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
+    <t>منطقه شکار ممنوع کوهستان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده هرمود</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع مهارلو</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع شیکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده هرمود</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوهستان</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع چاه نفت</t>
   </si>
   <si>
     <t>منطقه حفاظت شده مارگون</t>
   </si>
   <si>
+    <t>مناطق حفاظت‌شده</t>
+  </si>
+  <si>
     <t>مناطق ممنوعه شکار</t>
   </si>
   <si>
-    <t>مناطق حفاظت‌شده</t>
-  </si>
-  <si>
-    <t>1405-07-05</t>
-  </si>
-  <si>
-    <t>2026-09-27</t>
+    <t>1405-07-06</t>
+  </si>
+  <si>
+    <t>2026-09-28</t>
   </si>
   <si>
     <t>بسیار شدید</t>
@@ -628,16 +628,16 @@
         <v>47</v>
       </c>
       <c r="E2">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>67.63</v>
+        <v>79.75</v>
       </c>
       <c r="G2">
-        <v>76.22</v>
+        <v>85.66</v>
       </c>
       <c r="H2">
-        <v>85.51000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -648,7 +648,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s">
         <v>46</v>
@@ -657,16 +657,16 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>66.41</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="G3">
-        <v>75.09999999999999</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="H3">
-        <v>79.09999999999999</v>
+        <v>77.19</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -677,7 +677,7 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C4" t="s">
         <v>46</v>
@@ -686,16 +686,16 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F4">
-        <v>65.34999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="G4">
-        <v>71.62</v>
+        <v>73.26000000000001</v>
       </c>
       <c r="H4">
-        <v>78.12</v>
+        <v>77.23</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -715,16 +715,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F5">
-        <v>60.51</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="G5">
-        <v>70.91</v>
+        <v>73</v>
       </c>
       <c r="H5">
-        <v>74.56</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -744,16 +744,16 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F6">
-        <v>69.41</v>
+        <v>62.95</v>
       </c>
       <c r="G6">
-        <v>70.67</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="H6">
-        <v>72.12</v>
+        <v>82.27</v>
       </c>
       <c r="I6" t="s">
         <v>48</v>
@@ -764,7 +764,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
         <v>46</v>
@@ -773,16 +773,16 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F7">
-        <v>62.9</v>
+        <v>67.51000000000001</v>
       </c>
       <c r="G7">
-        <v>70.23999999999999</v>
+        <v>71.70999999999999</v>
       </c>
       <c r="H7">
-        <v>75.59999999999999</v>
+        <v>74.62</v>
       </c>
       <c r="I7" t="s">
         <v>48</v>
@@ -802,19 +802,19 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F8">
-        <v>62.66</v>
+        <v>63.85</v>
       </c>
       <c r="G8">
-        <v>68.68000000000001</v>
+        <v>71.53</v>
       </c>
       <c r="H8">
-        <v>73.93000000000001</v>
+        <v>78.52</v>
       </c>
       <c r="I8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -822,7 +822,7 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
         <v>46</v>
@@ -834,16 +834,16 @@
         <v>18</v>
       </c>
       <c r="F9">
-        <v>62.9</v>
+        <v>66.29000000000001</v>
       </c>
       <c r="G9">
-        <v>68.40000000000001</v>
+        <v>71.41</v>
       </c>
       <c r="H9">
-        <v>73.54000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="I9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -860,19 +860,19 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="F10">
-        <v>68.26000000000001</v>
+        <v>56.89</v>
       </c>
       <c r="G10">
-        <v>68.26000000000001</v>
+        <v>70.64</v>
       </c>
       <c r="H10">
-        <v>68.26000000000001</v>
+        <v>81.31</v>
       </c>
       <c r="I10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -880,7 +880,7 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s">
         <v>46</v>
@@ -889,16 +889,16 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F11">
-        <v>63.98</v>
+        <v>68.63</v>
       </c>
       <c r="G11">
-        <v>67.97</v>
+        <v>69.83</v>
       </c>
       <c r="H11">
-        <v>72.40000000000001</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="I11" t="s">
         <v>49</v>
@@ -909,7 +909,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
         <v>46</v>
@@ -918,16 +918,16 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F12">
-        <v>56.65</v>
+        <v>61.51</v>
       </c>
       <c r="G12">
-        <v>67.83</v>
+        <v>68.87</v>
       </c>
       <c r="H12">
-        <v>76.98</v>
+        <v>75.45999999999999</v>
       </c>
       <c r="I12" t="s">
         <v>49</v>
@@ -947,16 +947,16 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F13">
-        <v>54.06</v>
+        <v>59.77</v>
       </c>
       <c r="G13">
-        <v>67.42</v>
+        <v>68.45</v>
       </c>
       <c r="H13">
-        <v>74.67</v>
+        <v>81.52</v>
       </c>
       <c r="I13" t="s">
         <v>49</v>
@@ -976,16 +976,16 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F14">
-        <v>60.73</v>
+        <v>55.82</v>
       </c>
       <c r="G14">
-        <v>66.77</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="H14">
-        <v>70.59</v>
+        <v>75.7</v>
       </c>
       <c r="I14" t="s">
         <v>49</v>
@@ -1005,16 +1005,16 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="F15">
-        <v>62.79</v>
+        <v>56.5</v>
       </c>
       <c r="G15">
-        <v>66.55</v>
+        <v>67.39</v>
       </c>
       <c r="H15">
-        <v>72.34</v>
+        <v>76.76000000000001</v>
       </c>
       <c r="I15" t="s">
         <v>49</v>
@@ -1025,7 +1025,7 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
         <v>46</v>
@@ -1034,16 +1034,16 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F16">
-        <v>61.54</v>
+        <v>62.84</v>
       </c>
       <c r="G16">
-        <v>66.2</v>
+        <v>67.3</v>
       </c>
       <c r="H16">
-        <v>71.54000000000001</v>
+        <v>69.97</v>
       </c>
       <c r="I16" t="s">
         <v>49</v>
@@ -1054,7 +1054,7 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C17" t="s">
         <v>46</v>
@@ -1063,16 +1063,16 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="F17">
-        <v>57.7</v>
+        <v>62.09</v>
       </c>
       <c r="G17">
-        <v>65.75</v>
+        <v>66.87</v>
       </c>
       <c r="H17">
-        <v>71.28</v>
+        <v>74.68000000000001</v>
       </c>
       <c r="I17" t="s">
         <v>49</v>
@@ -1092,16 +1092,16 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="F18">
-        <v>56.46</v>
+        <v>60.71</v>
       </c>
       <c r="G18">
-        <v>65.06</v>
+        <v>66.54000000000001</v>
       </c>
       <c r="H18">
-        <v>79.67</v>
+        <v>70.13</v>
       </c>
       <c r="I18" t="s">
         <v>49</v>
@@ -1112,7 +1112,7 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
         <v>46</v>
@@ -1121,16 +1121,16 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>117</v>
+        <v>8</v>
       </c>
       <c r="F19">
-        <v>55.87</v>
+        <v>59.42</v>
       </c>
       <c r="G19">
-        <v>64.68000000000001</v>
+        <v>66.19</v>
       </c>
       <c r="H19">
-        <v>79.67</v>
+        <v>72.98</v>
       </c>
       <c r="I19" t="s">
         <v>49</v>
@@ -1150,16 +1150,16 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F20">
-        <v>59.05</v>
+        <v>60.02</v>
       </c>
       <c r="G20">
-        <v>64.65000000000001</v>
+        <v>66.17</v>
       </c>
       <c r="H20">
-        <v>72.48999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="I20" t="s">
         <v>49</v>
@@ -1179,16 +1179,16 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F21">
-        <v>56.65</v>
+        <v>63.16</v>
       </c>
       <c r="G21">
-        <v>64.16</v>
+        <v>65.67</v>
       </c>
       <c r="H21">
-        <v>70.77</v>
+        <v>69.51000000000001</v>
       </c>
       <c r="I21" t="s">
         <v>49</v>
@@ -1208,16 +1208,16 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F22">
-        <v>60.24</v>
+        <v>57.84</v>
       </c>
       <c r="G22">
-        <v>63.2</v>
+        <v>65.34</v>
       </c>
       <c r="H22">
-        <v>65.70999999999999</v>
+        <v>70.02</v>
       </c>
       <c r="I22" t="s">
         <v>49</v>
@@ -1228,7 +1228,7 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C23" t="s">
         <v>46</v>
@@ -1237,16 +1237,16 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="F23">
-        <v>56.6</v>
+        <v>60.7</v>
       </c>
       <c r="G23">
-        <v>63.19</v>
+        <v>64.78</v>
       </c>
       <c r="H23">
-        <v>74.11</v>
+        <v>69.83</v>
       </c>
       <c r="I23" t="s">
         <v>49</v>
@@ -1257,7 +1257,7 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C24" t="s">
         <v>46</v>
@@ -1266,16 +1266,16 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="F24">
-        <v>58.95</v>
+        <v>57.32</v>
       </c>
       <c r="G24">
-        <v>62.9</v>
+        <v>64.34</v>
       </c>
       <c r="H24">
-        <v>68.09</v>
+        <v>72.76000000000001</v>
       </c>
       <c r="I24" t="s">
         <v>49</v>
@@ -1286,7 +1286,7 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C25" t="s">
         <v>46</v>
@@ -1295,16 +1295,16 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="F25">
-        <v>60.36</v>
+        <v>58.74</v>
       </c>
       <c r="G25">
-        <v>62.89</v>
+        <v>64.31</v>
       </c>
       <c r="H25">
-        <v>67.34</v>
+        <v>69.08</v>
       </c>
       <c r="I25" t="s">
         <v>49</v>
@@ -1315,7 +1315,7 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s">
         <v>46</v>
@@ -1324,16 +1324,16 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F26">
-        <v>56.34</v>
+        <v>60.16</v>
       </c>
       <c r="G26">
-        <v>62.29</v>
+        <v>63.69</v>
       </c>
       <c r="H26">
-        <v>69.79000000000001</v>
+        <v>67.42</v>
       </c>
       <c r="I26" t="s">
         <v>49</v>
@@ -1353,16 +1353,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="F27">
-        <v>58.29</v>
+        <v>54.79</v>
       </c>
       <c r="G27">
-        <v>62.06</v>
+        <v>63.03</v>
       </c>
       <c r="H27">
-        <v>66.04000000000001</v>
+        <v>78.28</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1382,16 +1382,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>117</v>
       </c>
       <c r="F28">
-        <v>59.67</v>
+        <v>54.13</v>
       </c>
       <c r="G28">
-        <v>61.94</v>
+        <v>62.41</v>
       </c>
       <c r="H28">
-        <v>63.27</v>
+        <v>78.28</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
@@ -1414,13 +1414,13 @@
         <v>4</v>
       </c>
       <c r="F29">
-        <v>56.84</v>
+        <v>62.15</v>
       </c>
       <c r="G29">
-        <v>60</v>
+        <v>62.15</v>
       </c>
       <c r="H29">
-        <v>63.13</v>
+        <v>62.15</v>
       </c>
       <c r="I29" t="s">
         <v>49</v>
@@ -1440,16 +1440,16 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="F30">
-        <v>56.96</v>
+        <v>58.52</v>
       </c>
       <c r="G30">
-        <v>59.7</v>
+        <v>61.66</v>
       </c>
       <c r="H30">
-        <v>62.72</v>
+        <v>65.05</v>
       </c>
       <c r="I30" t="s">
         <v>49</v>
@@ -1460,7 +1460,7 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C31" t="s">
         <v>46</v>
@@ -1469,16 +1469,16 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="F31">
-        <v>56.84</v>
+        <v>49.64</v>
       </c>
       <c r="G31">
-        <v>57.43</v>
+        <v>61.59</v>
       </c>
       <c r="H31">
-        <v>58.03</v>
+        <v>77.55</v>
       </c>
       <c r="I31" t="s">
         <v>49</v>
@@ -1498,16 +1498,16 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F32">
-        <v>55.14</v>
+        <v>60.19</v>
       </c>
       <c r="G32">
-        <v>57.32</v>
+        <v>60.19</v>
       </c>
       <c r="H32">
-        <v>60.04</v>
+        <v>60.19</v>
       </c>
       <c r="I32" t="s">
         <v>49</v>
@@ -1527,16 +1527,16 @@
         <v>47</v>
       </c>
       <c r="E33">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F33">
-        <v>53.14</v>
+        <v>57.15</v>
       </c>
       <c r="G33">
-        <v>57.09</v>
+        <v>58.86</v>
       </c>
       <c r="H33">
-        <v>60.81</v>
+        <v>61.49</v>
       </c>
       <c r="I33" t="s">
         <v>49</v>
@@ -1547,7 +1547,7 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C34" t="s">
         <v>46</v>
@@ -1556,16 +1556,16 @@
         <v>47</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F34">
-        <v>53.64</v>
+        <v>53.57</v>
       </c>
       <c r="G34">
-        <v>53.64</v>
+        <v>55.96</v>
       </c>
       <c r="H34">
-        <v>53.64</v>
+        <v>61.51</v>
       </c>
       <c r="I34" t="s">
         <v>49</v>
@@ -1576,7 +1576,7 @@
         <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C35" t="s">
         <v>46</v>
@@ -1596,7 +1596,7 @@
         <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C36" t="s">
         <v>46</v>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -46,121 +46,121 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده برم فیروز</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دالان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوهستان</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع مل بلند</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>پارک ملي قطرويه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مزايجان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه دراء</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بناب</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع شیکوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع توت سياه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بصيران</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
     <t>پناهگاه حيات وحش دره باغ</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دالان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بصيران</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بناب</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه دراء</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>پارک ملي قطرويه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع شیکوه</t>
+    <t>منطقه شکار ممنوع مهارلو</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع کوه هوا و</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوهستان</t>
-  </si>
-  <si>
     <t>منطقه حفاظت شده هرمود</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع چاه نفت</t>
   </si>
   <si>
     <t>منطقه حفاظت شده مارگون</t>
   </si>
   <si>
+    <t>مناطق ممنوعه شکار</t>
+  </si>
+  <si>
     <t>مناطق حفاظت‌شده</t>
   </si>
   <si>
-    <t>مناطق ممنوعه شکار</t>
-  </si>
-  <si>
-    <t>1405-07-06</t>
-  </si>
-  <si>
-    <t>2026-09-28</t>
+    <t>1405-07-07</t>
+  </si>
+  <si>
+    <t>2026-09-29</t>
   </si>
   <si>
     <t>بسیار شدید</t>
@@ -628,16 +628,16 @@
         <v>47</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F2">
-        <v>79.75</v>
+        <v>67.52</v>
       </c>
       <c r="G2">
-        <v>85.66</v>
+        <v>76.26000000000001</v>
       </c>
       <c r="H2">
-        <v>92.8</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -648,7 +648,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C3" t="s">
         <v>46</v>
@@ -660,13 +660,13 @@
         <v>3</v>
       </c>
       <c r="F3">
-        <v>72.18000000000001</v>
+        <v>71.19</v>
       </c>
       <c r="G3">
-        <v>74.09999999999999</v>
+        <v>75.22</v>
       </c>
       <c r="H3">
-        <v>77.19</v>
+        <v>79.3</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -686,16 +686,16 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F4">
-        <v>67.3</v>
+        <v>65.66</v>
       </c>
       <c r="G4">
-        <v>73.26000000000001</v>
+        <v>74.31999999999999</v>
       </c>
       <c r="H4">
-        <v>77.23</v>
+        <v>84.09</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -715,16 +715,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>66.01000000000001</v>
+        <v>68.67</v>
       </c>
       <c r="G5">
-        <v>73</v>
+        <v>73.89</v>
       </c>
       <c r="H5">
-        <v>82.04000000000001</v>
+        <v>81.33</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -744,16 +744,16 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F6">
-        <v>62.95</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="G6">
-        <v>72.68000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="H6">
-        <v>82.27</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="I6" t="s">
         <v>48</v>
@@ -764,7 +764,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
         <v>46</v>
@@ -776,13 +776,13 @@
         <v>8</v>
       </c>
       <c r="F7">
-        <v>67.51000000000001</v>
+        <v>66.48</v>
       </c>
       <c r="G7">
-        <v>71.70999999999999</v>
+        <v>72.43000000000001</v>
       </c>
       <c r="H7">
-        <v>74.62</v>
+        <v>74.89</v>
       </c>
       <c r="I7" t="s">
         <v>48</v>
@@ -793,7 +793,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
         <v>46</v>
@@ -802,16 +802,16 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F8">
-        <v>63.85</v>
+        <v>72.19</v>
       </c>
       <c r="G8">
-        <v>71.53</v>
+        <v>72.19</v>
       </c>
       <c r="H8">
-        <v>78.52</v>
+        <v>72.19</v>
       </c>
       <c r="I8" t="s">
         <v>48</v>
@@ -822,7 +822,7 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s">
         <v>46</v>
@@ -831,16 +831,16 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="F9">
-        <v>66.29000000000001</v>
+        <v>69.44</v>
       </c>
       <c r="G9">
-        <v>71.41</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="H9">
-        <v>78.2</v>
+        <v>74.56</v>
       </c>
       <c r="I9" t="s">
         <v>48</v>
@@ -851,7 +851,7 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
         <v>46</v>
@@ -860,16 +860,16 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="F10">
-        <v>56.89</v>
+        <v>65.67</v>
       </c>
       <c r="G10">
-        <v>70.64</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="H10">
-        <v>81.31</v>
+        <v>76.45</v>
       </c>
       <c r="I10" t="s">
         <v>48</v>
@@ -889,19 +889,19 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F11">
-        <v>68.63</v>
+        <v>70.66</v>
       </c>
       <c r="G11">
-        <v>69.83</v>
+        <v>70.66</v>
       </c>
       <c r="H11">
-        <v>71.04000000000001</v>
+        <v>70.66</v>
       </c>
       <c r="I11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -909,7 +909,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
         <v>46</v>
@@ -918,16 +918,16 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F12">
-        <v>61.51</v>
+        <v>63.6</v>
       </c>
       <c r="G12">
-        <v>68.87</v>
+        <v>69.72</v>
       </c>
       <c r="H12">
-        <v>75.45999999999999</v>
+        <v>72.17</v>
       </c>
       <c r="I12" t="s">
         <v>49</v>
@@ -947,16 +947,16 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="F13">
-        <v>59.77</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="G13">
-        <v>68.45</v>
+        <v>67.97</v>
       </c>
       <c r="H13">
-        <v>81.52</v>
+        <v>71.23</v>
       </c>
       <c r="I13" t="s">
         <v>49</v>
@@ -967,7 +967,7 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
         <v>46</v>
@@ -976,16 +976,16 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="F14">
-        <v>55.82</v>
+        <v>58.2</v>
       </c>
       <c r="G14">
-        <v>67.98999999999999</v>
+        <v>67.58</v>
       </c>
       <c r="H14">
-        <v>75.7</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I14" t="s">
         <v>49</v>
@@ -1005,16 +1005,16 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>62</v>
+        <v>117</v>
       </c>
       <c r="F15">
-        <v>56.5</v>
+        <v>57.13</v>
       </c>
       <c r="G15">
-        <v>67.39</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="H15">
-        <v>76.76000000000001</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I15" t="s">
         <v>49</v>
@@ -1025,7 +1025,7 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
         <v>46</v>
@@ -1034,16 +1034,16 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F16">
-        <v>62.84</v>
+        <v>61.7</v>
       </c>
       <c r="G16">
-        <v>67.3</v>
+        <v>67.17</v>
       </c>
       <c r="H16">
-        <v>69.97</v>
+        <v>71.51000000000001</v>
       </c>
       <c r="I16" t="s">
         <v>49</v>
@@ -1054,7 +1054,7 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
         <v>46</v>
@@ -1066,13 +1066,13 @@
         <v>33</v>
       </c>
       <c r="F17">
-        <v>62.09</v>
+        <v>60.48</v>
       </c>
       <c r="G17">
-        <v>66.87</v>
+        <v>66.63</v>
       </c>
       <c r="H17">
-        <v>74.68000000000001</v>
+        <v>79.34</v>
       </c>
       <c r="I17" t="s">
         <v>49</v>
@@ -1083,7 +1083,7 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
         <v>46</v>
@@ -1092,16 +1092,16 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="F18">
-        <v>60.71</v>
+        <v>55.87</v>
       </c>
       <c r="G18">
-        <v>66.54000000000001</v>
+        <v>66.27</v>
       </c>
       <c r="H18">
-        <v>70.13</v>
+        <v>73.59</v>
       </c>
       <c r="I18" t="s">
         <v>49</v>
@@ -1121,16 +1121,16 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F19">
-        <v>59.42</v>
+        <v>60.5</v>
       </c>
       <c r="G19">
-        <v>66.19</v>
+        <v>66.26000000000001</v>
       </c>
       <c r="H19">
-        <v>72.98</v>
+        <v>72.88</v>
       </c>
       <c r="I19" t="s">
         <v>49</v>
@@ -1141,7 +1141,7 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C20" t="s">
         <v>46</v>
@@ -1150,16 +1150,16 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F20">
-        <v>60.02</v>
+        <v>58.25</v>
       </c>
       <c r="G20">
-        <v>66.17</v>
+        <v>66.11</v>
       </c>
       <c r="H20">
-        <v>71.75</v>
+        <v>72.14</v>
       </c>
       <c r="I20" t="s">
         <v>49</v>
@@ -1182,13 +1182,13 @@
         <v>3</v>
       </c>
       <c r="F21">
-        <v>63.16</v>
+        <v>63.67</v>
       </c>
       <c r="G21">
-        <v>65.67</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="H21">
-        <v>69.51000000000001</v>
+        <v>66.26000000000001</v>
       </c>
       <c r="I21" t="s">
         <v>49</v>
@@ -1208,16 +1208,16 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F22">
-        <v>57.84</v>
+        <v>59.7</v>
       </c>
       <c r="G22">
-        <v>65.34</v>
+        <v>64.75</v>
       </c>
       <c r="H22">
-        <v>70.02</v>
+        <v>72.17</v>
       </c>
       <c r="I22" t="s">
         <v>49</v>
@@ -1228,7 +1228,7 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C23" t="s">
         <v>46</v>
@@ -1237,16 +1237,16 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F23">
-        <v>60.7</v>
+        <v>60.21</v>
       </c>
       <c r="G23">
-        <v>64.78</v>
+        <v>64.58</v>
       </c>
       <c r="H23">
-        <v>69.83</v>
+        <v>73.11</v>
       </c>
       <c r="I23" t="s">
         <v>49</v>
@@ -1257,7 +1257,7 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C24" t="s">
         <v>46</v>
@@ -1269,13 +1269,13 @@
         <v>4</v>
       </c>
       <c r="F24">
-        <v>57.32</v>
+        <v>56</v>
       </c>
       <c r="G24">
-        <v>64.34</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="H24">
-        <v>72.76000000000001</v>
+        <v>70.77</v>
       </c>
       <c r="I24" t="s">
         <v>49</v>
@@ -1295,16 +1295,16 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F25">
-        <v>58.74</v>
+        <v>55.35</v>
       </c>
       <c r="G25">
-        <v>64.31</v>
+        <v>64.25</v>
       </c>
       <c r="H25">
-        <v>69.08</v>
+        <v>76.27</v>
       </c>
       <c r="I25" t="s">
         <v>49</v>
@@ -1324,16 +1324,16 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F26">
-        <v>60.16</v>
+        <v>62.09</v>
       </c>
       <c r="G26">
-        <v>63.69</v>
+        <v>64.19</v>
       </c>
       <c r="H26">
-        <v>67.42</v>
+        <v>68.81</v>
       </c>
       <c r="I26" t="s">
         <v>49</v>
@@ -1353,16 +1353,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="F27">
-        <v>54.79</v>
+        <v>49.7</v>
       </c>
       <c r="G27">
-        <v>63.03</v>
+        <v>62.9</v>
       </c>
       <c r="H27">
-        <v>78.28</v>
+        <v>82.97</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1382,16 +1382,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>117</v>
+        <v>20</v>
       </c>
       <c r="F28">
-        <v>54.13</v>
+        <v>56.44</v>
       </c>
       <c r="G28">
-        <v>62.41</v>
+        <v>62.44</v>
       </c>
       <c r="H28">
-        <v>78.28</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
@@ -1402,7 +1402,7 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C29" t="s">
         <v>46</v>
@@ -1411,16 +1411,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F29">
-        <v>62.15</v>
+        <v>55.16</v>
       </c>
       <c r="G29">
-        <v>62.15</v>
+        <v>62.23</v>
       </c>
       <c r="H29">
-        <v>62.15</v>
+        <v>68.67</v>
       </c>
       <c r="I29" t="s">
         <v>49</v>
@@ -1440,16 +1440,16 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="F30">
-        <v>58.52</v>
+        <v>54.94</v>
       </c>
       <c r="G30">
-        <v>61.66</v>
+        <v>59.69</v>
       </c>
       <c r="H30">
-        <v>65.05</v>
+        <v>65.63</v>
       </c>
       <c r="I30" t="s">
         <v>49</v>
@@ -1469,16 +1469,16 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="F31">
-        <v>49.64</v>
+        <v>54.62</v>
       </c>
       <c r="G31">
-        <v>61.59</v>
+        <v>58.76</v>
       </c>
       <c r="H31">
-        <v>77.55</v>
+        <v>63.02</v>
       </c>
       <c r="I31" t="s">
         <v>49</v>
@@ -1489,7 +1489,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C32" t="s">
         <v>46</v>
@@ -1498,16 +1498,16 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F32">
-        <v>60.19</v>
+        <v>53.66</v>
       </c>
       <c r="G32">
-        <v>60.19</v>
+        <v>58.61</v>
       </c>
       <c r="H32">
-        <v>60.19</v>
+        <v>63.3</v>
       </c>
       <c r="I32" t="s">
         <v>49</v>
@@ -1527,16 +1527,16 @@
         <v>47</v>
       </c>
       <c r="E33">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="F33">
-        <v>57.15</v>
+        <v>49.3</v>
       </c>
       <c r="G33">
-        <v>58.86</v>
+        <v>56.17</v>
       </c>
       <c r="H33">
-        <v>61.49</v>
+        <v>63.52</v>
       </c>
       <c r="I33" t="s">
         <v>49</v>
@@ -1556,16 +1556,16 @@
         <v>47</v>
       </c>
       <c r="E34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F34">
-        <v>53.57</v>
+        <v>48.62</v>
       </c>
       <c r="G34">
-        <v>55.96</v>
+        <v>56.1</v>
       </c>
       <c r="H34">
-        <v>61.51</v>
+        <v>61.13</v>
       </c>
       <c r="I34" t="s">
         <v>49</v>
@@ -1576,7 +1576,7 @@
         <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C35" t="s">
         <v>46</v>
@@ -1596,7 +1596,7 @@
         <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C36" t="s">
         <v>46</v>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -46,102 +46,102 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع شیکوه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه دراء</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بصيران</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده برم فیروز</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دالان</t>
+  </si>
+  <si>
     <t>منطقه حفاظت شده ارژن و پريشان</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه هوا و</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بناب</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
   </si>
   <si>
     <t>منطقه حفاظت شده بهرام گور</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دالان</t>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مهارلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع توت سياه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>پارک ملي قطرويه</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع کوهستان</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>پارک ملي قطرويه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع مزايجان</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه دراء</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بناب</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع شیکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بصيران</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه هوا و</t>
-  </si>
-  <si>
     <t>منطقه حفاظت شده هرمود</t>
   </si>
   <si>
@@ -151,16 +151,16 @@
     <t>منطقه حفاظت شده مارگون</t>
   </si>
   <si>
+    <t>مناطق حفاظت‌شده</t>
+  </si>
+  <si>
     <t>مناطق ممنوعه شکار</t>
   </si>
   <si>
-    <t>مناطق حفاظت‌شده</t>
-  </si>
-  <si>
-    <t>1405-07-07</t>
-  </si>
-  <si>
-    <t>2026-09-29</t>
+    <t>1405-07-08</t>
+  </si>
+  <si>
+    <t>2026-09-30</t>
   </si>
   <si>
     <t>بسیار شدید</t>
@@ -628,16 +628,16 @@
         <v>47</v>
       </c>
       <c r="E2">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>67.52</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="G2">
-        <v>76.26000000000001</v>
+        <v>88.15000000000001</v>
       </c>
       <c r="H2">
-        <v>83.54000000000001</v>
+        <v>90.09</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -648,7 +648,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s">
         <v>46</v>
@@ -660,13 +660,13 @@
         <v>3</v>
       </c>
       <c r="F3">
-        <v>71.19</v>
+        <v>85.93000000000001</v>
       </c>
       <c r="G3">
-        <v>75.22</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="H3">
-        <v>79.3</v>
+        <v>89.05</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -686,16 +686,16 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="F4">
-        <v>65.66</v>
+        <v>68.12</v>
       </c>
       <c r="G4">
-        <v>74.31999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="H4">
-        <v>84.09</v>
+        <v>89.78</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -715,16 +715,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F5">
-        <v>68.67</v>
+        <v>69.45</v>
       </c>
       <c r="G5">
-        <v>73.89</v>
+        <v>76.23</v>
       </c>
       <c r="H5">
-        <v>81.33</v>
+        <v>89.31999999999999</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -744,16 +744,16 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>66.43000000000001</v>
+        <v>62.84</v>
       </c>
       <c r="G6">
-        <v>73.7</v>
+        <v>75.89</v>
       </c>
       <c r="H6">
-        <v>80.84999999999999</v>
+        <v>88.84</v>
       </c>
       <c r="I6" t="s">
         <v>48</v>
@@ -764,7 +764,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
         <v>46</v>
@@ -776,13 +776,13 @@
         <v>8</v>
       </c>
       <c r="F7">
-        <v>66.48</v>
+        <v>73.48999999999999</v>
       </c>
       <c r="G7">
-        <v>72.43000000000001</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="H7">
-        <v>74.89</v>
+        <v>79.27</v>
       </c>
       <c r="I7" t="s">
         <v>48</v>
@@ -802,16 +802,16 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="F8">
-        <v>72.19</v>
+        <v>68.73</v>
       </c>
       <c r="G8">
-        <v>72.19</v>
+        <v>72.65000000000001</v>
       </c>
       <c r="H8">
-        <v>72.19</v>
+        <v>78.3</v>
       </c>
       <c r="I8" t="s">
         <v>48</v>
@@ -822,7 +822,7 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
         <v>46</v>
@@ -831,16 +831,16 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F9">
-        <v>69.44</v>
+        <v>62.08</v>
       </c>
       <c r="G9">
-        <v>71.93000000000001</v>
+        <v>70.63</v>
       </c>
       <c r="H9">
-        <v>74.56</v>
+        <v>82.69</v>
       </c>
       <c r="I9" t="s">
         <v>48</v>
@@ -851,7 +851,7 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
         <v>46</v>
@@ -860,19 +860,19 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="F10">
-        <v>65.67</v>
+        <v>58.92</v>
       </c>
       <c r="G10">
-        <v>71.34999999999999</v>
+        <v>68.87</v>
       </c>
       <c r="H10">
-        <v>76.45</v>
+        <v>79.56</v>
       </c>
       <c r="I10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -880,7 +880,7 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
         <v>46</v>
@@ -889,19 +889,19 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F11">
-        <v>70.66</v>
+        <v>64.88</v>
       </c>
       <c r="G11">
-        <v>70.66</v>
+        <v>68.15000000000001</v>
       </c>
       <c r="H11">
-        <v>70.66</v>
+        <v>72.3</v>
       </c>
       <c r="I11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -918,16 +918,16 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F12">
-        <v>63.6</v>
+        <v>58.54</v>
       </c>
       <c r="G12">
-        <v>69.72</v>
+        <v>65.87</v>
       </c>
       <c r="H12">
-        <v>72.17</v>
+        <v>71.25</v>
       </c>
       <c r="I12" t="s">
         <v>49</v>
@@ -938,7 +938,7 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s">
         <v>46</v>
@@ -947,16 +947,16 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="F13">
-        <v>64.70999999999999</v>
+        <v>55.21</v>
       </c>
       <c r="G13">
-        <v>67.97</v>
+        <v>65.64</v>
       </c>
       <c r="H13">
-        <v>71.23</v>
+        <v>72.87</v>
       </c>
       <c r="I13" t="s">
         <v>49</v>
@@ -976,16 +976,16 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F14">
-        <v>58.2</v>
+        <v>53.4</v>
       </c>
       <c r="G14">
-        <v>67.58</v>
+        <v>65.41</v>
       </c>
       <c r="H14">
-        <v>78.40000000000001</v>
+        <v>77.08</v>
       </c>
       <c r="I14" t="s">
         <v>49</v>
@@ -1005,16 +1005,16 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>117</v>
+        <v>12</v>
       </c>
       <c r="F15">
-        <v>57.13</v>
+        <v>59.22</v>
       </c>
       <c r="G15">
-        <v>67.31999999999999</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="H15">
-        <v>78.40000000000001</v>
+        <v>71.69</v>
       </c>
       <c r="I15" t="s">
         <v>49</v>
@@ -1025,7 +1025,7 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
         <v>46</v>
@@ -1034,16 +1034,16 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F16">
-        <v>61.7</v>
+        <v>57.98</v>
       </c>
       <c r="G16">
-        <v>67.17</v>
+        <v>63.72</v>
       </c>
       <c r="H16">
-        <v>71.51000000000001</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="I16" t="s">
         <v>49</v>
@@ -1054,7 +1054,7 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C17" t="s">
         <v>46</v>
@@ -1063,16 +1063,16 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F17">
-        <v>60.48</v>
+        <v>57.36</v>
       </c>
       <c r="G17">
-        <v>66.63</v>
+        <v>63.24</v>
       </c>
       <c r="H17">
-        <v>79.34</v>
+        <v>69.13</v>
       </c>
       <c r="I17" t="s">
         <v>49</v>
@@ -1083,7 +1083,7 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C18" t="s">
         <v>46</v>
@@ -1092,16 +1092,16 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="F18">
-        <v>55.87</v>
+        <v>57.56</v>
       </c>
       <c r="G18">
-        <v>66.27</v>
+        <v>63.16</v>
       </c>
       <c r="H18">
-        <v>73.59</v>
+        <v>71.55</v>
       </c>
       <c r="I18" t="s">
         <v>49</v>
@@ -1121,16 +1121,16 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F19">
-        <v>60.5</v>
+        <v>55.12</v>
       </c>
       <c r="G19">
-        <v>66.26000000000001</v>
+        <v>62.64</v>
       </c>
       <c r="H19">
-        <v>72.88</v>
+        <v>67.3</v>
       </c>
       <c r="I19" t="s">
         <v>49</v>
@@ -1150,16 +1150,16 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="F20">
-        <v>58.25</v>
+        <v>54.31</v>
       </c>
       <c r="G20">
-        <v>66.11</v>
+        <v>62.02</v>
       </c>
       <c r="H20">
-        <v>72.14</v>
+        <v>73.55</v>
       </c>
       <c r="I20" t="s">
         <v>49</v>
@@ -1170,7 +1170,7 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C21" t="s">
         <v>46</v>
@@ -1179,16 +1179,16 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F21">
-        <v>63.67</v>
+        <v>52.19</v>
       </c>
       <c r="G21">
-        <v>65.04000000000001</v>
+        <v>61.95</v>
       </c>
       <c r="H21">
-        <v>66.26000000000001</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="I21" t="s">
         <v>49</v>
@@ -1208,16 +1208,16 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>12</v>
+        <v>117</v>
       </c>
       <c r="F22">
-        <v>59.7</v>
+        <v>53.78</v>
       </c>
       <c r="G22">
-        <v>64.75</v>
+        <v>61.93</v>
       </c>
       <c r="H22">
-        <v>72.17</v>
+        <v>73.55</v>
       </c>
       <c r="I22" t="s">
         <v>49</v>
@@ -1228,7 +1228,7 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C23" t="s">
         <v>46</v>
@@ -1237,16 +1237,16 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F23">
-        <v>60.21</v>
+        <v>54.35</v>
       </c>
       <c r="G23">
-        <v>64.58</v>
+        <v>61.83</v>
       </c>
       <c r="H23">
-        <v>73.11</v>
+        <v>71.39</v>
       </c>
       <c r="I23" t="s">
         <v>49</v>
@@ -1266,16 +1266,16 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F24">
-        <v>56</v>
+        <v>58.69</v>
       </c>
       <c r="G24">
-        <v>64.40000000000001</v>
+        <v>61.49</v>
       </c>
       <c r="H24">
-        <v>70.77</v>
+        <v>65.27</v>
       </c>
       <c r="I24" t="s">
         <v>49</v>
@@ -1295,16 +1295,16 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F25">
-        <v>55.35</v>
+        <v>53.39</v>
       </c>
       <c r="G25">
-        <v>64.25</v>
+        <v>61.46</v>
       </c>
       <c r="H25">
-        <v>76.27</v>
+        <v>67.23999999999999</v>
       </c>
       <c r="I25" t="s">
         <v>49</v>
@@ -1324,16 +1324,16 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F26">
-        <v>62.09</v>
+        <v>54.89</v>
       </c>
       <c r="G26">
-        <v>64.19</v>
+        <v>60.56</v>
       </c>
       <c r="H26">
-        <v>68.81</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="I26" t="s">
         <v>49</v>
@@ -1344,7 +1344,7 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
         <v>46</v>
@@ -1353,16 +1353,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F27">
-        <v>49.7</v>
+        <v>54.79</v>
       </c>
       <c r="G27">
-        <v>62.9</v>
+        <v>59.53</v>
       </c>
       <c r="H27">
-        <v>82.97</v>
+        <v>66.26000000000001</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1373,7 +1373,7 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C28" t="s">
         <v>46</v>
@@ -1382,16 +1382,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F28">
-        <v>56.44</v>
+        <v>57.5</v>
       </c>
       <c r="G28">
-        <v>62.44</v>
+        <v>58.22</v>
       </c>
       <c r="H28">
-        <v>66.65000000000001</v>
+        <v>58.94</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
@@ -1411,16 +1411,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F29">
-        <v>55.16</v>
+        <v>51.45</v>
       </c>
       <c r="G29">
-        <v>62.23</v>
+        <v>58.15</v>
       </c>
       <c r="H29">
-        <v>68.67</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="I29" t="s">
         <v>49</v>
@@ -1431,7 +1431,7 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C30" t="s">
         <v>46</v>
@@ -1440,16 +1440,16 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F30">
-        <v>54.94</v>
+        <v>57.79</v>
       </c>
       <c r="G30">
-        <v>59.69</v>
+        <v>57.79</v>
       </c>
       <c r="H30">
-        <v>65.63</v>
+        <v>57.79</v>
       </c>
       <c r="I30" t="s">
         <v>49</v>
@@ -1469,16 +1469,16 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F31">
-        <v>54.62</v>
+        <v>56.44</v>
       </c>
       <c r="G31">
-        <v>58.76</v>
+        <v>56.44</v>
       </c>
       <c r="H31">
-        <v>63.02</v>
+        <v>56.44</v>
       </c>
       <c r="I31" t="s">
         <v>49</v>
@@ -1489,7 +1489,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C32" t="s">
         <v>46</v>
@@ -1498,16 +1498,16 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F32">
-        <v>53.66</v>
+        <v>52.12</v>
       </c>
       <c r="G32">
-        <v>58.61</v>
+        <v>56.22</v>
       </c>
       <c r="H32">
-        <v>63.3</v>
+        <v>59.48</v>
       </c>
       <c r="I32" t="s">
         <v>49</v>
@@ -1518,7 +1518,7 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C33" t="s">
         <v>46</v>
@@ -1527,16 +1527,16 @@
         <v>47</v>
       </c>
       <c r="E33">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="F33">
-        <v>49.3</v>
+        <v>49.52</v>
       </c>
       <c r="G33">
-        <v>56.17</v>
+        <v>54.7</v>
       </c>
       <c r="H33">
-        <v>63.52</v>
+        <v>59.46</v>
       </c>
       <c r="I33" t="s">
         <v>49</v>
@@ -1547,7 +1547,7 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C34" t="s">
         <v>46</v>
@@ -1559,13 +1559,13 @@
         <v>9</v>
       </c>
       <c r="F34">
-        <v>48.62</v>
+        <v>48.12</v>
       </c>
       <c r="G34">
-        <v>56.1</v>
+        <v>50.44</v>
       </c>
       <c r="H34">
-        <v>61.13</v>
+        <v>53.71</v>
       </c>
       <c r="I34" t="s">
         <v>49</v>
@@ -1576,7 +1576,7 @@
         <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C35" t="s">
         <v>46</v>
@@ -1596,7 +1596,7 @@
         <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C36" t="s">
         <v>46</v>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="52">
   <si>
     <t>نام منطقه</t>
   </si>
@@ -46,99 +46,99 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه دراء</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
+  </si>
+  <si>
+    <t>پارک ملي قطرويه</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بصيران</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع شیکوه</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه دراء</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بصيران</t>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع توت سياه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
   </si>
   <si>
     <t>منطقه حفاظت شده برم فیروز</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع دالان</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوهستان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مهارلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بناب</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع کوه هوا و</t>
   </si>
   <si>
-    <t>پناهگاه حيات وحش دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بناب</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>پارک ملي قطرويه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوهستان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع مزايجان</t>
   </si>
   <si>
@@ -151,22 +151,25 @@
     <t>منطقه حفاظت شده مارگون</t>
   </si>
   <si>
+    <t>مناطق ممنوعه شکار</t>
+  </si>
+  <si>
     <t>مناطق حفاظت‌شده</t>
   </si>
   <si>
-    <t>مناطق ممنوعه شکار</t>
-  </si>
-  <si>
-    <t>1405-07-08</t>
-  </si>
-  <si>
-    <t>2026-09-30</t>
+    <t>1405-07-09</t>
+  </si>
+  <si>
+    <t>2026-10-01</t>
   </si>
   <si>
     <t>بسیار شدید</t>
   </si>
   <si>
     <t>شدید</t>
+  </si>
+  <si>
+    <t>خیلی زیاد</t>
   </si>
   <si>
     <t>بدون داده</t>
@@ -631,13 +634,13 @@
         <v>3</v>
       </c>
       <c r="F2">
-        <v>84.31999999999999</v>
+        <v>80.56</v>
       </c>
       <c r="G2">
-        <v>88.15000000000001</v>
+        <v>83.02</v>
       </c>
       <c r="H2">
-        <v>90.09</v>
+        <v>85.43000000000001</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -657,16 +660,16 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="F3">
-        <v>85.93000000000001</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="G3">
-        <v>87.59999999999999</v>
+        <v>80.79000000000001</v>
       </c>
       <c r="H3">
-        <v>89.05</v>
+        <v>86.83</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -686,16 +689,16 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F4">
-        <v>68.12</v>
+        <v>71.44</v>
       </c>
       <c r="G4">
-        <v>79.40000000000001</v>
+        <v>77.61</v>
       </c>
       <c r="H4">
-        <v>89.78</v>
+        <v>83.16</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -715,16 +718,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F5">
-        <v>69.45</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="G5">
-        <v>76.23</v>
+        <v>75.83</v>
       </c>
       <c r="H5">
-        <v>89.31999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -735,7 +738,7 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
         <v>46</v>
@@ -744,16 +747,16 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>62.84</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="G6">
-        <v>75.89</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="H6">
-        <v>88.84</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="I6" t="s">
         <v>48</v>
@@ -773,16 +776,16 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>73.48999999999999</v>
+        <v>69.58</v>
       </c>
       <c r="G7">
-        <v>75.56999999999999</v>
+        <v>71.27</v>
       </c>
       <c r="H7">
-        <v>79.27</v>
+        <v>72.33</v>
       </c>
       <c r="I7" t="s">
         <v>48</v>
@@ -802,16 +805,16 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F8">
-        <v>68.73</v>
+        <v>65.92</v>
       </c>
       <c r="G8">
-        <v>72.65000000000001</v>
+        <v>70.73999999999999</v>
       </c>
       <c r="H8">
-        <v>78.3</v>
+        <v>77.05</v>
       </c>
       <c r="I8" t="s">
         <v>48</v>
@@ -822,7 +825,7 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s">
         <v>46</v>
@@ -831,16 +834,16 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F9">
-        <v>62.08</v>
+        <v>64.72</v>
       </c>
       <c r="G9">
-        <v>70.63</v>
+        <v>70.22</v>
       </c>
       <c r="H9">
-        <v>82.69</v>
+        <v>74.67</v>
       </c>
       <c r="I9" t="s">
         <v>48</v>
@@ -851,7 +854,7 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
         <v>46</v>
@@ -860,16 +863,16 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="F10">
-        <v>58.92</v>
+        <v>64.31</v>
       </c>
       <c r="G10">
-        <v>68.87</v>
+        <v>69.62</v>
       </c>
       <c r="H10">
-        <v>79.56</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="I10" t="s">
         <v>49</v>
@@ -880,7 +883,7 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s">
         <v>46</v>
@@ -889,16 +892,16 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="F11">
         <v>64.88</v>
       </c>
       <c r="G11">
-        <v>68.15000000000001</v>
+        <v>69.27</v>
       </c>
       <c r="H11">
-        <v>72.3</v>
+        <v>75.59</v>
       </c>
       <c r="I11" t="s">
         <v>49</v>
@@ -918,16 +921,16 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F12">
-        <v>58.54</v>
+        <v>61.13</v>
       </c>
       <c r="G12">
-        <v>65.87</v>
+        <v>68.56</v>
       </c>
       <c r="H12">
-        <v>71.25</v>
+        <v>74.03</v>
       </c>
       <c r="I12" t="s">
         <v>49</v>
@@ -938,7 +941,7 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
         <v>46</v>
@@ -947,16 +950,16 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F13">
-        <v>55.21</v>
+        <v>59.82</v>
       </c>
       <c r="G13">
-        <v>65.64</v>
+        <v>66.31</v>
       </c>
       <c r="H13">
-        <v>72.87</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="I13" t="s">
         <v>49</v>
@@ -967,7 +970,7 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
         <v>46</v>
@@ -979,13 +982,13 @@
         <v>62</v>
       </c>
       <c r="F14">
-        <v>53.4</v>
+        <v>60.55</v>
       </c>
       <c r="G14">
-        <v>65.41</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="H14">
-        <v>77.08</v>
+        <v>80</v>
       </c>
       <c r="I14" t="s">
         <v>49</v>
@@ -1005,16 +1008,16 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F15">
-        <v>59.22</v>
+        <v>62.66</v>
       </c>
       <c r="G15">
-        <v>64.98999999999999</v>
+        <v>65.88</v>
       </c>
       <c r="H15">
-        <v>71.69</v>
+        <v>69.73999999999999</v>
       </c>
       <c r="I15" t="s">
         <v>49</v>
@@ -1025,7 +1028,7 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
         <v>46</v>
@@ -1034,16 +1037,16 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F16">
-        <v>57.98</v>
+        <v>59.1</v>
       </c>
       <c r="G16">
-        <v>63.72</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="H16">
-        <v>68.65000000000001</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="I16" t="s">
         <v>49</v>
@@ -1054,7 +1057,7 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
         <v>46</v>
@@ -1063,16 +1066,16 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F17">
-        <v>57.36</v>
+        <v>63.97</v>
       </c>
       <c r="G17">
-        <v>63.24</v>
+        <v>64.62</v>
       </c>
       <c r="H17">
-        <v>69.13</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="I17" t="s">
         <v>49</v>
@@ -1092,16 +1095,16 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F18">
-        <v>57.56</v>
+        <v>62.71</v>
       </c>
       <c r="G18">
-        <v>63.16</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="H18">
-        <v>71.55</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="I18" t="s">
         <v>49</v>
@@ -1121,16 +1124,16 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F19">
-        <v>55.12</v>
+        <v>56.09</v>
       </c>
       <c r="G19">
-        <v>62.64</v>
+        <v>64.28</v>
       </c>
       <c r="H19">
-        <v>67.3</v>
+        <v>71.19</v>
       </c>
       <c r="I19" t="s">
         <v>49</v>
@@ -1150,16 +1153,16 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="F20">
-        <v>54.31</v>
+        <v>62.83</v>
       </c>
       <c r="G20">
-        <v>62.02</v>
+        <v>62.83</v>
       </c>
       <c r="H20">
-        <v>73.55</v>
+        <v>62.83</v>
       </c>
       <c r="I20" t="s">
         <v>49</v>
@@ -1179,16 +1182,16 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F21">
-        <v>52.19</v>
+        <v>53.53</v>
       </c>
       <c r="G21">
-        <v>61.95</v>
+        <v>62.47</v>
       </c>
       <c r="H21">
-        <v>70.48999999999999</v>
+        <v>68.97</v>
       </c>
       <c r="I21" t="s">
         <v>49</v>
@@ -1199,7 +1202,7 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C22" t="s">
         <v>46</v>
@@ -1208,16 +1211,16 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>117</v>
+        <v>65</v>
       </c>
       <c r="F22">
-        <v>53.78</v>
+        <v>54.02</v>
       </c>
       <c r="G22">
-        <v>61.93</v>
+        <v>62.22</v>
       </c>
       <c r="H22">
-        <v>73.55</v>
+        <v>74.47</v>
       </c>
       <c r="I22" t="s">
         <v>49</v>
@@ -1237,16 +1240,16 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F23">
-        <v>54.35</v>
+        <v>57.08</v>
       </c>
       <c r="G23">
-        <v>61.83</v>
+        <v>62.13</v>
       </c>
       <c r="H23">
-        <v>71.39</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="I23" t="s">
         <v>49</v>
@@ -1257,7 +1260,7 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C24" t="s">
         <v>46</v>
@@ -1266,16 +1269,16 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>16</v>
+        <v>117</v>
       </c>
       <c r="F24">
-        <v>58.69</v>
+        <v>54.02</v>
       </c>
       <c r="G24">
-        <v>61.49</v>
+        <v>61.95</v>
       </c>
       <c r="H24">
-        <v>65.27</v>
+        <v>74.47</v>
       </c>
       <c r="I24" t="s">
         <v>49</v>
@@ -1286,7 +1289,7 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C25" t="s">
         <v>46</v>
@@ -1295,16 +1298,16 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F25">
-        <v>53.39</v>
+        <v>56.22</v>
       </c>
       <c r="G25">
-        <v>61.46</v>
+        <v>59.69</v>
       </c>
       <c r="H25">
-        <v>67.23999999999999</v>
+        <v>68.55</v>
       </c>
       <c r="I25" t="s">
         <v>49</v>
@@ -1315,7 +1318,7 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C26" t="s">
         <v>46</v>
@@ -1324,16 +1327,16 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F26">
-        <v>54.89</v>
+        <v>56.9</v>
       </c>
       <c r="G26">
-        <v>60.56</v>
+        <v>59.37</v>
       </c>
       <c r="H26">
-        <v>65.51000000000001</v>
+        <v>62.52</v>
       </c>
       <c r="I26" t="s">
         <v>49</v>
@@ -1344,7 +1347,7 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
         <v>46</v>
@@ -1353,16 +1356,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F27">
-        <v>54.79</v>
+        <v>57.88</v>
       </c>
       <c r="G27">
-        <v>59.53</v>
+        <v>59.04</v>
       </c>
       <c r="H27">
-        <v>66.26000000000001</v>
+        <v>60.19</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1373,7 +1376,7 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C28" t="s">
         <v>46</v>
@@ -1382,16 +1385,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F28">
-        <v>57.5</v>
+        <v>55.52</v>
       </c>
       <c r="G28">
-        <v>58.22</v>
+        <v>57.8</v>
       </c>
       <c r="H28">
-        <v>58.94</v>
+        <v>61.89</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
@@ -1402,7 +1405,7 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C29" t="s">
         <v>46</v>
@@ -1411,16 +1414,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F29">
-        <v>51.45</v>
+        <v>55.19</v>
       </c>
       <c r="G29">
-        <v>58.15</v>
+        <v>56.78</v>
       </c>
       <c r="H29">
-        <v>66.81999999999999</v>
+        <v>60.94</v>
       </c>
       <c r="I29" t="s">
         <v>49</v>
@@ -1440,16 +1443,16 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F30">
-        <v>57.79</v>
+        <v>52.91</v>
       </c>
       <c r="G30">
-        <v>57.79</v>
+        <v>56.16</v>
       </c>
       <c r="H30">
-        <v>57.79</v>
+        <v>62.95</v>
       </c>
       <c r="I30" t="s">
         <v>49</v>
@@ -1460,7 +1463,7 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C31" t="s">
         <v>46</v>
@@ -1469,16 +1472,16 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="F31">
-        <v>56.44</v>
+        <v>46.05</v>
       </c>
       <c r="G31">
-        <v>56.44</v>
+        <v>54.55</v>
       </c>
       <c r="H31">
-        <v>56.44</v>
+        <v>58.68</v>
       </c>
       <c r="I31" t="s">
         <v>49</v>
@@ -1489,7 +1492,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C32" t="s">
         <v>46</v>
@@ -1498,19 +1501,19 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="F32">
-        <v>52.12</v>
+        <v>45.24</v>
       </c>
       <c r="G32">
-        <v>56.22</v>
+        <v>49.75</v>
       </c>
       <c r="H32">
-        <v>59.48</v>
+        <v>57.19</v>
       </c>
       <c r="I32" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -1518,7 +1521,7 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C33" t="s">
         <v>46</v>
@@ -1530,16 +1533,16 @@
         <v>15</v>
       </c>
       <c r="F33">
-        <v>49.52</v>
+        <v>46.88</v>
       </c>
       <c r="G33">
-        <v>54.7</v>
+        <v>49.04</v>
       </c>
       <c r="H33">
-        <v>59.46</v>
+        <v>50.98</v>
       </c>
       <c r="I33" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1547,7 +1550,7 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C34" t="s">
         <v>46</v>
@@ -1559,16 +1562,16 @@
         <v>9</v>
       </c>
       <c r="F34">
-        <v>48.12</v>
+        <v>39.33</v>
       </c>
       <c r="G34">
-        <v>50.44</v>
+        <v>42.09</v>
       </c>
       <c r="H34">
-        <v>53.71</v>
+        <v>45.75</v>
       </c>
       <c r="I34" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -1576,7 +1579,7 @@
         <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C35" t="s">
         <v>46</v>
@@ -1588,7 +1591,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -1596,7 +1599,7 @@
         <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C36" t="s">
         <v>46</v>
@@ -1608,7 +1611,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -46,99 +46,99 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده برم فیروز</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>پارک ملي قطرويه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بصيران</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
     <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع شیکوه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بناب</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع توت سياه</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مهارلو</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع کوه دراء</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
-  </si>
-  <si>
-    <t>پارک ملي قطرويه</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بصيران</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع شیکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع دالان</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه هوا و</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع کوهستان</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بناب</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه هوا و</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع مزايجان</t>
   </si>
   <si>
@@ -157,10 +157,10 @@
     <t>مناطق حفاظت‌شده</t>
   </si>
   <si>
-    <t>1405-07-09</t>
-  </si>
-  <si>
-    <t>2026-10-01</t>
+    <t>1405-07-10</t>
+  </si>
+  <si>
+    <t>2026-10-02</t>
   </si>
   <si>
     <t>بسیار شدید</t>
@@ -631,16 +631,16 @@
         <v>47</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>80.56</v>
+        <v>68.79000000000001</v>
       </c>
       <c r="G2">
-        <v>83.02</v>
+        <v>72.38</v>
       </c>
       <c r="H2">
-        <v>85.43000000000001</v>
+        <v>78.06</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -651,7 +651,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C3" t="s">
         <v>46</v>
@@ -660,16 +660,16 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>75.98999999999999</v>
+        <v>60.33</v>
       </c>
       <c r="G3">
-        <v>80.79000000000001</v>
+        <v>70.87</v>
       </c>
       <c r="H3">
-        <v>86.83</v>
+        <v>78.06</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -692,16 +692,16 @@
         <v>20</v>
       </c>
       <c r="F4">
-        <v>71.44</v>
+        <v>51.21</v>
       </c>
       <c r="G4">
-        <v>77.61</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="H4">
-        <v>83.16</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="I4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -709,7 +709,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
         <v>46</v>
@@ -718,19 +718,19 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F5">
-        <v>68.01000000000001</v>
+        <v>60.17</v>
       </c>
       <c r="G5">
-        <v>75.83</v>
+        <v>68.63</v>
       </c>
       <c r="H5">
-        <v>83.90000000000001</v>
+        <v>79.29000000000001</v>
       </c>
       <c r="I5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -738,7 +738,7 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s">
         <v>46</v>
@@ -747,19 +747,19 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F6">
-        <v>71.59999999999999</v>
+        <v>59.03</v>
       </c>
       <c r="G6">
-        <v>71.59999999999999</v>
+        <v>67.13</v>
       </c>
       <c r="H6">
-        <v>71.59999999999999</v>
+        <v>78.95</v>
       </c>
       <c r="I6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -767,7 +767,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
         <v>46</v>
@@ -776,19 +776,19 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F7">
-        <v>69.58</v>
+        <v>61.52</v>
       </c>
       <c r="G7">
-        <v>71.27</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="H7">
-        <v>72.33</v>
+        <v>73.45999999999999</v>
       </c>
       <c r="I7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -796,7 +796,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C8" t="s">
         <v>46</v>
@@ -805,19 +805,19 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F8">
-        <v>65.92</v>
+        <v>65.47</v>
       </c>
       <c r="G8">
-        <v>70.73999999999999</v>
+        <v>65.47</v>
       </c>
       <c r="H8">
-        <v>77.05</v>
+        <v>65.47</v>
       </c>
       <c r="I8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -834,19 +834,19 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F9">
-        <v>64.72</v>
+        <v>54.44</v>
       </c>
       <c r="G9">
-        <v>70.22</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="H9">
-        <v>74.67</v>
+        <v>69.41</v>
       </c>
       <c r="I9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -863,16 +863,16 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="F10">
-        <v>64.31</v>
+        <v>53.77</v>
       </c>
       <c r="G10">
-        <v>69.62</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="H10">
-        <v>83.09999999999999</v>
+        <v>72.38</v>
       </c>
       <c r="I10" t="s">
         <v>49</v>
@@ -895,13 +895,13 @@
         <v>16</v>
       </c>
       <c r="F11">
-        <v>64.88</v>
+        <v>57.51</v>
       </c>
       <c r="G11">
-        <v>69.27</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="H11">
-        <v>75.59</v>
+        <v>69.97</v>
       </c>
       <c r="I11" t="s">
         <v>49</v>
@@ -921,16 +921,16 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F12">
-        <v>61.13</v>
+        <v>60.9</v>
       </c>
       <c r="G12">
-        <v>68.56</v>
+        <v>64.05</v>
       </c>
       <c r="H12">
-        <v>74.03</v>
+        <v>68.27</v>
       </c>
       <c r="I12" t="s">
         <v>49</v>
@@ -950,16 +950,16 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="F13">
-        <v>59.82</v>
+        <v>50.21</v>
       </c>
       <c r="G13">
-        <v>66.31</v>
+        <v>63.98</v>
       </c>
       <c r="H13">
-        <v>73.15000000000001</v>
+        <v>75.58</v>
       </c>
       <c r="I13" t="s">
         <v>49</v>
@@ -970,7 +970,7 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
         <v>46</v>
@@ -979,16 +979,16 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="F14">
-        <v>60.55</v>
+        <v>57.51</v>
       </c>
       <c r="G14">
-        <v>66.18000000000001</v>
+        <v>63.44</v>
       </c>
       <c r="H14">
-        <v>80</v>
+        <v>72.89</v>
       </c>
       <c r="I14" t="s">
         <v>49</v>
@@ -1008,16 +1008,16 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F15">
-        <v>62.66</v>
+        <v>53.24</v>
       </c>
       <c r="G15">
-        <v>65.88</v>
+        <v>62.68</v>
       </c>
       <c r="H15">
-        <v>69.73999999999999</v>
+        <v>71.95999999999999</v>
       </c>
       <c r="I15" t="s">
         <v>49</v>
@@ -1040,13 +1040,13 @@
         <v>12</v>
       </c>
       <c r="F16">
-        <v>59.1</v>
+        <v>50.21</v>
       </c>
       <c r="G16">
-        <v>65.65000000000001</v>
+        <v>61.3</v>
       </c>
       <c r="H16">
-        <v>75.26000000000001</v>
+        <v>73.37</v>
       </c>
       <c r="I16" t="s">
         <v>49</v>
@@ -1057,7 +1057,7 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C17" t="s">
         <v>46</v>
@@ -1066,16 +1066,16 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F17">
-        <v>63.97</v>
+        <v>57.82</v>
       </c>
       <c r="G17">
-        <v>64.62</v>
+        <v>59.92</v>
       </c>
       <c r="H17">
-        <v>65.93000000000001</v>
+        <v>61.99</v>
       </c>
       <c r="I17" t="s">
         <v>49</v>
@@ -1086,7 +1086,7 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
         <v>46</v>
@@ -1095,16 +1095,16 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F18">
-        <v>62.71</v>
+        <v>58.19</v>
       </c>
       <c r="G18">
-        <v>64.51000000000001</v>
+        <v>59.71</v>
       </c>
       <c r="H18">
-        <v>65.34999999999999</v>
+        <v>60.83</v>
       </c>
       <c r="I18" t="s">
         <v>49</v>
@@ -1115,7 +1115,7 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C19" t="s">
         <v>46</v>
@@ -1124,16 +1124,16 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F19">
-        <v>56.09</v>
+        <v>53.92</v>
       </c>
       <c r="G19">
-        <v>64.28</v>
+        <v>59.63</v>
       </c>
       <c r="H19">
-        <v>71.19</v>
+        <v>67.63</v>
       </c>
       <c r="I19" t="s">
         <v>49</v>
@@ -1153,16 +1153,16 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="F20">
-        <v>62.83</v>
+        <v>54.86</v>
       </c>
       <c r="G20">
-        <v>62.83</v>
+        <v>59.23</v>
       </c>
       <c r="H20">
-        <v>62.83</v>
+        <v>61.23</v>
       </c>
       <c r="I20" t="s">
         <v>49</v>
@@ -1182,16 +1182,16 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="F21">
-        <v>53.53</v>
+        <v>50.79</v>
       </c>
       <c r="G21">
-        <v>62.47</v>
+        <v>59.14</v>
       </c>
       <c r="H21">
-        <v>68.97</v>
+        <v>70.27</v>
       </c>
       <c r="I21" t="s">
         <v>49</v>
@@ -1202,7 +1202,7 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C22" t="s">
         <v>46</v>
@@ -1211,16 +1211,16 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="F22">
-        <v>54.02</v>
+        <v>55.63</v>
       </c>
       <c r="G22">
-        <v>62.22</v>
+        <v>58.9</v>
       </c>
       <c r="H22">
-        <v>74.47</v>
+        <v>62.18</v>
       </c>
       <c r="I22" t="s">
         <v>49</v>
@@ -1231,7 +1231,7 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C23" t="s">
         <v>46</v>
@@ -1240,16 +1240,16 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>18</v>
+        <v>117</v>
       </c>
       <c r="F23">
-        <v>57.08</v>
+        <v>50.09</v>
       </c>
       <c r="G23">
-        <v>62.13</v>
+        <v>58.69</v>
       </c>
       <c r="H23">
-        <v>69.70999999999999</v>
+        <v>70.27</v>
       </c>
       <c r="I23" t="s">
         <v>49</v>
@@ -1260,7 +1260,7 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C24" t="s">
         <v>46</v>
@@ -1269,16 +1269,16 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>117</v>
+        <v>20</v>
       </c>
       <c r="F24">
-        <v>54.02</v>
+        <v>52.05</v>
       </c>
       <c r="G24">
-        <v>61.95</v>
+        <v>57.55</v>
       </c>
       <c r="H24">
-        <v>74.47</v>
+        <v>66.31</v>
       </c>
       <c r="I24" t="s">
         <v>49</v>
@@ -1289,7 +1289,7 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C25" t="s">
         <v>46</v>
@@ -1298,16 +1298,16 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F25">
-        <v>56.22</v>
+        <v>52.78</v>
       </c>
       <c r="G25">
-        <v>59.69</v>
+        <v>57.52</v>
       </c>
       <c r="H25">
-        <v>68.55</v>
+        <v>60.91</v>
       </c>
       <c r="I25" t="s">
         <v>49</v>
@@ -1318,7 +1318,7 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s">
         <v>46</v>
@@ -1327,16 +1327,16 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F26">
-        <v>56.9</v>
+        <v>51.98</v>
       </c>
       <c r="G26">
-        <v>59.37</v>
+        <v>57.49</v>
       </c>
       <c r="H26">
-        <v>62.52</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="I26" t="s">
         <v>49</v>
@@ -1356,16 +1356,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F27">
-        <v>57.88</v>
+        <v>54.49</v>
       </c>
       <c r="G27">
-        <v>59.04</v>
+        <v>56.88</v>
       </c>
       <c r="H27">
-        <v>60.19</v>
+        <v>57.92</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1385,16 +1385,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="F28">
-        <v>55.52</v>
+        <v>50.11</v>
       </c>
       <c r="G28">
-        <v>57.8</v>
+        <v>56.35</v>
       </c>
       <c r="H28">
-        <v>61.89</v>
+        <v>69.17</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
@@ -1414,16 +1414,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F29">
-        <v>55.19</v>
+        <v>53.7</v>
       </c>
       <c r="G29">
-        <v>56.78</v>
+        <v>55.68</v>
       </c>
       <c r="H29">
-        <v>60.94</v>
+        <v>57.54</v>
       </c>
       <c r="I29" t="s">
         <v>49</v>
@@ -1443,16 +1443,16 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F30">
-        <v>52.91</v>
+        <v>50.09</v>
       </c>
       <c r="G30">
-        <v>56.16</v>
+        <v>53.23</v>
       </c>
       <c r="H30">
-        <v>62.95</v>
+        <v>56.71</v>
       </c>
       <c r="I30" t="s">
         <v>49</v>
@@ -1472,16 +1472,16 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F31">
-        <v>46.05</v>
+        <v>45.94</v>
       </c>
       <c r="G31">
-        <v>54.55</v>
+        <v>52.11</v>
       </c>
       <c r="H31">
-        <v>58.68</v>
+        <v>62.33</v>
       </c>
       <c r="I31" t="s">
         <v>49</v>
@@ -1501,19 +1501,19 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="F32">
-        <v>45.24</v>
+        <v>51.95</v>
       </c>
       <c r="G32">
-        <v>49.75</v>
+        <v>51.95</v>
       </c>
       <c r="H32">
-        <v>57.19</v>
+        <v>51.95</v>
       </c>
       <c r="I32" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -1533,13 +1533,13 @@
         <v>15</v>
       </c>
       <c r="F33">
-        <v>46.88</v>
+        <v>46.55</v>
       </c>
       <c r="G33">
-        <v>49.04</v>
+        <v>48.86</v>
       </c>
       <c r="H33">
-        <v>50.98</v>
+        <v>51.46</v>
       </c>
       <c r="I33" t="s">
         <v>50</v>
@@ -1562,13 +1562,13 @@
         <v>9</v>
       </c>
       <c r="F34">
-        <v>39.33</v>
+        <v>43.14</v>
       </c>
       <c r="G34">
-        <v>42.09</v>
+        <v>44.78</v>
       </c>
       <c r="H34">
-        <v>45.75</v>
+        <v>48.05</v>
       </c>
       <c r="I34" t="s">
         <v>50</v>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -46,102 +46,102 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
     <t>منطقه حفاظت شده تنگ بستانک</t>
   </si>
   <si>
+    <t>پناهگاه حيات وحش دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بصيران</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع توت سياه</t>
+  </si>
+  <si>
     <t>منطقه حفاظت شده برم فیروز</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع شیکوه</t>
+  </si>
+  <si>
     <t>منطقه حفاظت شده ارژن و پريشان</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع کوه خم</t>
   </si>
   <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع پادنا</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
+    <t>منطقه شکار ممنوع مهارلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بناب</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه دراء</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دالان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
   </si>
   <si>
     <t>پارک ملي قطرويه</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بصيران</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع شیکوه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بناب</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه دراء</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دالان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
+    <t>منطقه شکار ممنوع مزايجان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوهستان</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع کوه هوا و</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوهستان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
-  </si>
-  <si>
     <t>منطقه حفاظت شده هرمود</t>
   </si>
   <si>
@@ -157,10 +157,10 @@
     <t>مناطق حفاظت‌شده</t>
   </si>
   <si>
-    <t>1405-07-10</t>
-  </si>
-  <si>
-    <t>2026-10-02</t>
+    <t>1405-07-11</t>
+  </si>
+  <si>
+    <t>2026-10-03</t>
   </si>
   <si>
     <t>بسیار شدید</t>
@@ -631,16 +631,16 @@
         <v>47</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>68.79000000000001</v>
+        <v>70.38</v>
       </c>
       <c r="G2">
-        <v>72.38</v>
+        <v>73.2</v>
       </c>
       <c r="H2">
-        <v>78.06</v>
+        <v>76.09</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -651,7 +651,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s">
         <v>46</v>
@@ -660,16 +660,16 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>60.33</v>
+        <v>63.63</v>
       </c>
       <c r="G3">
-        <v>70.87</v>
+        <v>73.08</v>
       </c>
       <c r="H3">
-        <v>78.06</v>
+        <v>88</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -689,19 +689,19 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>51.21</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="G4">
-        <v>69.34999999999999</v>
+        <v>71.53</v>
       </c>
       <c r="H4">
-        <v>77.59999999999999</v>
+        <v>76.65000000000001</v>
       </c>
       <c r="I4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -709,7 +709,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
         <v>46</v>
@@ -718,19 +718,19 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>60.17</v>
+        <v>68.56</v>
       </c>
       <c r="G5">
-        <v>68.63</v>
+        <v>70.64</v>
       </c>
       <c r="H5">
-        <v>79.29000000000001</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="I5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -747,19 +747,19 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F6">
-        <v>59.03</v>
+        <v>66.94</v>
       </c>
       <c r="G6">
-        <v>67.13</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="H6">
-        <v>78.95</v>
+        <v>82.73</v>
       </c>
       <c r="I6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -776,16 +776,16 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>61.52</v>
+        <v>63.8</v>
       </c>
       <c r="G7">
-        <v>66.98999999999999</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="H7">
-        <v>73.45999999999999</v>
+        <v>74</v>
       </c>
       <c r="I7" t="s">
         <v>49</v>
@@ -805,16 +805,16 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F8">
-        <v>65.47</v>
+        <v>61.28</v>
       </c>
       <c r="G8">
-        <v>65.47</v>
+        <v>69.78</v>
       </c>
       <c r="H8">
-        <v>65.47</v>
+        <v>75.47</v>
       </c>
       <c r="I8" t="s">
         <v>49</v>
@@ -834,16 +834,16 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F9">
-        <v>54.44</v>
+        <v>64.91</v>
       </c>
       <c r="G9">
-        <v>64.84999999999999</v>
+        <v>68.08</v>
       </c>
       <c r="H9">
-        <v>69.41</v>
+        <v>70.33</v>
       </c>
       <c r="I9" t="s">
         <v>49</v>
@@ -863,16 +863,16 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>62</v>
+        <v>3</v>
       </c>
       <c r="F10">
-        <v>53.77</v>
+        <v>62.9</v>
       </c>
       <c r="G10">
-        <v>64.73999999999999</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="H10">
-        <v>72.38</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="I10" t="s">
         <v>49</v>
@@ -892,16 +892,16 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F11">
-        <v>57.51</v>
+        <v>57.66</v>
       </c>
       <c r="G11">
-        <v>64.43000000000001</v>
+        <v>66.88</v>
       </c>
       <c r="H11">
-        <v>69.97</v>
+        <v>72.98</v>
       </c>
       <c r="I11" t="s">
         <v>49</v>
@@ -921,16 +921,16 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F12">
-        <v>60.9</v>
+        <v>58.98</v>
       </c>
       <c r="G12">
-        <v>64.05</v>
+        <v>66.8</v>
       </c>
       <c r="H12">
-        <v>68.27</v>
+        <v>73.20999999999999</v>
       </c>
       <c r="I12" t="s">
         <v>49</v>
@@ -950,16 +950,16 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="F13">
-        <v>50.21</v>
+        <v>61.73</v>
       </c>
       <c r="G13">
-        <v>63.98</v>
+        <v>65.94</v>
       </c>
       <c r="H13">
-        <v>75.58</v>
+        <v>68.59</v>
       </c>
       <c r="I13" t="s">
         <v>49</v>
@@ -970,7 +970,7 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
         <v>46</v>
@@ -979,16 +979,16 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="F14">
-        <v>57.51</v>
+        <v>63.59</v>
       </c>
       <c r="G14">
-        <v>63.44</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="H14">
-        <v>72.89</v>
+        <v>67.72</v>
       </c>
       <c r="I14" t="s">
         <v>49</v>
@@ -999,7 +999,7 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
         <v>46</v>
@@ -1008,16 +1008,16 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="F15">
-        <v>53.24</v>
+        <v>57.87</v>
       </c>
       <c r="G15">
-        <v>62.68</v>
+        <v>64.38</v>
       </c>
       <c r="H15">
-        <v>71.95999999999999</v>
+        <v>73.55</v>
       </c>
       <c r="I15" t="s">
         <v>49</v>
@@ -1037,16 +1037,16 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F16">
-        <v>50.21</v>
+        <v>58.59</v>
       </c>
       <c r="G16">
-        <v>61.3</v>
+        <v>64.34999999999999</v>
       </c>
       <c r="H16">
-        <v>73.37</v>
+        <v>69.06999999999999</v>
       </c>
       <c r="I16" t="s">
         <v>49</v>
@@ -1066,16 +1066,16 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="F17">
-        <v>57.82</v>
+        <v>53.21</v>
       </c>
       <c r="G17">
-        <v>59.92</v>
+        <v>64.13</v>
       </c>
       <c r="H17">
-        <v>61.99</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="I17" t="s">
         <v>49</v>
@@ -1086,7 +1086,7 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C18" t="s">
         <v>46</v>
@@ -1095,16 +1095,16 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="F18">
-        <v>58.19</v>
+        <v>61.1</v>
       </c>
       <c r="G18">
-        <v>59.71</v>
+        <v>63.44</v>
       </c>
       <c r="H18">
-        <v>60.83</v>
+        <v>65.64</v>
       </c>
       <c r="I18" t="s">
         <v>49</v>
@@ -1124,16 +1124,16 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F19">
-        <v>53.92</v>
+        <v>53.73</v>
       </c>
       <c r="G19">
-        <v>59.63</v>
+        <v>62.31</v>
       </c>
       <c r="H19">
-        <v>67.63</v>
+        <v>66.98</v>
       </c>
       <c r="I19" t="s">
         <v>49</v>
@@ -1144,7 +1144,7 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C20" t="s">
         <v>46</v>
@@ -1153,16 +1153,16 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="F20">
-        <v>54.86</v>
+        <v>48.84</v>
       </c>
       <c r="G20">
-        <v>59.23</v>
+        <v>61.16</v>
       </c>
       <c r="H20">
-        <v>61.23</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="I20" t="s">
         <v>49</v>
@@ -1182,16 +1182,16 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="F21">
-        <v>50.79</v>
+        <v>48.84</v>
       </c>
       <c r="G21">
-        <v>59.14</v>
+        <v>60.73</v>
       </c>
       <c r="H21">
-        <v>70.27</v>
+        <v>70.61</v>
       </c>
       <c r="I21" t="s">
         <v>49</v>
@@ -1211,16 +1211,16 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="F22">
-        <v>55.63</v>
+        <v>49.06</v>
       </c>
       <c r="G22">
-        <v>58.9</v>
+        <v>59.46</v>
       </c>
       <c r="H22">
-        <v>62.18</v>
+        <v>66.28</v>
       </c>
       <c r="I22" t="s">
         <v>49</v>
@@ -1231,7 +1231,7 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C23" t="s">
         <v>46</v>
@@ -1240,16 +1240,16 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>117</v>
+        <v>10</v>
       </c>
       <c r="F23">
-        <v>50.09</v>
+        <v>54.91</v>
       </c>
       <c r="G23">
-        <v>58.69</v>
+        <v>59.2</v>
       </c>
       <c r="H23">
-        <v>70.27</v>
+        <v>62.18</v>
       </c>
       <c r="I23" t="s">
         <v>49</v>
@@ -1272,13 +1272,13 @@
         <v>20</v>
       </c>
       <c r="F24">
-        <v>52.05</v>
+        <v>52.72</v>
       </c>
       <c r="G24">
-        <v>57.55</v>
+        <v>58.38</v>
       </c>
       <c r="H24">
-        <v>66.31</v>
+        <v>66.89</v>
       </c>
       <c r="I24" t="s">
         <v>49</v>
@@ -1298,16 +1298,16 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F25">
-        <v>52.78</v>
+        <v>47.96</v>
       </c>
       <c r="G25">
-        <v>57.52</v>
+        <v>57.07</v>
       </c>
       <c r="H25">
-        <v>60.91</v>
+        <v>61.11</v>
       </c>
       <c r="I25" t="s">
         <v>49</v>
@@ -1318,7 +1318,7 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C26" t="s">
         <v>46</v>
@@ -1327,16 +1327,16 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="F26">
-        <v>51.98</v>
+        <v>50.94</v>
       </c>
       <c r="G26">
-        <v>57.49</v>
+        <v>56.88</v>
       </c>
       <c r="H26">
-        <v>65.04000000000001</v>
+        <v>63.86</v>
       </c>
       <c r="I26" t="s">
         <v>49</v>
@@ -1356,16 +1356,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F27">
-        <v>54.49</v>
+        <v>56.35</v>
       </c>
       <c r="G27">
         <v>56.88</v>
       </c>
       <c r="H27">
-        <v>57.92</v>
+        <v>58.34</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1385,16 +1385,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F28">
-        <v>50.11</v>
+        <v>50.62</v>
       </c>
       <c r="G28">
-        <v>56.35</v>
+        <v>56.09</v>
       </c>
       <c r="H28">
-        <v>69.17</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
@@ -1405,7 +1405,7 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C29" t="s">
         <v>46</v>
@@ -1414,16 +1414,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F29">
-        <v>53.7</v>
+        <v>51.43</v>
       </c>
       <c r="G29">
-        <v>55.68</v>
+        <v>55.14</v>
       </c>
       <c r="H29">
-        <v>57.54</v>
+        <v>61.91</v>
       </c>
       <c r="I29" t="s">
         <v>49</v>
@@ -1434,7 +1434,7 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C30" t="s">
         <v>46</v>
@@ -1443,16 +1443,16 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F30">
-        <v>50.09</v>
+        <v>53.62</v>
       </c>
       <c r="G30">
-        <v>53.23</v>
+        <v>53.62</v>
       </c>
       <c r="H30">
-        <v>56.71</v>
+        <v>53.62</v>
       </c>
       <c r="I30" t="s">
         <v>49</v>
@@ -1472,16 +1472,16 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="F31">
-        <v>45.94</v>
+        <v>46.93</v>
       </c>
       <c r="G31">
-        <v>52.11</v>
+        <v>52.04</v>
       </c>
       <c r="H31">
-        <v>62.33</v>
+        <v>55.67</v>
       </c>
       <c r="I31" t="s">
         <v>49</v>
@@ -1504,13 +1504,13 @@
         <v>2</v>
       </c>
       <c r="F32">
-        <v>51.95</v>
+        <v>50.2</v>
       </c>
       <c r="G32">
-        <v>51.95</v>
+        <v>50.2</v>
       </c>
       <c r="H32">
-        <v>51.95</v>
+        <v>50.2</v>
       </c>
       <c r="I32" t="s">
         <v>49</v>
@@ -1530,19 +1530,19 @@
         <v>47</v>
       </c>
       <c r="E33">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="F33">
-        <v>46.55</v>
+        <v>43.57</v>
       </c>
       <c r="G33">
-        <v>48.86</v>
+        <v>50.03</v>
       </c>
       <c r="H33">
-        <v>51.46</v>
+        <v>58.57</v>
       </c>
       <c r="I33" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1562,13 +1562,13 @@
         <v>9</v>
       </c>
       <c r="F34">
-        <v>43.14</v>
+        <v>46.04</v>
       </c>
       <c r="G34">
-        <v>44.78</v>
+        <v>48.55</v>
       </c>
       <c r="H34">
-        <v>48.05</v>
+        <v>52.96</v>
       </c>
       <c r="I34" t="s">
         <v>50</v>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="50">
   <si>
     <t>نام منطقه</t>
   </si>
@@ -46,105 +46,105 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>پناهگاه حيات وحش دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
     <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
+    <t>منطقه شکار ممنوع بصيران</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه دراء</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دالان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده هرمود</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده برم فیروز</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>پارک ملي قطرويه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع توت سياه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع شیکوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه هوا و</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوهستان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
   </si>
   <si>
     <t>منطقه حفاظت شده تنگ بستانک</t>
   </si>
   <si>
-    <t>پناهگاه حيات وحش دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بصيران</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع شیکوه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بناب</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مهارلو</t>
   </si>
   <si>
     <t>منطقه شکار ممن.ع آق جلو</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بناب</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه دراء</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دالان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
-  </si>
-  <si>
-    <t>پارک ملي قطرويه</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع مزايجان</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوهستان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه هوا و</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده هرمود</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع چاه نفت</t>
   </si>
   <si>
@@ -157,19 +157,13 @@
     <t>مناطق حفاظت‌شده</t>
   </si>
   <si>
-    <t>1405-07-11</t>
-  </si>
-  <si>
-    <t>2026-10-03</t>
-  </si>
-  <si>
-    <t>بسیار شدید</t>
+    <t>1405-07-12</t>
+  </si>
+  <si>
+    <t>2026-10-04</t>
   </si>
   <si>
     <t>شدید</t>
-  </si>
-  <si>
-    <t>خیلی زیاد</t>
   </si>
   <si>
     <t>بدون داده</t>
@@ -634,13 +628,13 @@
         <v>3</v>
       </c>
       <c r="F2">
-        <v>70.38</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="G2">
-        <v>73.2</v>
+        <v>69.2</v>
       </c>
       <c r="H2">
-        <v>76.09</v>
+        <v>73.22</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -663,13 +657,13 @@
         <v>12</v>
       </c>
       <c r="F3">
-        <v>63.63</v>
+        <v>61.56</v>
       </c>
       <c r="G3">
-        <v>73.08</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="H3">
-        <v>88</v>
+        <v>74.31</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -689,16 +683,16 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="F4">
-        <v>65.26000000000001</v>
+        <v>58.52</v>
       </c>
       <c r="G4">
-        <v>71.53</v>
+        <v>67.25</v>
       </c>
       <c r="H4">
-        <v>76.65000000000001</v>
+        <v>73.11</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -718,16 +712,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="F5">
-        <v>68.56</v>
+        <v>54.03</v>
       </c>
       <c r="G5">
-        <v>70.64</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="H5">
-        <v>72.84999999999999</v>
+        <v>73.25</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -738,7 +732,7 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
         <v>46</v>
@@ -747,16 +741,16 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>66.94</v>
+        <v>63.08</v>
       </c>
       <c r="G6">
-        <v>70.20999999999999</v>
+        <v>66.87</v>
       </c>
       <c r="H6">
-        <v>82.73</v>
+        <v>70.14</v>
       </c>
       <c r="I6" t="s">
         <v>48</v>
@@ -776,19 +770,19 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="F7">
-        <v>63.8</v>
+        <v>55.6</v>
       </c>
       <c r="G7">
-        <v>69.98999999999999</v>
+        <v>64.13</v>
       </c>
       <c r="H7">
-        <v>74</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="I7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -805,19 +799,19 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F8">
-        <v>61.28</v>
+        <v>58.27</v>
       </c>
       <c r="G8">
-        <v>69.78</v>
+        <v>62.66</v>
       </c>
       <c r="H8">
-        <v>75.47</v>
+        <v>66.75</v>
       </c>
       <c r="I8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -834,19 +828,19 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="F9">
-        <v>64.91</v>
+        <v>58.48</v>
       </c>
       <c r="G9">
-        <v>68.08</v>
+        <v>62.07</v>
       </c>
       <c r="H9">
-        <v>70.33</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="I9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -863,19 +857,19 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F10">
-        <v>62.9</v>
+        <v>59.73</v>
       </c>
       <c r="G10">
-        <v>67.98999999999999</v>
+        <v>61.1</v>
       </c>
       <c r="H10">
-        <v>71.68000000000001</v>
+        <v>63.74</v>
       </c>
       <c r="I10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -883,7 +877,7 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
         <v>46</v>
@@ -892,19 +886,19 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F11">
-        <v>57.66</v>
+        <v>56.81</v>
       </c>
       <c r="G11">
-        <v>66.88</v>
+        <v>61.04</v>
       </c>
       <c r="H11">
-        <v>72.98</v>
+        <v>66.2</v>
       </c>
       <c r="I11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -912,7 +906,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
         <v>46</v>
@@ -921,19 +915,19 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F12">
-        <v>58.98</v>
+        <v>59.12</v>
       </c>
       <c r="G12">
-        <v>66.8</v>
+        <v>60.96</v>
       </c>
       <c r="H12">
-        <v>73.20999999999999</v>
+        <v>63.58</v>
       </c>
       <c r="I12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -941,7 +935,7 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s">
         <v>46</v>
@@ -950,19 +944,19 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F13">
-        <v>61.73</v>
+        <v>54.3</v>
       </c>
       <c r="G13">
-        <v>65.94</v>
+        <v>60.74</v>
       </c>
       <c r="H13">
-        <v>68.59</v>
+        <v>64.84</v>
       </c>
       <c r="I13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -970,7 +964,7 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
         <v>46</v>
@@ -979,19 +973,19 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="F14">
-        <v>63.59</v>
+        <v>52.47</v>
       </c>
       <c r="G14">
-        <v>65.65000000000001</v>
+        <v>60.47</v>
       </c>
       <c r="H14">
-        <v>67.72</v>
+        <v>65.87</v>
       </c>
       <c r="I14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -999,7 +993,7 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s">
         <v>46</v>
@@ -1008,19 +1002,19 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="F15">
-        <v>57.87</v>
+        <v>59.39</v>
       </c>
       <c r="G15">
-        <v>64.38</v>
+        <v>59.39</v>
       </c>
       <c r="H15">
-        <v>73.55</v>
+        <v>59.39</v>
       </c>
       <c r="I15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1037,19 +1031,19 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F16">
-        <v>58.59</v>
+        <v>53.4</v>
       </c>
       <c r="G16">
-        <v>64.34999999999999</v>
+        <v>58.96</v>
       </c>
       <c r="H16">
-        <v>69.06999999999999</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="I16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1057,7 +1051,7 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
         <v>46</v>
@@ -1066,19 +1060,19 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F17">
-        <v>53.21</v>
+        <v>54.82</v>
       </c>
       <c r="G17">
-        <v>64.13</v>
+        <v>58.71</v>
       </c>
       <c r="H17">
-        <v>74.45999999999999</v>
+        <v>63.11</v>
       </c>
       <c r="I17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1086,7 +1080,7 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
         <v>46</v>
@@ -1095,19 +1089,19 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F18">
-        <v>61.1</v>
+        <v>53.2</v>
       </c>
       <c r="G18">
-        <v>63.44</v>
+        <v>57.83</v>
       </c>
       <c r="H18">
-        <v>65.64</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="I18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1115,7 +1109,7 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
         <v>46</v>
@@ -1124,19 +1118,19 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="F19">
-        <v>53.73</v>
+        <v>54.79</v>
       </c>
       <c r="G19">
-        <v>62.31</v>
+        <v>57.39</v>
       </c>
       <c r="H19">
-        <v>66.98</v>
+        <v>61.65</v>
       </c>
       <c r="I19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1144,7 +1138,7 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C20" t="s">
         <v>46</v>
@@ -1153,19 +1147,19 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="F20">
-        <v>48.84</v>
+        <v>50.96</v>
       </c>
       <c r="G20">
-        <v>61.16</v>
+        <v>57.16</v>
       </c>
       <c r="H20">
-        <v>68.81999999999999</v>
+        <v>63.3</v>
       </c>
       <c r="I20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1182,19 +1176,19 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>117</v>
+        <v>16</v>
       </c>
       <c r="F21">
-        <v>48.84</v>
+        <v>52.38</v>
       </c>
       <c r="G21">
-        <v>60.73</v>
+        <v>56.7</v>
       </c>
       <c r="H21">
-        <v>70.61</v>
+        <v>64.48999999999999</v>
       </c>
       <c r="I21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -1211,19 +1205,19 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F22">
-        <v>49.06</v>
+        <v>48.97</v>
       </c>
       <c r="G22">
-        <v>59.46</v>
+        <v>56.61</v>
       </c>
       <c r="H22">
-        <v>66.28</v>
+        <v>63</v>
       </c>
       <c r="I22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1240,19 +1234,19 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="F23">
-        <v>54.91</v>
+        <v>51.01</v>
       </c>
       <c r="G23">
-        <v>59.2</v>
+        <v>56.1</v>
       </c>
       <c r="H23">
-        <v>62.18</v>
+        <v>59.56</v>
       </c>
       <c r="I23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -1269,19 +1263,19 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F24">
-        <v>52.72</v>
+        <v>55.7</v>
       </c>
       <c r="G24">
-        <v>58.38</v>
+        <v>55.7</v>
       </c>
       <c r="H24">
-        <v>66.89</v>
+        <v>55.7</v>
       </c>
       <c r="I24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -1301,16 +1295,16 @@
         <v>20</v>
       </c>
       <c r="F25">
-        <v>47.96</v>
+        <v>51.5</v>
       </c>
       <c r="G25">
-        <v>57.07</v>
+        <v>55.66</v>
       </c>
       <c r="H25">
-        <v>61.11</v>
+        <v>57.71</v>
       </c>
       <c r="I25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -1327,19 +1321,19 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="F26">
-        <v>50.94</v>
+        <v>49.09</v>
       </c>
       <c r="G26">
-        <v>56.88</v>
+        <v>55.31</v>
       </c>
       <c r="H26">
-        <v>63.86</v>
+        <v>60.62</v>
       </c>
       <c r="I26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -1347,7 +1341,7 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
         <v>46</v>
@@ -1356,19 +1350,19 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F27">
-        <v>56.35</v>
+        <v>53.95</v>
       </c>
       <c r="G27">
-        <v>56.88</v>
+        <v>54.75</v>
       </c>
       <c r="H27">
-        <v>58.34</v>
+        <v>55.72</v>
       </c>
       <c r="I27" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -1376,7 +1370,7 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C28" t="s">
         <v>46</v>
@@ -1385,19 +1379,19 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>12</v>
+        <v>117</v>
       </c>
       <c r="F28">
-        <v>50.62</v>
+        <v>49.75</v>
       </c>
       <c r="G28">
-        <v>56.09</v>
+        <v>54.68</v>
       </c>
       <c r="H28">
-        <v>64.43000000000001</v>
+        <v>63.8</v>
       </c>
       <c r="I28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -1414,19 +1408,19 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="F29">
-        <v>51.43</v>
+        <v>49.75</v>
       </c>
       <c r="G29">
-        <v>55.14</v>
+        <v>54.54</v>
       </c>
       <c r="H29">
-        <v>61.91</v>
+        <v>63.8</v>
       </c>
       <c r="I29" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -1434,7 +1428,7 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C30" t="s">
         <v>46</v>
@@ -1443,19 +1437,19 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F30">
-        <v>53.62</v>
+        <v>47.38</v>
       </c>
       <c r="G30">
-        <v>53.62</v>
+        <v>54.32</v>
       </c>
       <c r="H30">
-        <v>53.62</v>
+        <v>57.66</v>
       </c>
       <c r="I30" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -1472,19 +1466,19 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F31">
-        <v>46.93</v>
+        <v>52.17</v>
       </c>
       <c r="G31">
-        <v>52.04</v>
+        <v>53.89</v>
       </c>
       <c r="H31">
-        <v>55.67</v>
+        <v>56.7</v>
       </c>
       <c r="I31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -1501,19 +1495,19 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F32">
         <v>50.2</v>
       </c>
       <c r="G32">
-        <v>50.2</v>
+        <v>53.37</v>
       </c>
       <c r="H32">
-        <v>50.2</v>
+        <v>63.37</v>
       </c>
       <c r="I32" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -1530,19 +1524,19 @@
         <v>47</v>
       </c>
       <c r="E33">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="F33">
-        <v>43.57</v>
+        <v>51.8</v>
       </c>
       <c r="G33">
-        <v>50.03</v>
+        <v>53.25</v>
       </c>
       <c r="H33">
-        <v>58.57</v>
+        <v>54.7</v>
       </c>
       <c r="I33" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1550,7 +1544,7 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C34" t="s">
         <v>46</v>
@@ -1559,19 +1553,19 @@
         <v>47</v>
       </c>
       <c r="E34">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F34">
-        <v>46.04</v>
+        <v>47.98</v>
       </c>
       <c r="G34">
-        <v>48.55</v>
+        <v>52.99</v>
       </c>
       <c r="H34">
-        <v>52.96</v>
+        <v>56.6</v>
       </c>
       <c r="I34" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -1591,7 +1585,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -1611,7 +1605,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="52">
   <si>
     <t>نام منطقه</t>
   </si>
@@ -46,124 +46,130 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع کوه دراء</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بناب</t>
+  </si>
+  <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مزايجان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
+  </si>
+  <si>
+    <t>پارک ملي قطرويه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده هرمود</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بصيران</t>
+  </si>
+  <si>
     <t>پناهگاه حيات وحش دره باغ</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بصيران</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه دراء</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع دالان</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده هرمود</t>
+    <t>منطقه شکار ممنوع توت سياه</t>
   </si>
   <si>
     <t>منطقه حفاظت شده برم فیروز</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>پارک ملي قطرويه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع شیکوه</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
+    <t>منطقه شکار ممنوع مهارلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوهستان</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع کوه هوا و</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوهستان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بناب</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع چاه نفت</t>
   </si>
   <si>
     <t>منطقه حفاظت شده مارگون</t>
   </si>
   <si>
+    <t>مناطق حفاظت‌شده</t>
+  </si>
+  <si>
     <t>مناطق ممنوعه شکار</t>
   </si>
   <si>
-    <t>مناطق حفاظت‌شده</t>
-  </si>
-  <si>
-    <t>1405-07-12</t>
-  </si>
-  <si>
-    <t>2026-10-04</t>
+    <t>1405-07-13</t>
+  </si>
+  <si>
+    <t>2026-10-05</t>
+  </si>
+  <si>
+    <t>بسیار شدید</t>
   </si>
   <si>
     <t>شدید</t>
+  </si>
+  <si>
+    <t>خیلی زیاد</t>
   </si>
   <si>
     <t>بدون داده</t>
@@ -625,16 +631,16 @@
         <v>47</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="F2">
-        <v>66.90000000000001</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="G2">
-        <v>69.2</v>
+        <v>71.36</v>
       </c>
       <c r="H2">
-        <v>73.22</v>
+        <v>78.48</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -654,19 +660,19 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F3">
-        <v>61.56</v>
+        <v>57.05</v>
       </c>
       <c r="G3">
-        <v>69.09999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="H3">
-        <v>74.31</v>
+        <v>71.81999999999999</v>
       </c>
       <c r="I3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -683,19 +689,19 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F4">
-        <v>58.52</v>
+        <v>56.75</v>
       </c>
       <c r="G4">
-        <v>67.25</v>
+        <v>62.07</v>
       </c>
       <c r="H4">
-        <v>73.11</v>
+        <v>70.64</v>
       </c>
       <c r="I4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -712,19 +718,19 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="F5">
-        <v>54.03</v>
+        <v>54.65</v>
       </c>
       <c r="G5">
-        <v>67.09999999999999</v>
+        <v>61.31</v>
       </c>
       <c r="H5">
-        <v>73.25</v>
+        <v>65.05</v>
       </c>
       <c r="I5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -741,19 +747,19 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="F6">
-        <v>63.08</v>
+        <v>55.95</v>
       </c>
       <c r="G6">
-        <v>66.87</v>
+        <v>60.77</v>
       </c>
       <c r="H6">
-        <v>70.14</v>
+        <v>65.61</v>
       </c>
       <c r="I6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -761,7 +767,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
         <v>46</v>
@@ -770,19 +776,19 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="F7">
-        <v>55.6</v>
+        <v>55.42</v>
       </c>
       <c r="G7">
-        <v>64.13</v>
+        <v>60.18</v>
       </c>
       <c r="H7">
-        <v>71.20999999999999</v>
+        <v>66.34</v>
       </c>
       <c r="I7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -790,7 +796,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
         <v>46</v>
@@ -799,19 +805,19 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="F8">
-        <v>58.27</v>
+        <v>57.41</v>
       </c>
       <c r="G8">
-        <v>62.66</v>
+        <v>59.74</v>
       </c>
       <c r="H8">
-        <v>66.75</v>
+        <v>63.03</v>
       </c>
       <c r="I8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -819,7 +825,7 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
         <v>46</v>
@@ -828,19 +834,19 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F9">
-        <v>58.48</v>
+        <v>54.28</v>
       </c>
       <c r="G9">
-        <v>62.07</v>
+        <v>58.79</v>
       </c>
       <c r="H9">
-        <v>64.56999999999999</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="I9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -857,19 +863,19 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F10">
-        <v>59.73</v>
+        <v>50.97</v>
       </c>
       <c r="G10">
-        <v>61.1</v>
+        <v>58.54</v>
       </c>
       <c r="H10">
-        <v>63.74</v>
+        <v>66.70999999999999</v>
       </c>
       <c r="I10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -877,7 +883,7 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s">
         <v>46</v>
@@ -886,19 +892,19 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F11">
-        <v>56.81</v>
+        <v>49.71</v>
       </c>
       <c r="G11">
-        <v>61.04</v>
+        <v>58.43</v>
       </c>
       <c r="H11">
-        <v>66.2</v>
+        <v>61.82</v>
       </c>
       <c r="I11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -906,7 +912,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
         <v>46</v>
@@ -915,19 +921,19 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F12">
-        <v>59.12</v>
+        <v>56.69</v>
       </c>
       <c r="G12">
-        <v>60.96</v>
+        <v>58.32</v>
       </c>
       <c r="H12">
-        <v>63.58</v>
+        <v>60.4</v>
       </c>
       <c r="I12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -944,19 +950,19 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F13">
-        <v>54.3</v>
+        <v>52.03</v>
       </c>
       <c r="G13">
-        <v>60.74</v>
+        <v>58.3</v>
       </c>
       <c r="H13">
-        <v>64.84</v>
+        <v>63.39</v>
       </c>
       <c r="I13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -964,7 +970,7 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
         <v>46</v>
@@ -973,19 +979,19 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F14">
-        <v>52.47</v>
+        <v>54.31</v>
       </c>
       <c r="G14">
-        <v>60.47</v>
+        <v>57.47</v>
       </c>
       <c r="H14">
-        <v>65.87</v>
+        <v>59.7</v>
       </c>
       <c r="I14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -993,7 +999,7 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
         <v>46</v>
@@ -1002,19 +1008,19 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>4</v>
+        <v>117</v>
       </c>
       <c r="F15">
-        <v>59.39</v>
+        <v>47.77</v>
       </c>
       <c r="G15">
-        <v>59.39</v>
+        <v>56.65</v>
       </c>
       <c r="H15">
-        <v>59.39</v>
+        <v>65.73</v>
       </c>
       <c r="I15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1022,7 +1028,7 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
         <v>46</v>
@@ -1031,19 +1037,19 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F16">
-        <v>53.4</v>
+        <v>50.39</v>
       </c>
       <c r="G16">
-        <v>58.96</v>
+        <v>56.57</v>
       </c>
       <c r="H16">
-        <v>65.26000000000001</v>
+        <v>64.38</v>
       </c>
       <c r="I16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1060,19 +1066,19 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>4</v>
+        <v>65</v>
       </c>
       <c r="F17">
-        <v>54.82</v>
+        <v>47.77</v>
       </c>
       <c r="G17">
-        <v>58.71</v>
+        <v>55.98</v>
       </c>
       <c r="H17">
-        <v>63.11</v>
+        <v>65.73</v>
       </c>
       <c r="I17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1080,7 +1086,7 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C18" t="s">
         <v>46</v>
@@ -1089,19 +1095,19 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F18">
-        <v>53.2</v>
+        <v>50.46</v>
       </c>
       <c r="G18">
-        <v>57.83</v>
+        <v>55.94</v>
       </c>
       <c r="H18">
-        <v>64.65000000000001</v>
+        <v>64.41</v>
       </c>
       <c r="I18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1109,7 +1115,7 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C19" t="s">
         <v>46</v>
@@ -1118,19 +1124,19 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F19">
-        <v>54.79</v>
+        <v>46.88</v>
       </c>
       <c r="G19">
-        <v>57.39</v>
+        <v>55.49</v>
       </c>
       <c r="H19">
-        <v>61.65</v>
+        <v>63.72</v>
       </c>
       <c r="I19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1147,19 +1153,19 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F20">
-        <v>50.96</v>
+        <v>48.03</v>
       </c>
       <c r="G20">
-        <v>57.16</v>
+        <v>55.45</v>
       </c>
       <c r="H20">
-        <v>63.3</v>
+        <v>65.13</v>
       </c>
       <c r="I20" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1176,19 +1182,19 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="F21">
-        <v>52.38</v>
+        <v>52.57</v>
       </c>
       <c r="G21">
-        <v>56.7</v>
+        <v>55.42</v>
       </c>
       <c r="H21">
-        <v>64.48999999999999</v>
+        <v>58.27</v>
       </c>
       <c r="I21" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -1205,19 +1211,19 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="F22">
-        <v>48.97</v>
+        <v>55.3</v>
       </c>
       <c r="G22">
-        <v>56.61</v>
+        <v>55.3</v>
       </c>
       <c r="H22">
-        <v>63</v>
+        <v>55.3</v>
       </c>
       <c r="I22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1234,19 +1240,19 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>62</v>
+        <v>9</v>
       </c>
       <c r="F23">
-        <v>51.01</v>
+        <v>52.08</v>
       </c>
       <c r="G23">
-        <v>56.1</v>
+        <v>55.21</v>
       </c>
       <c r="H23">
-        <v>59.56</v>
+        <v>60.01</v>
       </c>
       <c r="I23" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -1263,19 +1269,19 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="F24">
-        <v>55.7</v>
+        <v>48.42</v>
       </c>
       <c r="G24">
-        <v>55.7</v>
+        <v>54.79</v>
       </c>
       <c r="H24">
-        <v>55.7</v>
+        <v>57.91</v>
       </c>
       <c r="I24" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -1283,7 +1289,7 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C25" t="s">
         <v>46</v>
@@ -1292,19 +1298,19 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F25">
-        <v>51.5</v>
+        <v>49.85</v>
       </c>
       <c r="G25">
-        <v>55.66</v>
+        <v>54.46</v>
       </c>
       <c r="H25">
-        <v>57.71</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="I25" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -1321,19 +1327,19 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F26">
-        <v>49.09</v>
+        <v>52.14</v>
       </c>
       <c r="G26">
-        <v>55.31</v>
+        <v>54.43</v>
       </c>
       <c r="H26">
-        <v>60.62</v>
+        <v>58.64</v>
       </c>
       <c r="I26" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -1350,19 +1356,19 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F27">
-        <v>53.95</v>
+        <v>52.49</v>
       </c>
       <c r="G27">
-        <v>54.75</v>
+        <v>54.15</v>
       </c>
       <c r="H27">
-        <v>55.72</v>
+        <v>55.24</v>
       </c>
       <c r="I27" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -1379,19 +1385,19 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>117</v>
+        <v>4</v>
       </c>
       <c r="F28">
-        <v>49.75</v>
+        <v>53.54</v>
       </c>
       <c r="G28">
-        <v>54.68</v>
+        <v>53.93</v>
       </c>
       <c r="H28">
-        <v>63.8</v>
+        <v>54.13</v>
       </c>
       <c r="I28" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -1399,7 +1405,7 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C29" t="s">
         <v>46</v>
@@ -1408,19 +1414,19 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>65</v>
+        <v>8</v>
       </c>
       <c r="F29">
-        <v>49.75</v>
+        <v>48.5</v>
       </c>
       <c r="G29">
-        <v>54.54</v>
+        <v>53.38</v>
       </c>
       <c r="H29">
-        <v>63.8</v>
+        <v>60.4</v>
       </c>
       <c r="I29" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -1428,7 +1434,7 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C30" t="s">
         <v>46</v>
@@ -1437,19 +1443,19 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F30">
-        <v>47.38</v>
+        <v>50.69</v>
       </c>
       <c r="G30">
-        <v>54.32</v>
+        <v>52.9</v>
       </c>
       <c r="H30">
-        <v>57.66</v>
+        <v>55.09</v>
       </c>
       <c r="I30" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -1457,7 +1463,7 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C31" t="s">
         <v>46</v>
@@ -1466,19 +1472,19 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F31">
-        <v>52.17</v>
+        <v>46.02</v>
       </c>
       <c r="G31">
-        <v>53.89</v>
+        <v>52.78</v>
       </c>
       <c r="H31">
-        <v>56.7</v>
+        <v>57.1</v>
       </c>
       <c r="I31" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -1486,7 +1492,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C32" t="s">
         <v>46</v>
@@ -1498,16 +1504,16 @@
         <v>10</v>
       </c>
       <c r="F32">
-        <v>50.2</v>
+        <v>49.57</v>
       </c>
       <c r="G32">
-        <v>53.37</v>
+        <v>51.64</v>
       </c>
       <c r="H32">
-        <v>63.37</v>
+        <v>55.29</v>
       </c>
       <c r="I32" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -1515,7 +1521,7 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C33" t="s">
         <v>46</v>
@@ -1527,16 +1533,16 @@
         <v>2</v>
       </c>
       <c r="F33">
-        <v>51.8</v>
+        <v>48.77</v>
       </c>
       <c r="G33">
-        <v>53.25</v>
+        <v>48.77</v>
       </c>
       <c r="H33">
-        <v>54.7</v>
+        <v>48.77</v>
       </c>
       <c r="I33" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1544,7 +1550,7 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C34" t="s">
         <v>46</v>
@@ -1553,19 +1559,19 @@
         <v>47</v>
       </c>
       <c r="E34">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="F34">
-        <v>47.98</v>
+        <v>43.44</v>
       </c>
       <c r="G34">
-        <v>52.99</v>
+        <v>48.06</v>
       </c>
       <c r="H34">
-        <v>56.6</v>
+        <v>54.28</v>
       </c>
       <c r="I34" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -1573,7 +1579,7 @@
         <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C35" t="s">
         <v>46</v>
@@ -1585,7 +1591,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -1593,7 +1599,7 @@
         <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C36" t="s">
         <v>46</v>
@@ -1605,7 +1611,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="51">
   <si>
     <t>نام منطقه</t>
   </si>
@@ -49,19 +49,43 @@
     <t>منطقه شکار ممنوع کوه دراء</t>
   </si>
   <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
     <t>منطقه حفاظت شده میانجنگل فسا</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع کوه خم</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع مزايجان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دالان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع کوه خرسي</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بناب</t>
   </si>
   <si>
     <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
@@ -70,69 +94,48 @@
     <t>منطقه شکار ممنوع کوه گورم</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بناب</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
+    <t>منطقه حفاظت شده هرمود</t>
+  </si>
+  <si>
+    <t>پارک ملي قطرويه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش دره باغ</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بصيران</t>
   </si>
   <si>
     <t>پناهگاه حيات وحش بختگان</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
     <t>منطقه شکار ممن.ع آق جلو</t>
   </si>
   <si>
-    <t>پارک ملي قطرويه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده هرمود</t>
+    <t>منطقه حفاظت شده برم فیروز</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع توت سياه</t>
   </si>
   <si>
     <t>منطقه حفاظت شده بهرام گور</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع بصيران</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دالان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع خرمنکوه</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع کوه هوا و</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع شیکوه</t>
   </si>
   <si>
@@ -142,9 +145,6 @@
     <t>منطقه شکار ممنوع کوهستان</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه هوا و</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع چاه نفت</t>
   </si>
   <si>
@@ -157,13 +157,10 @@
     <t>مناطق ممنوعه شکار</t>
   </si>
   <si>
-    <t>1405-07-13</t>
-  </si>
-  <si>
-    <t>2026-10-05</t>
-  </si>
-  <si>
-    <t>بسیار شدید</t>
+    <t>1405-07-14</t>
+  </si>
+  <si>
+    <t>2026-10-06</t>
   </si>
   <si>
     <t>شدید</t>
@@ -634,13 +631,13 @@
         <v>33</v>
       </c>
       <c r="F2">
-        <v>65.48999999999999</v>
+        <v>62.18</v>
       </c>
       <c r="G2">
-        <v>71.36</v>
+        <v>67.78</v>
       </c>
       <c r="H2">
-        <v>78.48</v>
+        <v>70.52</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -660,19 +657,19 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F3">
-        <v>57.05</v>
+        <v>56.77</v>
       </c>
       <c r="G3">
-        <v>62.6</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="H3">
-        <v>71.81999999999999</v>
+        <v>70.58</v>
       </c>
       <c r="I3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -689,19 +686,19 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F4">
-        <v>56.75</v>
+        <v>57.02</v>
       </c>
       <c r="G4">
-        <v>62.07</v>
+        <v>64.05</v>
       </c>
       <c r="H4">
-        <v>70.64</v>
+        <v>70.77</v>
       </c>
       <c r="I4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -709,7 +706,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
         <v>46</v>
@@ -718,19 +715,19 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="F5">
-        <v>54.65</v>
+        <v>57.54</v>
       </c>
       <c r="G5">
-        <v>61.31</v>
+        <v>63.22</v>
       </c>
       <c r="H5">
-        <v>65.05</v>
+        <v>71.01000000000001</v>
       </c>
       <c r="I5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -747,19 +744,19 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F6">
-        <v>55.95</v>
+        <v>58.4</v>
       </c>
       <c r="G6">
-        <v>60.77</v>
+        <v>62.86</v>
       </c>
       <c r="H6">
-        <v>65.61</v>
+        <v>71.37</v>
       </c>
       <c r="I6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -776,19 +773,19 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F7">
-        <v>55.42</v>
+        <v>52.42</v>
       </c>
       <c r="G7">
-        <v>60.18</v>
+        <v>62.32</v>
       </c>
       <c r="H7">
-        <v>66.34</v>
+        <v>70.16</v>
       </c>
       <c r="I7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -796,7 +793,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C8" t="s">
         <v>46</v>
@@ -805,19 +802,19 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F8">
-        <v>57.41</v>
+        <v>57.23</v>
       </c>
       <c r="G8">
-        <v>59.74</v>
+        <v>62.26</v>
       </c>
       <c r="H8">
-        <v>63.03</v>
+        <v>67.87</v>
       </c>
       <c r="I8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -834,19 +831,19 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F9">
-        <v>54.28</v>
+        <v>61.67</v>
       </c>
       <c r="G9">
-        <v>58.79</v>
+        <v>62.23</v>
       </c>
       <c r="H9">
-        <v>65.45999999999999</v>
+        <v>62.58</v>
       </c>
       <c r="I9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -863,19 +860,19 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F10">
-        <v>50.97</v>
+        <v>58.91</v>
       </c>
       <c r="G10">
-        <v>58.54</v>
+        <v>62.04</v>
       </c>
       <c r="H10">
-        <v>66.70999999999999</v>
+        <v>65.42</v>
       </c>
       <c r="I10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -883,7 +880,7 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
         <v>46</v>
@@ -892,19 +889,19 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F11">
-        <v>49.71</v>
+        <v>55.7</v>
       </c>
       <c r="G11">
-        <v>58.43</v>
+        <v>61.08</v>
       </c>
       <c r="H11">
-        <v>61.82</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="I11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -912,7 +909,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
         <v>46</v>
@@ -921,19 +918,19 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F12">
-        <v>56.69</v>
+        <v>54.73</v>
       </c>
       <c r="G12">
-        <v>58.32</v>
+        <v>60.44</v>
       </c>
       <c r="H12">
-        <v>60.4</v>
+        <v>67.61</v>
       </c>
       <c r="I12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -950,19 +947,19 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="F13">
-        <v>52.03</v>
+        <v>52.04</v>
       </c>
       <c r="G13">
-        <v>58.3</v>
+        <v>60.03</v>
       </c>
       <c r="H13">
-        <v>63.39</v>
+        <v>68.19</v>
       </c>
       <c r="I13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -970,7 +967,7 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
         <v>46</v>
@@ -979,19 +976,19 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F14">
-        <v>54.31</v>
+        <v>52</v>
       </c>
       <c r="G14">
-        <v>57.47</v>
+        <v>59.74</v>
       </c>
       <c r="H14">
-        <v>59.7</v>
+        <v>64.89</v>
       </c>
       <c r="I14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -999,7 +996,7 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s">
         <v>46</v>
@@ -1008,19 +1005,19 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>117</v>
+        <v>20</v>
       </c>
       <c r="F15">
-        <v>47.77</v>
+        <v>53.57</v>
       </c>
       <c r="G15">
-        <v>56.65</v>
+        <v>59.37</v>
       </c>
       <c r="H15">
-        <v>65.73</v>
+        <v>62.1</v>
       </c>
       <c r="I15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1028,7 +1025,7 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
         <v>46</v>
@@ -1037,19 +1034,19 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F16">
-        <v>50.39</v>
+        <v>57.35</v>
       </c>
       <c r="G16">
-        <v>56.57</v>
+        <v>58.91</v>
       </c>
       <c r="H16">
-        <v>64.38</v>
+        <v>61.82</v>
       </c>
       <c r="I16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1057,7 +1054,7 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C17" t="s">
         <v>46</v>
@@ -1066,19 +1063,19 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="F17">
-        <v>47.77</v>
+        <v>54.38</v>
       </c>
       <c r="G17">
-        <v>55.98</v>
+        <v>58.68</v>
       </c>
       <c r="H17">
-        <v>65.73</v>
+        <v>65.7</v>
       </c>
       <c r="I17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1086,7 +1083,7 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
         <v>46</v>
@@ -1095,19 +1092,19 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F18">
-        <v>50.46</v>
+        <v>54.19</v>
       </c>
       <c r="G18">
-        <v>55.94</v>
+        <v>58.37</v>
       </c>
       <c r="H18">
-        <v>64.41</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="I18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1115,7 +1112,7 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
         <v>46</v>
@@ -1124,19 +1121,19 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F19">
-        <v>46.88</v>
+        <v>58.18</v>
       </c>
       <c r="G19">
-        <v>55.49</v>
+        <v>58.18</v>
       </c>
       <c r="H19">
-        <v>63.72</v>
+        <v>58.18</v>
       </c>
       <c r="I19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1156,16 +1153,16 @@
         <v>16</v>
       </c>
       <c r="F20">
-        <v>48.03</v>
+        <v>49.35</v>
       </c>
       <c r="G20">
-        <v>55.45</v>
+        <v>57.49</v>
       </c>
       <c r="H20">
-        <v>65.13</v>
+        <v>66.2</v>
       </c>
       <c r="I20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1182,19 +1179,19 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F21">
-        <v>52.57</v>
+        <v>49.48</v>
       </c>
       <c r="G21">
-        <v>55.42</v>
+        <v>57.44</v>
       </c>
       <c r="H21">
-        <v>58.27</v>
+        <v>63.72</v>
       </c>
       <c r="I21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -1211,19 +1208,19 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F22">
-        <v>55.3</v>
+        <v>54.25</v>
       </c>
       <c r="G22">
-        <v>55.3</v>
+        <v>56.82</v>
       </c>
       <c r="H22">
-        <v>55.3</v>
+        <v>61.41</v>
       </c>
       <c r="I22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1240,19 +1237,19 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="F23">
-        <v>52.08</v>
+        <v>47.64</v>
       </c>
       <c r="G23">
-        <v>55.21</v>
+        <v>55.3</v>
       </c>
       <c r="H23">
-        <v>60.01</v>
+        <v>69.22</v>
       </c>
       <c r="I23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -1260,7 +1257,7 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C24" t="s">
         <v>46</v>
@@ -1269,19 +1266,19 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F24">
-        <v>48.42</v>
+        <v>46.19</v>
       </c>
       <c r="G24">
-        <v>54.79</v>
+        <v>55.05</v>
       </c>
       <c r="H24">
-        <v>57.91</v>
+        <v>64.55</v>
       </c>
       <c r="I24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -1289,7 +1286,7 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C25" t="s">
         <v>46</v>
@@ -1298,19 +1295,19 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>28</v>
+        <v>117</v>
       </c>
       <c r="F25">
-        <v>49.85</v>
+        <v>47.64</v>
       </c>
       <c r="G25">
-        <v>54.46</v>
+        <v>54.8</v>
       </c>
       <c r="H25">
-        <v>66.43000000000001</v>
+        <v>69.22</v>
       </c>
       <c r="I25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -1318,7 +1315,7 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s">
         <v>46</v>
@@ -1327,19 +1324,19 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F26">
-        <v>52.14</v>
+        <v>50.51</v>
       </c>
       <c r="G26">
-        <v>54.43</v>
+        <v>54.21</v>
       </c>
       <c r="H26">
-        <v>58.64</v>
+        <v>57.9</v>
       </c>
       <c r="I26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -1347,7 +1344,7 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
         <v>46</v>
@@ -1359,16 +1356,16 @@
         <v>8</v>
       </c>
       <c r="F27">
-        <v>52.49</v>
+        <v>46.42</v>
       </c>
       <c r="G27">
-        <v>54.15</v>
+        <v>54.14</v>
       </c>
       <c r="H27">
-        <v>55.24</v>
+        <v>65.42</v>
       </c>
       <c r="I27" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -1388,16 +1385,16 @@
         <v>4</v>
       </c>
       <c r="F28">
-        <v>53.54</v>
+        <v>52.66</v>
       </c>
       <c r="G28">
-        <v>53.93</v>
+        <v>53.56</v>
       </c>
       <c r="H28">
-        <v>54.13</v>
+        <v>54.97</v>
       </c>
       <c r="I28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -1414,19 +1411,19 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F29">
-        <v>48.5</v>
+        <v>48.38</v>
       </c>
       <c r="G29">
-        <v>53.38</v>
+        <v>53.52</v>
       </c>
       <c r="H29">
-        <v>60.4</v>
+        <v>59.89</v>
       </c>
       <c r="I29" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -1446,16 +1443,16 @@
         <v>12</v>
       </c>
       <c r="F30">
-        <v>50.69</v>
+        <v>49.47</v>
       </c>
       <c r="G30">
-        <v>52.9</v>
+        <v>53.26</v>
       </c>
       <c r="H30">
-        <v>55.09</v>
+        <v>59.35</v>
       </c>
       <c r="I30" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -1472,19 +1469,19 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="F31">
-        <v>46.02</v>
+        <v>48.9</v>
       </c>
       <c r="G31">
-        <v>52.78</v>
+        <v>52.55</v>
       </c>
       <c r="H31">
-        <v>57.1</v>
+        <v>54.98</v>
       </c>
       <c r="I31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -1501,19 +1498,19 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F32">
-        <v>49.57</v>
+        <v>47.93</v>
       </c>
       <c r="G32">
-        <v>51.64</v>
+        <v>51.86</v>
       </c>
       <c r="H32">
-        <v>55.29</v>
+        <v>55.6</v>
       </c>
       <c r="I32" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -1530,19 +1527,19 @@
         <v>47</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F33">
-        <v>48.77</v>
+        <v>48.84</v>
       </c>
       <c r="G33">
-        <v>48.77</v>
+        <v>50.89</v>
       </c>
       <c r="H33">
-        <v>48.77</v>
+        <v>56.03</v>
       </c>
       <c r="I33" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1559,19 +1556,19 @@
         <v>47</v>
       </c>
       <c r="E34">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="F34">
-        <v>43.44</v>
+        <v>49.49</v>
       </c>
       <c r="G34">
-        <v>48.06</v>
+        <v>49.49</v>
       </c>
       <c r="H34">
-        <v>54.28</v>
+        <v>49.49</v>
       </c>
       <c r="I34" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -1591,7 +1588,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -1611,7 +1608,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -49,99 +49,99 @@
     <t>منطقه شکار ممنوع کوه دراء</t>
   </si>
   <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دالان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده برم فیروز</t>
+  </si>
+  <si>
     <t>منطقه حفاظت شده ارژن و پريشان</t>
   </si>
   <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع پادنا</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده هرمود</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
+  </si>
+  <si>
+    <t>پارک ملي قطرويه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع توت سياه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بناب</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع شیکوه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دره باغ</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع مزايجان</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دالان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بناب</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده هرمود</t>
-  </si>
-  <si>
-    <t>پارک ملي قطرويه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
-  </si>
-  <si>
     <t>پناهگاه حيات وحش دره باغ</t>
   </si>
   <si>
     <t>پارک ملي بختگان</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع کوه هوا و</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مهارلو</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع بصيران</t>
   </si>
   <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه هوا و</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع شیکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع کوهستان</t>
   </si>
   <si>
@@ -157,16 +157,16 @@
     <t>مناطق ممنوعه شکار</t>
   </si>
   <si>
-    <t>1405-07-14</t>
-  </si>
-  <si>
-    <t>2026-10-06</t>
+    <t>1405-07-15</t>
+  </si>
+  <si>
+    <t>2026-10-07</t>
+  </si>
+  <si>
+    <t>بسیار شدید</t>
   </si>
   <si>
     <t>شدید</t>
-  </si>
-  <si>
-    <t>خیلی زیاد</t>
   </si>
   <si>
     <t>بدون داده</t>
@@ -631,13 +631,13 @@
         <v>33</v>
       </c>
       <c r="F2">
-        <v>62.18</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="G2">
-        <v>67.78</v>
+        <v>70.34</v>
       </c>
       <c r="H2">
-        <v>70.52</v>
+        <v>73.69</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -657,19 +657,19 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F3">
-        <v>56.77</v>
+        <v>60.08</v>
       </c>
       <c r="G3">
-        <v>66.09999999999999</v>
+        <v>68.36</v>
       </c>
       <c r="H3">
-        <v>70.58</v>
+        <v>77.95</v>
       </c>
       <c r="I3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -677,7 +677,7 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C4" t="s">
         <v>46</v>
@@ -686,19 +686,19 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>57.02</v>
+        <v>63.96</v>
       </c>
       <c r="G4">
-        <v>64.05</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="H4">
-        <v>70.77</v>
+        <v>70.08</v>
       </c>
       <c r="I4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -706,7 +706,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
         <v>46</v>
@@ -715,19 +715,19 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F5">
-        <v>57.54</v>
+        <v>62.43</v>
       </c>
       <c r="G5">
-        <v>63.22</v>
+        <v>65.94</v>
       </c>
       <c r="H5">
-        <v>71.01000000000001</v>
+        <v>68.19</v>
       </c>
       <c r="I5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -744,19 +744,19 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>58.4</v>
+        <v>62.58</v>
       </c>
       <c r="G6">
-        <v>62.86</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="H6">
-        <v>71.37</v>
+        <v>76.28</v>
       </c>
       <c r="I6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -773,19 +773,19 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F7">
-        <v>52.42</v>
+        <v>64.92</v>
       </c>
       <c r="G7">
-        <v>62.32</v>
+        <v>65.56</v>
       </c>
       <c r="H7">
-        <v>70.16</v>
+        <v>67.02</v>
       </c>
       <c r="I7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -793,7 +793,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
         <v>46</v>
@@ -802,19 +802,19 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F8">
-        <v>57.23</v>
+        <v>59.73</v>
       </c>
       <c r="G8">
-        <v>62.26</v>
+        <v>65.42</v>
       </c>
       <c r="H8">
-        <v>67.87</v>
+        <v>72.72</v>
       </c>
       <c r="I8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -822,7 +822,7 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s">
         <v>46</v>
@@ -831,19 +831,19 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F9">
-        <v>61.67</v>
+        <v>58.92</v>
       </c>
       <c r="G9">
-        <v>62.23</v>
+        <v>65.25</v>
       </c>
       <c r="H9">
-        <v>62.58</v>
+        <v>68.98</v>
       </c>
       <c r="I9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -860,19 +860,19 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="F10">
-        <v>58.91</v>
+        <v>52.83</v>
       </c>
       <c r="G10">
-        <v>62.04</v>
+        <v>64.92</v>
       </c>
       <c r="H10">
-        <v>65.42</v>
+        <v>70.94</v>
       </c>
       <c r="I10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -880,7 +880,7 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s">
         <v>46</v>
@@ -889,19 +889,19 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F11">
-        <v>55.7</v>
+        <v>53.74</v>
       </c>
       <c r="G11">
-        <v>61.08</v>
+        <v>64.47</v>
       </c>
       <c r="H11">
-        <v>64.01000000000001</v>
+        <v>70.79000000000001</v>
       </c>
       <c r="I11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -918,19 +918,19 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F12">
-        <v>54.73</v>
+        <v>56.66</v>
       </c>
       <c r="G12">
-        <v>60.44</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="H12">
-        <v>67.61</v>
+        <v>70.66</v>
       </c>
       <c r="I12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -947,19 +947,19 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="F13">
-        <v>52.04</v>
+        <v>55.53</v>
       </c>
       <c r="G13">
-        <v>60.03</v>
+        <v>61.83</v>
       </c>
       <c r="H13">
-        <v>68.19</v>
+        <v>67.8</v>
       </c>
       <c r="I13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -979,16 +979,16 @@
         <v>13</v>
       </c>
       <c r="F14">
-        <v>52</v>
+        <v>58.94</v>
       </c>
       <c r="G14">
-        <v>59.74</v>
+        <v>61.82</v>
       </c>
       <c r="H14">
-        <v>64.89</v>
+        <v>63.41</v>
       </c>
       <c r="I14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -996,7 +996,7 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
         <v>46</v>
@@ -1005,19 +1005,19 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F15">
-        <v>53.57</v>
+        <v>60.39</v>
       </c>
       <c r="G15">
-        <v>59.37</v>
+        <v>61.47</v>
       </c>
       <c r="H15">
-        <v>62.1</v>
+        <v>62.69</v>
       </c>
       <c r="I15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1034,19 +1034,19 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F16">
-        <v>57.35</v>
+        <v>59.23</v>
       </c>
       <c r="G16">
-        <v>58.91</v>
+        <v>61.38</v>
       </c>
       <c r="H16">
-        <v>61.82</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="I16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1063,19 +1063,19 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="F17">
-        <v>54.38</v>
+        <v>53.47</v>
       </c>
       <c r="G17">
-        <v>58.68</v>
+        <v>61.15</v>
       </c>
       <c r="H17">
-        <v>65.7</v>
+        <v>70.68000000000001</v>
       </c>
       <c r="I17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1083,7 +1083,7 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C18" t="s">
         <v>46</v>
@@ -1092,19 +1092,19 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F18">
-        <v>54.19</v>
+        <v>58.02</v>
       </c>
       <c r="G18">
-        <v>58.37</v>
+        <v>60.68</v>
       </c>
       <c r="H18">
-        <v>64.23999999999999</v>
+        <v>63.33</v>
       </c>
       <c r="I18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1124,16 +1124,16 @@
         <v>4</v>
       </c>
       <c r="F19">
-        <v>58.18</v>
+        <v>60.61</v>
       </c>
       <c r="G19">
-        <v>58.18</v>
+        <v>60.61</v>
       </c>
       <c r="H19">
-        <v>58.18</v>
+        <v>60.61</v>
       </c>
       <c r="I19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1141,7 +1141,7 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C20" t="s">
         <v>46</v>
@@ -1150,19 +1150,19 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F20">
-        <v>49.35</v>
+        <v>56.3</v>
       </c>
       <c r="G20">
-        <v>57.49</v>
+        <v>60.43</v>
       </c>
       <c r="H20">
-        <v>66.2</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="I20" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1170,7 +1170,7 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C21" t="s">
         <v>46</v>
@@ -1179,19 +1179,19 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F21">
-        <v>49.48</v>
+        <v>53.86</v>
       </c>
       <c r="G21">
-        <v>57.44</v>
+        <v>60.39</v>
       </c>
       <c r="H21">
-        <v>63.72</v>
+        <v>66.26000000000001</v>
       </c>
       <c r="I21" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -1199,7 +1199,7 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C22" t="s">
         <v>46</v>
@@ -1208,19 +1208,19 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F22">
-        <v>54.25</v>
+        <v>56.55</v>
       </c>
       <c r="G22">
-        <v>56.82</v>
+        <v>59.99</v>
       </c>
       <c r="H22">
-        <v>61.41</v>
+        <v>62.71</v>
       </c>
       <c r="I22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1228,7 +1228,7 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C23" t="s">
         <v>46</v>
@@ -1237,19 +1237,19 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="F23">
-        <v>47.64</v>
+        <v>51.27</v>
       </c>
       <c r="G23">
-        <v>55.3</v>
+        <v>59.83</v>
       </c>
       <c r="H23">
-        <v>69.22</v>
+        <v>65.91</v>
       </c>
       <c r="I23" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -1266,19 +1266,19 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="F24">
-        <v>46.19</v>
+        <v>52.12</v>
       </c>
       <c r="G24">
-        <v>55.05</v>
+        <v>59.3</v>
       </c>
       <c r="H24">
-        <v>64.55</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="I24" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -1295,19 +1295,19 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="F25">
-        <v>47.64</v>
+        <v>53.95</v>
       </c>
       <c r="G25">
-        <v>54.8</v>
+        <v>58.48</v>
       </c>
       <c r="H25">
-        <v>69.22</v>
+        <v>63.14</v>
       </c>
       <c r="I25" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -1324,19 +1324,19 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F26">
-        <v>50.51</v>
+        <v>41.8</v>
       </c>
       <c r="G26">
-        <v>54.21</v>
+        <v>57.76</v>
       </c>
       <c r="H26">
-        <v>57.9</v>
+        <v>68</v>
       </c>
       <c r="I26" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -1344,7 +1344,7 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
         <v>46</v>
@@ -1353,19 +1353,19 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F27">
-        <v>46.42</v>
+        <v>51.46</v>
       </c>
       <c r="G27">
-        <v>54.14</v>
+        <v>57.31</v>
       </c>
       <c r="H27">
-        <v>65.42</v>
+        <v>65.08</v>
       </c>
       <c r="I27" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -1373,7 +1373,7 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C28" t="s">
         <v>46</v>
@@ -1382,19 +1382,19 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F28">
-        <v>52.66</v>
+        <v>51.89</v>
       </c>
       <c r="G28">
-        <v>53.56</v>
+        <v>57.22</v>
       </c>
       <c r="H28">
-        <v>54.97</v>
+        <v>61.62</v>
       </c>
       <c r="I28" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -1411,19 +1411,19 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="F29">
-        <v>48.38</v>
+        <v>49.89</v>
       </c>
       <c r="G29">
-        <v>53.52</v>
+        <v>56.47</v>
       </c>
       <c r="H29">
-        <v>59.89</v>
+        <v>74.58</v>
       </c>
       <c r="I29" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -1440,19 +1440,19 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="F30">
-        <v>49.47</v>
+        <v>52.51</v>
       </c>
       <c r="G30">
-        <v>53.26</v>
+        <v>56.43</v>
       </c>
       <c r="H30">
-        <v>59.35</v>
+        <v>60.31</v>
       </c>
       <c r="I30" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -1460,7 +1460,7 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C31" t="s">
         <v>46</v>
@@ -1469,19 +1469,19 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>37</v>
+        <v>117</v>
       </c>
       <c r="F31">
-        <v>48.9</v>
+        <v>49.89</v>
       </c>
       <c r="G31">
-        <v>52.55</v>
+        <v>56.08</v>
       </c>
       <c r="H31">
-        <v>54.98</v>
+        <v>74.58</v>
       </c>
       <c r="I31" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -1498,19 +1498,19 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F32">
-        <v>47.93</v>
+        <v>50.49</v>
       </c>
       <c r="G32">
-        <v>51.86</v>
+        <v>55.03</v>
       </c>
       <c r="H32">
-        <v>55.6</v>
+        <v>60.86</v>
       </c>
       <c r="I32" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -1527,19 +1527,19 @@
         <v>47</v>
       </c>
       <c r="E33">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F33">
-        <v>48.84</v>
+        <v>40.3</v>
       </c>
       <c r="G33">
-        <v>50.89</v>
+        <v>54.87</v>
       </c>
       <c r="H33">
-        <v>56.03</v>
+        <v>69.81999999999999</v>
       </c>
       <c r="I33" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1559,13 +1559,13 @@
         <v>2</v>
       </c>
       <c r="F34">
-        <v>49.49</v>
+        <v>52.78</v>
       </c>
       <c r="G34">
-        <v>49.49</v>
+        <v>52.78</v>
       </c>
       <c r="H34">
-        <v>49.49</v>
+        <v>52.78</v>
       </c>
       <c r="I34" t="s">
         <v>49</v>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="52">
   <si>
     <t>نام منطقه</t>
   </si>
@@ -46,102 +46,102 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع کوه دراء</t>
   </si>
   <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دالان</t>
+  </si>
+  <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
     <t>منطقه حفاظت شده میانجنگل فسا</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دالان</t>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
   </si>
   <si>
     <t>منطقه حفاظت شده برم فیروز</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع پادنا</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده هرمود</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع کوه گورم</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده هرمود</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
+    <t>منطقه شکار ممنوع مزايجان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بناب</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بصيران</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه هوا و</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع توت سياه</t>
   </si>
   <si>
     <t>پارک ملي قطرويه</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
+    <t>پناهگاه حيات وحش دره باغ</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع خرمنکوه</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع بناب</t>
+    <t>منطقه شکار ممنوع مهارلو</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع شیکوه</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش دره باغ</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه هوا و</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بصيران</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع کوهستان</t>
   </si>
   <si>
@@ -157,16 +157,19 @@
     <t>مناطق ممنوعه شکار</t>
   </si>
   <si>
-    <t>1405-07-15</t>
-  </si>
-  <si>
-    <t>2026-10-07</t>
+    <t>1405-07-16</t>
+  </si>
+  <si>
+    <t>2026-10-08</t>
   </si>
   <si>
     <t>بسیار شدید</t>
   </si>
   <si>
     <t>شدید</t>
+  </si>
+  <si>
+    <t>خیلی زیاد</t>
   </si>
   <si>
     <t>بدون داده</t>
@@ -628,16 +631,16 @@
         <v>47</v>
       </c>
       <c r="E2">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>64.95999999999999</v>
+        <v>64.31</v>
       </c>
       <c r="G2">
-        <v>70.34</v>
+        <v>70.42</v>
       </c>
       <c r="H2">
-        <v>73.69</v>
+        <v>79.95999999999999</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -648,7 +651,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C3" t="s">
         <v>46</v>
@@ -657,16 +660,16 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F3">
-        <v>60.08</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="G3">
-        <v>68.36</v>
+        <v>68.7</v>
       </c>
       <c r="H3">
-        <v>77.95</v>
+        <v>73.62</v>
       </c>
       <c r="I3" t="s">
         <v>49</v>
@@ -677,7 +680,7 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C4" t="s">
         <v>46</v>
@@ -686,16 +689,16 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>63.96</v>
+        <v>66.48999999999999</v>
       </c>
       <c r="G4">
-        <v>66.98999999999999</v>
+        <v>68.05</v>
       </c>
       <c r="H4">
-        <v>70.08</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="I4" t="s">
         <v>49</v>
@@ -715,16 +718,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>62.43</v>
+        <v>63.27</v>
       </c>
       <c r="G5">
-        <v>65.94</v>
+        <v>66.97</v>
       </c>
       <c r="H5">
-        <v>68.19</v>
+        <v>68.3</v>
       </c>
       <c r="I5" t="s">
         <v>49</v>
@@ -735,7 +738,7 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s">
         <v>46</v>
@@ -744,16 +747,16 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F6">
-        <v>62.58</v>
+        <v>62.1</v>
       </c>
       <c r="G6">
-        <v>65.68000000000001</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="H6">
-        <v>76.28</v>
+        <v>72.23</v>
       </c>
       <c r="I6" t="s">
         <v>49</v>
@@ -764,7 +767,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
         <v>46</v>
@@ -773,16 +776,16 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F7">
-        <v>64.92</v>
+        <v>60.85</v>
       </c>
       <c r="G7">
-        <v>65.56</v>
+        <v>66.45</v>
       </c>
       <c r="H7">
-        <v>67.02</v>
+        <v>69.8</v>
       </c>
       <c r="I7" t="s">
         <v>49</v>
@@ -793,7 +796,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C8" t="s">
         <v>46</v>
@@ -802,16 +805,16 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F8">
-        <v>59.73</v>
+        <v>56.86</v>
       </c>
       <c r="G8">
-        <v>65.42</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="H8">
-        <v>72.72</v>
+        <v>74.67</v>
       </c>
       <c r="I8" t="s">
         <v>49</v>
@@ -831,16 +834,16 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F9">
-        <v>58.92</v>
+        <v>62.91</v>
       </c>
       <c r="G9">
-        <v>65.25</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="H9">
-        <v>68.98</v>
+        <v>67.77</v>
       </c>
       <c r="I9" t="s">
         <v>49</v>
@@ -860,16 +863,16 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F10">
-        <v>52.83</v>
+        <v>53.74</v>
       </c>
       <c r="G10">
-        <v>64.92</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="H10">
-        <v>70.94</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="I10" t="s">
         <v>49</v>
@@ -889,16 +892,16 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F11">
-        <v>53.74</v>
+        <v>57.4</v>
       </c>
       <c r="G11">
-        <v>64.47</v>
+        <v>64.44</v>
       </c>
       <c r="H11">
-        <v>70.79000000000001</v>
+        <v>70.58</v>
       </c>
       <c r="I11" t="s">
         <v>49</v>
@@ -909,7 +912,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
         <v>46</v>
@@ -918,16 +921,16 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F12">
-        <v>56.66</v>
+        <v>57.84</v>
       </c>
       <c r="G12">
-        <v>64.09999999999999</v>
+        <v>63.92</v>
       </c>
       <c r="H12">
-        <v>70.66</v>
+        <v>73.04000000000001</v>
       </c>
       <c r="I12" t="s">
         <v>49</v>
@@ -938,7 +941,7 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
         <v>46</v>
@@ -947,16 +950,16 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F13">
-        <v>55.53</v>
+        <v>59.16</v>
       </c>
       <c r="G13">
-        <v>61.83</v>
+        <v>63.41</v>
       </c>
       <c r="H13">
-        <v>67.8</v>
+        <v>65.03</v>
       </c>
       <c r="I13" t="s">
         <v>49</v>
@@ -979,13 +982,13 @@
         <v>13</v>
       </c>
       <c r="F14">
-        <v>58.94</v>
+        <v>59.13</v>
       </c>
       <c r="G14">
-        <v>61.82</v>
+        <v>63.3</v>
       </c>
       <c r="H14">
-        <v>63.41</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="I14" t="s">
         <v>49</v>
@@ -1005,16 +1008,16 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F15">
-        <v>60.39</v>
+        <v>55.37</v>
       </c>
       <c r="G15">
-        <v>61.47</v>
+        <v>63.14</v>
       </c>
       <c r="H15">
-        <v>62.69</v>
+        <v>69.48999999999999</v>
       </c>
       <c r="I15" t="s">
         <v>49</v>
@@ -1025,7 +1028,7 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
         <v>46</v>
@@ -1034,16 +1037,16 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F16">
-        <v>59.23</v>
+        <v>56.22</v>
       </c>
       <c r="G16">
-        <v>61.38</v>
+        <v>62.32</v>
       </c>
       <c r="H16">
-        <v>65.40000000000001</v>
+        <v>67.06</v>
       </c>
       <c r="I16" t="s">
         <v>49</v>
@@ -1066,13 +1069,13 @@
         <v>62</v>
       </c>
       <c r="F17">
-        <v>53.47</v>
+        <v>53.77</v>
       </c>
       <c r="G17">
-        <v>61.15</v>
+        <v>61.51</v>
       </c>
       <c r="H17">
-        <v>70.68000000000001</v>
+        <v>72.38</v>
       </c>
       <c r="I17" t="s">
         <v>49</v>
@@ -1083,7 +1086,7 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
         <v>46</v>
@@ -1092,16 +1095,16 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F18">
-        <v>58.02</v>
+        <v>58.67</v>
       </c>
       <c r="G18">
-        <v>60.68</v>
+        <v>61.35</v>
       </c>
       <c r="H18">
-        <v>63.33</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="I18" t="s">
         <v>49</v>
@@ -1112,7 +1115,7 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C19" t="s">
         <v>46</v>
@@ -1121,16 +1124,16 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F19">
-        <v>60.61</v>
+        <v>54.37</v>
       </c>
       <c r="G19">
-        <v>60.61</v>
+        <v>60.95</v>
       </c>
       <c r="H19">
-        <v>60.61</v>
+        <v>68.78</v>
       </c>
       <c r="I19" t="s">
         <v>49</v>
@@ -1150,16 +1153,16 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F20">
-        <v>56.3</v>
+        <v>52.67</v>
       </c>
       <c r="G20">
-        <v>60.43</v>
+        <v>60.45</v>
       </c>
       <c r="H20">
-        <v>64.20999999999999</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="I20" t="s">
         <v>49</v>
@@ -1170,7 +1173,7 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C21" t="s">
         <v>46</v>
@@ -1179,16 +1182,16 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F21">
-        <v>53.86</v>
+        <v>52.33</v>
       </c>
       <c r="G21">
-        <v>60.39</v>
+        <v>59.96</v>
       </c>
       <c r="H21">
-        <v>66.26000000000001</v>
+        <v>65.55</v>
       </c>
       <c r="I21" t="s">
         <v>49</v>
@@ -1211,13 +1214,13 @@
         <v>12</v>
       </c>
       <c r="F22">
-        <v>56.55</v>
+        <v>47.81</v>
       </c>
       <c r="G22">
-        <v>59.99</v>
+        <v>57.78</v>
       </c>
       <c r="H22">
-        <v>62.71</v>
+        <v>70.64</v>
       </c>
       <c r="I22" t="s">
         <v>49</v>
@@ -1237,16 +1240,16 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F23">
-        <v>51.27</v>
+        <v>47.81</v>
       </c>
       <c r="G23">
-        <v>59.83</v>
+        <v>57.78</v>
       </c>
       <c r="H23">
-        <v>65.91</v>
+        <v>73.31</v>
       </c>
       <c r="I23" t="s">
         <v>49</v>
@@ -1257,7 +1260,7 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C24" t="s">
         <v>46</v>
@@ -1266,16 +1269,16 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>65</v>
       </c>
       <c r="F24">
-        <v>52.12</v>
+        <v>47.73</v>
       </c>
       <c r="G24">
-        <v>59.3</v>
+        <v>57.47</v>
       </c>
       <c r="H24">
-        <v>66.59999999999999</v>
+        <v>70.88</v>
       </c>
       <c r="I24" t="s">
         <v>49</v>
@@ -1295,16 +1298,16 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="F25">
-        <v>53.95</v>
+        <v>46.56</v>
       </c>
       <c r="G25">
-        <v>58.48</v>
+        <v>57.03</v>
       </c>
       <c r="H25">
-        <v>63.14</v>
+        <v>70.88</v>
       </c>
       <c r="I25" t="s">
         <v>49</v>
@@ -1324,16 +1327,16 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="F26">
-        <v>41.8</v>
+        <v>51.99</v>
       </c>
       <c r="G26">
-        <v>57.76</v>
+        <v>56.73</v>
       </c>
       <c r="H26">
-        <v>68</v>
+        <v>63.35</v>
       </c>
       <c r="I26" t="s">
         <v>49</v>
@@ -1344,7 +1347,7 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
         <v>46</v>
@@ -1353,16 +1356,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F27">
-        <v>51.46</v>
+        <v>51.94</v>
       </c>
       <c r="G27">
-        <v>57.31</v>
+        <v>56.27</v>
       </c>
       <c r="H27">
-        <v>65.08</v>
+        <v>62.31</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1373,7 +1376,7 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C28" t="s">
         <v>46</v>
@@ -1382,16 +1385,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F28">
-        <v>51.89</v>
+        <v>52.43</v>
       </c>
       <c r="G28">
-        <v>57.22</v>
+        <v>56.23</v>
       </c>
       <c r="H28">
-        <v>61.62</v>
+        <v>59.77</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
@@ -1411,16 +1414,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>65</v>
+        <v>4</v>
       </c>
       <c r="F29">
-        <v>49.89</v>
+        <v>54.94</v>
       </c>
       <c r="G29">
-        <v>56.47</v>
+        <v>54.94</v>
       </c>
       <c r="H29">
-        <v>74.58</v>
+        <v>54.94</v>
       </c>
       <c r="I29" t="s">
         <v>49</v>
@@ -1431,7 +1434,7 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C30" t="s">
         <v>46</v>
@@ -1440,16 +1443,16 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="F30">
-        <v>52.51</v>
+        <v>51.98</v>
       </c>
       <c r="G30">
-        <v>56.43</v>
+        <v>54.47</v>
       </c>
       <c r="H30">
-        <v>60.31</v>
+        <v>58.68</v>
       </c>
       <c r="I30" t="s">
         <v>49</v>
@@ -1460,7 +1463,7 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C31" t="s">
         <v>46</v>
@@ -1469,16 +1472,16 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>117</v>
+        <v>12</v>
       </c>
       <c r="F31">
-        <v>49.89</v>
+        <v>47.23</v>
       </c>
       <c r="G31">
-        <v>56.08</v>
+        <v>53.6</v>
       </c>
       <c r="H31">
-        <v>74.58</v>
+        <v>61.97</v>
       </c>
       <c r="I31" t="s">
         <v>49</v>
@@ -1501,13 +1504,13 @@
         <v>10</v>
       </c>
       <c r="F32">
-        <v>50.49</v>
+        <v>48.51</v>
       </c>
       <c r="G32">
-        <v>55.03</v>
+        <v>51.27</v>
       </c>
       <c r="H32">
-        <v>60.86</v>
+        <v>54.96</v>
       </c>
       <c r="I32" t="s">
         <v>49</v>
@@ -1527,19 +1530,19 @@
         <v>47</v>
       </c>
       <c r="E33">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="F33">
-        <v>40.3</v>
+        <v>47.02</v>
       </c>
       <c r="G33">
-        <v>54.87</v>
+        <v>49.68</v>
       </c>
       <c r="H33">
-        <v>69.81999999999999</v>
+        <v>52.42</v>
       </c>
       <c r="I33" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1559,16 +1562,16 @@
         <v>2</v>
       </c>
       <c r="F34">
-        <v>52.78</v>
+        <v>49.31</v>
       </c>
       <c r="G34">
-        <v>52.78</v>
+        <v>49.31</v>
       </c>
       <c r="H34">
-        <v>52.78</v>
+        <v>49.31</v>
       </c>
       <c r="I34" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -1588,7 +1591,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -1608,7 +1611,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -46,102 +46,102 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه دراء</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بناب</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دالان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه هوا و</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع مل بلند</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه دراء</t>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده برم فیروز</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مزايجان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
   </si>
   <si>
     <t>منطقه شکار ممن.ع آق جلو</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع دالان</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
+    <t>منطقه شکار ممنوع کوه گورم</t>
   </si>
   <si>
     <t>منطقه حفاظت شده هرمود</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بناب</t>
+    <t>منطقه حفاظت شده بهرام گور</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع دره باغ</t>
   </si>
   <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>پارک ملي قطرويه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع توت سياه</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع بصيران</t>
   </si>
   <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه هوا و</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
-  </si>
-  <si>
-    <t>پارک ملي قطرويه</t>
-  </si>
-  <si>
     <t>پناهگاه حيات وحش دره باغ</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع خرمنکوه</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع شیکوه</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع مهارلو</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع شیکوه</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع کوهستان</t>
   </si>
   <si>
@@ -151,16 +151,16 @@
     <t>منطقه حفاظت شده مارگون</t>
   </si>
   <si>
+    <t>مناطق ممنوعه شکار</t>
+  </si>
+  <si>
     <t>مناطق حفاظت‌شده</t>
   </si>
   <si>
-    <t>مناطق ممنوعه شکار</t>
-  </si>
-  <si>
-    <t>1405-07-16</t>
-  </si>
-  <si>
-    <t>2026-10-08</t>
+    <t>1405-07-17</t>
+  </si>
+  <si>
+    <t>2026-10-09</t>
   </si>
   <si>
     <t>بسیار شدید</t>
@@ -631,16 +631,16 @@
         <v>47</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>64.31</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="G2">
-        <v>70.42</v>
+        <v>73.28</v>
       </c>
       <c r="H2">
-        <v>79.95999999999999</v>
+        <v>74.41</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -651,7 +651,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s">
         <v>46</v>
@@ -663,16 +663,16 @@
         <v>33</v>
       </c>
       <c r="F3">
-        <v>65.48999999999999</v>
+        <v>70.59</v>
       </c>
       <c r="G3">
-        <v>68.7</v>
+        <v>72.73</v>
       </c>
       <c r="H3">
-        <v>73.62</v>
+        <v>74.98</v>
       </c>
       <c r="I3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -680,7 +680,7 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C4" t="s">
         <v>46</v>
@@ -689,19 +689,19 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="F4">
-        <v>66.48999999999999</v>
+        <v>60.15</v>
       </c>
       <c r="G4">
-        <v>68.05</v>
+        <v>72.64</v>
       </c>
       <c r="H4">
-        <v>69.59999999999999</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="I4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -709,7 +709,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
         <v>46</v>
@@ -721,13 +721,13 @@
         <v>8</v>
       </c>
       <c r="F5">
-        <v>63.27</v>
+        <v>66.75</v>
       </c>
       <c r="G5">
-        <v>66.97</v>
+        <v>68.75</v>
       </c>
       <c r="H5">
-        <v>68.3</v>
+        <v>70.11</v>
       </c>
       <c r="I5" t="s">
         <v>49</v>
@@ -747,16 +747,16 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F6">
-        <v>62.1</v>
+        <v>60.82</v>
       </c>
       <c r="G6">
-        <v>66.65000000000001</v>
+        <v>67.69</v>
       </c>
       <c r="H6">
-        <v>72.23</v>
+        <v>74.7</v>
       </c>
       <c r="I6" t="s">
         <v>49</v>
@@ -767,7 +767,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
         <v>46</v>
@@ -779,13 +779,13 @@
         <v>5</v>
       </c>
       <c r="F7">
-        <v>60.85</v>
+        <v>61.09</v>
       </c>
       <c r="G7">
-        <v>66.45</v>
+        <v>67.37</v>
       </c>
       <c r="H7">
-        <v>69.8</v>
+        <v>70.56</v>
       </c>
       <c r="I7" t="s">
         <v>49</v>
@@ -805,16 +805,16 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F8">
-        <v>56.86</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="G8">
-        <v>66.01000000000001</v>
+        <v>67.06</v>
       </c>
       <c r="H8">
-        <v>74.67</v>
+        <v>68.56</v>
       </c>
       <c r="I8" t="s">
         <v>49</v>
@@ -834,16 +834,16 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F9">
-        <v>62.91</v>
+        <v>60.33</v>
       </c>
       <c r="G9">
-        <v>65.76000000000001</v>
+        <v>67</v>
       </c>
       <c r="H9">
-        <v>67.77</v>
+        <v>71.81</v>
       </c>
       <c r="I9" t="s">
         <v>49</v>
@@ -854,7 +854,7 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
         <v>46</v>
@@ -866,13 +866,13 @@
         <v>20</v>
       </c>
       <c r="F10">
-        <v>53.74</v>
+        <v>56.41</v>
       </c>
       <c r="G10">
-        <v>64.90000000000001</v>
+        <v>66.56</v>
       </c>
       <c r="H10">
-        <v>68.68000000000001</v>
+        <v>72.77</v>
       </c>
       <c r="I10" t="s">
         <v>49</v>
@@ -892,16 +892,16 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F11">
-        <v>57.4</v>
+        <v>59.27</v>
       </c>
       <c r="G11">
-        <v>64.44</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="H11">
-        <v>70.58</v>
+        <v>67.84</v>
       </c>
       <c r="I11" t="s">
         <v>49</v>
@@ -921,16 +921,16 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F12">
-        <v>57.84</v>
+        <v>58.02</v>
       </c>
       <c r="G12">
-        <v>63.92</v>
+        <v>63.48</v>
       </c>
       <c r="H12">
-        <v>73.04000000000001</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="I12" t="s">
         <v>49</v>
@@ -950,16 +950,16 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F13">
-        <v>59.16</v>
+        <v>57.37</v>
       </c>
       <c r="G13">
-        <v>63.41</v>
+        <v>63.09</v>
       </c>
       <c r="H13">
-        <v>65.03</v>
+        <v>71.8</v>
       </c>
       <c r="I13" t="s">
         <v>49</v>
@@ -979,16 +979,16 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F14">
-        <v>59.13</v>
+        <v>55.82</v>
       </c>
       <c r="G14">
-        <v>63.3</v>
+        <v>61.54</v>
       </c>
       <c r="H14">
-        <v>65.31999999999999</v>
+        <v>65.97</v>
       </c>
       <c r="I14" t="s">
         <v>49</v>
@@ -1008,16 +1008,16 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F15">
-        <v>55.37</v>
+        <v>54.39</v>
       </c>
       <c r="G15">
-        <v>63.14</v>
+        <v>61.15</v>
       </c>
       <c r="H15">
-        <v>69.48999999999999</v>
+        <v>64.27</v>
       </c>
       <c r="I15" t="s">
         <v>49</v>
@@ -1028,7 +1028,7 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
         <v>46</v>
@@ -1037,16 +1037,16 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F16">
-        <v>56.22</v>
+        <v>54.88</v>
       </c>
       <c r="G16">
-        <v>62.32</v>
+        <v>60.7</v>
       </c>
       <c r="H16">
-        <v>67.06</v>
+        <v>64.37</v>
       </c>
       <c r="I16" t="s">
         <v>49</v>
@@ -1057,7 +1057,7 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
         <v>46</v>
@@ -1069,13 +1069,13 @@
         <v>62</v>
       </c>
       <c r="F17">
-        <v>53.77</v>
+        <v>52.4</v>
       </c>
       <c r="G17">
-        <v>61.51</v>
+        <v>60.69</v>
       </c>
       <c r="H17">
-        <v>72.38</v>
+        <v>66.8</v>
       </c>
       <c r="I17" t="s">
         <v>49</v>
@@ -1095,16 +1095,16 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F18">
-        <v>58.67</v>
+        <v>53.76</v>
       </c>
       <c r="G18">
-        <v>61.35</v>
+        <v>60.48</v>
       </c>
       <c r="H18">
-        <v>64.79000000000001</v>
+        <v>66.25</v>
       </c>
       <c r="I18" t="s">
         <v>49</v>
@@ -1124,16 +1124,16 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F19">
-        <v>54.37</v>
+        <v>52.46</v>
       </c>
       <c r="G19">
-        <v>60.95</v>
+        <v>59.75</v>
       </c>
       <c r="H19">
-        <v>68.78</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="I19" t="s">
         <v>49</v>
@@ -1144,7 +1144,7 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C20" t="s">
         <v>46</v>
@@ -1153,16 +1153,16 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F20">
-        <v>52.67</v>
+        <v>58.26</v>
       </c>
       <c r="G20">
-        <v>60.45</v>
+        <v>58.39</v>
       </c>
       <c r="H20">
-        <v>66.43000000000001</v>
+        <v>58.51</v>
       </c>
       <c r="I20" t="s">
         <v>49</v>
@@ -1173,7 +1173,7 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C21" t="s">
         <v>46</v>
@@ -1185,13 +1185,13 @@
         <v>20</v>
       </c>
       <c r="F21">
-        <v>52.33</v>
+        <v>52.52</v>
       </c>
       <c r="G21">
-        <v>59.96</v>
+        <v>57.55</v>
       </c>
       <c r="H21">
-        <v>65.55</v>
+        <v>61.97</v>
       </c>
       <c r="I21" t="s">
         <v>49</v>
@@ -1211,16 +1211,16 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F22">
-        <v>47.81</v>
+        <v>55.84</v>
       </c>
       <c r="G22">
-        <v>57.78</v>
+        <v>57.43</v>
       </c>
       <c r="H22">
-        <v>70.64</v>
+        <v>60.64</v>
       </c>
       <c r="I22" t="s">
         <v>49</v>
@@ -1240,16 +1240,16 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F23">
-        <v>47.81</v>
+        <v>52.46</v>
       </c>
       <c r="G23">
-        <v>57.78</v>
+        <v>55.58</v>
       </c>
       <c r="H23">
-        <v>73.31</v>
+        <v>60.46</v>
       </c>
       <c r="I23" t="s">
         <v>49</v>
@@ -1269,16 +1269,16 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="F24">
-        <v>47.73</v>
+        <v>49.01</v>
       </c>
       <c r="G24">
-        <v>57.47</v>
+        <v>55.18</v>
       </c>
       <c r="H24">
-        <v>70.88</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="I24" t="s">
         <v>49</v>
@@ -1289,7 +1289,7 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C25" t="s">
         <v>46</v>
@@ -1301,13 +1301,13 @@
         <v>117</v>
       </c>
       <c r="F25">
-        <v>46.56</v>
+        <v>48.51</v>
       </c>
       <c r="G25">
-        <v>57.03</v>
+        <v>54.31</v>
       </c>
       <c r="H25">
-        <v>70.88</v>
+        <v>63.01</v>
       </c>
       <c r="I25" t="s">
         <v>49</v>
@@ -1327,16 +1327,16 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="F26">
-        <v>51.99</v>
+        <v>48.87</v>
       </c>
       <c r="G26">
-        <v>56.73</v>
+        <v>54.17</v>
       </c>
       <c r="H26">
-        <v>63.35</v>
+        <v>63.01</v>
       </c>
       <c r="I26" t="s">
         <v>49</v>
@@ -1347,7 +1347,7 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
         <v>46</v>
@@ -1356,16 +1356,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F27">
-        <v>51.94</v>
+        <v>53.78</v>
       </c>
       <c r="G27">
-        <v>56.27</v>
+        <v>53.78</v>
       </c>
       <c r="H27">
-        <v>62.31</v>
+        <v>53.78</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1376,7 +1376,7 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C28" t="s">
         <v>46</v>
@@ -1388,13 +1388,13 @@
         <v>4</v>
       </c>
       <c r="F28">
-        <v>52.43</v>
+        <v>51.88</v>
       </c>
       <c r="G28">
-        <v>56.23</v>
+        <v>53.77</v>
       </c>
       <c r="H28">
-        <v>59.77</v>
+        <v>55.22</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
@@ -1414,16 +1414,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="F29">
-        <v>54.94</v>
+        <v>42.85</v>
       </c>
       <c r="G29">
-        <v>54.94</v>
+        <v>53.45</v>
       </c>
       <c r="H29">
-        <v>54.94</v>
+        <v>75.3</v>
       </c>
       <c r="I29" t="s">
         <v>49</v>
@@ -1434,7 +1434,7 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C30" t="s">
         <v>46</v>
@@ -1446,13 +1446,13 @@
         <v>3</v>
       </c>
       <c r="F30">
-        <v>51.98</v>
+        <v>49.01</v>
       </c>
       <c r="G30">
-        <v>54.47</v>
+        <v>52.78</v>
       </c>
       <c r="H30">
-        <v>58.68</v>
+        <v>55.34</v>
       </c>
       <c r="I30" t="s">
         <v>49</v>
@@ -1463,7 +1463,7 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C31" t="s">
         <v>46</v>
@@ -1475,13 +1475,13 @@
         <v>12</v>
       </c>
       <c r="F31">
-        <v>47.23</v>
+        <v>49.4</v>
       </c>
       <c r="G31">
-        <v>53.6</v>
+        <v>52.6</v>
       </c>
       <c r="H31">
-        <v>61.97</v>
+        <v>59.61</v>
       </c>
       <c r="I31" t="s">
         <v>49</v>
@@ -1492,7 +1492,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C32" t="s">
         <v>46</v>
@@ -1501,16 +1501,16 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F32">
-        <v>48.51</v>
+        <v>46.17</v>
       </c>
       <c r="G32">
-        <v>51.27</v>
+        <v>51.75</v>
       </c>
       <c r="H32">
-        <v>54.96</v>
+        <v>59.74</v>
       </c>
       <c r="I32" t="s">
         <v>49</v>
@@ -1521,7 +1521,7 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C33" t="s">
         <v>46</v>
@@ -1530,19 +1530,19 @@
         <v>47</v>
       </c>
       <c r="E33">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F33">
-        <v>47.02</v>
+        <v>49.62</v>
       </c>
       <c r="G33">
-        <v>49.68</v>
+        <v>51.46</v>
       </c>
       <c r="H33">
-        <v>52.42</v>
+        <v>54.28</v>
       </c>
       <c r="I33" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1550,7 +1550,7 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C34" t="s">
         <v>46</v>
@@ -1562,13 +1562,13 @@
         <v>2</v>
       </c>
       <c r="F34">
-        <v>49.31</v>
+        <v>48.57</v>
       </c>
       <c r="G34">
-        <v>49.31</v>
+        <v>48.57</v>
       </c>
       <c r="H34">
-        <v>49.31</v>
+        <v>48.57</v>
       </c>
       <c r="I34" t="s">
         <v>50</v>
@@ -1579,7 +1579,7 @@
         <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C35" t="s">
         <v>46</v>
@@ -1599,7 +1599,7 @@
         <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C36" t="s">
         <v>46</v>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="51">
   <si>
     <t>نام منطقه</t>
   </si>
@@ -46,130 +46,127 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع مزايجان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بناب</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه دراء</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوهستان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دالان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه هوا و</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع توت سياه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>پارک ملي قطرويه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
     <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه دراء</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بناب</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دالان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه هوا و</t>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده هرمود</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده برم فیروز</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش دره باغ</t>
+  </si>
+  <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مهارلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بصيران</t>
   </si>
   <si>
     <t>منطقه حفاظت شده تنگ بستانک</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده هرمود</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>پارک ملي قطرويه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بصيران</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع شیکوه</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوهستان</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع چاه نفت</t>
   </si>
   <si>
     <t>منطقه حفاظت شده مارگون</t>
   </si>
   <si>
+    <t>مناطق حفاظت‌شده</t>
+  </si>
+  <si>
     <t>مناطق ممنوعه شکار</t>
   </si>
   <si>
-    <t>مناطق حفاظت‌شده</t>
-  </si>
-  <si>
-    <t>1405-07-17</t>
-  </si>
-  <si>
-    <t>2026-10-09</t>
+    <t>1405-07-18</t>
+  </si>
+  <si>
+    <t>2026-10-10</t>
   </si>
   <si>
     <t>بسیار شدید</t>
   </si>
   <si>
     <t>شدید</t>
-  </si>
-  <si>
-    <t>خیلی زیاد</t>
   </si>
   <si>
     <t>بدون داده</t>
@@ -631,16 +628,16 @@
         <v>47</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>71.34999999999999</v>
+        <v>81</v>
       </c>
       <c r="G2">
-        <v>73.28</v>
+        <v>85.19</v>
       </c>
       <c r="H2">
-        <v>74.41</v>
+        <v>88.75</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -651,7 +648,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C3" t="s">
         <v>46</v>
@@ -660,16 +657,16 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F3">
-        <v>70.59</v>
+        <v>75.22</v>
       </c>
       <c r="G3">
-        <v>72.73</v>
+        <v>82.12</v>
       </c>
       <c r="H3">
-        <v>74.98</v>
+        <v>86.8</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -680,7 +677,7 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C4" t="s">
         <v>46</v>
@@ -689,16 +686,16 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F4">
-        <v>60.15</v>
+        <v>74.2</v>
       </c>
       <c r="G4">
-        <v>72.64</v>
+        <v>78.29000000000001</v>
       </c>
       <c r="H4">
-        <v>78.56999999999999</v>
+        <v>82.23</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -709,7 +706,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
         <v>46</v>
@@ -718,19 +715,19 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>66.75</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="G5">
-        <v>68.75</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="H5">
-        <v>70.11</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="I5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -738,7 +735,7 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
         <v>46</v>
@@ -747,19 +744,19 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>60.82</v>
+        <v>69.17</v>
       </c>
       <c r="G6">
-        <v>67.69</v>
+        <v>73</v>
       </c>
       <c r="H6">
-        <v>74.7</v>
+        <v>75.17</v>
       </c>
       <c r="I6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -776,19 +773,19 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="F7">
-        <v>61.09</v>
+        <v>57.12</v>
       </c>
       <c r="G7">
-        <v>67.37</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="H7">
-        <v>70.56</v>
+        <v>86.58</v>
       </c>
       <c r="I7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -796,7 +793,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
         <v>46</v>
@@ -805,19 +802,19 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F8">
-        <v>64.51000000000001</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="G8">
-        <v>67.06</v>
+        <v>71.01000000000001</v>
       </c>
       <c r="H8">
-        <v>68.56</v>
+        <v>75.84</v>
       </c>
       <c r="I8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -834,16 +831,16 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F9">
-        <v>60.33</v>
+        <v>60.51</v>
       </c>
       <c r="G9">
-        <v>67</v>
+        <v>69.20999999999999</v>
       </c>
       <c r="H9">
-        <v>71.81</v>
+        <v>84.92</v>
       </c>
       <c r="I9" t="s">
         <v>49</v>
@@ -863,16 +860,16 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F10">
-        <v>56.41</v>
+        <v>62.93</v>
       </c>
       <c r="G10">
-        <v>66.56</v>
+        <v>67.59</v>
       </c>
       <c r="H10">
-        <v>72.77</v>
+        <v>69.7</v>
       </c>
       <c r="I10" t="s">
         <v>49</v>
@@ -892,16 +889,16 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F11">
-        <v>59.27</v>
+        <v>63.32</v>
       </c>
       <c r="G11">
-        <v>65.18000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="H11">
-        <v>67.84</v>
+        <v>69.73999999999999</v>
       </c>
       <c r="I11" t="s">
         <v>49</v>
@@ -912,7 +909,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
         <v>46</v>
@@ -924,13 +921,13 @@
         <v>20</v>
       </c>
       <c r="F12">
-        <v>58.02</v>
+        <v>59.93</v>
       </c>
       <c r="G12">
-        <v>63.48</v>
+        <v>66.52</v>
       </c>
       <c r="H12">
-        <v>67.56999999999999</v>
+        <v>71.03</v>
       </c>
       <c r="I12" t="s">
         <v>49</v>
@@ -950,16 +947,16 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F13">
-        <v>57.37</v>
+        <v>57.96</v>
       </c>
       <c r="G13">
-        <v>63.09</v>
+        <v>66.5</v>
       </c>
       <c r="H13">
-        <v>71.8</v>
+        <v>74.81999999999999</v>
       </c>
       <c r="I13" t="s">
         <v>49</v>
@@ -970,7 +967,7 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
         <v>46</v>
@@ -979,16 +976,16 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F14">
-        <v>55.82</v>
+        <v>66.14</v>
       </c>
       <c r="G14">
-        <v>61.54</v>
+        <v>66.14</v>
       </c>
       <c r="H14">
-        <v>65.97</v>
+        <v>66.14</v>
       </c>
       <c r="I14" t="s">
         <v>49</v>
@@ -999,7 +996,7 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s">
         <v>46</v>
@@ -1008,16 +1005,16 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F15">
-        <v>54.39</v>
+        <v>59.37</v>
       </c>
       <c r="G15">
-        <v>61.15</v>
+        <v>65.14</v>
       </c>
       <c r="H15">
-        <v>64.27</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="I15" t="s">
         <v>49</v>
@@ -1037,16 +1034,16 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="F16">
-        <v>54.88</v>
+        <v>63.38</v>
       </c>
       <c r="G16">
-        <v>60.7</v>
+        <v>65.09</v>
       </c>
       <c r="H16">
-        <v>64.37</v>
+        <v>68.39</v>
       </c>
       <c r="I16" t="s">
         <v>49</v>
@@ -1057,7 +1054,7 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C17" t="s">
         <v>46</v>
@@ -1066,16 +1063,16 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="F17">
-        <v>52.4</v>
+        <v>61.78</v>
       </c>
       <c r="G17">
-        <v>60.69</v>
+        <v>64.41</v>
       </c>
       <c r="H17">
-        <v>66.8</v>
+        <v>68.03</v>
       </c>
       <c r="I17" t="s">
         <v>49</v>
@@ -1086,7 +1083,7 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C18" t="s">
         <v>46</v>
@@ -1095,16 +1092,16 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F18">
-        <v>53.76</v>
+        <v>56.9</v>
       </c>
       <c r="G18">
-        <v>60.48</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="H18">
-        <v>66.25</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="I18" t="s">
         <v>49</v>
@@ -1124,16 +1121,16 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F19">
-        <v>52.46</v>
+        <v>61.97</v>
       </c>
       <c r="G19">
-        <v>59.75</v>
+        <v>64.15000000000001</v>
       </c>
       <c r="H19">
-        <v>64.18000000000001</v>
+        <v>67.44</v>
       </c>
       <c r="I19" t="s">
         <v>49</v>
@@ -1153,16 +1150,16 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F20">
-        <v>58.26</v>
+        <v>55.99</v>
       </c>
       <c r="G20">
-        <v>58.39</v>
+        <v>62.04</v>
       </c>
       <c r="H20">
-        <v>58.51</v>
+        <v>70.06</v>
       </c>
       <c r="I20" t="s">
         <v>49</v>
@@ -1173,7 +1170,7 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C21" t="s">
         <v>46</v>
@@ -1182,16 +1179,16 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F21">
-        <v>52.52</v>
+        <v>58.22</v>
       </c>
       <c r="G21">
-        <v>57.55</v>
+        <v>61.65</v>
       </c>
       <c r="H21">
-        <v>61.97</v>
+        <v>63.88</v>
       </c>
       <c r="I21" t="s">
         <v>49</v>
@@ -1211,16 +1208,16 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F22">
-        <v>55.84</v>
+        <v>58.46</v>
       </c>
       <c r="G22">
-        <v>57.43</v>
+        <v>61.14</v>
       </c>
       <c r="H22">
-        <v>60.64</v>
+        <v>63.83</v>
       </c>
       <c r="I22" t="s">
         <v>49</v>
@@ -1231,7 +1228,7 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C23" t="s">
         <v>46</v>
@@ -1240,16 +1237,16 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F23">
-        <v>52.46</v>
+        <v>53.21</v>
       </c>
       <c r="G23">
-        <v>55.58</v>
+        <v>60.76</v>
       </c>
       <c r="H23">
-        <v>60.46</v>
+        <v>71.88</v>
       </c>
       <c r="I23" t="s">
         <v>49</v>
@@ -1260,7 +1257,7 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C24" t="s">
         <v>46</v>
@@ -1269,16 +1266,16 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="F24">
-        <v>49.01</v>
+        <v>50.99</v>
       </c>
       <c r="G24">
-        <v>55.18</v>
+        <v>60.73</v>
       </c>
       <c r="H24">
-        <v>65.68000000000001</v>
+        <v>73.45</v>
       </c>
       <c r="I24" t="s">
         <v>49</v>
@@ -1289,7 +1286,7 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C25" t="s">
         <v>46</v>
@@ -1301,13 +1298,13 @@
         <v>117</v>
       </c>
       <c r="F25">
-        <v>48.51</v>
+        <v>50.02</v>
       </c>
       <c r="G25">
-        <v>54.31</v>
+        <v>60.64</v>
       </c>
       <c r="H25">
-        <v>63.01</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="I25" t="s">
         <v>49</v>
@@ -1318,7 +1315,7 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C26" t="s">
         <v>46</v>
@@ -1330,13 +1327,13 @@
         <v>65</v>
       </c>
       <c r="F26">
-        <v>48.87</v>
+        <v>51.17</v>
       </c>
       <c r="G26">
-        <v>54.17</v>
+        <v>60.28</v>
       </c>
       <c r="H26">
-        <v>63.01</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="I26" t="s">
         <v>49</v>
@@ -1356,16 +1353,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F27">
-        <v>53.78</v>
+        <v>49.12</v>
       </c>
       <c r="G27">
-        <v>53.78</v>
+        <v>59.56</v>
       </c>
       <c r="H27">
-        <v>53.78</v>
+        <v>69.09</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1385,16 +1382,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F28">
-        <v>51.88</v>
+        <v>51.92</v>
       </c>
       <c r="G28">
-        <v>53.77</v>
+        <v>59.17</v>
       </c>
       <c r="H28">
-        <v>55.22</v>
+        <v>66.8</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
@@ -1414,16 +1411,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="F29">
-        <v>42.85</v>
+        <v>54.04</v>
       </c>
       <c r="G29">
-        <v>53.45</v>
+        <v>58.84</v>
       </c>
       <c r="H29">
-        <v>75.3</v>
+        <v>62.24</v>
       </c>
       <c r="I29" t="s">
         <v>49</v>
@@ -1434,7 +1431,7 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C30" t="s">
         <v>46</v>
@@ -1443,16 +1440,16 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="F30">
-        <v>49.01</v>
+        <v>52.04</v>
       </c>
       <c r="G30">
-        <v>52.78</v>
+        <v>57.07</v>
       </c>
       <c r="H30">
-        <v>55.34</v>
+        <v>63.18</v>
       </c>
       <c r="I30" t="s">
         <v>49</v>
@@ -1463,7 +1460,7 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C31" t="s">
         <v>46</v>
@@ -1472,16 +1469,16 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F31">
-        <v>49.4</v>
+        <v>53.36</v>
       </c>
       <c r="G31">
-        <v>52.6</v>
+        <v>56.63</v>
       </c>
       <c r="H31">
-        <v>59.61</v>
+        <v>64.91</v>
       </c>
       <c r="I31" t="s">
         <v>49</v>
@@ -1492,7 +1489,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C32" t="s">
         <v>46</v>
@@ -1501,16 +1498,16 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="F32">
-        <v>46.17</v>
+        <v>48.87</v>
       </c>
       <c r="G32">
-        <v>51.75</v>
+        <v>56.32</v>
       </c>
       <c r="H32">
-        <v>59.74</v>
+        <v>68.42</v>
       </c>
       <c r="I32" t="s">
         <v>49</v>
@@ -1530,16 +1527,16 @@
         <v>47</v>
       </c>
       <c r="E33">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F33">
-        <v>49.62</v>
+        <v>51.44</v>
       </c>
       <c r="G33">
-        <v>51.46</v>
+        <v>55.82</v>
       </c>
       <c r="H33">
-        <v>54.28</v>
+        <v>59.79</v>
       </c>
       <c r="I33" t="s">
         <v>49</v>
@@ -1550,7 +1547,7 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C34" t="s">
         <v>46</v>
@@ -1559,19 +1556,19 @@
         <v>47</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F34">
-        <v>48.57</v>
+        <v>48.39</v>
       </c>
       <c r="G34">
-        <v>48.57</v>
+        <v>51.42</v>
       </c>
       <c r="H34">
-        <v>48.57</v>
+        <v>54.23</v>
       </c>
       <c r="I34" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -1579,7 +1576,7 @@
         <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C35" t="s">
         <v>46</v>
@@ -1591,7 +1588,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -1599,7 +1596,7 @@
         <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C36" t="s">
         <v>46</v>
@@ -1611,7 +1608,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -46,102 +46,102 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع کوه دراء</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دالان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوهستان</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع مزايجان</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع کوه هوا و</t>
+  </si>
+  <si>
+    <t>پارک ملي قطرويه</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع بناب</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه دراء</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوهستان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دالان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه هوا و</t>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
   </si>
   <si>
     <t>منطقه حفاظت شده ارژن و پريشان</t>
   </si>
   <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
+  </si>
+  <si>
     <t>منطقه حفاظت شده بهرام گور</t>
   </si>
   <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده هرمود</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش دره باغ</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع توت سياه</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>پارک ملي قطرويه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده هرمود</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
+    <t>پارک ملي بختگان</t>
   </si>
   <si>
     <t>پناهگاه حيات وحش بختگان</t>
   </si>
   <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
+    <t>منطقه شکار ممنوع بصيران</t>
   </si>
   <si>
     <t>منطقه حفاظت شده برم فیروز</t>
   </si>
   <si>
-    <t>پناهگاه حيات وحش دره باغ</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع مهارلو</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع بصيران</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع شیکوه</t>
   </si>
   <si>
@@ -157,10 +157,10 @@
     <t>مناطق ممنوعه شکار</t>
   </si>
   <si>
-    <t>1405-07-18</t>
-  </si>
-  <si>
-    <t>2026-10-10</t>
+    <t>1405-07-19</t>
+  </si>
+  <si>
+    <t>2026-10-11</t>
   </si>
   <si>
     <t>بسیار شدید</t>
@@ -628,16 +628,16 @@
         <v>47</v>
       </c>
       <c r="E2">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="F2">
-        <v>81</v>
+        <v>72.36</v>
       </c>
       <c r="G2">
-        <v>85.19</v>
+        <v>76.34</v>
       </c>
       <c r="H2">
-        <v>88.75</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -657,16 +657,16 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>75.22</v>
+        <v>72.70999999999999</v>
       </c>
       <c r="G3">
-        <v>82.12</v>
+        <v>74.95</v>
       </c>
       <c r="H3">
-        <v>86.8</v>
+        <v>79.34</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -686,16 +686,16 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>74.2</v>
+        <v>71.16</v>
       </c>
       <c r="G4">
-        <v>78.29000000000001</v>
+        <v>71.16</v>
       </c>
       <c r="H4">
-        <v>82.23</v>
+        <v>71.16</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -715,19 +715,19 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F5">
-        <v>74.04000000000001</v>
+        <v>62.05</v>
       </c>
       <c r="G5">
-        <v>74.04000000000001</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="H5">
-        <v>74.04000000000001</v>
+        <v>71.03</v>
       </c>
       <c r="I5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -744,19 +744,19 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="F6">
-        <v>69.17</v>
+        <v>57.92</v>
       </c>
       <c r="G6">
-        <v>73</v>
+        <v>65.2</v>
       </c>
       <c r="H6">
-        <v>75.17</v>
+        <v>70.45</v>
       </c>
       <c r="I6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -764,7 +764,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
         <v>46</v>
@@ -773,19 +773,19 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>57.12</v>
+        <v>64.69</v>
       </c>
       <c r="G7">
-        <v>72.09999999999999</v>
+        <v>64.69</v>
       </c>
       <c r="H7">
-        <v>86.58</v>
+        <v>64.69</v>
       </c>
       <c r="I7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -793,7 +793,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C8" t="s">
         <v>46</v>
@@ -805,16 +805,16 @@
         <v>20</v>
       </c>
       <c r="F8">
-        <v>66.84999999999999</v>
+        <v>59.22</v>
       </c>
       <c r="G8">
-        <v>71.01000000000001</v>
+        <v>64.33</v>
       </c>
       <c r="H8">
-        <v>75.84</v>
+        <v>68.77</v>
       </c>
       <c r="I8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -822,7 +822,7 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
         <v>46</v>
@@ -831,16 +831,16 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="F9">
-        <v>60.51</v>
+        <v>60.04</v>
       </c>
       <c r="G9">
-        <v>69.20999999999999</v>
+        <v>64.06</v>
       </c>
       <c r="H9">
-        <v>84.92</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="I9" t="s">
         <v>49</v>
@@ -860,16 +860,16 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F10">
-        <v>62.93</v>
+        <v>59.51</v>
       </c>
       <c r="G10">
-        <v>67.59</v>
+        <v>63.44</v>
       </c>
       <c r="H10">
-        <v>69.7</v>
+        <v>68.66</v>
       </c>
       <c r="I10" t="s">
         <v>49</v>
@@ -892,13 +892,13 @@
         <v>12</v>
       </c>
       <c r="F11">
-        <v>63.32</v>
+        <v>57.61</v>
       </c>
       <c r="G11">
-        <v>66.67</v>
+        <v>63.12</v>
       </c>
       <c r="H11">
-        <v>69.73999999999999</v>
+        <v>68.39</v>
       </c>
       <c r="I11" t="s">
         <v>49</v>
@@ -918,16 +918,16 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F12">
-        <v>59.93</v>
+        <v>57.61</v>
       </c>
       <c r="G12">
-        <v>66.52</v>
+        <v>62.54</v>
       </c>
       <c r="H12">
-        <v>71.03</v>
+        <v>69.56</v>
       </c>
       <c r="I12" t="s">
         <v>49</v>
@@ -947,16 +947,16 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F13">
-        <v>57.96</v>
+        <v>57.48</v>
       </c>
       <c r="G13">
-        <v>66.5</v>
+        <v>62.54</v>
       </c>
       <c r="H13">
-        <v>74.81999999999999</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="I13" t="s">
         <v>49</v>
@@ -976,16 +976,16 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F14">
-        <v>66.14</v>
+        <v>55.28</v>
       </c>
       <c r="G14">
-        <v>66.14</v>
+        <v>61.69</v>
       </c>
       <c r="H14">
-        <v>66.14</v>
+        <v>68.89</v>
       </c>
       <c r="I14" t="s">
         <v>49</v>
@@ -1005,16 +1005,16 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F15">
-        <v>59.37</v>
+        <v>59.97</v>
       </c>
       <c r="G15">
-        <v>65.14</v>
+        <v>60.89</v>
       </c>
       <c r="H15">
-        <v>72.18000000000001</v>
+        <v>61.8</v>
       </c>
       <c r="I15" t="s">
         <v>49</v>
@@ -1034,16 +1034,16 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="F16">
-        <v>63.38</v>
+        <v>47.9</v>
       </c>
       <c r="G16">
-        <v>65.09</v>
+        <v>60.62</v>
       </c>
       <c r="H16">
-        <v>68.39</v>
+        <v>78.56</v>
       </c>
       <c r="I16" t="s">
         <v>49</v>
@@ -1054,7 +1054,7 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
         <v>46</v>
@@ -1063,16 +1063,16 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F17">
-        <v>61.78</v>
+        <v>54.18</v>
       </c>
       <c r="G17">
-        <v>64.41</v>
+        <v>60.16</v>
       </c>
       <c r="H17">
-        <v>68.03</v>
+        <v>63.62</v>
       </c>
       <c r="I17" t="s">
         <v>49</v>
@@ -1092,16 +1092,16 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F18">
-        <v>56.9</v>
+        <v>53.48</v>
       </c>
       <c r="G18">
-        <v>64.26000000000001</v>
+        <v>59.63</v>
       </c>
       <c r="H18">
-        <v>67.84999999999999</v>
+        <v>62.55</v>
       </c>
       <c r="I18" t="s">
         <v>49</v>
@@ -1112,7 +1112,7 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
         <v>46</v>
@@ -1121,16 +1121,16 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F19">
-        <v>61.97</v>
+        <v>55.06</v>
       </c>
       <c r="G19">
-        <v>64.15000000000001</v>
+        <v>59.55</v>
       </c>
       <c r="H19">
-        <v>67.44</v>
+        <v>63.28</v>
       </c>
       <c r="I19" t="s">
         <v>49</v>
@@ -1141,7 +1141,7 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C20" t="s">
         <v>46</v>
@@ -1150,16 +1150,16 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F20">
-        <v>55.99</v>
+        <v>54.5</v>
       </c>
       <c r="G20">
-        <v>62.04</v>
+        <v>59.54</v>
       </c>
       <c r="H20">
-        <v>70.06</v>
+        <v>65.92</v>
       </c>
       <c r="I20" t="s">
         <v>49</v>
@@ -1170,7 +1170,7 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C21" t="s">
         <v>46</v>
@@ -1179,16 +1179,16 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F21">
-        <v>58.22</v>
+        <v>55.91</v>
       </c>
       <c r="G21">
-        <v>61.65</v>
+        <v>58.56</v>
       </c>
       <c r="H21">
-        <v>63.88</v>
+        <v>60.1</v>
       </c>
       <c r="I21" t="s">
         <v>49</v>
@@ -1199,7 +1199,7 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C22" t="s">
         <v>46</v>
@@ -1208,16 +1208,16 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F22">
+        <v>53.79</v>
+      </c>
+      <c r="G22">
         <v>58.46</v>
       </c>
-      <c r="G22">
-        <v>61.14</v>
-      </c>
       <c r="H22">
-        <v>63.83</v>
+        <v>62.62</v>
       </c>
       <c r="I22" t="s">
         <v>49</v>
@@ -1228,7 +1228,7 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C23" t="s">
         <v>46</v>
@@ -1237,16 +1237,16 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>9</v>
+        <v>62</v>
       </c>
       <c r="F23">
-        <v>53.21</v>
+        <v>50.81</v>
       </c>
       <c r="G23">
-        <v>60.76</v>
+        <v>57.86</v>
       </c>
       <c r="H23">
-        <v>71.88</v>
+        <v>67.33</v>
       </c>
       <c r="I23" t="s">
         <v>49</v>
@@ -1257,7 +1257,7 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C24" t="s">
         <v>46</v>
@@ -1266,16 +1266,16 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>62</v>
+        <v>5</v>
       </c>
       <c r="F24">
-        <v>50.99</v>
+        <v>52.77</v>
       </c>
       <c r="G24">
-        <v>60.73</v>
+        <v>57.02</v>
       </c>
       <c r="H24">
-        <v>73.45</v>
+        <v>60.51</v>
       </c>
       <c r="I24" t="s">
         <v>49</v>
@@ -1286,7 +1286,7 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C25" t="s">
         <v>46</v>
@@ -1295,16 +1295,16 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>117</v>
+        <v>12</v>
       </c>
       <c r="F25">
-        <v>50.02</v>
+        <v>49.11</v>
       </c>
       <c r="G25">
-        <v>60.64</v>
+        <v>56.58</v>
       </c>
       <c r="H25">
-        <v>71.90000000000001</v>
+        <v>62.33</v>
       </c>
       <c r="I25" t="s">
         <v>49</v>
@@ -1315,7 +1315,7 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s">
         <v>46</v>
@@ -1324,16 +1324,16 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="F26">
-        <v>51.17</v>
+        <v>48.63</v>
       </c>
       <c r="G26">
-        <v>60.28</v>
+        <v>56.16</v>
       </c>
       <c r="H26">
-        <v>71.90000000000001</v>
+        <v>63.95</v>
       </c>
       <c r="I26" t="s">
         <v>49</v>
@@ -1344,7 +1344,7 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
         <v>46</v>
@@ -1353,16 +1353,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F27">
-        <v>49.12</v>
+        <v>53.45</v>
       </c>
       <c r="G27">
-        <v>59.56</v>
+        <v>55.97</v>
       </c>
       <c r="H27">
-        <v>69.09</v>
+        <v>59.64</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1373,7 +1373,7 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C28" t="s">
         <v>46</v>
@@ -1382,16 +1382,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F28">
-        <v>51.92</v>
+        <v>55.29</v>
       </c>
       <c r="G28">
-        <v>59.17</v>
+        <v>55.9</v>
       </c>
       <c r="H28">
-        <v>66.8</v>
+        <v>56.7</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
@@ -1411,16 +1411,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>65</v>
       </c>
       <c r="F29">
-        <v>54.04</v>
+        <v>49.5</v>
       </c>
       <c r="G29">
-        <v>58.84</v>
+        <v>54.8</v>
       </c>
       <c r="H29">
-        <v>62.24</v>
+        <v>70.36</v>
       </c>
       <c r="I29" t="s">
         <v>49</v>
@@ -1440,16 +1440,16 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>19</v>
+        <v>117</v>
       </c>
       <c r="F30">
-        <v>52.04</v>
+        <v>46.67</v>
       </c>
       <c r="G30">
-        <v>57.07</v>
+        <v>54.4</v>
       </c>
       <c r="H30">
-        <v>63.18</v>
+        <v>70.36</v>
       </c>
       <c r="I30" t="s">
         <v>49</v>
@@ -1469,16 +1469,16 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F31">
-        <v>53.36</v>
+        <v>50.22</v>
       </c>
       <c r="G31">
-        <v>56.63</v>
+        <v>53.54</v>
       </c>
       <c r="H31">
-        <v>64.91</v>
+        <v>65.84</v>
       </c>
       <c r="I31" t="s">
         <v>49</v>
@@ -1489,7 +1489,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C32" t="s">
         <v>46</v>
@@ -1498,16 +1498,16 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="F32">
-        <v>48.87</v>
+        <v>46.32</v>
       </c>
       <c r="G32">
-        <v>56.32</v>
+        <v>52.06</v>
       </c>
       <c r="H32">
-        <v>68.42</v>
+        <v>60.51</v>
       </c>
       <c r="I32" t="s">
         <v>49</v>
@@ -1518,7 +1518,7 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C33" t="s">
         <v>46</v>
@@ -1527,16 +1527,16 @@
         <v>47</v>
       </c>
       <c r="E33">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F33">
-        <v>51.44</v>
+        <v>47.67</v>
       </c>
       <c r="G33">
-        <v>55.82</v>
+        <v>50.4</v>
       </c>
       <c r="H33">
-        <v>59.79</v>
+        <v>55.86</v>
       </c>
       <c r="I33" t="s">
         <v>49</v>
@@ -1559,13 +1559,13 @@
         <v>3</v>
       </c>
       <c r="F34">
-        <v>48.39</v>
+        <v>49.02</v>
       </c>
       <c r="G34">
-        <v>51.42</v>
+        <v>50.03</v>
       </c>
       <c r="H34">
-        <v>54.23</v>
+        <v>51.71</v>
       </c>
       <c r="I34" t="s">
         <v>49</v>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="52">
   <si>
     <t>نام منطقه</t>
   </si>
@@ -46,105 +46,105 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع کوه دراء</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع دالان</t>
   </si>
   <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع کوهستان</t>
   </si>
   <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بناب</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>پارک ملي قطرويه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع مزايجان</t>
   </si>
   <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده برم فیروز</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع توت سياه</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع کوه هوا و</t>
   </si>
   <si>
-    <t>پارک ملي قطرويه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بناب</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
+    <t>منطقه شکار ممنوع شیکوه</t>
   </si>
   <si>
     <t>منطقه حفاظت شده هرمود</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع دره باغ</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع مهارلو</t>
+  </si>
+  <si>
     <t>پناهگاه حيات وحش دره باغ</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع بصيران</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع شیکوه</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع چاه نفت</t>
   </si>
   <si>
@@ -157,16 +157,19 @@
     <t>مناطق ممنوعه شکار</t>
   </si>
   <si>
-    <t>1405-07-19</t>
-  </si>
-  <si>
-    <t>2026-10-11</t>
+    <t>1405-07-20</t>
+  </si>
+  <si>
+    <t>2026-10-12</t>
   </si>
   <si>
     <t>بسیار شدید</t>
   </si>
   <si>
     <t>شدید</t>
+  </si>
+  <si>
+    <t>خیلی زیاد</t>
   </si>
   <si>
     <t>بدون داده</t>
@@ -628,16 +631,16 @@
         <v>47</v>
       </c>
       <c r="E2">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>72.36</v>
+        <v>64.97</v>
       </c>
       <c r="G2">
-        <v>76.34</v>
+        <v>71.8</v>
       </c>
       <c r="H2">
-        <v>81.81999999999999</v>
+        <v>76.55</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -648,7 +651,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s">
         <v>46</v>
@@ -657,19 +660,19 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F3">
-        <v>72.70999999999999</v>
+        <v>58.16</v>
       </c>
       <c r="G3">
-        <v>74.95</v>
+        <v>67.05</v>
       </c>
       <c r="H3">
-        <v>79.34</v>
+        <v>68.86</v>
       </c>
       <c r="I3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -686,19 +689,19 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="F4">
-        <v>71.16</v>
+        <v>63.1</v>
       </c>
       <c r="G4">
-        <v>71.16</v>
+        <v>66.17</v>
       </c>
       <c r="H4">
-        <v>71.16</v>
+        <v>71.77</v>
       </c>
       <c r="I4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -715,16 +718,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>62.05</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="G5">
-        <v>65.31999999999999</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="H5">
-        <v>71.03</v>
+        <v>65.86</v>
       </c>
       <c r="I5" t="s">
         <v>49</v>
@@ -735,7 +738,7 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s">
         <v>46</v>
@@ -744,16 +747,16 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="F6">
-        <v>57.92</v>
+        <v>58.13</v>
       </c>
       <c r="G6">
-        <v>65.2</v>
+        <v>64.22</v>
       </c>
       <c r="H6">
-        <v>70.45</v>
+        <v>74.12</v>
       </c>
       <c r="I6" t="s">
         <v>49</v>
@@ -764,7 +767,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
         <v>46</v>
@@ -773,16 +776,16 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>64.69</v>
+        <v>63.89</v>
       </c>
       <c r="G7">
-        <v>64.69</v>
+        <v>63.89</v>
       </c>
       <c r="H7">
-        <v>64.69</v>
+        <v>63.89</v>
       </c>
       <c r="I7" t="s">
         <v>49</v>
@@ -793,7 +796,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
         <v>46</v>
@@ -802,16 +805,16 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F8">
-        <v>59.22</v>
+        <v>60.13</v>
       </c>
       <c r="G8">
-        <v>64.33</v>
+        <v>63.89</v>
       </c>
       <c r="H8">
-        <v>68.77</v>
+        <v>65.88</v>
       </c>
       <c r="I8" t="s">
         <v>49</v>
@@ -831,16 +834,16 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F9">
-        <v>60.04</v>
+        <v>59.73</v>
       </c>
       <c r="G9">
-        <v>64.06</v>
+        <v>63.62</v>
       </c>
       <c r="H9">
-        <v>67.98999999999999</v>
+        <v>67.75</v>
       </c>
       <c r="I9" t="s">
         <v>49</v>
@@ -863,13 +866,13 @@
         <v>20</v>
       </c>
       <c r="F10">
-        <v>59.51</v>
+        <v>56.79</v>
       </c>
       <c r="G10">
-        <v>63.44</v>
+        <v>62.07</v>
       </c>
       <c r="H10">
-        <v>68.66</v>
+        <v>66.91</v>
       </c>
       <c r="I10" t="s">
         <v>49</v>
@@ -892,13 +895,13 @@
         <v>12</v>
       </c>
       <c r="F11">
-        <v>57.61</v>
+        <v>57.33</v>
       </c>
       <c r="G11">
-        <v>63.12</v>
+        <v>61.94</v>
       </c>
       <c r="H11">
-        <v>68.39</v>
+        <v>64.87</v>
       </c>
       <c r="I11" t="s">
         <v>49</v>
@@ -921,13 +924,13 @@
         <v>18</v>
       </c>
       <c r="F12">
-        <v>57.61</v>
+        <v>55.6</v>
       </c>
       <c r="G12">
-        <v>62.54</v>
+        <v>61.84</v>
       </c>
       <c r="H12">
-        <v>69.56</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="I12" t="s">
         <v>49</v>
@@ -938,7 +941,7 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s">
         <v>46</v>
@@ -950,13 +953,13 @@
         <v>20</v>
       </c>
       <c r="F13">
-        <v>57.48</v>
+        <v>54.88</v>
       </c>
       <c r="G13">
-        <v>62.54</v>
+        <v>61.68</v>
       </c>
       <c r="H13">
-        <v>73.43000000000001</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="I13" t="s">
         <v>49</v>
@@ -976,16 +979,16 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F14">
-        <v>55.28</v>
+        <v>61.53</v>
       </c>
       <c r="G14">
-        <v>61.69</v>
+        <v>61.53</v>
       </c>
       <c r="H14">
-        <v>68.89</v>
+        <v>61.53</v>
       </c>
       <c r="I14" t="s">
         <v>49</v>
@@ -1008,13 +1011,13 @@
         <v>2</v>
       </c>
       <c r="F15">
-        <v>59.97</v>
+        <v>60.95</v>
       </c>
       <c r="G15">
-        <v>60.89</v>
+        <v>60.98</v>
       </c>
       <c r="H15">
-        <v>61.8</v>
+        <v>61.01</v>
       </c>
       <c r="I15" t="s">
         <v>49</v>
@@ -1025,7 +1028,7 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
         <v>46</v>
@@ -1034,16 +1037,16 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F16">
-        <v>47.9</v>
+        <v>57.73</v>
       </c>
       <c r="G16">
-        <v>60.62</v>
+        <v>60.41</v>
       </c>
       <c r="H16">
-        <v>78.56</v>
+        <v>62.2</v>
       </c>
       <c r="I16" t="s">
         <v>49</v>
@@ -1054,7 +1057,7 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C17" t="s">
         <v>46</v>
@@ -1063,16 +1066,16 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F17">
-        <v>54.18</v>
+        <v>57.61</v>
       </c>
       <c r="G17">
-        <v>60.16</v>
+        <v>60.11</v>
       </c>
       <c r="H17">
-        <v>63.62</v>
+        <v>63.78</v>
       </c>
       <c r="I17" t="s">
         <v>49</v>
@@ -1083,7 +1086,7 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
         <v>46</v>
@@ -1092,16 +1095,16 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F18">
-        <v>53.48</v>
+        <v>53.31</v>
       </c>
       <c r="G18">
-        <v>59.63</v>
+        <v>59.47</v>
       </c>
       <c r="H18">
-        <v>62.55</v>
+        <v>66.08</v>
       </c>
       <c r="I18" t="s">
         <v>49</v>
@@ -1112,7 +1115,7 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C19" t="s">
         <v>46</v>
@@ -1121,16 +1124,16 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F19">
-        <v>55.06</v>
+        <v>55.32</v>
       </c>
       <c r="G19">
-        <v>59.55</v>
+        <v>59.09</v>
       </c>
       <c r="H19">
-        <v>63.28</v>
+        <v>60.48</v>
       </c>
       <c r="I19" t="s">
         <v>49</v>
@@ -1141,7 +1144,7 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C20" t="s">
         <v>46</v>
@@ -1150,16 +1153,16 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>20</v>
+        <v>117</v>
       </c>
       <c r="F20">
-        <v>54.5</v>
+        <v>51.23</v>
       </c>
       <c r="G20">
-        <v>59.54</v>
+        <v>58.91</v>
       </c>
       <c r="H20">
-        <v>65.92</v>
+        <v>68.8</v>
       </c>
       <c r="I20" t="s">
         <v>49</v>
@@ -1179,16 +1182,16 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>65</v>
       </c>
       <c r="F21">
-        <v>55.91</v>
+        <v>51.27</v>
       </c>
       <c r="G21">
-        <v>58.56</v>
+        <v>58.31</v>
       </c>
       <c r="H21">
-        <v>60.1</v>
+        <v>68.56</v>
       </c>
       <c r="I21" t="s">
         <v>49</v>
@@ -1211,13 +1214,13 @@
         <v>16</v>
       </c>
       <c r="F22">
-        <v>53.79</v>
+        <v>54.04</v>
       </c>
       <c r="G22">
-        <v>58.46</v>
+        <v>58.28</v>
       </c>
       <c r="H22">
-        <v>62.62</v>
+        <v>63.06</v>
       </c>
       <c r="I22" t="s">
         <v>49</v>
@@ -1240,13 +1243,13 @@
         <v>62</v>
       </c>
       <c r="F23">
-        <v>50.81</v>
+        <v>55.42</v>
       </c>
       <c r="G23">
-        <v>57.86</v>
+        <v>58.26</v>
       </c>
       <c r="H23">
-        <v>67.33</v>
+        <v>63.02</v>
       </c>
       <c r="I23" t="s">
         <v>49</v>
@@ -1266,16 +1269,16 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F24">
-        <v>52.77</v>
+        <v>55.78</v>
       </c>
       <c r="G24">
-        <v>57.02</v>
+        <v>57.72</v>
       </c>
       <c r="H24">
-        <v>60.51</v>
+        <v>59.13</v>
       </c>
       <c r="I24" t="s">
         <v>49</v>
@@ -1286,7 +1289,7 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C25" t="s">
         <v>46</v>
@@ -1295,16 +1298,16 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F25">
-        <v>49.11</v>
+        <v>52.94</v>
       </c>
       <c r="G25">
-        <v>56.58</v>
+        <v>56.32</v>
       </c>
       <c r="H25">
-        <v>62.33</v>
+        <v>61.23</v>
       </c>
       <c r="I25" t="s">
         <v>49</v>
@@ -1315,7 +1318,7 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C26" t="s">
         <v>46</v>
@@ -1324,16 +1327,16 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F26">
-        <v>48.63</v>
+        <v>53.18</v>
       </c>
       <c r="G26">
-        <v>56.16</v>
+        <v>55.95</v>
       </c>
       <c r="H26">
-        <v>63.95</v>
+        <v>57.61</v>
       </c>
       <c r="I26" t="s">
         <v>49</v>
@@ -1344,7 +1347,7 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
         <v>46</v>
@@ -1353,16 +1356,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F27">
-        <v>53.45</v>
+        <v>52.3</v>
       </c>
       <c r="G27">
-        <v>55.97</v>
+        <v>55.74</v>
       </c>
       <c r="H27">
-        <v>59.64</v>
+        <v>58.64</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1382,16 +1385,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="F28">
-        <v>55.29</v>
+        <v>50.02</v>
       </c>
       <c r="G28">
-        <v>55.9</v>
+        <v>54.81</v>
       </c>
       <c r="H28">
-        <v>56.7</v>
+        <v>62.91</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
@@ -1402,7 +1405,7 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C29" t="s">
         <v>46</v>
@@ -1411,16 +1414,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>65</v>
+        <v>3</v>
       </c>
       <c r="F29">
-        <v>49.5</v>
+        <v>46.26</v>
       </c>
       <c r="G29">
-        <v>54.8</v>
+        <v>53.7</v>
       </c>
       <c r="H29">
-        <v>70.36</v>
+        <v>59.52</v>
       </c>
       <c r="I29" t="s">
         <v>49</v>
@@ -1440,16 +1443,16 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>117</v>
+        <v>9</v>
       </c>
       <c r="F30">
-        <v>46.67</v>
+        <v>46.42</v>
       </c>
       <c r="G30">
-        <v>54.4</v>
+        <v>53.18</v>
       </c>
       <c r="H30">
-        <v>70.36</v>
+        <v>55.63</v>
       </c>
       <c r="I30" t="s">
         <v>49</v>
@@ -1469,16 +1472,16 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="F31">
-        <v>50.22</v>
+        <v>44.5</v>
       </c>
       <c r="G31">
-        <v>53.54</v>
+        <v>52.11</v>
       </c>
       <c r="H31">
-        <v>65.84</v>
+        <v>60.01</v>
       </c>
       <c r="I31" t="s">
         <v>49</v>
@@ -1489,7 +1492,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C32" t="s">
         <v>46</v>
@@ -1498,16 +1501,16 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F32">
-        <v>46.32</v>
+        <v>48.62</v>
       </c>
       <c r="G32">
-        <v>52.06</v>
+        <v>51.49</v>
       </c>
       <c r="H32">
-        <v>60.51</v>
+        <v>57.83</v>
       </c>
       <c r="I32" t="s">
         <v>49</v>
@@ -1518,7 +1521,7 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C33" t="s">
         <v>46</v>
@@ -1527,19 +1530,19 @@
         <v>47</v>
       </c>
       <c r="E33">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F33">
-        <v>47.67</v>
+        <v>46.93</v>
       </c>
       <c r="G33">
-        <v>50.4</v>
+        <v>49.17</v>
       </c>
       <c r="H33">
-        <v>55.86</v>
+        <v>52.16</v>
       </c>
       <c r="I33" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1556,19 +1559,19 @@
         <v>47</v>
       </c>
       <c r="E34">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="F34">
-        <v>49.02</v>
+        <v>42.41</v>
       </c>
       <c r="G34">
-        <v>50.03</v>
+        <v>49.14</v>
       </c>
       <c r="H34">
-        <v>51.71</v>
+        <v>64.72</v>
       </c>
       <c r="I34" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -1588,7 +1591,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -1608,7 +1611,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="51">
   <si>
     <t>نام منطقه</t>
   </si>
@@ -46,102 +46,102 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع بناب</t>
+  </si>
+  <si>
+    <t>پارک ملي قطرويه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه دراء</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مزايجان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دالان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده برم فیروز</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوهستان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده هرمود</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه هوا و</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع مل بلند</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه دراء</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دالان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوهستان</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بناب</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>پارک ملي قطرويه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
+    <t>پناهگاه حيات وحش دره باغ</t>
   </si>
   <si>
     <t>منطقه حفاظت شده ماله گاله</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع توت سياه</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه هوا و</t>
+    <t>منطقه شکار ممنوع مهارلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دره باغ</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع شیکوه</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده هرمود</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش دره باغ</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع بصيران</t>
   </si>
   <si>
@@ -157,13 +157,10 @@
     <t>مناطق ممنوعه شکار</t>
   </si>
   <si>
-    <t>1405-07-20</t>
-  </si>
-  <si>
-    <t>2026-10-12</t>
-  </si>
-  <si>
-    <t>بسیار شدید</t>
+    <t>1405-07-21</t>
+  </si>
+  <si>
+    <t>2026-10-13</t>
   </si>
   <si>
     <t>شدید</t>
@@ -631,16 +628,16 @@
         <v>47</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F2">
-        <v>64.97</v>
+        <v>48.78</v>
       </c>
       <c r="G2">
-        <v>71.8</v>
+        <v>62.71</v>
       </c>
       <c r="H2">
-        <v>76.55</v>
+        <v>69.33</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -660,19 +657,19 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>58.16</v>
+        <v>60.51</v>
       </c>
       <c r="G3">
-        <v>67.05</v>
+        <v>60.51</v>
       </c>
       <c r="H3">
-        <v>68.86</v>
+        <v>60.51</v>
       </c>
       <c r="I3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -692,16 +689,16 @@
         <v>33</v>
       </c>
       <c r="F4">
-        <v>63.1</v>
+        <v>51.53</v>
       </c>
       <c r="G4">
-        <v>66.17</v>
+        <v>58.66</v>
       </c>
       <c r="H4">
-        <v>71.77</v>
+        <v>64.91</v>
       </c>
       <c r="I4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -718,19 +715,19 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F5">
-        <v>64.76000000000001</v>
+        <v>51.68</v>
       </c>
       <c r="G5">
-        <v>65.20999999999999</v>
+        <v>57.56</v>
       </c>
       <c r="H5">
-        <v>65.86</v>
+        <v>66.45999999999999</v>
       </c>
       <c r="I5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -750,16 +747,16 @@
         <v>21</v>
       </c>
       <c r="F6">
-        <v>58.13</v>
+        <v>50.96</v>
       </c>
       <c r="G6">
-        <v>64.22</v>
+        <v>56.54</v>
       </c>
       <c r="H6">
-        <v>74.12</v>
+        <v>63.73</v>
       </c>
       <c r="I6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -767,7 +764,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
         <v>46</v>
@@ -776,19 +773,19 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="F7">
-        <v>63.89</v>
+        <v>50.84</v>
       </c>
       <c r="G7">
-        <v>63.89</v>
+        <v>56.34</v>
       </c>
       <c r="H7">
-        <v>63.89</v>
+        <v>61.72</v>
       </c>
       <c r="I7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -805,19 +802,19 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="F8">
-        <v>60.13</v>
+        <v>52.99</v>
       </c>
       <c r="G8">
-        <v>63.89</v>
+        <v>56.08</v>
       </c>
       <c r="H8">
-        <v>65.88</v>
+        <v>58.97</v>
       </c>
       <c r="I8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -837,16 +834,16 @@
         <v>20</v>
       </c>
       <c r="F9">
-        <v>59.73</v>
+        <v>51.25</v>
       </c>
       <c r="G9">
-        <v>63.62</v>
+        <v>55.61</v>
       </c>
       <c r="H9">
-        <v>67.75</v>
+        <v>58.52</v>
       </c>
       <c r="I9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -866,16 +863,16 @@
         <v>20</v>
       </c>
       <c r="F10">
-        <v>56.79</v>
+        <v>51.04</v>
       </c>
       <c r="G10">
-        <v>62.07</v>
+        <v>55.58</v>
       </c>
       <c r="H10">
-        <v>66.91</v>
+        <v>63.31</v>
       </c>
       <c r="I10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -892,19 +889,19 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F11">
-        <v>57.33</v>
+        <v>52.88</v>
       </c>
       <c r="G11">
-        <v>61.94</v>
+        <v>55.57</v>
       </c>
       <c r="H11">
-        <v>64.87</v>
+        <v>56.58</v>
       </c>
       <c r="I11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -912,7 +909,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
         <v>46</v>
@@ -921,19 +918,19 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F12">
-        <v>55.6</v>
+        <v>51.76</v>
       </c>
       <c r="G12">
-        <v>61.84</v>
+        <v>55.46</v>
       </c>
       <c r="H12">
-        <v>64.79000000000001</v>
+        <v>58.97</v>
       </c>
       <c r="I12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -950,19 +947,19 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F13">
-        <v>54.88</v>
+        <v>55.4</v>
       </c>
       <c r="G13">
-        <v>61.68</v>
+        <v>55.4</v>
       </c>
       <c r="H13">
-        <v>68.65000000000001</v>
+        <v>55.4</v>
       </c>
       <c r="I13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -979,19 +976,19 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F14">
-        <v>61.53</v>
+        <v>48.41</v>
       </c>
       <c r="G14">
-        <v>61.53</v>
+        <v>55.39</v>
       </c>
       <c r="H14">
-        <v>61.53</v>
+        <v>60.2</v>
       </c>
       <c r="I14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -1008,19 +1005,19 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="F15">
-        <v>60.95</v>
+        <v>49.22</v>
       </c>
       <c r="G15">
-        <v>60.98</v>
+        <v>55.35</v>
       </c>
       <c r="H15">
-        <v>61.01</v>
+        <v>61.25</v>
       </c>
       <c r="I15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1037,19 +1034,19 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F16">
-        <v>57.73</v>
+        <v>49.22</v>
       </c>
       <c r="G16">
-        <v>60.41</v>
+        <v>54.82</v>
       </c>
       <c r="H16">
-        <v>62.2</v>
+        <v>58.49</v>
       </c>
       <c r="I16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1066,19 +1063,19 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F17">
-        <v>57.61</v>
+        <v>53.77</v>
       </c>
       <c r="G17">
-        <v>60.11</v>
+        <v>54.64</v>
       </c>
       <c r="H17">
-        <v>63.78</v>
+        <v>55.51</v>
       </c>
       <c r="I17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1095,19 +1092,19 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F18">
-        <v>53.31</v>
+        <v>51.63</v>
       </c>
       <c r="G18">
-        <v>59.47</v>
+        <v>54.34</v>
       </c>
       <c r="H18">
-        <v>66.08</v>
+        <v>58.64</v>
       </c>
       <c r="I18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1124,19 +1121,19 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="F19">
-        <v>55.32</v>
+        <v>48.69</v>
       </c>
       <c r="G19">
-        <v>59.09</v>
+        <v>54.28</v>
       </c>
       <c r="H19">
-        <v>60.48</v>
+        <v>63.56</v>
       </c>
       <c r="I19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1144,7 +1141,7 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C20" t="s">
         <v>46</v>
@@ -1153,19 +1150,19 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>117</v>
+        <v>13</v>
       </c>
       <c r="F20">
-        <v>51.23</v>
+        <v>49.03</v>
       </c>
       <c r="G20">
-        <v>58.91</v>
+        <v>53.57</v>
       </c>
       <c r="H20">
-        <v>68.8</v>
+        <v>55.29</v>
       </c>
       <c r="I20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1182,19 +1179,19 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="F21">
-        <v>51.27</v>
+        <v>47.69</v>
       </c>
       <c r="G21">
-        <v>58.31</v>
+        <v>53.04</v>
       </c>
       <c r="H21">
-        <v>68.56</v>
+        <v>56.79</v>
       </c>
       <c r="I21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -1202,7 +1199,7 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C22" t="s">
         <v>46</v>
@@ -1211,19 +1208,19 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="F22">
-        <v>54.04</v>
+        <v>45.96</v>
       </c>
       <c r="G22">
-        <v>58.28</v>
+        <v>52.38</v>
       </c>
       <c r="H22">
-        <v>63.06</v>
+        <v>58.45</v>
       </c>
       <c r="I22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1231,7 +1228,7 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C23" t="s">
         <v>46</v>
@@ -1240,19 +1237,19 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F23">
-        <v>55.42</v>
+        <v>44.9</v>
       </c>
       <c r="G23">
-        <v>58.26</v>
+        <v>52.27</v>
       </c>
       <c r="H23">
-        <v>63.02</v>
+        <v>63.52</v>
       </c>
       <c r="I23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -1272,16 +1269,16 @@
         <v>3</v>
       </c>
       <c r="F24">
-        <v>55.78</v>
+        <v>51.46</v>
       </c>
       <c r="G24">
-        <v>57.72</v>
+        <v>51.9</v>
       </c>
       <c r="H24">
-        <v>59.13</v>
+        <v>52.34</v>
       </c>
       <c r="I24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -1298,19 +1295,19 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>8</v>
+        <v>117</v>
       </c>
       <c r="F25">
-        <v>52.94</v>
+        <v>44.9</v>
       </c>
       <c r="G25">
-        <v>56.32</v>
+        <v>51.4</v>
       </c>
       <c r="H25">
-        <v>61.23</v>
+        <v>63.52</v>
       </c>
       <c r="I25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -1318,7 +1315,7 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s">
         <v>46</v>
@@ -1327,19 +1324,19 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F26">
-        <v>53.18</v>
+        <v>46.63</v>
       </c>
       <c r="G26">
-        <v>55.95</v>
+        <v>50.1</v>
       </c>
       <c r="H26">
-        <v>57.61</v>
+        <v>53.24</v>
       </c>
       <c r="I26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -1356,16 +1353,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F27">
-        <v>52.3</v>
+        <v>46.98</v>
       </c>
       <c r="G27">
-        <v>55.74</v>
+        <v>48.89</v>
       </c>
       <c r="H27">
-        <v>58.64</v>
+        <v>51.49</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1376,7 +1373,7 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C28" t="s">
         <v>46</v>
@@ -1385,16 +1382,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="F28">
-        <v>50.02</v>
+        <v>48.48</v>
       </c>
       <c r="G28">
-        <v>54.81</v>
+        <v>48.89</v>
       </c>
       <c r="H28">
-        <v>62.91</v>
+        <v>49.48</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
@@ -1405,7 +1402,7 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C29" t="s">
         <v>46</v>
@@ -1414,16 +1411,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="F29">
-        <v>46.26</v>
+        <v>43.33</v>
       </c>
       <c r="G29">
-        <v>53.7</v>
+        <v>48.4</v>
       </c>
       <c r="H29">
-        <v>59.52</v>
+        <v>53.1</v>
       </c>
       <c r="I29" t="s">
         <v>49</v>
@@ -1434,7 +1431,7 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C30" t="s">
         <v>46</v>
@@ -1443,16 +1440,16 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F30">
-        <v>46.42</v>
+        <v>44.27</v>
       </c>
       <c r="G30">
-        <v>53.18</v>
+        <v>47.92</v>
       </c>
       <c r="H30">
-        <v>55.63</v>
+        <v>52.12</v>
       </c>
       <c r="I30" t="s">
         <v>49</v>
@@ -1472,16 +1469,16 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F31">
-        <v>44.5</v>
+        <v>45.41</v>
       </c>
       <c r="G31">
-        <v>52.11</v>
+        <v>47.72</v>
       </c>
       <c r="H31">
-        <v>60.01</v>
+        <v>51.94</v>
       </c>
       <c r="I31" t="s">
         <v>49</v>
@@ -1501,16 +1498,16 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F32">
-        <v>48.62</v>
+        <v>26.4</v>
       </c>
       <c r="G32">
-        <v>51.49</v>
+        <v>44.93</v>
       </c>
       <c r="H32">
-        <v>57.83</v>
+        <v>55.27</v>
       </c>
       <c r="I32" t="s">
         <v>49</v>
@@ -1521,7 +1518,7 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C33" t="s">
         <v>46</v>
@@ -1533,16 +1530,16 @@
         <v>3</v>
       </c>
       <c r="F33">
-        <v>46.93</v>
+        <v>38.55</v>
       </c>
       <c r="G33">
-        <v>49.17</v>
+        <v>43.37</v>
       </c>
       <c r="H33">
-        <v>52.16</v>
+        <v>52.03</v>
       </c>
       <c r="I33" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1562,16 +1559,16 @@
         <v>28</v>
       </c>
       <c r="F34">
-        <v>42.41</v>
+        <v>21.65</v>
       </c>
       <c r="G34">
-        <v>49.14</v>
+        <v>38.09</v>
       </c>
       <c r="H34">
-        <v>64.72</v>
+        <v>63.34</v>
       </c>
       <c r="I34" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -1591,7 +1588,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -1611,7 +1608,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="53">
   <si>
     <t>نام منطقه</t>
   </si>
@@ -49,102 +49,102 @@
     <t>منطقه شکار ممنوع بناب</t>
   </si>
   <si>
+    <t>منطقه حفاظت شده هرمود</t>
+  </si>
+  <si>
     <t>پارک ملي قطرويه</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دالان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه هوا و</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مزايجان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مهارلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع توت سياه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوهستان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع کوه دراء</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
   </si>
   <si>
     <t>منطقه حفاظت شده بهرام گور</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
+    <t>منطقه شکار ممنوع بصيران</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع شیکوه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده برم فیروز</t>
   </si>
   <si>
     <t>منطقه حفاظت شده تنگ بستانک</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دالان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوهستان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده هرمود</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه هوا و</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
     <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
   </si>
   <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع شیکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بصيران</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع چاه نفت</t>
   </si>
   <si>
@@ -157,16 +157,22 @@
     <t>مناطق ممنوعه شکار</t>
   </si>
   <si>
-    <t>1405-07-21</t>
-  </si>
-  <si>
-    <t>2026-10-13</t>
+    <t>1405-07-22</t>
+  </si>
+  <si>
+    <t>2026-10-14</t>
   </si>
   <si>
     <t>شدید</t>
   </si>
   <si>
     <t>خیلی زیاد</t>
+  </si>
+  <si>
+    <t>زیاد</t>
+  </si>
+  <si>
+    <t>متوسط</t>
   </si>
   <si>
     <t>بدون داده</t>
@@ -631,13 +637,13 @@
         <v>20</v>
       </c>
       <c r="F2">
-        <v>48.78</v>
+        <v>54.26</v>
       </c>
       <c r="G2">
-        <v>62.71</v>
+        <v>59.18</v>
       </c>
       <c r="H2">
-        <v>69.33</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -657,16 +663,16 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>60.51</v>
+        <v>52.96</v>
       </c>
       <c r="G3">
-        <v>60.51</v>
+        <v>57.27</v>
       </c>
       <c r="H3">
-        <v>60.51</v>
+        <v>63.5</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -677,7 +683,7 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C4" t="s">
         <v>46</v>
@@ -686,16 +692,16 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>51.53</v>
+        <v>56.9</v>
       </c>
       <c r="G4">
-        <v>58.66</v>
+        <v>56.9</v>
       </c>
       <c r="H4">
-        <v>64.91</v>
+        <v>56.9</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -715,16 +721,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F5">
-        <v>51.68</v>
+        <v>50.34</v>
       </c>
       <c r="G5">
-        <v>57.56</v>
+        <v>54.71</v>
       </c>
       <c r="H5">
-        <v>66.45999999999999</v>
+        <v>60.88</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -744,16 +750,16 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F6">
-        <v>50.96</v>
+        <v>49.12</v>
       </c>
       <c r="G6">
-        <v>56.54</v>
+        <v>54.52</v>
       </c>
       <c r="H6">
-        <v>63.73</v>
+        <v>63.61</v>
       </c>
       <c r="I6" t="s">
         <v>48</v>
@@ -764,7 +770,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
         <v>46</v>
@@ -773,16 +779,16 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F7">
-        <v>50.84</v>
+        <v>53.56</v>
       </c>
       <c r="G7">
-        <v>56.34</v>
+        <v>53.93</v>
       </c>
       <c r="H7">
-        <v>61.72</v>
+        <v>54.56</v>
       </c>
       <c r="I7" t="s">
         <v>48</v>
@@ -793,7 +799,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C8" t="s">
         <v>46</v>
@@ -802,16 +808,16 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="F8">
-        <v>52.99</v>
+        <v>46.91</v>
       </c>
       <c r="G8">
-        <v>56.08</v>
+        <v>52.37</v>
       </c>
       <c r="H8">
-        <v>58.97</v>
+        <v>57.31</v>
       </c>
       <c r="I8" t="s">
         <v>48</v>
@@ -831,16 +837,16 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F9">
-        <v>51.25</v>
+        <v>47.27</v>
       </c>
       <c r="G9">
-        <v>55.61</v>
+        <v>51.79</v>
       </c>
       <c r="H9">
-        <v>58.52</v>
+        <v>53.99</v>
       </c>
       <c r="I9" t="s">
         <v>48</v>
@@ -860,16 +866,16 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F10">
-        <v>51.04</v>
+        <v>44.11</v>
       </c>
       <c r="G10">
-        <v>55.58</v>
+        <v>51.4</v>
       </c>
       <c r="H10">
-        <v>63.31</v>
+        <v>55.98</v>
       </c>
       <c r="I10" t="s">
         <v>48</v>
@@ -889,16 +895,16 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="F11">
-        <v>52.88</v>
+        <v>40.58</v>
       </c>
       <c r="G11">
-        <v>55.57</v>
+        <v>50.91</v>
       </c>
       <c r="H11">
-        <v>56.58</v>
+        <v>57.66</v>
       </c>
       <c r="I11" t="s">
         <v>48</v>
@@ -909,7 +915,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
         <v>46</v>
@@ -918,16 +924,16 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F12">
-        <v>51.76</v>
+        <v>47.39</v>
       </c>
       <c r="G12">
-        <v>55.46</v>
+        <v>50.59</v>
       </c>
       <c r="H12">
-        <v>58.97</v>
+        <v>53.79</v>
       </c>
       <c r="I12" t="s">
         <v>48</v>
@@ -947,19 +953,19 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="F13">
-        <v>55.4</v>
+        <v>36.21</v>
       </c>
       <c r="G13">
-        <v>55.4</v>
+        <v>48.89</v>
       </c>
       <c r="H13">
-        <v>55.4</v>
+        <v>58.76</v>
       </c>
       <c r="I13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -976,19 +982,19 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F14">
-        <v>48.41</v>
+        <v>28.62</v>
       </c>
       <c r="G14">
-        <v>55.39</v>
+        <v>48.16</v>
       </c>
       <c r="H14">
-        <v>60.2</v>
+        <v>54.86</v>
       </c>
       <c r="I14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -1005,19 +1011,19 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F15">
-        <v>49.22</v>
+        <v>44.27</v>
       </c>
       <c r="G15">
-        <v>55.35</v>
+        <v>46.53</v>
       </c>
       <c r="H15">
-        <v>61.25</v>
+        <v>52.86</v>
       </c>
       <c r="I15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1034,19 +1040,19 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F16">
-        <v>49.22</v>
+        <v>41.23</v>
       </c>
       <c r="G16">
-        <v>54.82</v>
+        <v>44.82</v>
       </c>
       <c r="H16">
-        <v>58.49</v>
+        <v>47.43</v>
       </c>
       <c r="I16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1066,16 +1072,16 @@
         <v>2</v>
       </c>
       <c r="F17">
-        <v>53.77</v>
+        <v>43.99</v>
       </c>
       <c r="G17">
-        <v>54.64</v>
+        <v>43.99</v>
       </c>
       <c r="H17">
-        <v>55.51</v>
+        <v>43.99</v>
       </c>
       <c r="I17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1092,19 +1098,19 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F18">
-        <v>51.63</v>
+        <v>21.01</v>
       </c>
       <c r="G18">
-        <v>54.34</v>
+        <v>43.46</v>
       </c>
       <c r="H18">
-        <v>58.64</v>
+        <v>56.75</v>
       </c>
       <c r="I18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1121,19 +1127,19 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F19">
-        <v>48.69</v>
+        <v>31.12</v>
       </c>
       <c r="G19">
-        <v>54.28</v>
+        <v>43.03</v>
       </c>
       <c r="H19">
-        <v>63.56</v>
+        <v>54.58</v>
       </c>
       <c r="I19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1150,19 +1156,19 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F20">
-        <v>49.03</v>
+        <v>18.65</v>
       </c>
       <c r="G20">
-        <v>53.57</v>
+        <v>42.7</v>
       </c>
       <c r="H20">
-        <v>55.29</v>
+        <v>48.35</v>
       </c>
       <c r="I20" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1179,19 +1185,19 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="F21">
-        <v>47.69</v>
+        <v>9.99</v>
       </c>
       <c r="G21">
-        <v>53.04</v>
+        <v>42.67</v>
       </c>
       <c r="H21">
-        <v>56.79</v>
+        <v>60.22</v>
       </c>
       <c r="I21" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -1208,19 +1214,19 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="F22">
-        <v>45.96</v>
+        <v>26.41</v>
       </c>
       <c r="G22">
-        <v>52.38</v>
+        <v>41.02</v>
       </c>
       <c r="H22">
-        <v>58.45</v>
+        <v>51.38</v>
       </c>
       <c r="I22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1237,19 +1243,19 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="F23">
-        <v>44.9</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="G23">
-        <v>52.27</v>
+        <v>40.64</v>
       </c>
       <c r="H23">
-        <v>63.52</v>
+        <v>60.22</v>
       </c>
       <c r="I23" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -1257,7 +1263,7 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C24" t="s">
         <v>46</v>
@@ -1266,19 +1272,19 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="F24">
-        <v>51.46</v>
+        <v>16.93</v>
       </c>
       <c r="G24">
-        <v>51.9</v>
+        <v>39.44</v>
       </c>
       <c r="H24">
-        <v>52.34</v>
+        <v>60.33</v>
       </c>
       <c r="I24" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -1286,7 +1292,7 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C25" t="s">
         <v>46</v>
@@ -1295,19 +1301,19 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>117</v>
+        <v>12</v>
       </c>
       <c r="F25">
-        <v>44.9</v>
+        <v>18.56</v>
       </c>
       <c r="G25">
-        <v>51.4</v>
+        <v>38.52</v>
       </c>
       <c r="H25">
-        <v>63.52</v>
+        <v>62.09</v>
       </c>
       <c r="I25" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -1315,7 +1321,7 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C26" t="s">
         <v>46</v>
@@ -1324,19 +1330,19 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F26">
-        <v>46.63</v>
+        <v>26.41</v>
       </c>
       <c r="G26">
-        <v>50.1</v>
+        <v>38.08</v>
       </c>
       <c r="H26">
-        <v>53.24</v>
+        <v>51.38</v>
       </c>
       <c r="I26" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -1344,7 +1350,7 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
         <v>46</v>
@@ -1353,19 +1359,19 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F27">
-        <v>46.98</v>
+        <v>27.31</v>
       </c>
       <c r="G27">
-        <v>48.89</v>
+        <v>37.3</v>
       </c>
       <c r="H27">
-        <v>51.49</v>
+        <v>49.78</v>
       </c>
       <c r="I27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -1382,19 +1388,19 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="F28">
-        <v>48.48</v>
+        <v>14.57</v>
       </c>
       <c r="G28">
-        <v>48.89</v>
+        <v>34.95</v>
       </c>
       <c r="H28">
-        <v>49.48</v>
+        <v>57.11</v>
       </c>
       <c r="I28" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -1402,7 +1408,7 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C29" t="s">
         <v>46</v>
@@ -1411,19 +1417,19 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F29">
-        <v>43.33</v>
+        <v>7.94</v>
       </c>
       <c r="G29">
-        <v>48.4</v>
+        <v>29.62</v>
       </c>
       <c r="H29">
-        <v>53.1</v>
+        <v>57.74</v>
       </c>
       <c r="I29" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -1440,19 +1446,19 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F30">
-        <v>44.27</v>
+        <v>15.71</v>
       </c>
       <c r="G30">
-        <v>47.92</v>
+        <v>22.36</v>
       </c>
       <c r="H30">
-        <v>52.12</v>
+        <v>29.08</v>
       </c>
       <c r="I30" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -1469,19 +1475,19 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F31">
-        <v>45.41</v>
+        <v>6.04</v>
       </c>
       <c r="G31">
-        <v>47.72</v>
+        <v>20.3</v>
       </c>
       <c r="H31">
-        <v>51.94</v>
+        <v>48.51</v>
       </c>
       <c r="I31" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -1489,7 +1495,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C32" t="s">
         <v>46</v>
@@ -1498,19 +1504,19 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F32">
-        <v>26.4</v>
+        <v>8.33</v>
       </c>
       <c r="G32">
-        <v>44.93</v>
+        <v>18.32</v>
       </c>
       <c r="H32">
-        <v>55.27</v>
+        <v>29.63</v>
       </c>
       <c r="I32" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -1518,7 +1524,7 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C33" t="s">
         <v>46</v>
@@ -1527,19 +1533,19 @@
         <v>47</v>
       </c>
       <c r="E33">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F33">
-        <v>38.55</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="G33">
-        <v>43.37</v>
+        <v>17.79</v>
       </c>
       <c r="H33">
-        <v>52.03</v>
+        <v>28.37</v>
       </c>
       <c r="I33" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1547,7 +1553,7 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C34" t="s">
         <v>46</v>
@@ -1556,19 +1562,19 @@
         <v>47</v>
       </c>
       <c r="E34">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="F34">
-        <v>21.65</v>
+        <v>9.93</v>
       </c>
       <c r="G34">
-        <v>38.09</v>
+        <v>14.55</v>
       </c>
       <c r="H34">
-        <v>63.34</v>
+        <v>23.66</v>
       </c>
       <c r="I34" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -1588,7 +1594,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -1608,7 +1614,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -46,121 +46,121 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>منطقه حفاظت شده هرمود</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دالان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوهستان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه دراء</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه هوا و</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع بناب</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده هرمود</t>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
   </si>
   <si>
     <t>پارک ملي قطرويه</t>
   </si>
   <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مزايجان</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع کوه گورم</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مهارلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
     <t>منطقه حفاظت شده میانجنگل فسا</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع دالان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه هوا و</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع کوه سياه</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
+    <t>منطقه حفاظت شده بهرام گور</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع توت سياه</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوهستان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه دراء</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
+    <t>منطقه شکار ممنوع شیکوه</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع بصيران</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع شیکوه</t>
-  </si>
-  <si>
     <t>منطقه حفاظت شده برم فیروز</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع چاه نفت</t>
   </si>
   <si>
     <t>منطقه حفاظت شده مارگون</t>
   </si>
   <si>
+    <t>مناطق ممنوعه شکار</t>
+  </si>
+  <si>
     <t>مناطق حفاظت‌شده</t>
   </si>
   <si>
-    <t>مناطق ممنوعه شکار</t>
-  </si>
-  <si>
-    <t>1405-07-22</t>
-  </si>
-  <si>
-    <t>2026-10-14</t>
+    <t>1405-07-23</t>
+  </si>
+  <si>
+    <t>2026-10-15</t>
   </si>
   <si>
     <t>شدید</t>
@@ -634,16 +634,16 @@
         <v>47</v>
       </c>
       <c r="E2">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>54.26</v>
+        <v>54.27</v>
       </c>
       <c r="G2">
-        <v>59.18</v>
+        <v>55.95</v>
       </c>
       <c r="H2">
-        <v>64.29000000000001</v>
+        <v>57.51</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -663,16 +663,16 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>52.96</v>
+        <v>54.89</v>
       </c>
       <c r="G3">
-        <v>57.27</v>
+        <v>55.84</v>
       </c>
       <c r="H3">
-        <v>63.5</v>
+        <v>57.26</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -692,16 +692,16 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>56.9</v>
+        <v>55.62</v>
       </c>
       <c r="G4">
-        <v>56.9</v>
+        <v>55.62</v>
       </c>
       <c r="H4">
-        <v>56.9</v>
+        <v>55.62</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -712,7 +712,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
         <v>46</v>
@@ -721,16 +721,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F5">
-        <v>50.34</v>
+        <v>52.2</v>
       </c>
       <c r="G5">
-        <v>54.71</v>
+        <v>55.01</v>
       </c>
       <c r="H5">
-        <v>60.88</v>
+        <v>59.1</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -750,16 +750,16 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="F6">
-        <v>49.12</v>
+        <v>46.44</v>
       </c>
       <c r="G6">
-        <v>54.52</v>
+        <v>54.6</v>
       </c>
       <c r="H6">
-        <v>63.61</v>
+        <v>61.04</v>
       </c>
       <c r="I6" t="s">
         <v>48</v>
@@ -770,7 +770,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
         <v>46</v>
@@ -779,16 +779,16 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F7">
-        <v>53.56</v>
+        <v>48.83</v>
       </c>
       <c r="G7">
-        <v>53.93</v>
+        <v>54.56</v>
       </c>
       <c r="H7">
-        <v>54.56</v>
+        <v>58.32</v>
       </c>
       <c r="I7" t="s">
         <v>48</v>
@@ -808,16 +808,16 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="F8">
-        <v>46.91</v>
+        <v>41.58</v>
       </c>
       <c r="G8">
-        <v>52.37</v>
+        <v>53.9</v>
       </c>
       <c r="H8">
-        <v>57.31</v>
+        <v>61.96</v>
       </c>
       <c r="I8" t="s">
         <v>48</v>
@@ -837,16 +837,16 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F9">
-        <v>47.27</v>
+        <v>48.5</v>
       </c>
       <c r="G9">
-        <v>51.79</v>
+        <v>53.84</v>
       </c>
       <c r="H9">
-        <v>53.99</v>
+        <v>58.09</v>
       </c>
       <c r="I9" t="s">
         <v>48</v>
@@ -857,7 +857,7 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
         <v>46</v>
@@ -866,16 +866,16 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F10">
-        <v>44.11</v>
+        <v>50.2</v>
       </c>
       <c r="G10">
-        <v>51.4</v>
+        <v>53.57</v>
       </c>
       <c r="H10">
-        <v>55.98</v>
+        <v>56.94</v>
       </c>
       <c r="I10" t="s">
         <v>48</v>
@@ -895,16 +895,16 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="F11">
-        <v>40.58</v>
+        <v>53.46</v>
       </c>
       <c r="G11">
-        <v>50.91</v>
+        <v>53.46</v>
       </c>
       <c r="H11">
-        <v>57.66</v>
+        <v>53.46</v>
       </c>
       <c r="I11" t="s">
         <v>48</v>
@@ -924,16 +924,16 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>117</v>
       </c>
       <c r="F12">
-        <v>47.39</v>
+        <v>34.52</v>
       </c>
       <c r="G12">
-        <v>50.59</v>
+        <v>53.4</v>
       </c>
       <c r="H12">
-        <v>53.79</v>
+        <v>64.97</v>
       </c>
       <c r="I12" t="s">
         <v>48</v>
@@ -956,16 +956,16 @@
         <v>20</v>
       </c>
       <c r="F13">
-        <v>36.21</v>
+        <v>37.01</v>
       </c>
       <c r="G13">
-        <v>48.89</v>
+        <v>51.82</v>
       </c>
       <c r="H13">
-        <v>58.76</v>
+        <v>58.25</v>
       </c>
       <c r="I13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -982,19 +982,19 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F14">
-        <v>28.62</v>
+        <v>47.95</v>
       </c>
       <c r="G14">
-        <v>48.16</v>
+        <v>51.44</v>
       </c>
       <c r="H14">
-        <v>54.86</v>
+        <v>57.72</v>
       </c>
       <c r="I14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -1002,7 +1002,7 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
         <v>46</v>
@@ -1011,19 +1011,19 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F15">
-        <v>44.27</v>
+        <v>48.05</v>
       </c>
       <c r="G15">
-        <v>46.53</v>
+        <v>51.07</v>
       </c>
       <c r="H15">
-        <v>52.86</v>
+        <v>55.48</v>
       </c>
       <c r="I15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1031,7 +1031,7 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
         <v>46</v>
@@ -1040,16 +1040,16 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F16">
-        <v>41.23</v>
+        <v>43.46</v>
       </c>
       <c r="G16">
-        <v>44.82</v>
+        <v>49.76</v>
       </c>
       <c r="H16">
-        <v>47.43</v>
+        <v>55.23</v>
       </c>
       <c r="I16" t="s">
         <v>49</v>
@@ -1060,7 +1060,7 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
         <v>46</v>
@@ -1069,16 +1069,16 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F17">
-        <v>43.99</v>
+        <v>42.16</v>
       </c>
       <c r="G17">
-        <v>43.99</v>
+        <v>47.25</v>
       </c>
       <c r="H17">
-        <v>43.99</v>
+        <v>53.72</v>
       </c>
       <c r="I17" t="s">
         <v>49</v>
@@ -1098,16 +1098,16 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F18">
-        <v>21.01</v>
+        <v>33.16</v>
       </c>
       <c r="G18">
-        <v>43.46</v>
+        <v>47.25</v>
       </c>
       <c r="H18">
-        <v>56.75</v>
+        <v>59.6</v>
       </c>
       <c r="I18" t="s">
         <v>49</v>
@@ -1127,16 +1127,16 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F19">
-        <v>31.12</v>
+        <v>38.47</v>
       </c>
       <c r="G19">
-        <v>43.03</v>
+        <v>47.21</v>
       </c>
       <c r="H19">
-        <v>54.58</v>
+        <v>57.41</v>
       </c>
       <c r="I19" t="s">
         <v>49</v>
@@ -1147,7 +1147,7 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C20" t="s">
         <v>46</v>
@@ -1156,16 +1156,16 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="F20">
-        <v>18.65</v>
+        <v>28.35</v>
       </c>
       <c r="G20">
-        <v>42.7</v>
+        <v>46.22</v>
       </c>
       <c r="H20">
-        <v>48.35</v>
+        <v>56.84</v>
       </c>
       <c r="I20" t="s">
         <v>49</v>
@@ -1185,16 +1185,16 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>65</v>
+        <v>6</v>
       </c>
       <c r="F21">
-        <v>9.99</v>
+        <v>38.26</v>
       </c>
       <c r="G21">
-        <v>42.67</v>
+        <v>44.87</v>
       </c>
       <c r="H21">
-        <v>60.22</v>
+        <v>55.32</v>
       </c>
       <c r="I21" t="s">
         <v>49</v>
@@ -1205,7 +1205,7 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C22" t="s">
         <v>46</v>
@@ -1217,13 +1217,13 @@
         <v>12</v>
       </c>
       <c r="F22">
-        <v>26.41</v>
+        <v>35.78</v>
       </c>
       <c r="G22">
-        <v>41.02</v>
+        <v>44.53</v>
       </c>
       <c r="H22">
-        <v>51.38</v>
+        <v>52.52</v>
       </c>
       <c r="I22" t="s">
         <v>49</v>
@@ -1234,7 +1234,7 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C23" t="s">
         <v>46</v>
@@ -1243,16 +1243,16 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>117</v>
+        <v>16</v>
       </c>
       <c r="F23">
-        <v>8.220000000000001</v>
+        <v>36.8</v>
       </c>
       <c r="G23">
-        <v>40.64</v>
+        <v>44.44</v>
       </c>
       <c r="H23">
-        <v>60.22</v>
+        <v>57.74</v>
       </c>
       <c r="I23" t="s">
         <v>49</v>
@@ -1272,16 +1272,16 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="F24">
-        <v>16.93</v>
+        <v>38.17</v>
       </c>
       <c r="G24">
-        <v>39.44</v>
+        <v>43.22</v>
       </c>
       <c r="H24">
-        <v>60.33</v>
+        <v>49.63</v>
       </c>
       <c r="I24" t="s">
         <v>49</v>
@@ -1292,7 +1292,7 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C25" t="s">
         <v>46</v>
@@ -1304,13 +1304,13 @@
         <v>12</v>
       </c>
       <c r="F25">
-        <v>18.56</v>
+        <v>33.14</v>
       </c>
       <c r="G25">
-        <v>38.52</v>
+        <v>42.54</v>
       </c>
       <c r="H25">
-        <v>62.09</v>
+        <v>57.95</v>
       </c>
       <c r="I25" t="s">
         <v>49</v>
@@ -1330,16 +1330,16 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F26">
-        <v>26.41</v>
+        <v>19.45</v>
       </c>
       <c r="G26">
-        <v>38.08</v>
+        <v>41.8</v>
       </c>
       <c r="H26">
-        <v>51.38</v>
+        <v>58.68</v>
       </c>
       <c r="I26" t="s">
         <v>49</v>
@@ -1350,7 +1350,7 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
         <v>46</v>
@@ -1359,19 +1359,19 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F27">
-        <v>27.31</v>
+        <v>22.37</v>
       </c>
       <c r="G27">
-        <v>37.3</v>
+        <v>41.54</v>
       </c>
       <c r="H27">
-        <v>49.78</v>
+        <v>53.46</v>
       </c>
       <c r="I27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -1388,19 +1388,19 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F28">
-        <v>14.57</v>
+        <v>16.69</v>
       </c>
       <c r="G28">
-        <v>34.95</v>
+        <v>40.21</v>
       </c>
       <c r="H28">
-        <v>57.11</v>
+        <v>55.32</v>
       </c>
       <c r="I28" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -1417,19 +1417,19 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="F29">
-        <v>7.94</v>
+        <v>26.52</v>
       </c>
       <c r="G29">
-        <v>29.62</v>
+        <v>39.41</v>
       </c>
       <c r="H29">
-        <v>57.74</v>
+        <v>53.49</v>
       </c>
       <c r="I29" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -1446,16 +1446,16 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F30">
-        <v>15.71</v>
+        <v>12.77</v>
       </c>
       <c r="G30">
-        <v>22.36</v>
+        <v>35.01</v>
       </c>
       <c r="H30">
-        <v>29.08</v>
+        <v>51.04</v>
       </c>
       <c r="I30" t="s">
         <v>50</v>
@@ -1466,7 +1466,7 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C31" t="s">
         <v>46</v>
@@ -1475,19 +1475,19 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F31">
-        <v>6.04</v>
+        <v>23.97</v>
       </c>
       <c r="G31">
-        <v>20.3</v>
+        <v>29.33</v>
       </c>
       <c r="H31">
-        <v>48.51</v>
+        <v>43.72</v>
       </c>
       <c r="I31" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -1504,19 +1504,19 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F32">
-        <v>8.33</v>
+        <v>14.46</v>
       </c>
       <c r="G32">
-        <v>18.32</v>
+        <v>24.52</v>
       </c>
       <c r="H32">
-        <v>29.63</v>
+        <v>40.64</v>
       </c>
       <c r="I32" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -1533,19 +1533,19 @@
         <v>47</v>
       </c>
       <c r="E33">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="F33">
-        <v>9.619999999999999</v>
+        <v>4.56</v>
       </c>
       <c r="G33">
-        <v>17.79</v>
+        <v>24.27</v>
       </c>
       <c r="H33">
-        <v>28.37</v>
+        <v>47.2</v>
       </c>
       <c r="I33" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1553,7 +1553,7 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C34" t="s">
         <v>46</v>
@@ -1562,16 +1562,16 @@
         <v>47</v>
       </c>
       <c r="E34">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F34">
-        <v>9.93</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="G34">
-        <v>14.55</v>
+        <v>18.07</v>
       </c>
       <c r="H34">
-        <v>23.66</v>
+        <v>36.05</v>
       </c>
       <c r="I34" t="s">
         <v>51</v>
@@ -1582,7 +1582,7 @@
         <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C35" t="s">
         <v>46</v>
@@ -1602,7 +1602,7 @@
         <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C36" t="s">
         <v>46</v>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -46,121 +46,121 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع کوه هوا و</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دالان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوهستان</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه دراء</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بناب</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
     <t>منطقه حفاظت شده هرمود</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع دالان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوهستان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه دراء</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه هوا و</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بناب</t>
+    <t>منطقه شکار ممنوع مزايجان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع توت سياه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
   </si>
   <si>
     <t>پارک ملي بختگان</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
     <t>پارک ملی بمو</t>
   </si>
   <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بصيران</t>
+  </si>
+  <si>
     <t>منطقه شکار ممن.ع آق جلو</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع مهارلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
     <t>پارک ملي قطرويه</t>
   </si>
   <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع شیکوه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده برم فیروز</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع پادنا</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع شیکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بصيران</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع چاه نفت</t>
   </si>
   <si>
     <t>منطقه حفاظت شده مارگون</t>
   </si>
   <si>
+    <t>مناطق حفاظت‌شده</t>
+  </si>
+  <si>
     <t>مناطق ممنوعه شکار</t>
   </si>
   <si>
-    <t>مناطق حفاظت‌شده</t>
-  </si>
-  <si>
-    <t>1405-07-23</t>
-  </si>
-  <si>
-    <t>2026-10-15</t>
+    <t>1405-07-24</t>
+  </si>
+  <si>
+    <t>2026-10-16</t>
   </si>
   <si>
     <t>شدید</t>
@@ -634,16 +634,16 @@
         <v>47</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="F2">
-        <v>54.27</v>
+        <v>51.64</v>
       </c>
       <c r="G2">
-        <v>55.95</v>
+        <v>61.88</v>
       </c>
       <c r="H2">
-        <v>57.51</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -654,7 +654,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C3" t="s">
         <v>46</v>
@@ -666,13 +666,13 @@
         <v>8</v>
       </c>
       <c r="F3">
-        <v>54.89</v>
+        <v>59.13</v>
       </c>
       <c r="G3">
-        <v>55.84</v>
+        <v>60.58</v>
       </c>
       <c r="H3">
-        <v>57.26</v>
+        <v>62.74</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -683,7 +683,7 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C4" t="s">
         <v>46</v>
@@ -695,13 +695,13 @@
         <v>2</v>
       </c>
       <c r="F4">
-        <v>55.62</v>
+        <v>58.76</v>
       </c>
       <c r="G4">
-        <v>55.62</v>
+        <v>58.76</v>
       </c>
       <c r="H4">
-        <v>55.62</v>
+        <v>58.76</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -721,16 +721,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>52.2</v>
+        <v>56.02</v>
       </c>
       <c r="G5">
-        <v>55.01</v>
+        <v>58.14</v>
       </c>
       <c r="H5">
-        <v>59.1</v>
+        <v>61.69</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -741,7 +741,7 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
         <v>46</v>
@@ -750,16 +750,16 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F6">
-        <v>46.44</v>
+        <v>54.25</v>
       </c>
       <c r="G6">
-        <v>54.6</v>
+        <v>57.62</v>
       </c>
       <c r="H6">
-        <v>61.04</v>
+        <v>62.74</v>
       </c>
       <c r="I6" t="s">
         <v>48</v>
@@ -770,7 +770,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
         <v>46</v>
@@ -782,13 +782,13 @@
         <v>20</v>
       </c>
       <c r="F7">
-        <v>48.83</v>
+        <v>47.98</v>
       </c>
       <c r="G7">
-        <v>54.56</v>
+        <v>57.47</v>
       </c>
       <c r="H7">
-        <v>58.32</v>
+        <v>63.11</v>
       </c>
       <c r="I7" t="s">
         <v>48</v>
@@ -808,16 +808,16 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="F8">
-        <v>41.58</v>
+        <v>49.69</v>
       </c>
       <c r="G8">
-        <v>53.9</v>
+        <v>57.08</v>
       </c>
       <c r="H8">
-        <v>61.96</v>
+        <v>61.69</v>
       </c>
       <c r="I8" t="s">
         <v>48</v>
@@ -828,7 +828,7 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s">
         <v>46</v>
@@ -837,16 +837,16 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="F9">
-        <v>48.5</v>
+        <v>53.05</v>
       </c>
       <c r="G9">
-        <v>53.84</v>
+        <v>56.48</v>
       </c>
       <c r="H9">
-        <v>58.09</v>
+        <v>64.03</v>
       </c>
       <c r="I9" t="s">
         <v>48</v>
@@ -857,7 +857,7 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
         <v>46</v>
@@ -866,16 +866,16 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F10">
-        <v>50.2</v>
+        <v>48.68</v>
       </c>
       <c r="G10">
-        <v>53.57</v>
+        <v>56.04</v>
       </c>
       <c r="H10">
-        <v>56.94</v>
+        <v>61.58</v>
       </c>
       <c r="I10" t="s">
         <v>48</v>
@@ -886,7 +886,7 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
         <v>46</v>
@@ -895,16 +895,16 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F11">
-        <v>53.46</v>
+        <v>37.08</v>
       </c>
       <c r="G11">
-        <v>53.46</v>
+        <v>53.27</v>
       </c>
       <c r="H11">
-        <v>53.46</v>
+        <v>58.87</v>
       </c>
       <c r="I11" t="s">
         <v>48</v>
@@ -924,16 +924,16 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>117</v>
+        <v>4</v>
       </c>
       <c r="F12">
-        <v>34.52</v>
+        <v>47.3</v>
       </c>
       <c r="G12">
-        <v>53.4</v>
+        <v>53.05</v>
       </c>
       <c r="H12">
-        <v>64.97</v>
+        <v>59.02</v>
       </c>
       <c r="I12" t="s">
         <v>48</v>
@@ -953,16 +953,16 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F13">
-        <v>37.01</v>
+        <v>38.67</v>
       </c>
       <c r="G13">
-        <v>51.82</v>
+        <v>51.93</v>
       </c>
       <c r="H13">
-        <v>58.25</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="I13" t="s">
         <v>48</v>
@@ -973,7 +973,7 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
         <v>46</v>
@@ -982,16 +982,16 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F14">
-        <v>47.95</v>
+        <v>48.36</v>
       </c>
       <c r="G14">
-        <v>51.44</v>
+        <v>51.75</v>
       </c>
       <c r="H14">
-        <v>57.72</v>
+        <v>57.68</v>
       </c>
       <c r="I14" t="s">
         <v>48</v>
@@ -1011,16 +1011,16 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>20</v>
+        <v>117</v>
       </c>
       <c r="F15">
-        <v>48.05</v>
+        <v>45.3</v>
       </c>
       <c r="G15">
-        <v>51.07</v>
+        <v>51.63</v>
       </c>
       <c r="H15">
-        <v>55.48</v>
+        <v>64.94</v>
       </c>
       <c r="I15" t="s">
         <v>48</v>
@@ -1040,19 +1040,19 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="F16">
-        <v>43.46</v>
+        <v>45.61</v>
       </c>
       <c r="G16">
-        <v>49.76</v>
+        <v>51.35</v>
       </c>
       <c r="H16">
-        <v>55.23</v>
+        <v>64.94</v>
       </c>
       <c r="I16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1060,7 +1060,7 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C17" t="s">
         <v>46</v>
@@ -1069,19 +1069,19 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F17">
-        <v>42.16</v>
+        <v>39.94</v>
       </c>
       <c r="G17">
-        <v>47.25</v>
+        <v>50.44</v>
       </c>
       <c r="H17">
-        <v>53.72</v>
+        <v>57.22</v>
       </c>
       <c r="I17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1098,16 +1098,16 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F18">
-        <v>33.16</v>
+        <v>45.22</v>
       </c>
       <c r="G18">
-        <v>47.25</v>
+        <v>48.51</v>
       </c>
       <c r="H18">
-        <v>59.6</v>
+        <v>55.05</v>
       </c>
       <c r="I18" t="s">
         <v>49</v>
@@ -1118,7 +1118,7 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
         <v>46</v>
@@ -1127,16 +1127,16 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F19">
-        <v>38.47</v>
+        <v>40.86</v>
       </c>
       <c r="G19">
-        <v>47.21</v>
+        <v>48.47</v>
       </c>
       <c r="H19">
-        <v>57.41</v>
+        <v>57.52</v>
       </c>
       <c r="I19" t="s">
         <v>49</v>
@@ -1147,7 +1147,7 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C20" t="s">
         <v>46</v>
@@ -1156,16 +1156,16 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="F20">
-        <v>28.35</v>
+        <v>25.67</v>
       </c>
       <c r="G20">
-        <v>46.22</v>
+        <v>48.31</v>
       </c>
       <c r="H20">
-        <v>56.84</v>
+        <v>57.24</v>
       </c>
       <c r="I20" t="s">
         <v>49</v>
@@ -1176,7 +1176,7 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C21" t="s">
         <v>46</v>
@@ -1185,16 +1185,16 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F21">
-        <v>38.26</v>
+        <v>46.77</v>
       </c>
       <c r="G21">
-        <v>44.87</v>
+        <v>47.45</v>
       </c>
       <c r="H21">
-        <v>55.32</v>
+        <v>48.13</v>
       </c>
       <c r="I21" t="s">
         <v>49</v>
@@ -1205,7 +1205,7 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C22" t="s">
         <v>46</v>
@@ -1214,16 +1214,16 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F22">
-        <v>35.78</v>
+        <v>45.55</v>
       </c>
       <c r="G22">
-        <v>44.53</v>
+        <v>46.88</v>
       </c>
       <c r="H22">
-        <v>52.52</v>
+        <v>48.87</v>
       </c>
       <c r="I22" t="s">
         <v>49</v>
@@ -1243,16 +1243,16 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F23">
-        <v>36.8</v>
+        <v>41.82</v>
       </c>
       <c r="G23">
-        <v>44.44</v>
+        <v>46.2</v>
       </c>
       <c r="H23">
-        <v>57.74</v>
+        <v>53.64</v>
       </c>
       <c r="I23" t="s">
         <v>49</v>
@@ -1272,16 +1272,16 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="F24">
-        <v>38.17</v>
+        <v>27.42</v>
       </c>
       <c r="G24">
-        <v>43.22</v>
+        <v>45.81</v>
       </c>
       <c r="H24">
-        <v>49.63</v>
+        <v>54.9</v>
       </c>
       <c r="I24" t="s">
         <v>49</v>
@@ -1301,16 +1301,16 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F25">
-        <v>33.14</v>
+        <v>45.75</v>
       </c>
       <c r="G25">
-        <v>42.54</v>
+        <v>45.75</v>
       </c>
       <c r="H25">
-        <v>57.95</v>
+        <v>45.75</v>
       </c>
       <c r="I25" t="s">
         <v>49</v>
@@ -1321,7 +1321,7 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s">
         <v>46</v>
@@ -1330,16 +1330,16 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F26">
-        <v>19.45</v>
+        <v>39.4</v>
       </c>
       <c r="G26">
-        <v>41.8</v>
+        <v>43.51</v>
       </c>
       <c r="H26">
-        <v>58.68</v>
+        <v>46.74</v>
       </c>
       <c r="I26" t="s">
         <v>49</v>
@@ -1359,16 +1359,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F27">
-        <v>22.37</v>
+        <v>30.66</v>
       </c>
       <c r="G27">
-        <v>41.54</v>
+        <v>40.88</v>
       </c>
       <c r="H27">
-        <v>53.46</v>
+        <v>52.66</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1379,7 +1379,7 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C28" t="s">
         <v>46</v>
@@ -1388,16 +1388,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F28">
-        <v>16.69</v>
+        <v>35.41</v>
       </c>
       <c r="G28">
-        <v>40.21</v>
+        <v>39.18</v>
       </c>
       <c r="H28">
-        <v>55.32</v>
+        <v>45.3</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
@@ -1408,7 +1408,7 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C29" t="s">
         <v>46</v>
@@ -1417,16 +1417,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F29">
-        <v>26.52</v>
+        <v>23.43</v>
       </c>
       <c r="G29">
-        <v>39.41</v>
+        <v>38.23</v>
       </c>
       <c r="H29">
-        <v>53.49</v>
+        <v>53.12</v>
       </c>
       <c r="I29" t="s">
         <v>49</v>
@@ -1437,7 +1437,7 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C30" t="s">
         <v>46</v>
@@ -1446,16 +1446,16 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F30">
-        <v>12.77</v>
+        <v>12.16</v>
       </c>
       <c r="G30">
-        <v>35.01</v>
+        <v>35.97</v>
       </c>
       <c r="H30">
-        <v>51.04</v>
+        <v>53.91</v>
       </c>
       <c r="I30" t="s">
         <v>50</v>
@@ -1475,16 +1475,16 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F31">
-        <v>23.97</v>
+        <v>18.36</v>
       </c>
       <c r="G31">
-        <v>29.33</v>
+        <v>35.71</v>
       </c>
       <c r="H31">
-        <v>43.72</v>
+        <v>53.38</v>
       </c>
       <c r="I31" t="s">
         <v>50</v>
@@ -1507,13 +1507,13 @@
         <v>3</v>
       </c>
       <c r="F32">
-        <v>14.46</v>
+        <v>15.46</v>
       </c>
       <c r="G32">
-        <v>24.52</v>
+        <v>30.94</v>
       </c>
       <c r="H32">
-        <v>40.64</v>
+        <v>47.84</v>
       </c>
       <c r="I32" t="s">
         <v>50</v>
@@ -1533,19 +1533,19 @@
         <v>47</v>
       </c>
       <c r="E33">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="F33">
-        <v>4.56</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="G33">
-        <v>24.27</v>
+        <v>20.85</v>
       </c>
       <c r="H33">
-        <v>47.2</v>
+        <v>36.66</v>
       </c>
       <c r="I33" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1562,16 +1562,16 @@
         <v>47</v>
       </c>
       <c r="E34">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F34">
-        <v>8.359999999999999</v>
+        <v>6.38</v>
       </c>
       <c r="G34">
-        <v>18.07</v>
+        <v>17.62</v>
       </c>
       <c r="H34">
-        <v>36.05</v>
+        <v>50.16</v>
       </c>
       <c r="I34" t="s">
         <v>51</v>
@@ -1582,7 +1582,7 @@
         <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C35" t="s">
         <v>46</v>
@@ -1602,7 +1602,7 @@
         <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C36" t="s">
         <v>46</v>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="52">
   <si>
     <t>نام منطقه</t>
   </si>
@@ -46,105 +46,105 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع بناب</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دالان</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع کوه هوا و</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع دالان</t>
+    <t>منطقه شکار ممنوع کوه دراء</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مزايجان</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده هرمود</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بصيران</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>پارک ملي قطرويه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع توت سياه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع کوهستان</t>
   </si>
   <si>
-    <t>پناهگاه حيات وحش دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه دراء</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بناب</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده هرمود</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بصيران</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع مهارلو</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>پارک ملي قطرويه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
+    <t>منطقه شکار ممنوع پادنا</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع شیکوه</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
-  </si>
-  <si>
     <t>منطقه حفاظت شده برم فیروز</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع چاه نفت</t>
   </si>
   <si>
@@ -157,10 +157,10 @@
     <t>مناطق ممنوعه شکار</t>
   </si>
   <si>
-    <t>1405-07-24</t>
-  </si>
-  <si>
-    <t>2026-10-16</t>
+    <t>1405-07-25</t>
+  </si>
+  <si>
+    <t>2026-10-17</t>
   </si>
   <si>
     <t>شدید</t>
@@ -170,9 +170,6 @@
   </si>
   <si>
     <t>زیاد</t>
-  </si>
-  <si>
-    <t>متوسط</t>
   </si>
   <si>
     <t>بدون داده</t>
@@ -634,16 +631,16 @@
         <v>47</v>
       </c>
       <c r="E2">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F2">
-        <v>51.64</v>
+        <v>63.03</v>
       </c>
       <c r="G2">
-        <v>61.88</v>
+        <v>68.17</v>
       </c>
       <c r="H2">
-        <v>68.81999999999999</v>
+        <v>71.67</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -666,13 +663,13 @@
         <v>8</v>
       </c>
       <c r="F3">
-        <v>59.13</v>
+        <v>63.48</v>
       </c>
       <c r="G3">
-        <v>60.58</v>
+        <v>65.33</v>
       </c>
       <c r="H3">
-        <v>62.74</v>
+        <v>66.31</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -692,16 +689,16 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="F4">
-        <v>58.76</v>
+        <v>53.76</v>
       </c>
       <c r="G4">
-        <v>58.76</v>
+        <v>63.08</v>
       </c>
       <c r="H4">
-        <v>58.76</v>
+        <v>72.91</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -712,7 +709,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
         <v>46</v>
@@ -721,16 +718,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="F5">
-        <v>56.02</v>
+        <v>56.45</v>
       </c>
       <c r="G5">
-        <v>58.14</v>
+        <v>60.31</v>
       </c>
       <c r="H5">
-        <v>61.69</v>
+        <v>65.37</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -750,16 +747,16 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F6">
-        <v>54.25</v>
+        <v>50.34</v>
       </c>
       <c r="G6">
-        <v>57.62</v>
+        <v>58.97</v>
       </c>
       <c r="H6">
-        <v>62.74</v>
+        <v>68.8</v>
       </c>
       <c r="I6" t="s">
         <v>48</v>
@@ -779,16 +776,16 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F7">
-        <v>47.98</v>
+        <v>50.51</v>
       </c>
       <c r="G7">
-        <v>57.47</v>
+        <v>58.78</v>
       </c>
       <c r="H7">
-        <v>63.11</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="I7" t="s">
         <v>48</v>
@@ -808,16 +805,16 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F8">
-        <v>49.69</v>
+        <v>52.77</v>
       </c>
       <c r="G8">
-        <v>57.08</v>
+        <v>58.5</v>
       </c>
       <c r="H8">
-        <v>61.69</v>
+        <v>60.29</v>
       </c>
       <c r="I8" t="s">
         <v>48</v>
@@ -837,16 +834,16 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F9">
-        <v>53.05</v>
+        <v>54.72</v>
       </c>
       <c r="G9">
-        <v>56.48</v>
+        <v>57.76</v>
       </c>
       <c r="H9">
-        <v>64.03</v>
+        <v>61.89</v>
       </c>
       <c r="I9" t="s">
         <v>48</v>
@@ -857,7 +854,7 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
         <v>46</v>
@@ -866,16 +863,16 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F10">
-        <v>48.68</v>
+        <v>45.42</v>
       </c>
       <c r="G10">
-        <v>56.04</v>
+        <v>55.61</v>
       </c>
       <c r="H10">
-        <v>61.58</v>
+        <v>63.56</v>
       </c>
       <c r="I10" t="s">
         <v>48</v>
@@ -886,7 +883,7 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s">
         <v>46</v>
@@ -895,16 +892,16 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F11">
-        <v>37.08</v>
+        <v>50.25</v>
       </c>
       <c r="G11">
-        <v>53.27</v>
+        <v>55.5</v>
       </c>
       <c r="H11">
-        <v>58.87</v>
+        <v>59.77</v>
       </c>
       <c r="I11" t="s">
         <v>48</v>
@@ -924,16 +921,16 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F12">
-        <v>47.3</v>
+        <v>52.53</v>
       </c>
       <c r="G12">
-        <v>53.05</v>
+        <v>55.27</v>
       </c>
       <c r="H12">
-        <v>59.02</v>
+        <v>59.26</v>
       </c>
       <c r="I12" t="s">
         <v>48</v>
@@ -944,7 +941,7 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
         <v>46</v>
@@ -953,16 +950,16 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F13">
-        <v>38.67</v>
+        <v>51.22</v>
       </c>
       <c r="G13">
-        <v>51.93</v>
+        <v>54.83</v>
       </c>
       <c r="H13">
-        <v>65.73999999999999</v>
+        <v>61.5</v>
       </c>
       <c r="I13" t="s">
         <v>48</v>
@@ -985,13 +982,13 @@
         <v>20</v>
       </c>
       <c r="F14">
-        <v>48.36</v>
+        <v>46.59</v>
       </c>
       <c r="G14">
-        <v>51.75</v>
+        <v>54.19</v>
       </c>
       <c r="H14">
-        <v>57.68</v>
+        <v>59.2</v>
       </c>
       <c r="I14" t="s">
         <v>48</v>
@@ -1002,7 +999,7 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s">
         <v>46</v>
@@ -1011,16 +1008,16 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>117</v>
+        <v>2</v>
       </c>
       <c r="F15">
-        <v>45.3</v>
+        <v>52.86</v>
       </c>
       <c r="G15">
-        <v>51.63</v>
+        <v>54.14</v>
       </c>
       <c r="H15">
-        <v>64.94</v>
+        <v>55.43</v>
       </c>
       <c r="I15" t="s">
         <v>48</v>
@@ -1040,16 +1037,16 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="F16">
-        <v>45.61</v>
+        <v>47.59</v>
       </c>
       <c r="G16">
-        <v>51.35</v>
+        <v>53.69</v>
       </c>
       <c r="H16">
-        <v>64.94</v>
+        <v>59.34</v>
       </c>
       <c r="I16" t="s">
         <v>48</v>
@@ -1060,7 +1057,7 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
         <v>46</v>
@@ -1069,16 +1066,16 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="F17">
-        <v>39.94</v>
+        <v>44.14</v>
       </c>
       <c r="G17">
-        <v>50.44</v>
+        <v>52.99</v>
       </c>
       <c r="H17">
-        <v>57.22</v>
+        <v>61.25</v>
       </c>
       <c r="I17" t="s">
         <v>48</v>
@@ -1089,7 +1086,7 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C18" t="s">
         <v>46</v>
@@ -1098,19 +1095,19 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F18">
-        <v>45.22</v>
+        <v>31.05</v>
       </c>
       <c r="G18">
-        <v>48.51</v>
+        <v>52.8</v>
       </c>
       <c r="H18">
-        <v>55.05</v>
+        <v>68.2</v>
       </c>
       <c r="I18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1127,19 +1124,19 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="F19">
-        <v>40.86</v>
+        <v>42.54</v>
       </c>
       <c r="G19">
-        <v>48.47</v>
+        <v>52.52</v>
       </c>
       <c r="H19">
-        <v>57.52</v>
+        <v>61.25</v>
       </c>
       <c r="I19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1156,19 +1153,19 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="F20">
-        <v>25.67</v>
+        <v>47.43</v>
       </c>
       <c r="G20">
-        <v>48.31</v>
+        <v>52.17</v>
       </c>
       <c r="H20">
-        <v>57.24</v>
+        <v>59.91</v>
       </c>
       <c r="I20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1176,7 +1173,7 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C21" t="s">
         <v>46</v>
@@ -1185,19 +1182,19 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="F21">
-        <v>46.77</v>
+        <v>45.41</v>
       </c>
       <c r="G21">
-        <v>47.45</v>
+        <v>51.92</v>
       </c>
       <c r="H21">
-        <v>48.13</v>
+        <v>55.59</v>
       </c>
       <c r="I21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -1205,7 +1202,7 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C22" t="s">
         <v>46</v>
@@ -1214,19 +1211,19 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F22">
-        <v>45.55</v>
+        <v>43.7</v>
       </c>
       <c r="G22">
-        <v>46.88</v>
+        <v>50.2</v>
       </c>
       <c r="H22">
-        <v>48.87</v>
+        <v>54.23</v>
       </c>
       <c r="I22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1243,16 +1240,16 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F23">
-        <v>41.82</v>
+        <v>44.1</v>
       </c>
       <c r="G23">
-        <v>46.2</v>
+        <v>49.87</v>
       </c>
       <c r="H23">
-        <v>53.64</v>
+        <v>55.35</v>
       </c>
       <c r="I23" t="s">
         <v>49</v>
@@ -1263,7 +1260,7 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C24" t="s">
         <v>46</v>
@@ -1272,16 +1269,16 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="F24">
-        <v>27.42</v>
+        <v>44.64</v>
       </c>
       <c r="G24">
-        <v>45.81</v>
+        <v>49.09</v>
       </c>
       <c r="H24">
-        <v>54.9</v>
+        <v>56.47</v>
       </c>
       <c r="I24" t="s">
         <v>49</v>
@@ -1304,13 +1301,13 @@
         <v>4</v>
       </c>
       <c r="F25">
-        <v>45.75</v>
+        <v>49.06</v>
       </c>
       <c r="G25">
-        <v>45.75</v>
+        <v>49.06</v>
       </c>
       <c r="H25">
-        <v>45.75</v>
+        <v>49.06</v>
       </c>
       <c r="I25" t="s">
         <v>49</v>
@@ -1330,16 +1327,16 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F26">
-        <v>39.4</v>
+        <v>45.6</v>
       </c>
       <c r="G26">
-        <v>43.51</v>
+        <v>49.05</v>
       </c>
       <c r="H26">
-        <v>46.74</v>
+        <v>52.77</v>
       </c>
       <c r="I26" t="s">
         <v>49</v>
@@ -1350,7 +1347,7 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
         <v>46</v>
@@ -1359,16 +1356,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F27">
-        <v>30.66</v>
+        <v>40.03</v>
       </c>
       <c r="G27">
-        <v>40.88</v>
+        <v>48.03</v>
       </c>
       <c r="H27">
-        <v>52.66</v>
+        <v>51.94</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1388,16 +1385,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F28">
-        <v>35.41</v>
+        <v>48.01</v>
       </c>
       <c r="G28">
-        <v>39.18</v>
+        <v>48.01</v>
       </c>
       <c r="H28">
-        <v>45.3</v>
+        <v>48.01</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
@@ -1417,16 +1414,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F29">
-        <v>23.43</v>
+        <v>45.41</v>
       </c>
       <c r="G29">
-        <v>38.23</v>
+        <v>47.28</v>
       </c>
       <c r="H29">
-        <v>53.12</v>
+        <v>50.54</v>
       </c>
       <c r="I29" t="s">
         <v>49</v>
@@ -1437,7 +1434,7 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C30" t="s">
         <v>46</v>
@@ -1446,19 +1443,19 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F30">
-        <v>12.16</v>
+        <v>41.67</v>
       </c>
       <c r="G30">
-        <v>35.97</v>
+        <v>47.04</v>
       </c>
       <c r="H30">
-        <v>53.91</v>
+        <v>54.16</v>
       </c>
       <c r="I30" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -1466,7 +1463,7 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C31" t="s">
         <v>46</v>
@@ -1475,19 +1472,19 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F31">
-        <v>18.36</v>
+        <v>42.1</v>
       </c>
       <c r="G31">
-        <v>35.71</v>
+        <v>45.37</v>
       </c>
       <c r="H31">
-        <v>53.38</v>
+        <v>49.05</v>
       </c>
       <c r="I31" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -1495,7 +1492,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C32" t="s">
         <v>46</v>
@@ -1504,19 +1501,19 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="F32">
-        <v>15.46</v>
+        <v>35.12</v>
       </c>
       <c r="G32">
-        <v>30.94</v>
+        <v>44.79</v>
       </c>
       <c r="H32">
-        <v>47.84</v>
+        <v>58.57</v>
       </c>
       <c r="I32" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -1524,7 +1521,7 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C33" t="s">
         <v>46</v>
@@ -1533,19 +1530,19 @@
         <v>47</v>
       </c>
       <c r="E33">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F33">
-        <v>9.130000000000001</v>
+        <v>39.24</v>
       </c>
       <c r="G33">
-        <v>20.85</v>
+        <v>42.81</v>
       </c>
       <c r="H33">
-        <v>36.66</v>
+        <v>47.33</v>
       </c>
       <c r="I33" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1553,7 +1550,7 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C34" t="s">
         <v>46</v>
@@ -1562,19 +1559,19 @@
         <v>47</v>
       </c>
       <c r="E34">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F34">
-        <v>6.38</v>
+        <v>30.36</v>
       </c>
       <c r="G34">
-        <v>17.62</v>
+        <v>36.66</v>
       </c>
       <c r="H34">
-        <v>50.16</v>
+        <v>51.88</v>
       </c>
       <c r="I34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -1594,7 +1591,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -1614,7 +1611,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -49,99 +49,99 @@
     <t>منطقه شکار ممنوع بناب</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع کوه هوا و</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مزايجان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه دراء</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع دالان</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه هوا و</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه دراء</t>
+    <t>منطقه شکار ممنوع شیکوه</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع دره باغ</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع روشن کوه</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش دره باغ</t>
+    <t>منطقه شکار ممن.ع آق جلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
   </si>
   <si>
     <t>منطقه حفاظت شده ارژن و پريشان</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوهستان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
   </si>
   <si>
     <t>منطقه حفاظت شده هرمود</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بصيران</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع توت سياه</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>پارک ملي قطرويه</t>
   </si>
   <si>
     <t>منطقه حفاظت شده بهرام گور</t>
   </si>
   <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بصيران</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>پارک ملي قطرويه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوهستان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع مهارلو</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع شیکوه</t>
-  </si>
-  <si>
     <t>منطقه حفاظت شده برم فیروز</t>
   </si>
   <si>
@@ -157,19 +157,19 @@
     <t>مناطق ممنوعه شکار</t>
   </si>
   <si>
-    <t>1405-07-25</t>
-  </si>
-  <si>
-    <t>2026-10-17</t>
+    <t>1405-07-26</t>
+  </si>
+  <si>
+    <t>2026-10-18</t>
+  </si>
+  <si>
+    <t>بسیار شدید</t>
   </si>
   <si>
     <t>شدید</t>
   </si>
   <si>
     <t>خیلی زیاد</t>
-  </si>
-  <si>
-    <t>زیاد</t>
   </si>
   <si>
     <t>بدون داده</t>
@@ -634,13 +634,13 @@
         <v>20</v>
       </c>
       <c r="F2">
-        <v>63.03</v>
+        <v>70.05</v>
       </c>
       <c r="G2">
-        <v>68.17</v>
+        <v>74.94</v>
       </c>
       <c r="H2">
-        <v>71.67</v>
+        <v>79.77</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -660,19 +660,19 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="F3">
-        <v>63.48</v>
+        <v>59.37</v>
       </c>
       <c r="G3">
-        <v>65.33</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="H3">
-        <v>66.31</v>
+        <v>78.47</v>
       </c>
       <c r="I3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -689,19 +689,19 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="F4">
-        <v>53.76</v>
+        <v>58.83</v>
       </c>
       <c r="G4">
-        <v>63.08</v>
+        <v>61.81</v>
       </c>
       <c r="H4">
-        <v>72.91</v>
+        <v>65.52</v>
       </c>
       <c r="I4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -721,16 +721,16 @@
         <v>33</v>
       </c>
       <c r="F5">
-        <v>56.45</v>
+        <v>57.95</v>
       </c>
       <c r="G5">
-        <v>60.31</v>
+        <v>60.98</v>
       </c>
       <c r="H5">
-        <v>65.37</v>
+        <v>68.59</v>
       </c>
       <c r="I5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -738,7 +738,7 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s">
         <v>46</v>
@@ -747,19 +747,19 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F6">
-        <v>50.34</v>
+        <v>53.75</v>
       </c>
       <c r="G6">
-        <v>58.97</v>
+        <v>60.88</v>
       </c>
       <c r="H6">
-        <v>68.8</v>
+        <v>68.06999999999999</v>
       </c>
       <c r="I6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -776,19 +776,19 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F7">
-        <v>50.51</v>
+        <v>57.48</v>
       </c>
       <c r="G7">
-        <v>58.78</v>
+        <v>60.66</v>
       </c>
       <c r="H7">
-        <v>64.76000000000001</v>
+        <v>67.01000000000001</v>
       </c>
       <c r="I7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -805,19 +805,19 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="F8">
-        <v>52.77</v>
+        <v>54.97</v>
       </c>
       <c r="G8">
-        <v>58.5</v>
+        <v>60</v>
       </c>
       <c r="H8">
-        <v>60.29</v>
+        <v>65.22</v>
       </c>
       <c r="I8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -825,7 +825,7 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
         <v>46</v>
@@ -834,19 +834,19 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F9">
-        <v>54.72</v>
+        <v>50.09</v>
       </c>
       <c r="G9">
-        <v>57.76</v>
+        <v>59.36</v>
       </c>
       <c r="H9">
-        <v>61.89</v>
+        <v>67.97</v>
       </c>
       <c r="I9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -854,7 +854,7 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
         <v>46</v>
@@ -863,19 +863,19 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F10">
-        <v>45.42</v>
+        <v>54.85</v>
       </c>
       <c r="G10">
-        <v>55.61</v>
+        <v>58.77</v>
       </c>
       <c r="H10">
-        <v>63.56</v>
+        <v>63.99</v>
       </c>
       <c r="I10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -883,7 +883,7 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
         <v>46</v>
@@ -892,19 +892,19 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="F11">
-        <v>50.25</v>
+        <v>54.1</v>
       </c>
       <c r="G11">
-        <v>55.5</v>
+        <v>58.6</v>
       </c>
       <c r="H11">
-        <v>59.77</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="I11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -921,19 +921,19 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F12">
-        <v>52.53</v>
+        <v>53.13</v>
       </c>
       <c r="G12">
-        <v>55.27</v>
+        <v>58.38</v>
       </c>
       <c r="H12">
-        <v>59.26</v>
+        <v>63.45</v>
       </c>
       <c r="I12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -950,19 +950,19 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="F13">
-        <v>51.22</v>
+        <v>49.93</v>
       </c>
       <c r="G13">
-        <v>54.83</v>
+        <v>57.89</v>
       </c>
       <c r="H13">
-        <v>61.5</v>
+        <v>60.66</v>
       </c>
       <c r="I13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -970,7 +970,7 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
         <v>46</v>
@@ -979,19 +979,19 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F14">
-        <v>46.59</v>
+        <v>56.47</v>
       </c>
       <c r="G14">
-        <v>54.19</v>
+        <v>57.65</v>
       </c>
       <c r="H14">
-        <v>59.2</v>
+        <v>58.63</v>
       </c>
       <c r="I14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -1008,19 +1008,19 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F15">
-        <v>52.86</v>
+        <v>51.18</v>
       </c>
       <c r="G15">
-        <v>54.14</v>
+        <v>57.11</v>
       </c>
       <c r="H15">
-        <v>55.43</v>
+        <v>62.11</v>
       </c>
       <c r="I15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1028,7 +1028,7 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
         <v>46</v>
@@ -1037,19 +1037,19 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="F16">
-        <v>47.59</v>
+        <v>53.33</v>
       </c>
       <c r="G16">
-        <v>53.69</v>
+        <v>55.82</v>
       </c>
       <c r="H16">
-        <v>59.34</v>
+        <v>58.31</v>
       </c>
       <c r="I16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1057,7 +1057,7 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C17" t="s">
         <v>46</v>
@@ -1066,19 +1066,19 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="F17">
-        <v>44.14</v>
+        <v>51.54</v>
       </c>
       <c r="G17">
-        <v>52.99</v>
+        <v>55.43</v>
       </c>
       <c r="H17">
-        <v>61.25</v>
+        <v>60.06</v>
       </c>
       <c r="I17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1095,19 +1095,19 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="F18">
-        <v>31.05</v>
+        <v>48.68</v>
       </c>
       <c r="G18">
-        <v>52.8</v>
+        <v>55.28</v>
       </c>
       <c r="H18">
-        <v>68.2</v>
+        <v>62.57</v>
       </c>
       <c r="I18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1124,19 +1124,19 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>117</v>
+        <v>20</v>
       </c>
       <c r="F19">
-        <v>42.54</v>
+        <v>48.35</v>
       </c>
       <c r="G19">
-        <v>52.52</v>
+        <v>54.94</v>
       </c>
       <c r="H19">
-        <v>61.25</v>
+        <v>59.72</v>
       </c>
       <c r="I19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1153,19 +1153,19 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="F20">
-        <v>47.43</v>
+        <v>48.18</v>
       </c>
       <c r="G20">
-        <v>52.17</v>
+        <v>53.99</v>
       </c>
       <c r="H20">
-        <v>59.91</v>
+        <v>59.35</v>
       </c>
       <c r="I20" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1173,7 +1173,7 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C21" t="s">
         <v>46</v>
@@ -1182,19 +1182,19 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="F21">
-        <v>45.41</v>
+        <v>53.84</v>
       </c>
       <c r="G21">
-        <v>51.92</v>
+        <v>53.84</v>
       </c>
       <c r="H21">
-        <v>55.59</v>
+        <v>53.84</v>
       </c>
       <c r="I21" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -1214,16 +1214,16 @@
         <v>16</v>
       </c>
       <c r="F22">
-        <v>43.7</v>
+        <v>49.9</v>
       </c>
       <c r="G22">
-        <v>50.2</v>
+        <v>52.88</v>
       </c>
       <c r="H22">
-        <v>54.23</v>
+        <v>54.97</v>
       </c>
       <c r="I22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1243,13 +1243,13 @@
         <v>13</v>
       </c>
       <c r="F23">
-        <v>44.1</v>
+        <v>45.85</v>
       </c>
       <c r="G23">
-        <v>49.87</v>
+        <v>52.1</v>
       </c>
       <c r="H23">
-        <v>55.35</v>
+        <v>54.31</v>
       </c>
       <c r="I23" t="s">
         <v>49</v>
@@ -1260,7 +1260,7 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C24" t="s">
         <v>46</v>
@@ -1269,16 +1269,16 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F24">
-        <v>44.64</v>
+        <v>42.59</v>
       </c>
       <c r="G24">
-        <v>49.09</v>
+        <v>52.08</v>
       </c>
       <c r="H24">
-        <v>56.47</v>
+        <v>61.84</v>
       </c>
       <c r="I24" t="s">
         <v>49</v>
@@ -1298,16 +1298,16 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>4</v>
+        <v>65</v>
       </c>
       <c r="F25">
-        <v>49.06</v>
+        <v>46.06</v>
       </c>
       <c r="G25">
-        <v>49.06</v>
+        <v>50.6</v>
       </c>
       <c r="H25">
-        <v>49.06</v>
+        <v>63.71</v>
       </c>
       <c r="I25" t="s">
         <v>49</v>
@@ -1318,7 +1318,7 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C26" t="s">
         <v>46</v>
@@ -1327,16 +1327,16 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F26">
-        <v>45.6</v>
+        <v>48.73</v>
       </c>
       <c r="G26">
-        <v>49.05</v>
+        <v>50.52</v>
       </c>
       <c r="H26">
-        <v>52.77</v>
+        <v>55.45</v>
       </c>
       <c r="I26" t="s">
         <v>49</v>
@@ -1359,13 +1359,13 @@
         <v>5</v>
       </c>
       <c r="F27">
-        <v>40.03</v>
+        <v>46.15</v>
       </c>
       <c r="G27">
-        <v>48.03</v>
+        <v>50.38</v>
       </c>
       <c r="H27">
-        <v>51.94</v>
+        <v>54.56</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1385,16 +1385,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="F28">
-        <v>48.01</v>
+        <v>40.04</v>
       </c>
       <c r="G28">
-        <v>48.01</v>
+        <v>50.35</v>
       </c>
       <c r="H28">
-        <v>48.01</v>
+        <v>73.16</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
@@ -1405,7 +1405,7 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C29" t="s">
         <v>46</v>
@@ -1414,16 +1414,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F29">
-        <v>45.41</v>
+        <v>46.83</v>
       </c>
       <c r="G29">
-        <v>47.28</v>
+        <v>50.19</v>
       </c>
       <c r="H29">
-        <v>50.54</v>
+        <v>55.83</v>
       </c>
       <c r="I29" t="s">
         <v>49</v>
@@ -1434,7 +1434,7 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C30" t="s">
         <v>46</v>
@@ -1443,16 +1443,16 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>12</v>
+        <v>117</v>
       </c>
       <c r="F30">
-        <v>41.67</v>
+        <v>44.74</v>
       </c>
       <c r="G30">
-        <v>47.04</v>
+        <v>50.07</v>
       </c>
       <c r="H30">
-        <v>54.16</v>
+        <v>63.71</v>
       </c>
       <c r="I30" t="s">
         <v>49</v>
@@ -1463,7 +1463,7 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C31" t="s">
         <v>46</v>
@@ -1472,19 +1472,19 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F31">
-        <v>42.1</v>
+        <v>48.64</v>
       </c>
       <c r="G31">
-        <v>45.37</v>
+        <v>48.64</v>
       </c>
       <c r="H31">
-        <v>49.05</v>
+        <v>48.64</v>
       </c>
       <c r="I31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -1492,7 +1492,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C32" t="s">
         <v>46</v>
@@ -1501,19 +1501,19 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F32">
-        <v>35.12</v>
+        <v>42.87</v>
       </c>
       <c r="G32">
-        <v>44.79</v>
+        <v>48.62</v>
       </c>
       <c r="H32">
-        <v>58.57</v>
+        <v>58.1</v>
       </c>
       <c r="I32" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -1530,19 +1530,19 @@
         <v>47</v>
       </c>
       <c r="E33">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F33">
-        <v>39.24</v>
+        <v>43.14</v>
       </c>
       <c r="G33">
-        <v>42.81</v>
+        <v>46.15</v>
       </c>
       <c r="H33">
-        <v>47.33</v>
+        <v>54.91</v>
       </c>
       <c r="I33" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1562,13 +1562,13 @@
         <v>8</v>
       </c>
       <c r="F34">
-        <v>30.36</v>
+        <v>34.29</v>
       </c>
       <c r="G34">
-        <v>36.66</v>
+        <v>43.31</v>
       </c>
       <c r="H34">
-        <v>51.88</v>
+        <v>49.83</v>
       </c>
       <c r="I34" t="s">
         <v>50</v>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="54">
   <si>
     <t>نام منطقه</t>
   </si>
@@ -49,102 +49,102 @@
     <t>منطقه شکار ممنوع بناب</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع کوه دراء</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مزايجان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دالان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
+  </si>
+  <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوهستان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده هرمود</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع کوه هوا و</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه دراء</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دالان</t>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مهارلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>پارک ملي قطرويه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده برم فیروز</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع شیکوه</t>
   </si>
   <si>
+    <t>پناهگاه حيات وحش دره باغ</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع دره باغ</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوهستان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده هرمود</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع بصيران</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع توت سياه</t>
   </si>
   <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>پارک ملي قطرويه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع چاه نفت</t>
   </si>
   <si>
@@ -157,19 +157,25 @@
     <t>مناطق ممنوعه شکار</t>
   </si>
   <si>
-    <t>1405-07-26</t>
-  </si>
-  <si>
-    <t>2026-10-18</t>
-  </si>
-  <si>
-    <t>بسیار شدید</t>
+    <t>1405-07-27</t>
+  </si>
+  <si>
+    <t>2026-10-19</t>
   </si>
   <si>
     <t>شدید</t>
   </si>
   <si>
     <t>خیلی زیاد</t>
+  </si>
+  <si>
+    <t>زیاد</t>
+  </si>
+  <si>
+    <t>متوسط</t>
+  </si>
+  <si>
+    <t>کم</t>
   </si>
   <si>
     <t>بدون داده</t>
@@ -634,13 +640,13 @@
         <v>20</v>
       </c>
       <c r="F2">
-        <v>70.05</v>
+        <v>58.17</v>
       </c>
       <c r="G2">
-        <v>74.94</v>
+        <v>65.02</v>
       </c>
       <c r="H2">
-        <v>79.77</v>
+        <v>69.66</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -660,19 +666,19 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F3">
-        <v>59.37</v>
+        <v>54.87</v>
       </c>
       <c r="G3">
-        <v>65.56999999999999</v>
+        <v>58.4</v>
       </c>
       <c r="H3">
-        <v>78.47</v>
+        <v>63.78</v>
       </c>
       <c r="I3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -692,16 +698,16 @@
         <v>15</v>
       </c>
       <c r="F4">
-        <v>58.83</v>
+        <v>54.4</v>
       </c>
       <c r="G4">
-        <v>61.81</v>
+        <v>58.16</v>
       </c>
       <c r="H4">
-        <v>65.52</v>
+        <v>64.81999999999999</v>
       </c>
       <c r="I4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -709,7 +715,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
         <v>46</v>
@@ -718,19 +724,19 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F5">
-        <v>57.95</v>
+        <v>53.31</v>
       </c>
       <c r="G5">
-        <v>60.98</v>
+        <v>57.4</v>
       </c>
       <c r="H5">
-        <v>68.59</v>
+        <v>62.36</v>
       </c>
       <c r="I5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -738,7 +744,7 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
         <v>46</v>
@@ -747,19 +753,19 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F6">
-        <v>53.75</v>
+        <v>52.34</v>
       </c>
       <c r="G6">
-        <v>60.88</v>
+        <v>56.93</v>
       </c>
       <c r="H6">
-        <v>68.06999999999999</v>
+        <v>63.2</v>
       </c>
       <c r="I6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -779,16 +785,16 @@
         <v>8</v>
       </c>
       <c r="F7">
-        <v>57.48</v>
+        <v>54.82</v>
       </c>
       <c r="G7">
-        <v>60.66</v>
+        <v>55.26</v>
       </c>
       <c r="H7">
-        <v>67.01000000000001</v>
+        <v>55.73</v>
       </c>
       <c r="I7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -796,7 +802,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
         <v>46</v>
@@ -808,16 +814,16 @@
         <v>3</v>
       </c>
       <c r="F8">
-        <v>54.97</v>
+        <v>51.04</v>
       </c>
       <c r="G8">
-        <v>60</v>
+        <v>52.69</v>
       </c>
       <c r="H8">
-        <v>65.22</v>
+        <v>55.12</v>
       </c>
       <c r="I8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -837,16 +843,16 @@
         <v>12</v>
       </c>
       <c r="F9">
-        <v>50.09</v>
+        <v>43.5</v>
       </c>
       <c r="G9">
-        <v>59.36</v>
+        <v>51.89</v>
       </c>
       <c r="H9">
-        <v>67.97</v>
+        <v>59.04</v>
       </c>
       <c r="I9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -854,7 +860,7 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
         <v>46</v>
@@ -863,19 +869,19 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F10">
-        <v>54.85</v>
+        <v>43.26</v>
       </c>
       <c r="G10">
-        <v>58.77</v>
+        <v>51.82</v>
       </c>
       <c r="H10">
-        <v>63.99</v>
+        <v>56.62</v>
       </c>
       <c r="I10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -883,7 +889,7 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s">
         <v>46</v>
@@ -892,19 +898,19 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F11">
-        <v>54.1</v>
+        <v>48.74</v>
       </c>
       <c r="G11">
-        <v>58.6</v>
+        <v>51.61</v>
       </c>
       <c r="H11">
-        <v>64.54000000000001</v>
+        <v>55.41</v>
       </c>
       <c r="I11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -912,7 +918,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
         <v>46</v>
@@ -921,19 +927,19 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F12">
-        <v>53.13</v>
+        <v>45.45</v>
       </c>
       <c r="G12">
-        <v>58.38</v>
+        <v>51.13</v>
       </c>
       <c r="H12">
-        <v>63.45</v>
+        <v>54.34</v>
       </c>
       <c r="I12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -941,7 +947,7 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s">
         <v>46</v>
@@ -950,19 +956,19 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="F13">
-        <v>49.93</v>
+        <v>50.66</v>
       </c>
       <c r="G13">
-        <v>57.89</v>
+        <v>50.66</v>
       </c>
       <c r="H13">
-        <v>60.66</v>
+        <v>50.66</v>
       </c>
       <c r="I13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -970,7 +976,7 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
         <v>46</v>
@@ -979,19 +985,19 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="F14">
-        <v>56.47</v>
+        <v>44.45</v>
       </c>
       <c r="G14">
-        <v>57.65</v>
+        <v>50.58</v>
       </c>
       <c r="H14">
-        <v>58.63</v>
+        <v>57.66</v>
       </c>
       <c r="I14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -999,7 +1005,7 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
         <v>46</v>
@@ -1008,19 +1014,19 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="F15">
-        <v>51.18</v>
+        <v>42.73</v>
       </c>
       <c r="G15">
-        <v>57.11</v>
+        <v>50.07</v>
       </c>
       <c r="H15">
-        <v>62.11</v>
+        <v>58.58</v>
       </c>
       <c r="I15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1037,16 +1043,16 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="F16">
-        <v>53.33</v>
+        <v>43.95</v>
       </c>
       <c r="G16">
-        <v>55.82</v>
+        <v>49.83</v>
       </c>
       <c r="H16">
-        <v>58.31</v>
+        <v>54.52</v>
       </c>
       <c r="I16" t="s">
         <v>49</v>
@@ -1057,7 +1063,7 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
         <v>46</v>
@@ -1066,16 +1072,16 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F17">
-        <v>51.54</v>
+        <v>46.11</v>
       </c>
       <c r="G17">
-        <v>55.43</v>
+        <v>49.54</v>
       </c>
       <c r="H17">
-        <v>60.06</v>
+        <v>53.33</v>
       </c>
       <c r="I17" t="s">
         <v>49</v>
@@ -1095,16 +1101,16 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="F18">
-        <v>48.68</v>
+        <v>45.57</v>
       </c>
       <c r="G18">
-        <v>55.28</v>
+        <v>49.03</v>
       </c>
       <c r="H18">
-        <v>62.57</v>
+        <v>52.48</v>
       </c>
       <c r="I18" t="s">
         <v>49</v>
@@ -1115,7 +1121,7 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C19" t="s">
         <v>46</v>
@@ -1124,16 +1130,16 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F19">
-        <v>48.35</v>
+        <v>45.43</v>
       </c>
       <c r="G19">
-        <v>54.94</v>
+        <v>48.92</v>
       </c>
       <c r="H19">
-        <v>59.72</v>
+        <v>53.88</v>
       </c>
       <c r="I19" t="s">
         <v>49</v>
@@ -1144,7 +1150,7 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C20" t="s">
         <v>46</v>
@@ -1153,16 +1159,16 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>12</v>
+        <v>117</v>
       </c>
       <c r="F20">
-        <v>48.18</v>
+        <v>29.28</v>
       </c>
       <c r="G20">
-        <v>53.99</v>
+        <v>48.76</v>
       </c>
       <c r="H20">
-        <v>59.35</v>
+        <v>58.58</v>
       </c>
       <c r="I20" t="s">
         <v>49</v>
@@ -1182,16 +1188,16 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="F21">
-        <v>53.84</v>
+        <v>43.62</v>
       </c>
       <c r="G21">
-        <v>53.84</v>
+        <v>48.75</v>
       </c>
       <c r="H21">
-        <v>53.84</v>
+        <v>52.96</v>
       </c>
       <c r="I21" t="s">
         <v>49</v>
@@ -1202,7 +1208,7 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C22" t="s">
         <v>46</v>
@@ -1211,16 +1217,16 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="F22">
-        <v>49.9</v>
+        <v>39.98</v>
       </c>
       <c r="G22">
-        <v>52.88</v>
+        <v>48.01</v>
       </c>
       <c r="H22">
-        <v>54.97</v>
+        <v>53.48</v>
       </c>
       <c r="I22" t="s">
         <v>49</v>
@@ -1231,7 +1237,7 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C23" t="s">
         <v>46</v>
@@ -1240,16 +1246,16 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F23">
-        <v>45.85</v>
+        <v>42.06</v>
       </c>
       <c r="G23">
-        <v>52.1</v>
+        <v>47.87</v>
       </c>
       <c r="H23">
-        <v>54.31</v>
+        <v>53.89</v>
       </c>
       <c r="I23" t="s">
         <v>49</v>
@@ -1260,7 +1266,7 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C24" t="s">
         <v>46</v>
@@ -1269,16 +1275,16 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F24">
-        <v>42.59</v>
+        <v>41.84</v>
       </c>
       <c r="G24">
-        <v>52.08</v>
+        <v>47.82</v>
       </c>
       <c r="H24">
-        <v>61.84</v>
+        <v>52.58</v>
       </c>
       <c r="I24" t="s">
         <v>49</v>
@@ -1289,7 +1295,7 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C25" t="s">
         <v>46</v>
@@ -1298,16 +1304,16 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="F25">
-        <v>46.06</v>
+        <v>44.42</v>
       </c>
       <c r="G25">
-        <v>50.6</v>
+        <v>47.16</v>
       </c>
       <c r="H25">
-        <v>63.71</v>
+        <v>53.89</v>
       </c>
       <c r="I25" t="s">
         <v>49</v>
@@ -1318,7 +1324,7 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s">
         <v>46</v>
@@ -1327,16 +1333,16 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F26">
-        <v>48.73</v>
+        <v>38.38</v>
       </c>
       <c r="G26">
-        <v>50.52</v>
+        <v>46.21</v>
       </c>
       <c r="H26">
-        <v>55.45</v>
+        <v>53.56</v>
       </c>
       <c r="I26" t="s">
         <v>49</v>
@@ -1356,16 +1362,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F27">
-        <v>46.15</v>
+        <v>41.3</v>
       </c>
       <c r="G27">
-        <v>50.38</v>
+        <v>41.3</v>
       </c>
       <c r="H27">
-        <v>54.56</v>
+        <v>41.3</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1376,7 +1382,7 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C28" t="s">
         <v>46</v>
@@ -1385,16 +1391,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="F28">
-        <v>40.04</v>
+        <v>34.44</v>
       </c>
       <c r="G28">
-        <v>50.35</v>
+        <v>38.16</v>
       </c>
       <c r="H28">
-        <v>73.16</v>
+        <v>46.22</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
@@ -1405,7 +1411,7 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C29" t="s">
         <v>46</v>
@@ -1414,19 +1420,19 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F29">
-        <v>46.83</v>
+        <v>6.91</v>
       </c>
       <c r="G29">
-        <v>50.19</v>
+        <v>32.24</v>
       </c>
       <c r="H29">
-        <v>55.83</v>
+        <v>53.02</v>
       </c>
       <c r="I29" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -1434,7 +1440,7 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C30" t="s">
         <v>46</v>
@@ -1443,19 +1449,19 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>117</v>
+        <v>3</v>
       </c>
       <c r="F30">
-        <v>44.74</v>
+        <v>9.25</v>
       </c>
       <c r="G30">
-        <v>50.07</v>
+        <v>23.38</v>
       </c>
       <c r="H30">
-        <v>63.71</v>
+        <v>41.52</v>
       </c>
       <c r="I30" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -1472,16 +1478,16 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F31">
-        <v>48.64</v>
+        <v>18.21</v>
       </c>
       <c r="G31">
-        <v>48.64</v>
+        <v>21.58</v>
       </c>
       <c r="H31">
-        <v>48.64</v>
+        <v>28.15</v>
       </c>
       <c r="I31" t="s">
         <v>50</v>
@@ -1492,7 +1498,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C32" t="s">
         <v>46</v>
@@ -1501,19 +1507,19 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F32">
-        <v>42.87</v>
+        <v>7.94</v>
       </c>
       <c r="G32">
-        <v>48.62</v>
+        <v>17.94</v>
       </c>
       <c r="H32">
-        <v>58.1</v>
+        <v>52.8</v>
       </c>
       <c r="I32" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -1530,19 +1536,19 @@
         <v>47</v>
       </c>
       <c r="E33">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F33">
-        <v>43.14</v>
+        <v>6.13</v>
       </c>
       <c r="G33">
-        <v>46.15</v>
+        <v>13.12</v>
       </c>
       <c r="H33">
-        <v>54.91</v>
+        <v>37.16</v>
       </c>
       <c r="I33" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1550,7 +1556,7 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C34" t="s">
         <v>46</v>
@@ -1559,19 +1565,19 @@
         <v>47</v>
       </c>
       <c r="E34">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F34">
-        <v>34.29</v>
+        <v>5.66</v>
       </c>
       <c r="G34">
-        <v>43.31</v>
+        <v>7.9</v>
       </c>
       <c r="H34">
-        <v>49.83</v>
+        <v>12.68</v>
       </c>
       <c r="I34" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -1591,7 +1597,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -1611,7 +1617,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="52">
   <si>
     <t>نام منطقه</t>
   </si>
@@ -46,105 +46,105 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع کوه دراء</t>
+  </si>
+  <si>
+    <t>پارک ملي قطرويه</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع بناب</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه دراء</t>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دالان</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه هوا و</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع مزايجان</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
     <t>منطقه حفاظت شده میانجنگل فسا</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دالان</t>
-  </si>
-  <si>
     <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع توت سياه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مهارلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع خرمنکوه</t>
   </si>
   <si>
-    <t>پارک ملی بمو</t>
+    <t>منطقه شکار ممنوع کوه سياه</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع کوهستان</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
   </si>
   <si>
     <t>منطقه حفاظت شده هرمود</t>
   </si>
   <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه هوا و</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>پارک ملي قطرويه</t>
+    <t>منطقه شکار ممنوع شیکوه</t>
   </si>
   <si>
     <t>منطقه حفاظت شده برم فیروز</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع شیکوه</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع بصيران</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع چاه نفت</t>
   </si>
   <si>
@@ -157,10 +157,10 @@
     <t>مناطق ممنوعه شکار</t>
   </si>
   <si>
-    <t>1405-07-27</t>
-  </si>
-  <si>
-    <t>2026-10-19</t>
+    <t>1405-07-28</t>
+  </si>
+  <si>
+    <t>2026-10-20</t>
   </si>
   <si>
     <t>شدید</t>
@@ -170,12 +170,6 @@
   </si>
   <si>
     <t>زیاد</t>
-  </si>
-  <si>
-    <t>متوسط</t>
-  </si>
-  <si>
-    <t>کم</t>
   </si>
   <si>
     <t>بدون داده</t>
@@ -637,16 +631,16 @@
         <v>47</v>
       </c>
       <c r="E2">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F2">
-        <v>58.17</v>
+        <v>49.14</v>
       </c>
       <c r="G2">
-        <v>65.02</v>
+        <v>54.93</v>
       </c>
       <c r="H2">
-        <v>69.66</v>
+        <v>61.77</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -657,7 +651,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s">
         <v>46</v>
@@ -666,16 +660,16 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>54.87</v>
+        <v>54.33</v>
       </c>
       <c r="G3">
-        <v>58.4</v>
+        <v>54.33</v>
       </c>
       <c r="H3">
-        <v>63.78</v>
+        <v>54.33</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -695,16 +689,16 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F4">
-        <v>54.4</v>
+        <v>46.85</v>
       </c>
       <c r="G4">
-        <v>58.16</v>
+        <v>54.09</v>
       </c>
       <c r="H4">
-        <v>64.81999999999999</v>
+        <v>57.23</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -724,16 +718,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F5">
-        <v>53.31</v>
+        <v>41.29</v>
       </c>
       <c r="G5">
-        <v>57.4</v>
+        <v>52.59</v>
       </c>
       <c r="H5">
-        <v>62.36</v>
+        <v>56.88</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -744,7 +738,7 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s">
         <v>46</v>
@@ -753,16 +747,16 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F6">
-        <v>52.34</v>
+        <v>47.75</v>
       </c>
       <c r="G6">
-        <v>56.93</v>
+        <v>51.39</v>
       </c>
       <c r="H6">
-        <v>63.2</v>
+        <v>54.33</v>
       </c>
       <c r="I6" t="s">
         <v>48</v>
@@ -785,13 +779,13 @@
         <v>8</v>
       </c>
       <c r="F7">
-        <v>54.82</v>
+        <v>49.13</v>
       </c>
       <c r="G7">
-        <v>55.26</v>
+        <v>51.14</v>
       </c>
       <c r="H7">
-        <v>55.73</v>
+        <v>53.03</v>
       </c>
       <c r="I7" t="s">
         <v>48</v>
@@ -811,16 +805,16 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>65</v>
       </c>
       <c r="F8">
-        <v>51.04</v>
+        <v>44.43</v>
       </c>
       <c r="G8">
-        <v>52.69</v>
+        <v>50.45</v>
       </c>
       <c r="H8">
-        <v>55.12</v>
+        <v>56.8</v>
       </c>
       <c r="I8" t="s">
         <v>48</v>
@@ -831,7 +825,7 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s">
         <v>46</v>
@@ -840,16 +834,16 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>12</v>
+        <v>117</v>
       </c>
       <c r="F9">
-        <v>43.5</v>
+        <v>44.43</v>
       </c>
       <c r="G9">
-        <v>51.89</v>
+        <v>50.24</v>
       </c>
       <c r="H9">
-        <v>59.04</v>
+        <v>57.06</v>
       </c>
       <c r="I9" t="s">
         <v>48</v>
@@ -860,7 +854,7 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
         <v>46</v>
@@ -872,16 +866,16 @@
         <v>20</v>
       </c>
       <c r="F10">
-        <v>43.26</v>
+        <v>47.16</v>
       </c>
       <c r="G10">
-        <v>51.82</v>
+        <v>49.92</v>
       </c>
       <c r="H10">
-        <v>56.62</v>
+        <v>53.37</v>
       </c>
       <c r="I10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -898,19 +892,19 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F11">
-        <v>48.74</v>
+        <v>46.49</v>
       </c>
       <c r="G11">
-        <v>51.61</v>
+        <v>49.73</v>
       </c>
       <c r="H11">
-        <v>55.41</v>
+        <v>55.83</v>
       </c>
       <c r="I11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -918,7 +912,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
         <v>46</v>
@@ -927,19 +921,19 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F12">
-        <v>45.45</v>
+        <v>35.65</v>
       </c>
       <c r="G12">
-        <v>51.13</v>
+        <v>49.66</v>
       </c>
       <c r="H12">
-        <v>54.34</v>
+        <v>58.09</v>
       </c>
       <c r="I12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -956,19 +950,19 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="F13">
-        <v>50.66</v>
+        <v>42.3</v>
       </c>
       <c r="G13">
-        <v>50.66</v>
+        <v>49.52</v>
       </c>
       <c r="H13">
-        <v>50.66</v>
+        <v>53.43</v>
       </c>
       <c r="I13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -985,19 +979,19 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F14">
-        <v>44.45</v>
+        <v>46.65</v>
       </c>
       <c r="G14">
-        <v>50.58</v>
+        <v>49.46</v>
       </c>
       <c r="H14">
-        <v>57.66</v>
+        <v>52.87</v>
       </c>
       <c r="I14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -1005,7 +999,7 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s">
         <v>46</v>
@@ -1014,19 +1008,19 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="F15">
-        <v>42.73</v>
+        <v>44.52</v>
       </c>
       <c r="G15">
-        <v>50.07</v>
+        <v>49.39</v>
       </c>
       <c r="H15">
-        <v>58.58</v>
+        <v>57.25</v>
       </c>
       <c r="I15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1043,16 +1037,16 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="F16">
-        <v>43.95</v>
+        <v>47.46</v>
       </c>
       <c r="G16">
-        <v>49.83</v>
+        <v>49.38</v>
       </c>
       <c r="H16">
-        <v>54.52</v>
+        <v>51.31</v>
       </c>
       <c r="I16" t="s">
         <v>49</v>
@@ -1063,7 +1057,7 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C17" t="s">
         <v>46</v>
@@ -1072,16 +1066,16 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F17">
-        <v>46.11</v>
+        <v>42.74</v>
       </c>
       <c r="G17">
-        <v>49.54</v>
+        <v>47.89</v>
       </c>
       <c r="H17">
-        <v>53.33</v>
+        <v>51.33</v>
       </c>
       <c r="I17" t="s">
         <v>49</v>
@@ -1092,7 +1086,7 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
         <v>46</v>
@@ -1101,16 +1095,16 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="F18">
-        <v>45.57</v>
+        <v>42.88</v>
       </c>
       <c r="G18">
-        <v>49.03</v>
+        <v>47.85</v>
       </c>
       <c r="H18">
-        <v>52.48</v>
+        <v>55.61</v>
       </c>
       <c r="I18" t="s">
         <v>49</v>
@@ -1121,7 +1115,7 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
         <v>46</v>
@@ -1130,16 +1124,16 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F19">
-        <v>45.43</v>
+        <v>46.49</v>
       </c>
       <c r="G19">
-        <v>48.92</v>
+        <v>47.61</v>
       </c>
       <c r="H19">
-        <v>53.88</v>
+        <v>49.65</v>
       </c>
       <c r="I19" t="s">
         <v>49</v>
@@ -1159,16 +1153,16 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>117</v>
+        <v>19</v>
       </c>
       <c r="F20">
-        <v>29.28</v>
+        <v>44.11</v>
       </c>
       <c r="G20">
-        <v>48.76</v>
+        <v>47.39</v>
       </c>
       <c r="H20">
-        <v>58.58</v>
+        <v>50.98</v>
       </c>
       <c r="I20" t="s">
         <v>49</v>
@@ -1188,16 +1182,16 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="F21">
-        <v>43.62</v>
+        <v>43.43</v>
       </c>
       <c r="G21">
-        <v>48.75</v>
+        <v>46.82</v>
       </c>
       <c r="H21">
-        <v>52.96</v>
+        <v>51.27</v>
       </c>
       <c r="I21" t="s">
         <v>49</v>
@@ -1208,7 +1202,7 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C22" t="s">
         <v>46</v>
@@ -1217,16 +1211,16 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>62</v>
+        <v>3</v>
       </c>
       <c r="F22">
-        <v>39.98</v>
+        <v>35.65</v>
       </c>
       <c r="G22">
-        <v>48.01</v>
+        <v>46.8</v>
       </c>
       <c r="H22">
-        <v>53.48</v>
+        <v>56.08</v>
       </c>
       <c r="I22" t="s">
         <v>49</v>
@@ -1237,7 +1231,7 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C23" t="s">
         <v>46</v>
@@ -1246,16 +1240,16 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F23">
-        <v>42.06</v>
+        <v>45.09</v>
       </c>
       <c r="G23">
-        <v>47.87</v>
+        <v>46.66</v>
       </c>
       <c r="H23">
-        <v>53.89</v>
+        <v>48.8</v>
       </c>
       <c r="I23" t="s">
         <v>49</v>
@@ -1275,16 +1269,16 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F24">
-        <v>41.84</v>
+        <v>42.65</v>
       </c>
       <c r="G24">
-        <v>47.82</v>
+        <v>46.16</v>
       </c>
       <c r="H24">
-        <v>52.58</v>
+        <v>54.38</v>
       </c>
       <c r="I24" t="s">
         <v>49</v>
@@ -1307,13 +1301,13 @@
         <v>10</v>
       </c>
       <c r="F25">
-        <v>44.42</v>
+        <v>44.15</v>
       </c>
       <c r="G25">
-        <v>47.16</v>
+        <v>45.73</v>
       </c>
       <c r="H25">
-        <v>53.89</v>
+        <v>48.52</v>
       </c>
       <c r="I25" t="s">
         <v>49</v>
@@ -1333,16 +1327,16 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="F26">
-        <v>38.38</v>
+        <v>38.25</v>
       </c>
       <c r="G26">
-        <v>46.21</v>
+        <v>45.49</v>
       </c>
       <c r="H26">
-        <v>53.56</v>
+        <v>55.02</v>
       </c>
       <c r="I26" t="s">
         <v>49</v>
@@ -1353,7 +1347,7 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
         <v>46</v>
@@ -1362,16 +1356,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F27">
-        <v>41.3</v>
+        <v>43.86</v>
       </c>
       <c r="G27">
-        <v>41.3</v>
+        <v>45.28</v>
       </c>
       <c r="H27">
-        <v>41.3</v>
+        <v>46.82</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1382,7 +1376,7 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C28" t="s">
         <v>46</v>
@@ -1391,16 +1385,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F28">
-        <v>34.44</v>
+        <v>40.82</v>
       </c>
       <c r="G28">
-        <v>38.16</v>
+        <v>45.24</v>
       </c>
       <c r="H28">
-        <v>46.22</v>
+        <v>52.57</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
@@ -1411,7 +1405,7 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C29" t="s">
         <v>46</v>
@@ -1420,19 +1414,19 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="F29">
-        <v>6.91</v>
+        <v>45.15</v>
       </c>
       <c r="G29">
-        <v>32.24</v>
+        <v>45.15</v>
       </c>
       <c r="H29">
-        <v>53.02</v>
+        <v>45.15</v>
       </c>
       <c r="I29" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -1440,7 +1434,7 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C30" t="s">
         <v>46</v>
@@ -1449,19 +1443,19 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F30">
-        <v>9.25</v>
+        <v>39.31</v>
       </c>
       <c r="G30">
-        <v>23.38</v>
+        <v>44.53</v>
       </c>
       <c r="H30">
-        <v>41.52</v>
+        <v>50.42</v>
       </c>
       <c r="I30" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -1478,19 +1472,19 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F31">
-        <v>18.21</v>
+        <v>42.84</v>
       </c>
       <c r="G31">
-        <v>21.58</v>
+        <v>44.01</v>
       </c>
       <c r="H31">
-        <v>28.15</v>
+        <v>45.94</v>
       </c>
       <c r="I31" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -1507,19 +1501,19 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F32">
-        <v>7.94</v>
+        <v>32.06</v>
       </c>
       <c r="G32">
-        <v>17.94</v>
+        <v>41.61</v>
       </c>
       <c r="H32">
-        <v>52.8</v>
+        <v>51.42</v>
       </c>
       <c r="I32" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -1527,7 +1521,7 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C33" t="s">
         <v>46</v>
@@ -1536,19 +1530,19 @@
         <v>47</v>
       </c>
       <c r="E33">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="F33">
-        <v>6.13</v>
+        <v>27.03</v>
       </c>
       <c r="G33">
-        <v>13.12</v>
+        <v>35.29</v>
       </c>
       <c r="H33">
-        <v>37.16</v>
+        <v>41.6</v>
       </c>
       <c r="I33" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1565,19 +1559,19 @@
         <v>47</v>
       </c>
       <c r="E34">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="F34">
-        <v>5.66</v>
+        <v>4.74</v>
       </c>
       <c r="G34">
-        <v>7.9</v>
+        <v>22.71</v>
       </c>
       <c r="H34">
-        <v>12.68</v>
+        <v>48.57</v>
       </c>
       <c r="I34" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -1597,7 +1591,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -1617,7 +1611,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -46,105 +46,105 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع کوهستان</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع کوه دراء</t>
   </si>
   <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
+  </si>
+  <si>
     <t>پارک ملي قطرويه</t>
   </si>
   <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده هرمود</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش دره باغ</t>
+  </si>
+  <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مزايجان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دالان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع بناب</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دالان</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع کوه گورم</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
+    <t>منطقه شکار ممنوع شیکوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مهارلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع توت سياه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع کوه هوا و</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
-  </si>
-  <si>
     <t>منطقه حفاظت شده ماله گاله</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوهستان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده هرمود</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع شیکوه</t>
+    <t>منطقه شکار ممنوع بصيران</t>
   </si>
   <si>
     <t>منطقه حفاظت شده برم فیروز</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع بصيران</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع چاه نفت</t>
   </si>
   <si>
@@ -157,10 +157,10 @@
     <t>مناطق ممنوعه شکار</t>
   </si>
   <si>
-    <t>1405-07-28</t>
-  </si>
-  <si>
-    <t>2026-10-20</t>
+    <t>1405-07-29</t>
+  </si>
+  <si>
+    <t>2026-10-21</t>
   </si>
   <si>
     <t>شدید</t>
@@ -631,16 +631,16 @@
         <v>47</v>
       </c>
       <c r="E2">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>49.14</v>
+        <v>60.58</v>
       </c>
       <c r="G2">
-        <v>54.93</v>
+        <v>60.58</v>
       </c>
       <c r="H2">
-        <v>61.77</v>
+        <v>60.58</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -651,7 +651,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C3" t="s">
         <v>46</v>
@@ -660,16 +660,16 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F3">
-        <v>54.33</v>
+        <v>56.36</v>
       </c>
       <c r="G3">
-        <v>54.33</v>
+        <v>59.63</v>
       </c>
       <c r="H3">
-        <v>54.33</v>
+        <v>64.63</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -680,7 +680,7 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C4" t="s">
         <v>46</v>
@@ -689,16 +689,16 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F4">
-        <v>46.85</v>
+        <v>50.88</v>
       </c>
       <c r="G4">
-        <v>54.09</v>
+        <v>54.79</v>
       </c>
       <c r="H4">
-        <v>57.23</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -718,16 +718,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>41.29</v>
+        <v>53.6</v>
       </c>
       <c r="G5">
-        <v>52.59</v>
+        <v>53.6</v>
       </c>
       <c r="H5">
-        <v>56.88</v>
+        <v>53.6</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -747,16 +747,16 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="F6">
-        <v>47.75</v>
+        <v>46.7</v>
       </c>
       <c r="G6">
-        <v>51.39</v>
+        <v>53.43</v>
       </c>
       <c r="H6">
-        <v>54.33</v>
+        <v>63.25</v>
       </c>
       <c r="I6" t="s">
         <v>48</v>
@@ -767,7 +767,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
         <v>46</v>
@@ -776,16 +776,16 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="F7">
-        <v>49.13</v>
+        <v>46.7</v>
       </c>
       <c r="G7">
-        <v>51.14</v>
+        <v>53.02</v>
       </c>
       <c r="H7">
-        <v>53.03</v>
+        <v>62.22</v>
       </c>
       <c r="I7" t="s">
         <v>48</v>
@@ -796,7 +796,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C8" t="s">
         <v>46</v>
@@ -805,16 +805,16 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="F8">
-        <v>44.43</v>
+        <v>47.29</v>
       </c>
       <c r="G8">
-        <v>50.45</v>
+        <v>52.63</v>
       </c>
       <c r="H8">
-        <v>56.8</v>
+        <v>58.9</v>
       </c>
       <c r="I8" t="s">
         <v>48</v>
@@ -834,16 +834,16 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>117</v>
+        <v>20</v>
       </c>
       <c r="F9">
-        <v>44.43</v>
+        <v>42.02</v>
       </c>
       <c r="G9">
-        <v>50.24</v>
+        <v>52.51</v>
       </c>
       <c r="H9">
-        <v>57.06</v>
+        <v>58.85</v>
       </c>
       <c r="I9" t="s">
         <v>48</v>
@@ -854,7 +854,7 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
         <v>46</v>
@@ -863,19 +863,19 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F10">
-        <v>47.16</v>
+        <v>48.27</v>
       </c>
       <c r="G10">
-        <v>49.92</v>
+        <v>51.62</v>
       </c>
       <c r="H10">
-        <v>53.37</v>
+        <v>53.99</v>
       </c>
       <c r="I10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -883,7 +883,7 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
         <v>46</v>
@@ -892,19 +892,19 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F11">
-        <v>46.49</v>
+        <v>47.29</v>
       </c>
       <c r="G11">
-        <v>49.73</v>
+        <v>51.56</v>
       </c>
       <c r="H11">
-        <v>55.83</v>
+        <v>57.51</v>
       </c>
       <c r="I11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -912,7 +912,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
         <v>46</v>
@@ -921,19 +921,19 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F12">
-        <v>35.65</v>
+        <v>47.9</v>
       </c>
       <c r="G12">
-        <v>49.66</v>
+        <v>50.98</v>
       </c>
       <c r="H12">
-        <v>58.09</v>
+        <v>54.44</v>
       </c>
       <c r="I12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -950,19 +950,19 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="F13">
-        <v>42.3</v>
+        <v>46.45</v>
       </c>
       <c r="G13">
-        <v>49.52</v>
+        <v>50.69</v>
       </c>
       <c r="H13">
-        <v>53.43</v>
+        <v>55.44</v>
       </c>
       <c r="I13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -979,19 +979,19 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F14">
-        <v>46.65</v>
+        <v>46.84</v>
       </c>
       <c r="G14">
-        <v>49.46</v>
+        <v>50.29</v>
       </c>
       <c r="H14">
-        <v>52.87</v>
+        <v>52.96</v>
       </c>
       <c r="I14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -1008,19 +1008,19 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F15">
-        <v>44.52</v>
+        <v>49.6</v>
       </c>
       <c r="G15">
-        <v>49.39</v>
+        <v>50.07</v>
       </c>
       <c r="H15">
-        <v>57.25</v>
+        <v>51.4</v>
       </c>
       <c r="I15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1037,16 +1037,16 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F16">
-        <v>47.46</v>
+        <v>47.03</v>
       </c>
       <c r="G16">
-        <v>49.38</v>
+        <v>49.6</v>
       </c>
       <c r="H16">
-        <v>51.31</v>
+        <v>52.88</v>
       </c>
       <c r="I16" t="s">
         <v>49</v>
@@ -1066,16 +1066,16 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="F17">
-        <v>42.74</v>
+        <v>46.44</v>
       </c>
       <c r="G17">
-        <v>47.89</v>
+        <v>49.41</v>
       </c>
       <c r="H17">
-        <v>51.33</v>
+        <v>52.38</v>
       </c>
       <c r="I17" t="s">
         <v>49</v>
@@ -1086,7 +1086,7 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C18" t="s">
         <v>46</v>
@@ -1095,16 +1095,16 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F18">
-        <v>42.88</v>
+        <v>42.54</v>
       </c>
       <c r="G18">
-        <v>47.85</v>
+        <v>48.64</v>
       </c>
       <c r="H18">
-        <v>55.61</v>
+        <v>53.09</v>
       </c>
       <c r="I18" t="s">
         <v>49</v>
@@ -1124,16 +1124,16 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="F19">
-        <v>46.49</v>
+        <v>44</v>
       </c>
       <c r="G19">
-        <v>47.61</v>
+        <v>48.63</v>
       </c>
       <c r="H19">
-        <v>49.65</v>
+        <v>53.99</v>
       </c>
       <c r="I19" t="s">
         <v>49</v>
@@ -1144,7 +1144,7 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C20" t="s">
         <v>46</v>
@@ -1153,16 +1153,16 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F20">
-        <v>44.11</v>
+        <v>42.62</v>
       </c>
       <c r="G20">
-        <v>47.39</v>
+        <v>48.35</v>
       </c>
       <c r="H20">
-        <v>50.98</v>
+        <v>53.73</v>
       </c>
       <c r="I20" t="s">
         <v>49</v>
@@ -1185,13 +1185,13 @@
         <v>20</v>
       </c>
       <c r="F21">
-        <v>43.43</v>
+        <v>46.65</v>
       </c>
       <c r="G21">
-        <v>46.82</v>
+        <v>48.09</v>
       </c>
       <c r="H21">
-        <v>51.27</v>
+        <v>50.43</v>
       </c>
       <c r="I21" t="s">
         <v>49</v>
@@ -1202,7 +1202,7 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C22" t="s">
         <v>46</v>
@@ -1214,13 +1214,13 @@
         <v>3</v>
       </c>
       <c r="F22">
-        <v>35.65</v>
+        <v>38.89</v>
       </c>
       <c r="G22">
-        <v>46.8</v>
+        <v>47.46</v>
       </c>
       <c r="H22">
-        <v>56.08</v>
+        <v>58.88</v>
       </c>
       <c r="I22" t="s">
         <v>49</v>
@@ -1240,16 +1240,16 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F23">
-        <v>45.09</v>
+        <v>42.64</v>
       </c>
       <c r="G23">
-        <v>46.66</v>
+        <v>47.41</v>
       </c>
       <c r="H23">
-        <v>48.8</v>
+        <v>54.26</v>
       </c>
       <c r="I23" t="s">
         <v>49</v>
@@ -1269,16 +1269,16 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="F24">
-        <v>42.65</v>
+        <v>46</v>
       </c>
       <c r="G24">
-        <v>46.16</v>
+        <v>47.16</v>
       </c>
       <c r="H24">
-        <v>54.38</v>
+        <v>48.99</v>
       </c>
       <c r="I24" t="s">
         <v>49</v>
@@ -1298,16 +1298,16 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F25">
-        <v>44.15</v>
+        <v>42.62</v>
       </c>
       <c r="G25">
-        <v>45.73</v>
+        <v>47.02</v>
       </c>
       <c r="H25">
-        <v>48.52</v>
+        <v>56.81</v>
       </c>
       <c r="I25" t="s">
         <v>49</v>
@@ -1330,13 +1330,13 @@
         <v>62</v>
       </c>
       <c r="F26">
-        <v>38.25</v>
+        <v>40.12</v>
       </c>
       <c r="G26">
-        <v>45.49</v>
+        <v>46.87</v>
       </c>
       <c r="H26">
-        <v>55.02</v>
+        <v>54</v>
       </c>
       <c r="I26" t="s">
         <v>49</v>
@@ -1356,16 +1356,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F27">
-        <v>43.86</v>
+        <v>45.23</v>
       </c>
       <c r="G27">
-        <v>45.28</v>
+        <v>46.09</v>
       </c>
       <c r="H27">
-        <v>46.82</v>
+        <v>48.96</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1385,16 +1385,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="F28">
-        <v>40.82</v>
+        <v>43.93</v>
       </c>
       <c r="G28">
-        <v>45.24</v>
+        <v>45.36</v>
       </c>
       <c r="H28">
-        <v>52.57</v>
+        <v>46.89</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
@@ -1414,16 +1414,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="F29">
-        <v>45.15</v>
+        <v>42.58</v>
       </c>
       <c r="G29">
-        <v>45.15</v>
+        <v>44.89</v>
       </c>
       <c r="H29">
-        <v>45.15</v>
+        <v>49.08</v>
       </c>
       <c r="I29" t="s">
         <v>49</v>
@@ -1446,13 +1446,13 @@
         <v>5</v>
       </c>
       <c r="F30">
-        <v>39.31</v>
+        <v>38.89</v>
       </c>
       <c r="G30">
-        <v>44.53</v>
+        <v>44.82</v>
       </c>
       <c r="H30">
-        <v>50.42</v>
+        <v>50.45</v>
       </c>
       <c r="I30" t="s">
         <v>49</v>
@@ -1463,7 +1463,7 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C31" t="s">
         <v>46</v>
@@ -1472,16 +1472,16 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="F31">
-        <v>42.84</v>
+        <v>41.96</v>
       </c>
       <c r="G31">
-        <v>44.01</v>
+        <v>44.53</v>
       </c>
       <c r="H31">
-        <v>45.94</v>
+        <v>46.6</v>
       </c>
       <c r="I31" t="s">
         <v>49</v>
@@ -1492,7 +1492,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C32" t="s">
         <v>46</v>
@@ -1501,16 +1501,16 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="F32">
-        <v>32.06</v>
+        <v>28.07</v>
       </c>
       <c r="G32">
-        <v>41.61</v>
+        <v>42.76</v>
       </c>
       <c r="H32">
-        <v>51.42</v>
+        <v>52.49</v>
       </c>
       <c r="I32" t="s">
         <v>49</v>
@@ -1521,7 +1521,7 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C33" t="s">
         <v>46</v>
@@ -1530,16 +1530,16 @@
         <v>47</v>
       </c>
       <c r="E33">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F33">
-        <v>27.03</v>
+        <v>22.36</v>
       </c>
       <c r="G33">
-        <v>35.29</v>
+        <v>36.91</v>
       </c>
       <c r="H33">
-        <v>41.6</v>
+        <v>55.64</v>
       </c>
       <c r="I33" t="s">
         <v>50</v>
@@ -1550,7 +1550,7 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C34" t="s">
         <v>46</v>
@@ -1559,16 +1559,16 @@
         <v>47</v>
       </c>
       <c r="E34">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="F34">
-        <v>4.74</v>
+        <v>27.71</v>
       </c>
       <c r="G34">
-        <v>22.71</v>
+        <v>33.19</v>
       </c>
       <c r="H34">
-        <v>48.57</v>
+        <v>43.07</v>
       </c>
       <c r="I34" t="s">
         <v>50</v>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="51">
   <si>
     <t>نام منطقه</t>
   </si>
@@ -46,105 +46,105 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بناب</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه دراء</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مزايجان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دالان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده هرمود</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده برم فیروز</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع کوهستان</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه دراء</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
-  </si>
-  <si>
     <t>پارک ملي قطرويه</t>
   </si>
   <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
+    <t>منطقه شکار ممنوع مهارلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه هوا و</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع دره باغ</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده هرمود</t>
+    <t>منطقه شکار ممنوع شیکوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع توت سياه</t>
   </si>
   <si>
     <t>پناهگاه حيات وحش دره باغ</t>
   </si>
   <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دالان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بناب</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع شیکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه هوا و</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع بصيران</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع چاه نفت</t>
   </si>
   <si>
@@ -157,19 +157,16 @@
     <t>مناطق ممنوعه شکار</t>
   </si>
   <si>
-    <t>1405-07-29</t>
-  </si>
-  <si>
-    <t>2026-10-21</t>
+    <t>1405-07-30</t>
+  </si>
+  <si>
+    <t>2026-10-22</t>
   </si>
   <si>
     <t>شدید</t>
   </si>
   <si>
     <t>خیلی زیاد</t>
-  </si>
-  <si>
-    <t>زیاد</t>
   </si>
   <si>
     <t>بدون داده</t>
@@ -631,16 +628,16 @@
         <v>47</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>60.58</v>
+        <v>59.3</v>
       </c>
       <c r="G2">
-        <v>60.58</v>
+        <v>63.51</v>
       </c>
       <c r="H2">
-        <v>60.58</v>
+        <v>65.83</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -651,7 +648,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s">
         <v>46</v>
@@ -660,16 +657,16 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>56.36</v>
+        <v>59.5</v>
       </c>
       <c r="G3">
-        <v>59.63</v>
+        <v>62.15</v>
       </c>
       <c r="H3">
-        <v>64.63</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -680,7 +677,7 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C4" t="s">
         <v>46</v>
@@ -689,16 +686,16 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>50.88</v>
+        <v>58.54</v>
       </c>
       <c r="G4">
-        <v>54.79</v>
+        <v>58.8</v>
       </c>
       <c r="H4">
-        <v>64.65000000000001</v>
+        <v>59.06</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -718,16 +715,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>53.6</v>
+        <v>50.87</v>
       </c>
       <c r="G5">
-        <v>53.6</v>
+        <v>58.01</v>
       </c>
       <c r="H5">
-        <v>53.6</v>
+        <v>63.38</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -747,16 +744,16 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>117</v>
+        <v>19</v>
       </c>
       <c r="F6">
-        <v>46.7</v>
+        <v>53.01</v>
       </c>
       <c r="G6">
-        <v>53.43</v>
+        <v>57.93</v>
       </c>
       <c r="H6">
-        <v>63.25</v>
+        <v>60.43</v>
       </c>
       <c r="I6" t="s">
         <v>48</v>
@@ -767,7 +764,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
         <v>46</v>
@@ -776,16 +773,16 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="F7">
-        <v>46.7</v>
+        <v>52.93</v>
       </c>
       <c r="G7">
-        <v>53.02</v>
+        <v>57.63</v>
       </c>
       <c r="H7">
-        <v>62.22</v>
+        <v>61.39</v>
       </c>
       <c r="I7" t="s">
         <v>48</v>
@@ -805,16 +802,16 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F8">
-        <v>47.29</v>
+        <v>53.02</v>
       </c>
       <c r="G8">
-        <v>52.63</v>
+        <v>56.9</v>
       </c>
       <c r="H8">
-        <v>58.9</v>
+        <v>61.61</v>
       </c>
       <c r="I8" t="s">
         <v>48</v>
@@ -825,7 +822,7 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
         <v>46</v>
@@ -837,13 +834,13 @@
         <v>20</v>
       </c>
       <c r="F9">
-        <v>42.02</v>
+        <v>53.08</v>
       </c>
       <c r="G9">
-        <v>52.51</v>
+        <v>55.15</v>
       </c>
       <c r="H9">
-        <v>58.85</v>
+        <v>57.12</v>
       </c>
       <c r="I9" t="s">
         <v>48</v>
@@ -863,16 +860,16 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F10">
-        <v>48.27</v>
+        <v>51.4</v>
       </c>
       <c r="G10">
-        <v>51.62</v>
+        <v>54.86</v>
       </c>
       <c r="H10">
-        <v>53.99</v>
+        <v>61.4</v>
       </c>
       <c r="I10" t="s">
         <v>48</v>
@@ -892,16 +889,16 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="F11">
-        <v>47.29</v>
+        <v>51.64</v>
       </c>
       <c r="G11">
-        <v>51.56</v>
+        <v>54.31</v>
       </c>
       <c r="H11">
-        <v>57.51</v>
+        <v>56.73</v>
       </c>
       <c r="I11" t="s">
         <v>48</v>
@@ -912,7 +909,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
         <v>46</v>
@@ -921,16 +918,16 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F12">
-        <v>47.9</v>
+        <v>51.14</v>
       </c>
       <c r="G12">
-        <v>50.98</v>
+        <v>54.3</v>
       </c>
       <c r="H12">
-        <v>54.44</v>
+        <v>55.75</v>
       </c>
       <c r="I12" t="s">
         <v>48</v>
@@ -941,7 +938,7 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
         <v>46</v>
@@ -950,16 +947,16 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F13">
-        <v>46.45</v>
+        <v>50.69</v>
       </c>
       <c r="G13">
-        <v>50.69</v>
+        <v>54.05</v>
       </c>
       <c r="H13">
-        <v>55.44</v>
+        <v>58.17</v>
       </c>
       <c r="I13" t="s">
         <v>48</v>
@@ -979,16 +976,16 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="F14">
-        <v>46.84</v>
+        <v>49.36</v>
       </c>
       <c r="G14">
-        <v>50.29</v>
+        <v>53.71</v>
       </c>
       <c r="H14">
-        <v>52.96</v>
+        <v>58.45</v>
       </c>
       <c r="I14" t="s">
         <v>48</v>
@@ -1008,16 +1005,16 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F15">
-        <v>49.6</v>
+        <v>48.7</v>
       </c>
       <c r="G15">
-        <v>50.07</v>
+        <v>53.65</v>
       </c>
       <c r="H15">
-        <v>51.4</v>
+        <v>56.55</v>
       </c>
       <c r="I15" t="s">
         <v>48</v>
@@ -1037,19 +1034,19 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c r="F16">
-        <v>47.03</v>
+        <v>47.02</v>
       </c>
       <c r="G16">
-        <v>49.6</v>
+        <v>53.54</v>
       </c>
       <c r="H16">
-        <v>52.88</v>
+        <v>60.44</v>
       </c>
       <c r="I16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1057,7 +1054,7 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
         <v>46</v>
@@ -1066,19 +1063,19 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="F17">
-        <v>46.44</v>
+        <v>47.35</v>
       </c>
       <c r="G17">
-        <v>49.41</v>
+        <v>53.21</v>
       </c>
       <c r="H17">
-        <v>52.38</v>
+        <v>64.92</v>
       </c>
       <c r="I17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1095,19 +1092,19 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F18">
-        <v>42.54</v>
+        <v>48.41</v>
       </c>
       <c r="G18">
-        <v>48.64</v>
+        <v>53.14</v>
       </c>
       <c r="H18">
-        <v>53.09</v>
+        <v>56.85</v>
       </c>
       <c r="I18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1115,7 +1112,7 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C19" t="s">
         <v>46</v>
@@ -1124,19 +1121,19 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F19">
-        <v>44</v>
+        <v>46.74</v>
       </c>
       <c r="G19">
-        <v>48.63</v>
+        <v>52.61</v>
       </c>
       <c r="H19">
-        <v>53.99</v>
+        <v>60.73</v>
       </c>
       <c r="I19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1144,7 +1141,7 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C20" t="s">
         <v>46</v>
@@ -1153,19 +1150,19 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>12</v>
+        <v>117</v>
       </c>
       <c r="F20">
-        <v>42.62</v>
+        <v>46.74</v>
       </c>
       <c r="G20">
-        <v>48.35</v>
+        <v>52.58</v>
       </c>
       <c r="H20">
-        <v>53.73</v>
+        <v>64.92</v>
       </c>
       <c r="I20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1182,19 +1179,19 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F21">
-        <v>46.65</v>
+        <v>50.28</v>
       </c>
       <c r="G21">
-        <v>48.09</v>
+        <v>51.42</v>
       </c>
       <c r="H21">
-        <v>50.43</v>
+        <v>52.24</v>
       </c>
       <c r="I21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -1202,7 +1199,7 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C22" t="s">
         <v>46</v>
@@ -1211,19 +1208,19 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="F22">
-        <v>38.89</v>
+        <v>47.22</v>
       </c>
       <c r="G22">
-        <v>47.46</v>
+        <v>50.97</v>
       </c>
       <c r="H22">
-        <v>58.88</v>
+        <v>58.1</v>
       </c>
       <c r="I22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1240,19 +1237,19 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F23">
-        <v>42.64</v>
+        <v>48.67</v>
       </c>
       <c r="G23">
-        <v>47.41</v>
+        <v>50.69</v>
       </c>
       <c r="H23">
-        <v>54.26</v>
+        <v>53.41</v>
       </c>
       <c r="I23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -1269,16 +1266,16 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F24">
-        <v>46</v>
+        <v>45.49</v>
       </c>
       <c r="G24">
-        <v>47.16</v>
+        <v>49.89</v>
       </c>
       <c r="H24">
-        <v>48.99</v>
+        <v>55.49</v>
       </c>
       <c r="I24" t="s">
         <v>49</v>
@@ -1289,7 +1286,7 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C25" t="s">
         <v>46</v>
@@ -1298,16 +1295,16 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F25">
-        <v>42.62</v>
+        <v>42.65</v>
       </c>
       <c r="G25">
-        <v>47.02</v>
+        <v>49.32</v>
       </c>
       <c r="H25">
-        <v>56.81</v>
+        <v>60.86</v>
       </c>
       <c r="I25" t="s">
         <v>49</v>
@@ -1327,16 +1324,16 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="F26">
-        <v>40.12</v>
+        <v>48.77</v>
       </c>
       <c r="G26">
-        <v>46.87</v>
+        <v>48.77</v>
       </c>
       <c r="H26">
-        <v>54</v>
+        <v>48.77</v>
       </c>
       <c r="I26" t="s">
         <v>49</v>
@@ -1347,7 +1344,7 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
         <v>46</v>
@@ -1356,16 +1353,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F27">
-        <v>45.23</v>
+        <v>48.12</v>
       </c>
       <c r="G27">
-        <v>46.09</v>
+        <v>48.12</v>
       </c>
       <c r="H27">
-        <v>48.96</v>
+        <v>48.12</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1385,16 +1382,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F28">
-        <v>43.93</v>
+        <v>44.75</v>
       </c>
       <c r="G28">
-        <v>45.36</v>
+        <v>46.42</v>
       </c>
       <c r="H28">
-        <v>46.89</v>
+        <v>49.92</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
@@ -1414,16 +1411,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F29">
-        <v>42.58</v>
+        <v>40.85</v>
       </c>
       <c r="G29">
-        <v>44.89</v>
+        <v>45.78</v>
       </c>
       <c r="H29">
-        <v>49.08</v>
+        <v>50.29</v>
       </c>
       <c r="I29" t="s">
         <v>49</v>
@@ -1434,7 +1431,7 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C30" t="s">
         <v>46</v>
@@ -1443,16 +1440,16 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F30">
-        <v>38.89</v>
+        <v>38.81</v>
       </c>
       <c r="G30">
-        <v>44.82</v>
+        <v>45.34</v>
       </c>
       <c r="H30">
-        <v>50.45</v>
+        <v>60.16</v>
       </c>
       <c r="I30" t="s">
         <v>49</v>
@@ -1472,16 +1469,16 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="F31">
-        <v>41.96</v>
+        <v>36.49</v>
       </c>
       <c r="G31">
-        <v>44.53</v>
+        <v>43.62</v>
       </c>
       <c r="H31">
-        <v>46.6</v>
+        <v>52.47</v>
       </c>
       <c r="I31" t="s">
         <v>49</v>
@@ -1492,7 +1489,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C32" t="s">
         <v>46</v>
@@ -1501,16 +1498,16 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F32">
-        <v>28.07</v>
+        <v>39.25</v>
       </c>
       <c r="G32">
-        <v>42.76</v>
+        <v>41.66</v>
       </c>
       <c r="H32">
-        <v>52.49</v>
+        <v>43.56</v>
       </c>
       <c r="I32" t="s">
         <v>49</v>
@@ -1521,7 +1518,7 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C33" t="s">
         <v>46</v>
@@ -1530,19 +1527,19 @@
         <v>47</v>
       </c>
       <c r="E33">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="F33">
-        <v>22.36</v>
+        <v>38.81</v>
       </c>
       <c r="G33">
-        <v>36.91</v>
+        <v>40.63</v>
       </c>
       <c r="H33">
-        <v>55.64</v>
+        <v>43.96</v>
       </c>
       <c r="I33" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1550,7 +1547,7 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C34" t="s">
         <v>46</v>
@@ -1559,19 +1556,19 @@
         <v>47</v>
       </c>
       <c r="E34">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F34">
-        <v>27.71</v>
+        <v>34.59</v>
       </c>
       <c r="G34">
-        <v>33.19</v>
+        <v>39.48</v>
       </c>
       <c r="H34">
-        <v>43.07</v>
+        <v>57.76</v>
       </c>
       <c r="I34" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -1591,7 +1588,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -1611,7 +1608,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="52">
   <si>
     <t>نام منطقه</t>
   </si>
@@ -49,102 +49,102 @@
     <t>منطقه شکار ممنوع مل بلند</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع بناب</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دالان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
     <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع مزايجان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه هوا و</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده هرمود</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه دراء</t>
+  </si>
+  <si>
     <t>منطقه شکار ممن.ع آق جلو</t>
   </si>
   <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مهارلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
+  </si>
+  <si>
+    <t>پارک ملي قطرويه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوهستان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع توت سياه</t>
+  </si>
+  <si>
     <t>منطقه حفاظت شده تنگ بستانک</t>
   </si>
   <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بناب</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه دراء</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دالان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده هرمود</t>
-  </si>
-  <si>
     <t>منطقه حفاظت شده برم فیروز</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوهستان</t>
-  </si>
-  <si>
-    <t>پارک ملي قطرويه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه هوا و</t>
+    <t>پناهگاه حيات وحش دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بصيران</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع شیکوه</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع دره باغ</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع شیکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بصيران</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع چاه نفت</t>
   </si>
   <si>
@@ -157,16 +157,19 @@
     <t>مناطق ممنوعه شکار</t>
   </si>
   <si>
-    <t>1405-07-30</t>
-  </si>
-  <si>
-    <t>2026-10-22</t>
+    <t>1405-08-01</t>
+  </si>
+  <si>
+    <t>2026-10-23</t>
   </si>
   <si>
     <t>شدید</t>
   </si>
   <si>
     <t>خیلی زیاد</t>
+  </si>
+  <si>
+    <t>زیاد</t>
   </si>
   <si>
     <t>بدون داده</t>
@@ -631,13 +634,13 @@
         <v>6</v>
       </c>
       <c r="F2">
-        <v>59.3</v>
+        <v>61.16</v>
       </c>
       <c r="G2">
-        <v>63.51</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="H2">
-        <v>65.83</v>
+        <v>68.91</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -648,7 +651,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C3" t="s">
         <v>46</v>
@@ -657,16 +660,16 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="F3">
-        <v>59.5</v>
+        <v>53.36</v>
       </c>
       <c r="G3">
-        <v>62.15</v>
+        <v>62.44</v>
       </c>
       <c r="H3">
-        <v>64.90000000000001</v>
+        <v>66.93000000000001</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -686,16 +689,16 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>58.54</v>
+        <v>59.16</v>
       </c>
       <c r="G4">
-        <v>58.8</v>
+        <v>60.84</v>
       </c>
       <c r="H4">
-        <v>59.06</v>
+        <v>62.27</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -715,16 +718,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F5">
-        <v>50.87</v>
+        <v>49.34</v>
       </c>
       <c r="G5">
-        <v>58.01</v>
+        <v>54.47</v>
       </c>
       <c r="H5">
-        <v>63.38</v>
+        <v>58.02</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -744,16 +747,16 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F6">
-        <v>53.01</v>
+        <v>49.22</v>
       </c>
       <c r="G6">
-        <v>57.93</v>
+        <v>54.18</v>
       </c>
       <c r="H6">
-        <v>60.43</v>
+        <v>57.38</v>
       </c>
       <c r="I6" t="s">
         <v>48</v>
@@ -764,7 +767,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
         <v>46</v>
@@ -773,16 +776,16 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>52.93</v>
+        <v>52.31</v>
       </c>
       <c r="G7">
-        <v>57.63</v>
+        <v>53.92</v>
       </c>
       <c r="H7">
-        <v>61.39</v>
+        <v>55.43</v>
       </c>
       <c r="I7" t="s">
         <v>48</v>
@@ -802,16 +805,16 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F8">
-        <v>53.02</v>
+        <v>49.08</v>
       </c>
       <c r="G8">
-        <v>56.9</v>
+        <v>53.8</v>
       </c>
       <c r="H8">
-        <v>61.61</v>
+        <v>56.04</v>
       </c>
       <c r="I8" t="s">
         <v>48</v>
@@ -831,16 +834,16 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F9">
-        <v>53.08</v>
+        <v>46.48</v>
       </c>
       <c r="G9">
-        <v>55.15</v>
+        <v>53.6</v>
       </c>
       <c r="H9">
-        <v>57.12</v>
+        <v>59.12</v>
       </c>
       <c r="I9" t="s">
         <v>48</v>
@@ -860,16 +863,16 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F10">
-        <v>51.4</v>
+        <v>40.71</v>
       </c>
       <c r="G10">
-        <v>54.86</v>
+        <v>53.3</v>
       </c>
       <c r="H10">
-        <v>61.4</v>
+        <v>64.48</v>
       </c>
       <c r="I10" t="s">
         <v>48</v>
@@ -889,16 +892,16 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F11">
-        <v>51.64</v>
+        <v>46.24</v>
       </c>
       <c r="G11">
-        <v>54.31</v>
+        <v>51.99</v>
       </c>
       <c r="H11">
-        <v>56.73</v>
+        <v>58.41</v>
       </c>
       <c r="I11" t="s">
         <v>48</v>
@@ -918,16 +921,16 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F12">
-        <v>51.14</v>
+        <v>48.58</v>
       </c>
       <c r="G12">
-        <v>54.3</v>
+        <v>51.71</v>
       </c>
       <c r="H12">
-        <v>55.75</v>
+        <v>60.97</v>
       </c>
       <c r="I12" t="s">
         <v>48</v>
@@ -938,7 +941,7 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s">
         <v>46</v>
@@ -950,13 +953,13 @@
         <v>20</v>
       </c>
       <c r="F13">
-        <v>50.69</v>
+        <v>46.39</v>
       </c>
       <c r="G13">
-        <v>54.05</v>
+        <v>51.28</v>
       </c>
       <c r="H13">
-        <v>58.17</v>
+        <v>56.79</v>
       </c>
       <c r="I13" t="s">
         <v>48</v>
@@ -979,13 +982,13 @@
         <v>33</v>
       </c>
       <c r="F14">
-        <v>49.36</v>
+        <v>44.32</v>
       </c>
       <c r="G14">
-        <v>53.71</v>
+        <v>50.6</v>
       </c>
       <c r="H14">
-        <v>58.45</v>
+        <v>58.58</v>
       </c>
       <c r="I14" t="s">
         <v>48</v>
@@ -1005,19 +1008,19 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F15">
-        <v>48.7</v>
+        <v>47.33</v>
       </c>
       <c r="G15">
-        <v>53.65</v>
+        <v>49.2</v>
       </c>
       <c r="H15">
-        <v>56.55</v>
+        <v>51.08</v>
       </c>
       <c r="I15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1025,7 +1028,7 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
         <v>46</v>
@@ -1034,19 +1037,19 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="F16">
-        <v>47.02</v>
+        <v>42.59</v>
       </c>
       <c r="G16">
-        <v>53.54</v>
+        <v>48.67</v>
       </c>
       <c r="H16">
-        <v>60.44</v>
+        <v>52.31</v>
       </c>
       <c r="I16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1066,16 +1069,16 @@
         <v>65</v>
       </c>
       <c r="F17">
-        <v>47.35</v>
+        <v>41.47</v>
       </c>
       <c r="G17">
-        <v>53.21</v>
+        <v>48.62</v>
       </c>
       <c r="H17">
-        <v>64.92</v>
+        <v>56.24</v>
       </c>
       <c r="I17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1083,7 +1086,7 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
         <v>46</v>
@@ -1092,19 +1095,19 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>15</v>
+        <v>117</v>
       </c>
       <c r="F18">
-        <v>48.41</v>
+        <v>40.44</v>
       </c>
       <c r="G18">
-        <v>53.14</v>
+        <v>48.35</v>
       </c>
       <c r="H18">
-        <v>56.85</v>
+        <v>56.24</v>
       </c>
       <c r="I18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1121,19 +1124,19 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F19">
-        <v>46.74</v>
+        <v>42.03</v>
       </c>
       <c r="G19">
-        <v>52.61</v>
+        <v>48.18</v>
       </c>
       <c r="H19">
-        <v>60.73</v>
+        <v>52.25</v>
       </c>
       <c r="I19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1141,7 +1144,7 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C20" t="s">
         <v>46</v>
@@ -1150,19 +1153,19 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>117</v>
+        <v>13</v>
       </c>
       <c r="F20">
-        <v>46.74</v>
+        <v>42.93</v>
       </c>
       <c r="G20">
-        <v>52.58</v>
+        <v>47.91</v>
       </c>
       <c r="H20">
-        <v>64.92</v>
+        <v>51.67</v>
       </c>
       <c r="I20" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1179,19 +1182,19 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F21">
-        <v>50.28</v>
+        <v>42.03</v>
       </c>
       <c r="G21">
-        <v>51.42</v>
+        <v>47.66</v>
       </c>
       <c r="H21">
-        <v>52.24</v>
+        <v>52.36</v>
       </c>
       <c r="I21" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -1208,19 +1211,19 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F22">
-        <v>47.22</v>
+        <v>42.77</v>
       </c>
       <c r="G22">
-        <v>50.97</v>
+        <v>47.14</v>
       </c>
       <c r="H22">
-        <v>58.1</v>
+        <v>51.68</v>
       </c>
       <c r="I22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1237,19 +1240,19 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F23">
-        <v>48.67</v>
+        <v>44.79</v>
       </c>
       <c r="G23">
-        <v>50.69</v>
+        <v>46.97</v>
       </c>
       <c r="H23">
-        <v>53.41</v>
+        <v>49.57</v>
       </c>
       <c r="I23" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -1257,7 +1260,7 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C24" t="s">
         <v>46</v>
@@ -1266,16 +1269,16 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F24">
-        <v>45.49</v>
+        <v>43.45</v>
       </c>
       <c r="G24">
-        <v>49.89</v>
+        <v>46.91</v>
       </c>
       <c r="H24">
-        <v>55.49</v>
+        <v>51.8</v>
       </c>
       <c r="I24" t="s">
         <v>49</v>
@@ -1295,16 +1298,16 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F25">
-        <v>42.65</v>
+        <v>45.53</v>
       </c>
       <c r="G25">
-        <v>49.32</v>
+        <v>45.53</v>
       </c>
       <c r="H25">
-        <v>60.86</v>
+        <v>45.53</v>
       </c>
       <c r="I25" t="s">
         <v>49</v>
@@ -1324,16 +1327,16 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="F26">
-        <v>48.77</v>
+        <v>13.29</v>
       </c>
       <c r="G26">
-        <v>48.77</v>
+        <v>40.86</v>
       </c>
       <c r="H26">
-        <v>48.77</v>
+        <v>48.83</v>
       </c>
       <c r="I26" t="s">
         <v>49</v>
@@ -1344,7 +1347,7 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
         <v>46</v>
@@ -1353,16 +1356,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F27">
-        <v>48.12</v>
+        <v>39.32</v>
       </c>
       <c r="G27">
-        <v>48.12</v>
+        <v>39.32</v>
       </c>
       <c r="H27">
-        <v>48.12</v>
+        <v>39.32</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1382,19 +1385,19 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F28">
-        <v>44.75</v>
+        <v>33.66</v>
       </c>
       <c r="G28">
-        <v>46.42</v>
+        <v>36.5</v>
       </c>
       <c r="H28">
-        <v>49.92</v>
+        <v>41.44</v>
       </c>
       <c r="I28" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -1402,7 +1405,7 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C29" t="s">
         <v>46</v>
@@ -1411,19 +1414,19 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="F29">
-        <v>40.85</v>
+        <v>23.49</v>
       </c>
       <c r="G29">
-        <v>45.78</v>
+        <v>33.4</v>
       </c>
       <c r="H29">
-        <v>50.29</v>
+        <v>37.09</v>
       </c>
       <c r="I29" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -1431,7 +1434,7 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C30" t="s">
         <v>46</v>
@@ -1440,19 +1443,19 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F30">
-        <v>38.81</v>
+        <v>28.66</v>
       </c>
       <c r="G30">
-        <v>45.34</v>
+        <v>32.65</v>
       </c>
       <c r="H30">
-        <v>60.16</v>
+        <v>35.82</v>
       </c>
       <c r="I30" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -1460,7 +1463,7 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C31" t="s">
         <v>46</v>
@@ -1472,16 +1475,16 @@
         <v>3</v>
       </c>
       <c r="F31">
-        <v>36.49</v>
+        <v>21.6</v>
       </c>
       <c r="G31">
-        <v>43.62</v>
+        <v>26.66</v>
       </c>
       <c r="H31">
-        <v>52.47</v>
+        <v>32.55</v>
       </c>
       <c r="I31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -1498,19 +1501,19 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="F32">
-        <v>39.25</v>
+        <v>7.68</v>
       </c>
       <c r="G32">
-        <v>41.66</v>
+        <v>24.61</v>
       </c>
       <c r="H32">
-        <v>43.56</v>
+        <v>42.48</v>
       </c>
       <c r="I32" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -1518,7 +1521,7 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C33" t="s">
         <v>46</v>
@@ -1530,16 +1533,16 @@
         <v>3</v>
       </c>
       <c r="F33">
-        <v>38.81</v>
+        <v>18.47</v>
       </c>
       <c r="G33">
-        <v>40.63</v>
+        <v>23.66</v>
       </c>
       <c r="H33">
-        <v>43.96</v>
+        <v>30.67</v>
       </c>
       <c r="I33" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1556,19 +1559,19 @@
         <v>47</v>
       </c>
       <c r="E34">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="F34">
-        <v>34.59</v>
+        <v>10.93</v>
       </c>
       <c r="G34">
-        <v>39.48</v>
+        <v>23.33</v>
       </c>
       <c r="H34">
-        <v>57.76</v>
+        <v>46.1</v>
       </c>
       <c r="I34" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -1588,7 +1591,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -1608,7 +1611,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="53">
   <si>
     <t>نام منطقه</t>
   </si>
@@ -46,105 +46,105 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع دالان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مزايجان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه دراء</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده هرمود</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بناب</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع مل بلند</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع بناب</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دالان</t>
+    <t>پارک ملي قطرويه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
   </si>
   <si>
     <t>منطقه حفاظت شده ماله گاله</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه هوا و</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مهارلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بصيران</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع شیکوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوهستان</t>
   </si>
   <si>
     <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه هوا و</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده هرمود</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه دراء</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع روشن کوه</t>
   </si>
   <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
-    <t>پارک ملي قطرويه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوهستان</t>
+    <t>منطقه حفاظت شده برم فیروز</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع توت سياه</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بصيران</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع شیکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع چاه نفت</t>
   </si>
   <si>
@@ -157,10 +157,10 @@
     <t>مناطق ممنوعه شکار</t>
   </si>
   <si>
-    <t>1405-08-01</t>
-  </si>
-  <si>
-    <t>2026-10-23</t>
+    <t>1405-08-02</t>
+  </si>
+  <si>
+    <t>2026-10-24</t>
   </si>
   <si>
     <t>شدید</t>
@@ -170,6 +170,9 @@
   </si>
   <si>
     <t>زیاد</t>
+  </si>
+  <si>
+    <t>متوسط</t>
   </si>
   <si>
     <t>بدون داده</t>
@@ -631,16 +634,16 @@
         <v>47</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>61.16</v>
+        <v>55.45</v>
       </c>
       <c r="G2">
-        <v>65.68000000000001</v>
+        <v>56.62</v>
       </c>
       <c r="H2">
-        <v>68.91</v>
+        <v>59.97</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -660,16 +663,16 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F3">
-        <v>53.36</v>
+        <v>46.58</v>
       </c>
       <c r="G3">
-        <v>62.44</v>
+        <v>53.57</v>
       </c>
       <c r="H3">
-        <v>66.93000000000001</v>
+        <v>58.86</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -689,16 +692,16 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F4">
-        <v>59.16</v>
+        <v>45.31</v>
       </c>
       <c r="G4">
-        <v>60.84</v>
+        <v>51.73</v>
       </c>
       <c r="H4">
-        <v>62.27</v>
+        <v>57.98</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -709,7 +712,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
         <v>46</v>
@@ -718,16 +721,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F5">
-        <v>49.34</v>
+        <v>46.09</v>
       </c>
       <c r="G5">
-        <v>54.47</v>
+        <v>50.66</v>
       </c>
       <c r="H5">
-        <v>58.02</v>
+        <v>55.43</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -747,19 +750,19 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F6">
-        <v>49.22</v>
+        <v>46.42</v>
       </c>
       <c r="G6">
-        <v>54.18</v>
+        <v>48.55</v>
       </c>
       <c r="H6">
-        <v>57.38</v>
+        <v>53.68</v>
       </c>
       <c r="I6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -767,7 +770,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
         <v>46</v>
@@ -776,19 +779,19 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="F7">
-        <v>52.31</v>
+        <v>38.02</v>
       </c>
       <c r="G7">
-        <v>53.92</v>
+        <v>48.09</v>
       </c>
       <c r="H7">
-        <v>55.43</v>
+        <v>56.65</v>
       </c>
       <c r="I7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -796,7 +799,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
         <v>46</v>
@@ -805,19 +808,19 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F8">
-        <v>49.08</v>
+        <v>44.02</v>
       </c>
       <c r="G8">
-        <v>53.8</v>
+        <v>47.98</v>
       </c>
       <c r="H8">
-        <v>56.04</v>
+        <v>54.32</v>
       </c>
       <c r="I8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -825,7 +828,7 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s">
         <v>46</v>
@@ -834,19 +837,19 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="F9">
-        <v>46.48</v>
+        <v>40.79</v>
       </c>
       <c r="G9">
-        <v>53.6</v>
+        <v>47.89</v>
       </c>
       <c r="H9">
-        <v>59.12</v>
+        <v>51.88</v>
       </c>
       <c r="I9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -854,7 +857,7 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
         <v>46</v>
@@ -866,16 +869,16 @@
         <v>20</v>
       </c>
       <c r="F10">
-        <v>40.71</v>
+        <v>41.33</v>
       </c>
       <c r="G10">
-        <v>53.3</v>
+        <v>47.05</v>
       </c>
       <c r="H10">
-        <v>64.48</v>
+        <v>51.23</v>
       </c>
       <c r="I10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -883,7 +886,7 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s">
         <v>46</v>
@@ -892,19 +895,19 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F11">
-        <v>46.24</v>
+        <v>32.93</v>
       </c>
       <c r="G11">
-        <v>51.99</v>
+        <v>46.69</v>
       </c>
       <c r="H11">
-        <v>58.41</v>
+        <v>57.14</v>
       </c>
       <c r="I11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -921,19 +924,19 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F12">
-        <v>48.58</v>
+        <v>43.29</v>
       </c>
       <c r="G12">
-        <v>51.71</v>
+        <v>46.46</v>
       </c>
       <c r="H12">
-        <v>60.97</v>
+        <v>49.76</v>
       </c>
       <c r="I12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -941,7 +944,7 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
         <v>46</v>
@@ -950,19 +953,19 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F13">
-        <v>46.39</v>
+        <v>46.17</v>
       </c>
       <c r="G13">
-        <v>51.28</v>
+        <v>46.17</v>
       </c>
       <c r="H13">
-        <v>56.79</v>
+        <v>46.17</v>
       </c>
       <c r="I13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -970,7 +973,7 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
         <v>46</v>
@@ -979,19 +982,19 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F14">
-        <v>44.32</v>
+        <v>42.56</v>
       </c>
       <c r="G14">
-        <v>50.6</v>
+        <v>46.15</v>
       </c>
       <c r="H14">
-        <v>58.58</v>
+        <v>50.19</v>
       </c>
       <c r="I14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -999,7 +1002,7 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
         <v>46</v>
@@ -1008,16 +1011,16 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>117</v>
       </c>
       <c r="F15">
-        <v>47.33</v>
+        <v>34.14</v>
       </c>
       <c r="G15">
-        <v>49.2</v>
+        <v>45.52</v>
       </c>
       <c r="H15">
-        <v>51.08</v>
+        <v>57.52</v>
       </c>
       <c r="I15" t="s">
         <v>49</v>
@@ -1028,7 +1031,7 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
         <v>46</v>
@@ -1037,16 +1040,16 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F16">
-        <v>42.59</v>
+        <v>39.39</v>
       </c>
       <c r="G16">
-        <v>48.67</v>
+        <v>45.07</v>
       </c>
       <c r="H16">
-        <v>52.31</v>
+        <v>50.84</v>
       </c>
       <c r="I16" t="s">
         <v>49</v>
@@ -1066,16 +1069,16 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="F17">
-        <v>41.47</v>
+        <v>40.46</v>
       </c>
       <c r="G17">
-        <v>48.62</v>
+        <v>44.94</v>
       </c>
       <c r="H17">
-        <v>56.24</v>
+        <v>52.64</v>
       </c>
       <c r="I17" t="s">
         <v>49</v>
@@ -1095,16 +1098,16 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>117</v>
+        <v>65</v>
       </c>
       <c r="F18">
-        <v>40.44</v>
+        <v>34.14</v>
       </c>
       <c r="G18">
-        <v>48.35</v>
+        <v>44.89</v>
       </c>
       <c r="H18">
-        <v>56.24</v>
+        <v>57.52</v>
       </c>
       <c r="I18" t="s">
         <v>49</v>
@@ -1124,16 +1127,16 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="F19">
-        <v>42.03</v>
+        <v>39.95</v>
       </c>
       <c r="G19">
-        <v>48.18</v>
+        <v>44.72</v>
       </c>
       <c r="H19">
-        <v>52.25</v>
+        <v>49.57</v>
       </c>
       <c r="I19" t="s">
         <v>49</v>
@@ -1153,16 +1156,16 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="F20">
-        <v>42.93</v>
+        <v>23.43</v>
       </c>
       <c r="G20">
-        <v>47.91</v>
+        <v>43.49</v>
       </c>
       <c r="H20">
-        <v>51.67</v>
+        <v>50.37</v>
       </c>
       <c r="I20" t="s">
         <v>49</v>
@@ -1173,7 +1176,7 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C21" t="s">
         <v>46</v>
@@ -1182,16 +1185,16 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F21">
-        <v>42.03</v>
+        <v>32.93</v>
       </c>
       <c r="G21">
-        <v>47.66</v>
+        <v>42.85</v>
       </c>
       <c r="H21">
-        <v>52.36</v>
+        <v>55.22</v>
       </c>
       <c r="I21" t="s">
         <v>49</v>
@@ -1202,7 +1205,7 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C22" t="s">
         <v>46</v>
@@ -1211,16 +1214,16 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F22">
-        <v>42.77</v>
+        <v>39.98</v>
       </c>
       <c r="G22">
-        <v>47.14</v>
+        <v>42.13</v>
       </c>
       <c r="H22">
-        <v>51.68</v>
+        <v>44.88</v>
       </c>
       <c r="I22" t="s">
         <v>49</v>
@@ -1243,13 +1246,13 @@
         <v>10</v>
       </c>
       <c r="F23">
-        <v>44.79</v>
+        <v>36.85</v>
       </c>
       <c r="G23">
-        <v>46.97</v>
+        <v>41.24</v>
       </c>
       <c r="H23">
-        <v>49.57</v>
+        <v>44.56</v>
       </c>
       <c r="I23" t="s">
         <v>49</v>
@@ -1269,19 +1272,19 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F24">
-        <v>43.45</v>
+        <v>30.06</v>
       </c>
       <c r="G24">
-        <v>46.91</v>
+        <v>36.67</v>
       </c>
       <c r="H24">
-        <v>51.8</v>
+        <v>43.28</v>
       </c>
       <c r="I24" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -1289,7 +1292,7 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C25" t="s">
         <v>46</v>
@@ -1298,19 +1301,19 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F25">
-        <v>45.53</v>
+        <v>17.17</v>
       </c>
       <c r="G25">
-        <v>45.53</v>
+        <v>36.14</v>
       </c>
       <c r="H25">
-        <v>45.53</v>
+        <v>51.84</v>
       </c>
       <c r="I25" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -1327,19 +1330,19 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="F26">
-        <v>13.29</v>
+        <v>24.81</v>
       </c>
       <c r="G26">
-        <v>40.86</v>
+        <v>35.41</v>
       </c>
       <c r="H26">
-        <v>48.83</v>
+        <v>50.13</v>
       </c>
       <c r="I26" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -1356,19 +1359,19 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F27">
-        <v>39.32</v>
+        <v>28.56</v>
       </c>
       <c r="G27">
-        <v>39.32</v>
+        <v>33.66</v>
       </c>
       <c r="H27">
-        <v>39.32</v>
+        <v>40.05</v>
       </c>
       <c r="I27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -1385,16 +1388,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F28">
-        <v>33.66</v>
+        <v>33.01</v>
       </c>
       <c r="G28">
-        <v>36.5</v>
+        <v>33.01</v>
       </c>
       <c r="H28">
-        <v>41.44</v>
+        <v>33.01</v>
       </c>
       <c r="I28" t="s">
         <v>50</v>
@@ -1414,16 +1417,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F29">
-        <v>23.49</v>
+        <v>29</v>
       </c>
       <c r="G29">
-        <v>33.4</v>
+        <v>32.35</v>
       </c>
       <c r="H29">
-        <v>37.09</v>
+        <v>35.83</v>
       </c>
       <c r="I29" t="s">
         <v>50</v>
@@ -1443,16 +1446,16 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F30">
-        <v>28.66</v>
+        <v>22.78</v>
       </c>
       <c r="G30">
-        <v>32.65</v>
+        <v>31.6</v>
       </c>
       <c r="H30">
-        <v>35.82</v>
+        <v>43.07</v>
       </c>
       <c r="I30" t="s">
         <v>50</v>
@@ -1472,16 +1475,16 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F31">
-        <v>21.6</v>
+        <v>17.76</v>
       </c>
       <c r="G31">
-        <v>26.66</v>
+        <v>31.12</v>
       </c>
       <c r="H31">
-        <v>32.55</v>
+        <v>38.82</v>
       </c>
       <c r="I31" t="s">
         <v>50</v>
@@ -1501,16 +1504,16 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="F32">
-        <v>7.68</v>
+        <v>12.63</v>
       </c>
       <c r="G32">
-        <v>24.61</v>
+        <v>30.4</v>
       </c>
       <c r="H32">
-        <v>42.48</v>
+        <v>49.17</v>
       </c>
       <c r="I32" t="s">
         <v>50</v>
@@ -1521,7 +1524,7 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C33" t="s">
         <v>46</v>
@@ -1530,16 +1533,16 @@
         <v>47</v>
       </c>
       <c r="E33">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F33">
-        <v>18.47</v>
+        <v>17.48</v>
       </c>
       <c r="G33">
-        <v>23.66</v>
+        <v>27.17</v>
       </c>
       <c r="H33">
-        <v>30.67</v>
+        <v>35.15</v>
       </c>
       <c r="I33" t="s">
         <v>50</v>
@@ -1559,19 +1562,19 @@
         <v>47</v>
       </c>
       <c r="E34">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F34">
-        <v>10.93</v>
+        <v>9.09</v>
       </c>
       <c r="G34">
-        <v>23.33</v>
+        <v>12.35</v>
       </c>
       <c r="H34">
-        <v>46.1</v>
+        <v>19.38</v>
       </c>
       <c r="I34" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -1591,7 +1594,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -1611,7 +1614,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -46,105 +46,105 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع دالان</t>
   </si>
   <si>
+    <t>پارک ملي قطرويه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بناب</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه هوا و</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه دراء</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع مزايجان</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه دراء</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع پادنا</t>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مهارلو</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوهستان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
   </si>
   <si>
     <t>منطقه حفاظت شده هرمود</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بناب</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع دره باغ</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
-  </si>
-  <si>
-    <t>پارک ملي قطرويه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه هوا و</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
+    <t>منطقه شکار ممنوع توت سياه</t>
   </si>
   <si>
     <t>پناهگاه حيات وحش دره باغ</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
+    <t>منطقه شکار ممنوع شیکوه</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع بصيران</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع شیکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوهستان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
+    <t>منطقه حفاظت شده برم فیروز</t>
   </si>
   <si>
     <t>منطقه حفاظت شده تنگ بستانک</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع چاه نفت</t>
   </si>
   <si>
@@ -157,10 +157,13 @@
     <t>مناطق ممنوعه شکار</t>
   </si>
   <si>
-    <t>1405-08-02</t>
-  </si>
-  <si>
-    <t>2026-10-24</t>
+    <t>1405-08-03</t>
+  </si>
+  <si>
+    <t>2026-10-25</t>
+  </si>
+  <si>
+    <t>بسیار شدید</t>
   </si>
   <si>
     <t>شدید</t>
@@ -170,9 +173,6 @@
   </si>
   <si>
     <t>زیاد</t>
-  </si>
-  <si>
-    <t>متوسط</t>
   </si>
   <si>
     <t>بدون داده</t>
@@ -634,16 +634,16 @@
         <v>47</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>55.45</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="G2">
-        <v>56.62</v>
+        <v>73.59</v>
       </c>
       <c r="H2">
-        <v>59.97</v>
+        <v>79.95</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -663,19 +663,19 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>46.58</v>
+        <v>67.26000000000001</v>
       </c>
       <c r="G3">
-        <v>53.57</v>
+        <v>68.81</v>
       </c>
       <c r="H3">
-        <v>58.86</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="I3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -683,7 +683,7 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C4" t="s">
         <v>46</v>
@@ -692,19 +692,19 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>45.31</v>
+        <v>67.17</v>
       </c>
       <c r="G4">
-        <v>51.73</v>
+        <v>67.17</v>
       </c>
       <c r="H4">
-        <v>57.98</v>
+        <v>67.17</v>
       </c>
       <c r="I4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -712,7 +712,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
         <v>46</v>
@@ -721,19 +721,19 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F5">
-        <v>46.09</v>
+        <v>61.55</v>
       </c>
       <c r="G5">
-        <v>50.66</v>
+        <v>65.66</v>
       </c>
       <c r="H5">
-        <v>55.43</v>
+        <v>76.23999999999999</v>
       </c>
       <c r="I5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -741,7 +741,7 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
         <v>46</v>
@@ -750,16 +750,16 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F6">
-        <v>46.42</v>
+        <v>56.82</v>
       </c>
       <c r="G6">
-        <v>48.55</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="H6">
-        <v>53.68</v>
+        <v>72.02</v>
       </c>
       <c r="I6" t="s">
         <v>49</v>
@@ -779,16 +779,16 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F7">
-        <v>38.02</v>
+        <v>54.72</v>
       </c>
       <c r="G7">
-        <v>48.09</v>
+        <v>64.16</v>
       </c>
       <c r="H7">
-        <v>56.65</v>
+        <v>76.42</v>
       </c>
       <c r="I7" t="s">
         <v>49</v>
@@ -808,16 +808,16 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="F8">
-        <v>44.02</v>
+        <v>49.65</v>
       </c>
       <c r="G8">
-        <v>47.98</v>
+        <v>62.05</v>
       </c>
       <c r="H8">
-        <v>54.32</v>
+        <v>74.41</v>
       </c>
       <c r="I8" t="s">
         <v>49</v>
@@ -837,16 +837,16 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>20</v>
+        <v>117</v>
       </c>
       <c r="F9">
-        <v>40.79</v>
+        <v>35.24</v>
       </c>
       <c r="G9">
-        <v>47.89</v>
+        <v>60.94</v>
       </c>
       <c r="H9">
-        <v>51.88</v>
+        <v>74.41</v>
       </c>
       <c r="I9" t="s">
         <v>49</v>
@@ -857,7 +857,7 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
         <v>46</v>
@@ -866,16 +866,16 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F10">
-        <v>41.33</v>
+        <v>53.32</v>
       </c>
       <c r="G10">
-        <v>47.05</v>
+        <v>60.32</v>
       </c>
       <c r="H10">
-        <v>51.23</v>
+        <v>69.83</v>
       </c>
       <c r="I10" t="s">
         <v>49</v>
@@ -895,16 +895,16 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="F11">
-        <v>32.93</v>
+        <v>52.02</v>
       </c>
       <c r="G11">
-        <v>46.69</v>
+        <v>56.91</v>
       </c>
       <c r="H11">
-        <v>57.14</v>
+        <v>61.38</v>
       </c>
       <c r="I11" t="s">
         <v>49</v>
@@ -924,16 +924,16 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F12">
-        <v>43.29</v>
+        <v>53.9</v>
       </c>
       <c r="G12">
-        <v>46.46</v>
+        <v>56.82</v>
       </c>
       <c r="H12">
-        <v>49.76</v>
+        <v>59.75</v>
       </c>
       <c r="I12" t="s">
         <v>49</v>
@@ -944,7 +944,7 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s">
         <v>46</v>
@@ -953,16 +953,16 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F13">
-        <v>46.17</v>
+        <v>44.53</v>
       </c>
       <c r="G13">
-        <v>46.17</v>
+        <v>56.49</v>
       </c>
       <c r="H13">
-        <v>46.17</v>
+        <v>66.89</v>
       </c>
       <c r="I13" t="s">
         <v>49</v>
@@ -973,7 +973,7 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
         <v>46</v>
@@ -982,16 +982,16 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F14">
-        <v>42.56</v>
+        <v>50.06</v>
       </c>
       <c r="G14">
-        <v>46.15</v>
+        <v>56.16</v>
       </c>
       <c r="H14">
-        <v>50.19</v>
+        <v>62.65</v>
       </c>
       <c r="I14" t="s">
         <v>49</v>
@@ -1002,7 +1002,7 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s">
         <v>46</v>
@@ -1011,16 +1011,16 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>117</v>
+        <v>13</v>
       </c>
       <c r="F15">
-        <v>34.14</v>
+        <v>52.53</v>
       </c>
       <c r="G15">
-        <v>45.52</v>
+        <v>55.98</v>
       </c>
       <c r="H15">
-        <v>57.52</v>
+        <v>57.64</v>
       </c>
       <c r="I15" t="s">
         <v>49</v>
@@ -1031,7 +1031,7 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
         <v>46</v>
@@ -1040,16 +1040,16 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F16">
-        <v>39.39</v>
+        <v>49.53</v>
       </c>
       <c r="G16">
-        <v>45.07</v>
+        <v>55.15</v>
       </c>
       <c r="H16">
-        <v>50.84</v>
+        <v>61.49</v>
       </c>
       <c r="I16" t="s">
         <v>49</v>
@@ -1060,7 +1060,7 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C17" t="s">
         <v>46</v>
@@ -1069,16 +1069,16 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F17">
-        <v>40.46</v>
+        <v>49.66</v>
       </c>
       <c r="G17">
-        <v>44.94</v>
+        <v>53.86</v>
       </c>
       <c r="H17">
-        <v>52.64</v>
+        <v>57.08</v>
       </c>
       <c r="I17" t="s">
         <v>49</v>
@@ -1089,7 +1089,7 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C18" t="s">
         <v>46</v>
@@ -1098,16 +1098,16 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="F18">
-        <v>34.14</v>
+        <v>50.98</v>
       </c>
       <c r="G18">
-        <v>44.89</v>
+        <v>53.65</v>
       </c>
       <c r="H18">
-        <v>57.52</v>
+        <v>56.78</v>
       </c>
       <c r="I18" t="s">
         <v>49</v>
@@ -1118,7 +1118,7 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
         <v>46</v>
@@ -1127,16 +1127,16 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="F19">
-        <v>39.95</v>
+        <v>51.68</v>
       </c>
       <c r="G19">
-        <v>44.72</v>
+        <v>52.87</v>
       </c>
       <c r="H19">
-        <v>49.57</v>
+        <v>54.6</v>
       </c>
       <c r="I19" t="s">
         <v>49</v>
@@ -1147,7 +1147,7 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C20" t="s">
         <v>46</v>
@@ -1156,16 +1156,16 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="F20">
-        <v>23.43</v>
+        <v>48.08</v>
       </c>
       <c r="G20">
-        <v>43.49</v>
+        <v>52.25</v>
       </c>
       <c r="H20">
-        <v>50.37</v>
+        <v>59.61</v>
       </c>
       <c r="I20" t="s">
         <v>49</v>
@@ -1176,7 +1176,7 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C21" t="s">
         <v>46</v>
@@ -1185,16 +1185,16 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F21">
-        <v>32.93</v>
+        <v>38.73</v>
       </c>
       <c r="G21">
-        <v>42.85</v>
+        <v>52.11</v>
       </c>
       <c r="H21">
-        <v>55.22</v>
+        <v>57.7</v>
       </c>
       <c r="I21" t="s">
         <v>49</v>
@@ -1214,16 +1214,16 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F22">
-        <v>39.98</v>
+        <v>43.66</v>
       </c>
       <c r="G22">
-        <v>42.13</v>
+        <v>51.86</v>
       </c>
       <c r="H22">
-        <v>44.88</v>
+        <v>58.83</v>
       </c>
       <c r="I22" t="s">
         <v>49</v>
@@ -1246,16 +1246,16 @@
         <v>10</v>
       </c>
       <c r="F23">
-        <v>36.85</v>
+        <v>45.46</v>
       </c>
       <c r="G23">
-        <v>41.24</v>
+        <v>49.83</v>
       </c>
       <c r="H23">
-        <v>44.56</v>
+        <v>54.91</v>
       </c>
       <c r="I23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -1263,7 +1263,7 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C24" t="s">
         <v>46</v>
@@ -1272,16 +1272,16 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F24">
-        <v>30.06</v>
+        <v>46.16</v>
       </c>
       <c r="G24">
-        <v>36.67</v>
+        <v>49.42</v>
       </c>
       <c r="H24">
-        <v>43.28</v>
+        <v>55.52</v>
       </c>
       <c r="I24" t="s">
         <v>50</v>
@@ -1301,16 +1301,16 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="F25">
-        <v>17.17</v>
+        <v>48.95</v>
       </c>
       <c r="G25">
-        <v>36.14</v>
+        <v>48.95</v>
       </c>
       <c r="H25">
-        <v>51.84</v>
+        <v>48.95</v>
       </c>
       <c r="I25" t="s">
         <v>50</v>
@@ -1330,16 +1330,16 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="F26">
-        <v>24.81</v>
+        <v>40.7</v>
       </c>
       <c r="G26">
-        <v>35.41</v>
+        <v>48.46</v>
       </c>
       <c r="H26">
-        <v>50.13</v>
+        <v>56.68</v>
       </c>
       <c r="I26" t="s">
         <v>50</v>
@@ -1350,7 +1350,7 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
         <v>46</v>
@@ -1359,16 +1359,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F27">
-        <v>28.56</v>
+        <v>44.8</v>
       </c>
       <c r="G27">
-        <v>33.66</v>
+        <v>47.47</v>
       </c>
       <c r="H27">
-        <v>40.05</v>
+        <v>49.8</v>
       </c>
       <c r="I27" t="s">
         <v>50</v>
@@ -1388,16 +1388,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F28">
-        <v>33.01</v>
+        <v>34.98</v>
       </c>
       <c r="G28">
-        <v>33.01</v>
+        <v>46.36</v>
       </c>
       <c r="H28">
-        <v>33.01</v>
+        <v>60.67</v>
       </c>
       <c r="I28" t="s">
         <v>50</v>
@@ -1408,7 +1408,7 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C29" t="s">
         <v>46</v>
@@ -1417,16 +1417,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F29">
-        <v>29</v>
+        <v>38.98</v>
       </c>
       <c r="G29">
-        <v>32.35</v>
+        <v>44.09</v>
       </c>
       <c r="H29">
-        <v>35.83</v>
+        <v>47.36</v>
       </c>
       <c r="I29" t="s">
         <v>50</v>
@@ -1446,16 +1446,16 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="F30">
-        <v>22.78</v>
+        <v>36.49</v>
       </c>
       <c r="G30">
-        <v>31.6</v>
+        <v>43.22</v>
       </c>
       <c r="H30">
-        <v>43.07</v>
+        <v>53</v>
       </c>
       <c r="I30" t="s">
         <v>50</v>
@@ -1466,7 +1466,7 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C31" t="s">
         <v>46</v>
@@ -1475,16 +1475,16 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F31">
-        <v>17.76</v>
+        <v>39.44</v>
       </c>
       <c r="G31">
-        <v>31.12</v>
+        <v>41.15</v>
       </c>
       <c r="H31">
-        <v>38.82</v>
+        <v>42.15</v>
       </c>
       <c r="I31" t="s">
         <v>50</v>
@@ -1504,19 +1504,19 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="F32">
-        <v>12.63</v>
+        <v>26.03</v>
       </c>
       <c r="G32">
-        <v>30.4</v>
+        <v>37.16</v>
       </c>
       <c r="H32">
-        <v>49.17</v>
+        <v>45.68</v>
       </c>
       <c r="I32" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -1536,16 +1536,16 @@
         <v>8</v>
       </c>
       <c r="F33">
-        <v>17.48</v>
+        <v>12.88</v>
       </c>
       <c r="G33">
-        <v>27.17</v>
+        <v>35.42</v>
       </c>
       <c r="H33">
-        <v>35.15</v>
+        <v>59.91</v>
       </c>
       <c r="I33" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1553,7 +1553,7 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C34" t="s">
         <v>46</v>
@@ -1562,16 +1562,16 @@
         <v>47</v>
       </c>
       <c r="E34">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F34">
-        <v>9.09</v>
+        <v>8.51</v>
       </c>
       <c r="G34">
-        <v>12.35</v>
+        <v>32.88</v>
       </c>
       <c r="H34">
-        <v>19.38</v>
+        <v>43.99</v>
       </c>
       <c r="I34" t="s">
         <v>51</v>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="51">
   <si>
     <t>نام منطقه</t>
   </si>
@@ -49,19 +49,28 @@
     <t>منطقه شکار ممنوع مل بلند</t>
   </si>
   <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بناب</t>
+  </si>
+  <si>
+    <t>پارک ملي قطرويه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه هوا و</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع دالان</t>
   </si>
   <si>
-    <t>پارک ملي قطرويه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بناب</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه هوا و</t>
+    <t>منطقه شکار ممنوع کوه دراء</t>
   </si>
   <si>
     <t>پارک ملي بختگان</t>
@@ -70,81 +79,72 @@
     <t>پناهگاه حيات وحش بختگان</t>
   </si>
   <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه دراء</t>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
   </si>
   <si>
     <t>منطقه شکار ممن.ع آق جلو</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع مهارلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بصيران</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مزايجان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع روشن کوه</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
+    <t>منطقه حفاظت شده برم فیروز</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع کوهستان</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
+    <t>منطقه شکار ممنوع شیکوه</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
   </si>
   <si>
     <t>منطقه حفاظت شده هرمود</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع توت سياه</t>
   </si>
   <si>
-    <t>پناهگاه حيات وحش دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع شیکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بصيران</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع چاه نفت</t>
   </si>
   <si>
@@ -157,22 +157,16 @@
     <t>مناطق ممنوعه شکار</t>
   </si>
   <si>
-    <t>1405-08-03</t>
-  </si>
-  <si>
-    <t>2026-10-25</t>
-  </si>
-  <si>
-    <t>بسیار شدید</t>
+    <t>1405-08-04</t>
+  </si>
+  <si>
+    <t>2026-10-26</t>
   </si>
   <si>
     <t>شدید</t>
   </si>
   <si>
     <t>خیلی زیاد</t>
-  </si>
-  <si>
-    <t>زیاد</t>
   </si>
   <si>
     <t>بدون داده</t>
@@ -637,13 +631,13 @@
         <v>6</v>
       </c>
       <c r="F2">
-        <v>66.73999999999999</v>
+        <v>59.2</v>
       </c>
       <c r="G2">
-        <v>73.59</v>
+        <v>67.42</v>
       </c>
       <c r="H2">
-        <v>79.95</v>
+        <v>75.65000000000001</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -654,7 +648,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s">
         <v>46</v>
@@ -663,19 +657,19 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F3">
-        <v>67.26000000000001</v>
+        <v>59.18</v>
       </c>
       <c r="G3">
-        <v>68.81</v>
+        <v>66.45999999999999</v>
       </c>
       <c r="H3">
-        <v>71.59999999999999</v>
+        <v>74.13</v>
       </c>
       <c r="I3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -683,7 +677,7 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C4" t="s">
         <v>46</v>
@@ -692,19 +686,19 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F4">
-        <v>67.17</v>
+        <v>52.2</v>
       </c>
       <c r="G4">
-        <v>67.17</v>
+        <v>66.20999999999999</v>
       </c>
       <c r="H4">
-        <v>67.17</v>
+        <v>75.42</v>
       </c>
       <c r="I4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -721,19 +715,19 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>61.55</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="G5">
-        <v>65.66</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="H5">
-        <v>76.23999999999999</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="I5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -750,19 +744,19 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F6">
-        <v>56.82</v>
+        <v>56.61</v>
       </c>
       <c r="G6">
-        <v>64.56999999999999</v>
+        <v>63.45</v>
       </c>
       <c r="H6">
-        <v>72.02</v>
+        <v>73.19</v>
       </c>
       <c r="I6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -770,7 +764,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
         <v>46</v>
@@ -779,19 +773,19 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>54.72</v>
+        <v>61.18</v>
       </c>
       <c r="G7">
-        <v>64.16</v>
+        <v>63.09</v>
       </c>
       <c r="H7">
-        <v>76.42</v>
+        <v>64.19</v>
       </c>
       <c r="I7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -808,19 +802,19 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="F8">
-        <v>49.65</v>
+        <v>52.76</v>
       </c>
       <c r="G8">
-        <v>62.05</v>
+        <v>62.78</v>
       </c>
       <c r="H8">
-        <v>74.41</v>
+        <v>75.53</v>
       </c>
       <c r="I8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -828,7 +822,7 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
         <v>46</v>
@@ -837,19 +831,19 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>117</v>
+        <v>8</v>
       </c>
       <c r="F9">
-        <v>35.24</v>
+        <v>58.48</v>
       </c>
       <c r="G9">
-        <v>60.94</v>
+        <v>60.24</v>
       </c>
       <c r="H9">
-        <v>74.41</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="I9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -857,7 +851,7 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
         <v>46</v>
@@ -866,19 +860,19 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F10">
-        <v>53.32</v>
+        <v>57.32</v>
       </c>
       <c r="G10">
-        <v>60.32</v>
+        <v>60.14</v>
       </c>
       <c r="H10">
-        <v>69.83</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="I10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -886,7 +880,7 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
         <v>46</v>
@@ -895,19 +889,19 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="F11">
-        <v>52.02</v>
+        <v>51.16</v>
       </c>
       <c r="G11">
-        <v>56.91</v>
+        <v>59.96</v>
       </c>
       <c r="H11">
-        <v>61.38</v>
+        <v>67.48</v>
       </c>
       <c r="I11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -915,7 +909,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
         <v>46</v>
@@ -924,19 +918,19 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>117</v>
       </c>
       <c r="F12">
-        <v>53.9</v>
+        <v>46.59</v>
       </c>
       <c r="G12">
-        <v>56.82</v>
+        <v>59.32</v>
       </c>
       <c r="H12">
-        <v>59.75</v>
+        <v>67.48</v>
       </c>
       <c r="I12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -944,7 +938,7 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
         <v>46</v>
@@ -953,19 +947,19 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F13">
-        <v>44.53</v>
+        <v>49.87</v>
       </c>
       <c r="G13">
-        <v>56.49</v>
+        <v>58.64</v>
       </c>
       <c r="H13">
-        <v>66.89</v>
+        <v>64.08</v>
       </c>
       <c r="I13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -985,16 +979,16 @@
         <v>20</v>
       </c>
       <c r="F14">
-        <v>50.06</v>
+        <v>51.27</v>
       </c>
       <c r="G14">
-        <v>56.16</v>
+        <v>57.33</v>
       </c>
       <c r="H14">
-        <v>62.65</v>
+        <v>63.7</v>
       </c>
       <c r="I14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -1002,7 +996,7 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
         <v>46</v>
@@ -1011,19 +1005,19 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F15">
-        <v>52.53</v>
+        <v>50.47</v>
       </c>
       <c r="G15">
-        <v>55.98</v>
+        <v>56.84</v>
       </c>
       <c r="H15">
-        <v>57.64</v>
+        <v>62.94</v>
       </c>
       <c r="I15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1031,7 +1025,7 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
         <v>46</v>
@@ -1040,19 +1034,19 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F16">
-        <v>49.53</v>
+        <v>52.17</v>
       </c>
       <c r="G16">
-        <v>55.15</v>
+        <v>53.85</v>
       </c>
       <c r="H16">
-        <v>61.49</v>
+        <v>55.52</v>
       </c>
       <c r="I16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1069,19 +1063,19 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F17">
-        <v>49.66</v>
+        <v>50.74</v>
       </c>
       <c r="G17">
-        <v>53.86</v>
+        <v>52.31</v>
       </c>
       <c r="H17">
-        <v>57.08</v>
+        <v>56.8</v>
       </c>
       <c r="I17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1098,19 +1092,19 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F18">
-        <v>50.98</v>
+        <v>48.04</v>
       </c>
       <c r="G18">
-        <v>53.65</v>
+        <v>52.15</v>
       </c>
       <c r="H18">
-        <v>56.78</v>
+        <v>57.86</v>
       </c>
       <c r="I18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1118,7 +1112,7 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C19" t="s">
         <v>46</v>
@@ -1127,19 +1121,19 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="F19">
-        <v>51.68</v>
+        <v>41.87</v>
       </c>
       <c r="G19">
-        <v>52.87</v>
+        <v>52.04</v>
       </c>
       <c r="H19">
-        <v>54.6</v>
+        <v>60.38</v>
       </c>
       <c r="I19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1147,7 +1141,7 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C20" t="s">
         <v>46</v>
@@ -1156,19 +1150,19 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F20">
-        <v>48.08</v>
+        <v>45.72</v>
       </c>
       <c r="G20">
-        <v>52.25</v>
+        <v>51.15</v>
       </c>
       <c r="H20">
-        <v>59.61</v>
+        <v>63.98</v>
       </c>
       <c r="I20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1185,19 +1179,19 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F21">
-        <v>38.73</v>
+        <v>41.75</v>
       </c>
       <c r="G21">
-        <v>52.11</v>
+        <v>50.37</v>
       </c>
       <c r="H21">
-        <v>57.7</v>
+        <v>57.91</v>
       </c>
       <c r="I21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -1214,19 +1208,19 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F22">
-        <v>43.66</v>
+        <v>37.2</v>
       </c>
       <c r="G22">
-        <v>51.86</v>
+        <v>50.13</v>
       </c>
       <c r="H22">
-        <v>58.83</v>
+        <v>60.38</v>
       </c>
       <c r="I22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1234,7 +1228,7 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C23" t="s">
         <v>46</v>
@@ -1243,19 +1237,19 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F23">
-        <v>45.46</v>
+        <v>46.46</v>
       </c>
       <c r="G23">
-        <v>49.83</v>
+        <v>49.71</v>
       </c>
       <c r="H23">
-        <v>54.91</v>
+        <v>54.58</v>
       </c>
       <c r="I23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -1263,7 +1257,7 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C24" t="s">
         <v>46</v>
@@ -1272,19 +1266,19 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F24">
-        <v>46.16</v>
+        <v>45.27</v>
       </c>
       <c r="G24">
-        <v>49.42</v>
+        <v>48.81</v>
       </c>
       <c r="H24">
-        <v>55.52</v>
+        <v>51.77</v>
       </c>
       <c r="I24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -1301,19 +1295,19 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="F25">
-        <v>48.95</v>
+        <v>40.02</v>
       </c>
       <c r="G25">
-        <v>48.95</v>
+        <v>48.65</v>
       </c>
       <c r="H25">
-        <v>48.95</v>
+        <v>56.33</v>
       </c>
       <c r="I25" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -1330,19 +1324,19 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="F26">
-        <v>40.7</v>
+        <v>41.56</v>
       </c>
       <c r="G26">
-        <v>48.46</v>
+        <v>46.07</v>
       </c>
       <c r="H26">
-        <v>56.68</v>
+        <v>48.36</v>
       </c>
       <c r="I26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -1350,7 +1344,7 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
         <v>46</v>
@@ -1359,19 +1353,19 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F27">
-        <v>44.8</v>
+        <v>39.82</v>
       </c>
       <c r="G27">
-        <v>47.47</v>
+        <v>45.91</v>
       </c>
       <c r="H27">
-        <v>49.8</v>
+        <v>56.15</v>
       </c>
       <c r="I27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -1379,7 +1373,7 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C28" t="s">
         <v>46</v>
@@ -1388,19 +1382,19 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F28">
-        <v>34.98</v>
+        <v>35.1</v>
       </c>
       <c r="G28">
-        <v>46.36</v>
+        <v>45.63</v>
       </c>
       <c r="H28">
-        <v>60.67</v>
+        <v>57.6</v>
       </c>
       <c r="I28" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -1417,19 +1411,19 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F29">
-        <v>38.98</v>
+        <v>45.6</v>
       </c>
       <c r="G29">
-        <v>44.09</v>
+        <v>45.6</v>
       </c>
       <c r="H29">
-        <v>47.36</v>
+        <v>45.6</v>
       </c>
       <c r="I29" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -1437,7 +1431,7 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C30" t="s">
         <v>46</v>
@@ -1449,16 +1443,16 @@
         <v>3</v>
       </c>
       <c r="F30">
-        <v>36.49</v>
+        <v>43.6</v>
       </c>
       <c r="G30">
-        <v>43.22</v>
+        <v>45.31</v>
       </c>
       <c r="H30">
-        <v>53</v>
+        <v>47.37</v>
       </c>
       <c r="I30" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -1466,7 +1460,7 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C31" t="s">
         <v>46</v>
@@ -1478,16 +1472,16 @@
         <v>3</v>
       </c>
       <c r="F31">
-        <v>39.44</v>
+        <v>40.55</v>
       </c>
       <c r="G31">
-        <v>41.15</v>
+        <v>44.86</v>
       </c>
       <c r="H31">
-        <v>42.15</v>
+        <v>53.07</v>
       </c>
       <c r="I31" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -1495,7 +1489,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C32" t="s">
         <v>46</v>
@@ -1504,19 +1498,19 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="F32">
-        <v>26.03</v>
+        <v>37.66</v>
       </c>
       <c r="G32">
-        <v>37.16</v>
+        <v>44.84</v>
       </c>
       <c r="H32">
-        <v>45.68</v>
+        <v>47.9</v>
       </c>
       <c r="I32" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -1533,19 +1527,19 @@
         <v>47</v>
       </c>
       <c r="E33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F33">
-        <v>12.88</v>
+        <v>40.93</v>
       </c>
       <c r="G33">
-        <v>35.42</v>
+        <v>44.08</v>
       </c>
       <c r="H33">
-        <v>59.91</v>
+        <v>47.51</v>
       </c>
       <c r="I33" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1553,7 +1547,7 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C34" t="s">
         <v>46</v>
@@ -1562,19 +1556,19 @@
         <v>47</v>
       </c>
       <c r="E34">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F34">
-        <v>8.51</v>
+        <v>40</v>
       </c>
       <c r="G34">
-        <v>32.88</v>
+        <v>41.69</v>
       </c>
       <c r="H34">
-        <v>43.99</v>
+        <v>43.83</v>
       </c>
       <c r="I34" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -1594,7 +1588,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -1614,7 +1608,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="52">
   <si>
     <t>نام منطقه</t>
   </si>
@@ -46,105 +46,105 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع بناب</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع مل بلند</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع دالان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه هوا و</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مزايجان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوهستان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بصيران</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
     <t>پارک ملی بمو</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع بناب</t>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مهارلو</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع شیکوه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
   </si>
   <si>
     <t>پارک ملي قطرويه</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه هوا و</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دالان</t>
+    <t>منطقه حفاظت شده هرمود</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع توت سياه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده برم فیروز</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع کوه دراء</t>
   </si>
   <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بصيران</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوهستان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع شیکوه</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده هرمود</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع چاه نفت</t>
   </si>
   <si>
@@ -157,16 +157,19 @@
     <t>مناطق ممنوعه شکار</t>
   </si>
   <si>
-    <t>1405-08-04</t>
-  </si>
-  <si>
-    <t>2026-10-26</t>
+    <t>1405-08-05</t>
+  </si>
+  <si>
+    <t>2026-10-27</t>
   </si>
   <si>
     <t>شدید</t>
   </si>
   <si>
     <t>خیلی زیاد</t>
+  </si>
+  <si>
+    <t>زیاد</t>
   </si>
   <si>
     <t>بدون داده</t>
@@ -628,16 +631,16 @@
         <v>47</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F2">
-        <v>59.2</v>
+        <v>60.65</v>
       </c>
       <c r="G2">
-        <v>67.42</v>
+        <v>68.56</v>
       </c>
       <c r="H2">
-        <v>75.65000000000001</v>
+        <v>74.66</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -648,7 +651,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C3" t="s">
         <v>46</v>
@@ -657,16 +660,16 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>59.18</v>
+        <v>58.68</v>
       </c>
       <c r="G3">
-        <v>66.45999999999999</v>
+        <v>61.83</v>
       </c>
       <c r="H3">
-        <v>74.13</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -686,16 +689,16 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>52.2</v>
+        <v>60.45</v>
       </c>
       <c r="G4">
-        <v>66.20999999999999</v>
+        <v>61.79</v>
       </c>
       <c r="H4">
-        <v>75.42</v>
+        <v>64.05</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -706,7 +709,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
         <v>46</v>
@@ -715,16 +718,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="F5">
-        <v>65.26000000000001</v>
+        <v>51.26</v>
       </c>
       <c r="G5">
-        <v>65.26000000000001</v>
+        <v>61.57</v>
       </c>
       <c r="H5">
-        <v>65.26000000000001</v>
+        <v>77.06</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -744,16 +747,16 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="F6">
-        <v>56.61</v>
+        <v>43.26</v>
       </c>
       <c r="G6">
-        <v>63.45</v>
+        <v>52.64</v>
       </c>
       <c r="H6">
-        <v>73.19</v>
+        <v>58.55</v>
       </c>
       <c r="I6" t="s">
         <v>48</v>
@@ -764,7 +767,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
         <v>46</v>
@@ -773,16 +776,16 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="F7">
-        <v>61.18</v>
+        <v>39.73</v>
       </c>
       <c r="G7">
-        <v>63.09</v>
+        <v>51.22</v>
       </c>
       <c r="H7">
-        <v>64.19</v>
+        <v>57.46</v>
       </c>
       <c r="I7" t="s">
         <v>48</v>
@@ -793,7 +796,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C8" t="s">
         <v>46</v>
@@ -802,16 +805,16 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="F8">
-        <v>52.76</v>
+        <v>47.15</v>
       </c>
       <c r="G8">
-        <v>62.78</v>
+        <v>51.03</v>
       </c>
       <c r="H8">
-        <v>75.53</v>
+        <v>54.9</v>
       </c>
       <c r="I8" t="s">
         <v>48</v>
@@ -831,16 +834,16 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F9">
-        <v>58.48</v>
+        <v>44.84</v>
       </c>
       <c r="G9">
-        <v>60.24</v>
+        <v>50.12</v>
       </c>
       <c r="H9">
-        <v>64.56999999999999</v>
+        <v>55.49</v>
       </c>
       <c r="I9" t="s">
         <v>48</v>
@@ -860,16 +863,16 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F10">
-        <v>57.32</v>
+        <v>43.64</v>
       </c>
       <c r="G10">
-        <v>60.14</v>
+        <v>50.03</v>
       </c>
       <c r="H10">
-        <v>69.59999999999999</v>
+        <v>56.21</v>
       </c>
       <c r="I10" t="s">
         <v>48</v>
@@ -889,19 +892,19 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>65</v>
+        <v>3</v>
       </c>
       <c r="F11">
-        <v>51.16</v>
+        <v>45.95</v>
       </c>
       <c r="G11">
-        <v>59.96</v>
+        <v>48.54</v>
       </c>
       <c r="H11">
-        <v>67.48</v>
+        <v>49.97</v>
       </c>
       <c r="I11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -918,19 +921,19 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>117</v>
+        <v>23</v>
       </c>
       <c r="F12">
-        <v>46.59</v>
+        <v>40.17</v>
       </c>
       <c r="G12">
-        <v>59.32</v>
+        <v>48.36</v>
       </c>
       <c r="H12">
-        <v>67.48</v>
+        <v>57.09</v>
       </c>
       <c r="I12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -938,7 +941,7 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s">
         <v>46</v>
@@ -947,19 +950,19 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F13">
-        <v>49.87</v>
+        <v>40.77</v>
       </c>
       <c r="G13">
-        <v>58.64</v>
+        <v>47.81</v>
       </c>
       <c r="H13">
-        <v>64.08</v>
+        <v>52.32</v>
       </c>
       <c r="I13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -976,19 +979,19 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F14">
-        <v>51.27</v>
+        <v>47.8</v>
       </c>
       <c r="G14">
-        <v>57.33</v>
+        <v>47.8</v>
       </c>
       <c r="H14">
-        <v>63.7</v>
+        <v>47.8</v>
       </c>
       <c r="I14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -996,7 +999,7 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s">
         <v>46</v>
@@ -1005,19 +1008,19 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F15">
-        <v>50.47</v>
+        <v>43.83</v>
       </c>
       <c r="G15">
-        <v>56.84</v>
+        <v>47.76</v>
       </c>
       <c r="H15">
-        <v>62.94</v>
+        <v>52.09</v>
       </c>
       <c r="I15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1034,19 +1037,19 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F16">
-        <v>52.17</v>
+        <v>37.44</v>
       </c>
       <c r="G16">
-        <v>53.85</v>
+        <v>47.47</v>
       </c>
       <c r="H16">
-        <v>55.52</v>
+        <v>54.66</v>
       </c>
       <c r="I16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1063,19 +1066,19 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F17">
-        <v>50.74</v>
+        <v>31.37</v>
       </c>
       <c r="G17">
-        <v>52.31</v>
+        <v>47.34</v>
       </c>
       <c r="H17">
-        <v>56.8</v>
+        <v>59.72</v>
       </c>
       <c r="I17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1095,16 +1098,16 @@
         <v>12</v>
       </c>
       <c r="F18">
-        <v>48.04</v>
+        <v>42.32</v>
       </c>
       <c r="G18">
-        <v>52.15</v>
+        <v>47.22</v>
       </c>
       <c r="H18">
-        <v>57.86</v>
+        <v>51.34</v>
       </c>
       <c r="I18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1112,7 +1115,7 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
         <v>46</v>
@@ -1121,19 +1124,19 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="F19">
-        <v>41.87</v>
+        <v>40.02</v>
       </c>
       <c r="G19">
-        <v>52.04</v>
+        <v>46.48</v>
       </c>
       <c r="H19">
-        <v>60.38</v>
+        <v>53.92</v>
       </c>
       <c r="I19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1141,7 +1144,7 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C20" t="s">
         <v>46</v>
@@ -1150,19 +1153,19 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F20">
-        <v>45.72</v>
+        <v>41.7</v>
       </c>
       <c r="G20">
-        <v>51.15</v>
+        <v>46.46</v>
       </c>
       <c r="H20">
-        <v>63.98</v>
+        <v>50.65</v>
       </c>
       <c r="I20" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1170,7 +1173,7 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C21" t="s">
         <v>46</v>
@@ -1179,19 +1182,19 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>20</v>
+        <v>117</v>
       </c>
       <c r="F21">
-        <v>41.75</v>
+        <v>37.74</v>
       </c>
       <c r="G21">
-        <v>50.37</v>
+        <v>45.96</v>
       </c>
       <c r="H21">
-        <v>57.91</v>
+        <v>53.92</v>
       </c>
       <c r="I21" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -1208,19 +1211,19 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F22">
-        <v>37.2</v>
+        <v>41.68</v>
       </c>
       <c r="G22">
-        <v>50.13</v>
+        <v>45.9</v>
       </c>
       <c r="H22">
-        <v>60.38</v>
+        <v>48.72</v>
       </c>
       <c r="I22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1237,16 +1240,16 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="F23">
-        <v>46.46</v>
+        <v>42.22</v>
       </c>
       <c r="G23">
-        <v>49.71</v>
+        <v>45.7</v>
       </c>
       <c r="H23">
-        <v>54.58</v>
+        <v>52.65</v>
       </c>
       <c r="I23" t="s">
         <v>49</v>
@@ -1257,7 +1260,7 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C24" t="s">
         <v>46</v>
@@ -1266,16 +1269,16 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F24">
-        <v>45.27</v>
+        <v>40.49</v>
       </c>
       <c r="G24">
-        <v>48.81</v>
+        <v>44.74</v>
       </c>
       <c r="H24">
-        <v>51.77</v>
+        <v>52.69</v>
       </c>
       <c r="I24" t="s">
         <v>49</v>
@@ -1295,16 +1298,16 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>62</v>
+        <v>3</v>
       </c>
       <c r="F25">
-        <v>40.02</v>
+        <v>40.06</v>
       </c>
       <c r="G25">
-        <v>48.65</v>
+        <v>44.47</v>
       </c>
       <c r="H25">
-        <v>56.33</v>
+        <v>50.59</v>
       </c>
       <c r="I25" t="s">
         <v>49</v>
@@ -1315,7 +1318,7 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C26" t="s">
         <v>46</v>
@@ -1324,16 +1327,16 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F26">
-        <v>41.56</v>
+        <v>26.14</v>
       </c>
       <c r="G26">
-        <v>46.07</v>
+        <v>42.45</v>
       </c>
       <c r="H26">
-        <v>48.36</v>
+        <v>63.13</v>
       </c>
       <c r="I26" t="s">
         <v>49</v>
@@ -1344,7 +1347,7 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
         <v>46</v>
@@ -1353,16 +1356,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F27">
-        <v>39.82</v>
+        <v>40.95</v>
       </c>
       <c r="G27">
-        <v>45.91</v>
+        <v>40.95</v>
       </c>
       <c r="H27">
-        <v>56.15</v>
+        <v>40.95</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1382,16 +1385,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F28">
-        <v>35.1</v>
+        <v>37.91</v>
       </c>
       <c r="G28">
-        <v>45.63</v>
+        <v>40.33</v>
       </c>
       <c r="H28">
-        <v>57.6</v>
+        <v>42.48</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
@@ -1402,7 +1405,7 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C29" t="s">
         <v>46</v>
@@ -1411,16 +1414,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F29">
-        <v>45.6</v>
+        <v>28.99</v>
       </c>
       <c r="G29">
-        <v>45.6</v>
+        <v>40.27</v>
       </c>
       <c r="H29">
-        <v>45.6</v>
+        <v>45.95</v>
       </c>
       <c r="I29" t="s">
         <v>49</v>
@@ -1440,16 +1443,16 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F30">
-        <v>43.6</v>
+        <v>37.69</v>
       </c>
       <c r="G30">
-        <v>45.31</v>
+        <v>39.41</v>
       </c>
       <c r="H30">
-        <v>47.37</v>
+        <v>39.98</v>
       </c>
       <c r="I30" t="s">
         <v>49</v>
@@ -1469,16 +1472,16 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="F31">
-        <v>40.55</v>
+        <v>29.91</v>
       </c>
       <c r="G31">
-        <v>44.86</v>
+        <v>39.08</v>
       </c>
       <c r="H31">
-        <v>53.07</v>
+        <v>52.53</v>
       </c>
       <c r="I31" t="s">
         <v>49</v>
@@ -1498,19 +1501,19 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F32">
-        <v>37.66</v>
+        <v>29.05</v>
       </c>
       <c r="G32">
-        <v>44.84</v>
+        <v>37.71</v>
       </c>
       <c r="H32">
-        <v>47.9</v>
+        <v>44.27</v>
       </c>
       <c r="I32" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -1518,7 +1521,7 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C33" t="s">
         <v>46</v>
@@ -1527,19 +1530,19 @@
         <v>47</v>
       </c>
       <c r="E33">
-        <v>9</v>
+        <v>62</v>
       </c>
       <c r="F33">
-        <v>40.93</v>
+        <v>28.21</v>
       </c>
       <c r="G33">
-        <v>44.08</v>
+        <v>36.91</v>
       </c>
       <c r="H33">
-        <v>47.51</v>
+        <v>45.73</v>
       </c>
       <c r="I33" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1556,19 +1559,19 @@
         <v>47</v>
       </c>
       <c r="E34">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F34">
-        <v>40</v>
+        <v>27.03</v>
       </c>
       <c r="G34">
-        <v>41.69</v>
+        <v>36.39</v>
       </c>
       <c r="H34">
-        <v>43.83</v>
+        <v>53.13</v>
       </c>
       <c r="I34" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -1588,7 +1591,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -1608,7 +1611,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -46,105 +46,105 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع کوه دراء</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دالان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه هوا و</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع توت سياه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع بناب</t>
   </si>
   <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش دره باغ</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع مل بلند</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع دالان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه هوا و</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>پارک ملي قطرويه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
+  </si>
+  <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع شیکوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مهارلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع مزايجان</t>
   </si>
   <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع پادنا</t>
+    <t>منطقه حفاظت شده ماله گاله</t>
   </si>
   <si>
     <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
+    <t>منطقه شکار ممنوع بصيران</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده هرمود</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع کوهستان</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بصيران</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع شیکوه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
-  </si>
-  <si>
-    <t>پارک ملي قطرويه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده هرمود</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
     <t>منطقه حفاظت شده برم فیروز</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه دراء</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع چاه نفت</t>
   </si>
   <si>
@@ -157,10 +157,10 @@
     <t>مناطق ممنوعه شکار</t>
   </si>
   <si>
-    <t>1405-08-05</t>
-  </si>
-  <si>
-    <t>2026-10-27</t>
+    <t>1405-08-06</t>
+  </si>
+  <si>
+    <t>2026-10-28</t>
   </si>
   <si>
     <t>شدید</t>
@@ -631,16 +631,16 @@
         <v>47</v>
       </c>
       <c r="E2">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F2">
-        <v>60.65</v>
+        <v>50.54</v>
       </c>
       <c r="G2">
-        <v>68.56</v>
+        <v>55.56</v>
       </c>
       <c r="H2">
-        <v>74.66</v>
+        <v>62.66</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -660,16 +660,16 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>58.68</v>
+        <v>50.52</v>
       </c>
       <c r="G3">
-        <v>61.83</v>
+        <v>51.09</v>
       </c>
       <c r="H3">
-        <v>64.54000000000001</v>
+        <v>52.47</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -689,16 +689,16 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="F4">
-        <v>60.45</v>
+        <v>46.03</v>
       </c>
       <c r="G4">
-        <v>61.79</v>
+        <v>50.87</v>
       </c>
       <c r="H4">
-        <v>64.05</v>
+        <v>54.12</v>
       </c>
       <c r="I4" t="s">
         <v>48</v>
@@ -718,19 +718,19 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>51.26</v>
+        <v>48.49</v>
       </c>
       <c r="G5">
-        <v>61.57</v>
+        <v>48.9</v>
       </c>
       <c r="H5">
-        <v>77.06</v>
+        <v>49.3</v>
       </c>
       <c r="I5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -747,19 +747,19 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>43.26</v>
+        <v>46.85</v>
       </c>
       <c r="G6">
-        <v>52.64</v>
+        <v>47.91</v>
       </c>
       <c r="H6">
-        <v>58.55</v>
+        <v>48.98</v>
       </c>
       <c r="I6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -767,7 +767,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
         <v>46</v>
@@ -776,19 +776,19 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F7">
-        <v>39.73</v>
+        <v>32.87</v>
       </c>
       <c r="G7">
-        <v>51.22</v>
+        <v>47.33</v>
       </c>
       <c r="H7">
-        <v>57.46</v>
+        <v>51.59</v>
       </c>
       <c r="I7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -805,19 +805,19 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F8">
-        <v>47.15</v>
+        <v>43.15</v>
       </c>
       <c r="G8">
-        <v>51.03</v>
+        <v>46.75</v>
       </c>
       <c r="H8">
-        <v>54.9</v>
+        <v>51.94</v>
       </c>
       <c r="I8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -825,7 +825,7 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s">
         <v>46</v>
@@ -834,19 +834,19 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F9">
-        <v>44.84</v>
+        <v>42.53</v>
       </c>
       <c r="G9">
-        <v>50.12</v>
+        <v>46.43</v>
       </c>
       <c r="H9">
-        <v>55.49</v>
+        <v>52.83</v>
       </c>
       <c r="I9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -866,16 +866,16 @@
         <v>20</v>
       </c>
       <c r="F10">
-        <v>43.64</v>
+        <v>39.91</v>
       </c>
       <c r="G10">
-        <v>50.03</v>
+        <v>46.08</v>
       </c>
       <c r="H10">
-        <v>56.21</v>
+        <v>50.56</v>
       </c>
       <c r="I10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -892,16 +892,16 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>117</v>
       </c>
       <c r="F11">
-        <v>45.95</v>
+        <v>39.09</v>
       </c>
       <c r="G11">
-        <v>48.54</v>
+        <v>45.58</v>
       </c>
       <c r="H11">
-        <v>49.97</v>
+        <v>56.24</v>
       </c>
       <c r="I11" t="s">
         <v>49</v>
@@ -921,16 +921,16 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="F12">
-        <v>40.17</v>
+        <v>43.58</v>
       </c>
       <c r="G12">
-        <v>48.36</v>
+        <v>45.42</v>
       </c>
       <c r="H12">
-        <v>57.09</v>
+        <v>48.08</v>
       </c>
       <c r="I12" t="s">
         <v>49</v>
@@ -941,7 +941,7 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
         <v>46</v>
@@ -950,16 +950,16 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="F13">
-        <v>40.77</v>
+        <v>39.31</v>
       </c>
       <c r="G13">
-        <v>47.81</v>
+        <v>45.34</v>
       </c>
       <c r="H13">
-        <v>52.32</v>
+        <v>50.72</v>
       </c>
       <c r="I13" t="s">
         <v>49</v>
@@ -979,16 +979,16 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="F14">
-        <v>47.8</v>
+        <v>38.25</v>
       </c>
       <c r="G14">
-        <v>47.8</v>
+        <v>44.74</v>
       </c>
       <c r="H14">
-        <v>47.8</v>
+        <v>55.02</v>
       </c>
       <c r="I14" t="s">
         <v>49</v>
@@ -1008,16 +1008,16 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F15">
-        <v>43.83</v>
+        <v>42.03</v>
       </c>
       <c r="G15">
-        <v>47.76</v>
+        <v>44.39</v>
       </c>
       <c r="H15">
-        <v>52.09</v>
+        <v>49.78</v>
       </c>
       <c r="I15" t="s">
         <v>49</v>
@@ -1037,16 +1037,16 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F16">
-        <v>37.44</v>
+        <v>42.2</v>
       </c>
       <c r="G16">
-        <v>47.47</v>
+        <v>44.05</v>
       </c>
       <c r="H16">
-        <v>54.66</v>
+        <v>46.45</v>
       </c>
       <c r="I16" t="s">
         <v>49</v>
@@ -1066,16 +1066,16 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="F17">
-        <v>31.37</v>
+        <v>38.79</v>
       </c>
       <c r="G17">
-        <v>47.34</v>
+        <v>43.18</v>
       </c>
       <c r="H17">
-        <v>59.72</v>
+        <v>47.73</v>
       </c>
       <c r="I17" t="s">
         <v>49</v>
@@ -1086,7 +1086,7 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
         <v>46</v>
@@ -1095,16 +1095,16 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F18">
-        <v>42.32</v>
+        <v>38.74</v>
       </c>
       <c r="G18">
-        <v>47.22</v>
+        <v>42.93</v>
       </c>
       <c r="H18">
-        <v>51.34</v>
+        <v>46.37</v>
       </c>
       <c r="I18" t="s">
         <v>49</v>
@@ -1124,16 +1124,16 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>65</v>
+        <v>4</v>
       </c>
       <c r="F19">
-        <v>40.02</v>
+        <v>42.68</v>
       </c>
       <c r="G19">
-        <v>46.48</v>
+        <v>42.68</v>
       </c>
       <c r="H19">
-        <v>53.92</v>
+        <v>42.68</v>
       </c>
       <c r="I19" t="s">
         <v>49</v>
@@ -1144,7 +1144,7 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C20" t="s">
         <v>46</v>
@@ -1153,16 +1153,16 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F20">
-        <v>41.7</v>
+        <v>37.91</v>
       </c>
       <c r="G20">
-        <v>46.46</v>
+        <v>42.54</v>
       </c>
       <c r="H20">
-        <v>50.65</v>
+        <v>47.09</v>
       </c>
       <c r="I20" t="s">
         <v>49</v>
@@ -1173,7 +1173,7 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C21" t="s">
         <v>46</v>
@@ -1182,16 +1182,16 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>117</v>
+        <v>12</v>
       </c>
       <c r="F21">
-        <v>37.74</v>
+        <v>40.8</v>
       </c>
       <c r="G21">
-        <v>45.96</v>
+        <v>42.14</v>
       </c>
       <c r="H21">
-        <v>53.92</v>
+        <v>43.72</v>
       </c>
       <c r="I21" t="s">
         <v>49</v>
@@ -1202,7 +1202,7 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C22" t="s">
         <v>46</v>
@@ -1211,16 +1211,16 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F22">
-        <v>41.68</v>
+        <v>37.32</v>
       </c>
       <c r="G22">
-        <v>45.9</v>
+        <v>41.55</v>
       </c>
       <c r="H22">
-        <v>48.72</v>
+        <v>46.83</v>
       </c>
       <c r="I22" t="s">
         <v>49</v>
@@ -1231,7 +1231,7 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C23" t="s">
         <v>46</v>
@@ -1243,13 +1243,13 @@
         <v>3</v>
       </c>
       <c r="F23">
-        <v>42.22</v>
+        <v>40.24</v>
       </c>
       <c r="G23">
-        <v>45.7</v>
+        <v>41.51</v>
       </c>
       <c r="H23">
-        <v>52.65</v>
+        <v>43.45</v>
       </c>
       <c r="I23" t="s">
         <v>49</v>
@@ -1260,7 +1260,7 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C24" t="s">
         <v>46</v>
@@ -1269,16 +1269,16 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F24">
-        <v>40.49</v>
+        <v>36.97</v>
       </c>
       <c r="G24">
-        <v>44.74</v>
+        <v>41.12</v>
       </c>
       <c r="H24">
-        <v>52.69</v>
+        <v>46.47</v>
       </c>
       <c r="I24" t="s">
         <v>49</v>
@@ -1298,16 +1298,16 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F25">
-        <v>40.06</v>
+        <v>39.13</v>
       </c>
       <c r="G25">
-        <v>44.47</v>
+        <v>40.85</v>
       </c>
       <c r="H25">
-        <v>50.59</v>
+        <v>41.92</v>
       </c>
       <c r="I25" t="s">
         <v>49</v>
@@ -1318,7 +1318,7 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s">
         <v>46</v>
@@ -1327,16 +1327,16 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="F26">
-        <v>26.14</v>
+        <v>23.47</v>
       </c>
       <c r="G26">
-        <v>42.45</v>
+        <v>40.57</v>
       </c>
       <c r="H26">
-        <v>63.13</v>
+        <v>47.97</v>
       </c>
       <c r="I26" t="s">
         <v>49</v>
@@ -1347,7 +1347,7 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
         <v>46</v>
@@ -1356,16 +1356,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F27">
-        <v>40.95</v>
+        <v>34.48</v>
       </c>
       <c r="G27">
-        <v>40.95</v>
+        <v>39.6</v>
       </c>
       <c r="H27">
-        <v>40.95</v>
+        <v>43.8</v>
       </c>
       <c r="I27" t="s">
         <v>49</v>
@@ -1385,16 +1385,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F28">
-        <v>37.91</v>
+        <v>35.24</v>
       </c>
       <c r="G28">
-        <v>40.33</v>
+        <v>39.22</v>
       </c>
       <c r="H28">
-        <v>42.48</v>
+        <v>47.69</v>
       </c>
       <c r="I28" t="s">
         <v>49</v>
@@ -1414,19 +1414,19 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F29">
-        <v>28.99</v>
+        <v>36.73</v>
       </c>
       <c r="G29">
-        <v>40.27</v>
+        <v>37.83</v>
       </c>
       <c r="H29">
-        <v>45.95</v>
+        <v>38.4</v>
       </c>
       <c r="I29" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -1443,19 +1443,19 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="F30">
-        <v>37.69</v>
+        <v>16.07</v>
       </c>
       <c r="G30">
-        <v>39.41</v>
+        <v>36.85</v>
       </c>
       <c r="H30">
-        <v>39.98</v>
+        <v>46.63</v>
       </c>
       <c r="I30" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -1472,19 +1472,19 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F31">
-        <v>29.91</v>
+        <v>29.18</v>
       </c>
       <c r="G31">
-        <v>39.08</v>
+        <v>35.18</v>
       </c>
       <c r="H31">
-        <v>52.53</v>
+        <v>39.18</v>
       </c>
       <c r="I31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -1501,16 +1501,16 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F32">
-        <v>29.05</v>
+        <v>28.6</v>
       </c>
       <c r="G32">
-        <v>37.71</v>
+        <v>33.5</v>
       </c>
       <c r="H32">
-        <v>44.27</v>
+        <v>39.52</v>
       </c>
       <c r="I32" t="s">
         <v>50</v>
@@ -1530,16 +1530,16 @@
         <v>47</v>
       </c>
       <c r="E33">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="F33">
-        <v>28.21</v>
+        <v>33.08</v>
       </c>
       <c r="G33">
-        <v>36.91</v>
+        <v>33.08</v>
       </c>
       <c r="H33">
-        <v>45.73</v>
+        <v>33.08</v>
       </c>
       <c r="I33" t="s">
         <v>50</v>
@@ -1550,7 +1550,7 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C34" t="s">
         <v>46</v>
@@ -1559,16 +1559,16 @@
         <v>47</v>
       </c>
       <c r="E34">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="F34">
-        <v>27.03</v>
+        <v>17.9</v>
       </c>
       <c r="G34">
-        <v>36.39</v>
+        <v>24.88</v>
       </c>
       <c r="H34">
-        <v>53.13</v>
+        <v>34.21</v>
       </c>
       <c r="I34" t="s">
         <v>50</v>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="54">
   <si>
     <t>نام منطقه</t>
   </si>
@@ -55,96 +55,96 @@
     <t>منطقه شکار ممنوع کوه هوا و</t>
   </si>
   <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
     <t>منطقه شکار ممن.ع آق جلو</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع بناب</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>پارک ملي قطرويه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مزايجان</t>
+  </si>
+  <si>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع شیکوه</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مهارلو</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده هرمود</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوهستان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+  </si>
+  <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده برم فیروز</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بصيران</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع توت سياه</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بناب</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش دره باغ</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>پارک ملي قطرويه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع شیکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بصيران</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده هرمود</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوهستان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع چاه نفت</t>
   </si>
   <si>
@@ -170,6 +170,12 @@
   </si>
   <si>
     <t>زیاد</t>
+  </si>
+  <si>
+    <t>متوسط</t>
+  </si>
+  <si>
+    <t>کم</t>
   </si>
   <si>
     <t>بدون داده</t>
@@ -634,13 +640,13 @@
         <v>33</v>
       </c>
       <c r="F2">
-        <v>50.54</v>
+        <v>49.57</v>
       </c>
       <c r="G2">
-        <v>55.56</v>
+        <v>55.86</v>
       </c>
       <c r="H2">
-        <v>62.66</v>
+        <v>64.86</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -663,13 +669,13 @@
         <v>8</v>
       </c>
       <c r="F3">
-        <v>50.52</v>
+        <v>51.95</v>
       </c>
       <c r="G3">
-        <v>51.09</v>
+        <v>52.78</v>
       </c>
       <c r="H3">
-        <v>52.47</v>
+        <v>54.56</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -692,16 +698,16 @@
         <v>37</v>
       </c>
       <c r="F4">
-        <v>46.03</v>
+        <v>44.67</v>
       </c>
       <c r="G4">
-        <v>50.87</v>
+        <v>49.42</v>
       </c>
       <c r="H4">
-        <v>54.12</v>
+        <v>52.67</v>
       </c>
       <c r="I4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -709,7 +715,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
         <v>46</v>
@@ -718,16 +724,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="F5">
-        <v>48.49</v>
+        <v>27.49</v>
       </c>
       <c r="G5">
-        <v>48.9</v>
+        <v>47.62</v>
       </c>
       <c r="H5">
-        <v>49.3</v>
+        <v>56.3</v>
       </c>
       <c r="I5" t="s">
         <v>49</v>
@@ -747,13 +753,13 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>46.85</v>
+        <v>45.62</v>
       </c>
       <c r="G6">
-        <v>47.91</v>
+        <v>47.3</v>
       </c>
       <c r="H6">
         <v>48.98</v>
@@ -767,7 +773,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
         <v>46</v>
@@ -779,13 +785,13 @@
         <v>20</v>
       </c>
       <c r="F7">
-        <v>32.87</v>
+        <v>40.35</v>
       </c>
       <c r="G7">
-        <v>47.33</v>
+        <v>45.44</v>
       </c>
       <c r="H7">
-        <v>51.59</v>
+        <v>49.81</v>
       </c>
       <c r="I7" t="s">
         <v>49</v>
@@ -796,7 +802,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
         <v>46</v>
@@ -805,16 +811,16 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F8">
-        <v>43.15</v>
+        <v>39.58</v>
       </c>
       <c r="G8">
-        <v>46.75</v>
+        <v>43.26</v>
       </c>
       <c r="H8">
-        <v>51.94</v>
+        <v>49.7</v>
       </c>
       <c r="I8" t="s">
         <v>49</v>
@@ -825,7 +831,7 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
         <v>46</v>
@@ -834,16 +840,16 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="F9">
-        <v>42.53</v>
+        <v>37.32</v>
       </c>
       <c r="G9">
-        <v>46.43</v>
+        <v>43.07</v>
       </c>
       <c r="H9">
-        <v>52.83</v>
+        <v>47.02</v>
       </c>
       <c r="I9" t="s">
         <v>49</v>
@@ -866,13 +872,13 @@
         <v>20</v>
       </c>
       <c r="F10">
-        <v>39.91</v>
+        <v>39.17</v>
       </c>
       <c r="G10">
-        <v>46.08</v>
+        <v>42.89</v>
       </c>
       <c r="H10">
-        <v>50.56</v>
+        <v>48.13</v>
       </c>
       <c r="I10" t="s">
         <v>49</v>
@@ -883,7 +889,7 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s">
         <v>46</v>
@@ -892,16 +898,16 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>117</v>
+        <v>20</v>
       </c>
       <c r="F11">
-        <v>39.09</v>
+        <v>31.35</v>
       </c>
       <c r="G11">
-        <v>45.58</v>
+        <v>41.61</v>
       </c>
       <c r="H11">
-        <v>56.24</v>
+        <v>47.31</v>
       </c>
       <c r="I11" t="s">
         <v>49</v>
@@ -921,16 +927,16 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F12">
-        <v>43.58</v>
+        <v>41.55</v>
       </c>
       <c r="G12">
-        <v>45.42</v>
+        <v>41.55</v>
       </c>
       <c r="H12">
-        <v>48.08</v>
+        <v>41.55</v>
       </c>
       <c r="I12" t="s">
         <v>49</v>
@@ -941,7 +947,7 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s">
         <v>46</v>
@@ -950,16 +956,16 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="F13">
-        <v>39.31</v>
+        <v>37.97</v>
       </c>
       <c r="G13">
-        <v>45.34</v>
+        <v>41.2</v>
       </c>
       <c r="H13">
-        <v>50.72</v>
+        <v>43.91</v>
       </c>
       <c r="I13" t="s">
         <v>49</v>
@@ -970,7 +976,7 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
         <v>46</v>
@@ -979,16 +985,16 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="F14">
-        <v>38.25</v>
+        <v>20.44</v>
       </c>
       <c r="G14">
-        <v>44.74</v>
+        <v>40.96</v>
       </c>
       <c r="H14">
-        <v>55.02</v>
+        <v>54.87</v>
       </c>
       <c r="I14" t="s">
         <v>49</v>
@@ -1008,16 +1014,16 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F15">
-        <v>42.03</v>
+        <v>36.55</v>
       </c>
       <c r="G15">
-        <v>44.39</v>
+        <v>39.88</v>
       </c>
       <c r="H15">
-        <v>49.78</v>
+        <v>45.29</v>
       </c>
       <c r="I15" t="s">
         <v>49</v>
@@ -1028,7 +1034,7 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
         <v>46</v>
@@ -1037,16 +1043,16 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>6</v>
+        <v>117</v>
       </c>
       <c r="F16">
-        <v>42.2</v>
+        <v>8.93</v>
       </c>
       <c r="G16">
-        <v>44.05</v>
+        <v>39.37</v>
       </c>
       <c r="H16">
-        <v>46.45</v>
+        <v>57.7</v>
       </c>
       <c r="I16" t="s">
         <v>49</v>
@@ -1066,19 +1072,19 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F17">
-        <v>38.79</v>
+        <v>27.64</v>
       </c>
       <c r="G17">
-        <v>43.18</v>
+        <v>36.84</v>
       </c>
       <c r="H17">
-        <v>47.73</v>
+        <v>42.48</v>
       </c>
       <c r="I17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1095,19 +1101,19 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F18">
-        <v>38.74</v>
+        <v>32.52</v>
       </c>
       <c r="G18">
-        <v>42.93</v>
+        <v>36.66</v>
       </c>
       <c r="H18">
-        <v>46.37</v>
+        <v>43.42</v>
       </c>
       <c r="I18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1115,7 +1121,7 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C19" t="s">
         <v>46</v>
@@ -1124,19 +1130,19 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F19">
-        <v>42.68</v>
+        <v>21.35</v>
       </c>
       <c r="G19">
-        <v>42.68</v>
+        <v>36.54</v>
       </c>
       <c r="H19">
-        <v>42.68</v>
+        <v>42.85</v>
       </c>
       <c r="I19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1144,7 +1150,7 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C20" t="s">
         <v>46</v>
@@ -1153,19 +1159,19 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F20">
-        <v>37.91</v>
+        <v>28.1</v>
       </c>
       <c r="G20">
-        <v>42.54</v>
+        <v>35.56</v>
       </c>
       <c r="H20">
-        <v>47.09</v>
+        <v>42.46</v>
       </c>
       <c r="I20" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1182,19 +1188,19 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F21">
-        <v>40.8</v>
+        <v>29.75</v>
       </c>
       <c r="G21">
-        <v>42.14</v>
+        <v>29.75</v>
       </c>
       <c r="H21">
-        <v>43.72</v>
+        <v>29.75</v>
       </c>
       <c r="I21" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -1211,19 +1217,19 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="F22">
-        <v>37.32</v>
+        <v>14.55</v>
       </c>
       <c r="G22">
-        <v>41.55</v>
+        <v>27.01</v>
       </c>
       <c r="H22">
-        <v>46.83</v>
+        <v>35.72</v>
       </c>
       <c r="I22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1231,7 +1237,7 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C23" t="s">
         <v>46</v>
@@ -1240,19 +1246,19 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="F23">
-        <v>40.24</v>
+        <v>14.4</v>
       </c>
       <c r="G23">
-        <v>41.51</v>
+        <v>25.44</v>
       </c>
       <c r="H23">
-        <v>43.45</v>
+        <v>41.99</v>
       </c>
       <c r="I23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -1269,19 +1275,19 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="F24">
-        <v>36.97</v>
+        <v>4.43</v>
       </c>
       <c r="G24">
-        <v>41.12</v>
+        <v>25.22</v>
       </c>
       <c r="H24">
-        <v>46.47</v>
+        <v>45.1</v>
       </c>
       <c r="I24" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -1298,19 +1304,19 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F25">
-        <v>39.13</v>
+        <v>8.15</v>
       </c>
       <c r="G25">
-        <v>40.85</v>
+        <v>24.69</v>
       </c>
       <c r="H25">
-        <v>41.92</v>
+        <v>39.29</v>
       </c>
       <c r="I25" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -1327,19 +1333,19 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="F26">
-        <v>23.47</v>
+        <v>16.3</v>
       </c>
       <c r="G26">
-        <v>40.57</v>
+        <v>22.58</v>
       </c>
       <c r="H26">
-        <v>47.97</v>
+        <v>43.31</v>
       </c>
       <c r="I26" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -1356,19 +1362,19 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F27">
-        <v>34.48</v>
+        <v>10.88</v>
       </c>
       <c r="G27">
-        <v>39.6</v>
+        <v>21.42</v>
       </c>
       <c r="H27">
-        <v>43.8</v>
+        <v>42.8</v>
       </c>
       <c r="I27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -1385,19 +1391,19 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="F28">
-        <v>35.24</v>
+        <v>14.73</v>
       </c>
       <c r="G28">
-        <v>39.22</v>
+        <v>20.73</v>
       </c>
       <c r="H28">
-        <v>47.69</v>
+        <v>25.28</v>
       </c>
       <c r="I28" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -1405,7 +1411,7 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C29" t="s">
         <v>46</v>
@@ -1414,19 +1420,19 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F29">
-        <v>36.73</v>
+        <v>14.73</v>
       </c>
       <c r="G29">
-        <v>37.83</v>
+        <v>20.72</v>
       </c>
       <c r="H29">
-        <v>38.4</v>
+        <v>25.28</v>
       </c>
       <c r="I29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -1434,7 +1440,7 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C30" t="s">
         <v>46</v>
@@ -1443,19 +1449,19 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="F30">
-        <v>16.07</v>
+        <v>7.29</v>
       </c>
       <c r="G30">
-        <v>36.85</v>
+        <v>20.06</v>
       </c>
       <c r="H30">
-        <v>46.63</v>
+        <v>35.42</v>
       </c>
       <c r="I30" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -1472,19 +1478,19 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="F31">
-        <v>29.18</v>
+        <v>6.82</v>
       </c>
       <c r="G31">
-        <v>35.18</v>
+        <v>17.17</v>
       </c>
       <c r="H31">
-        <v>39.18</v>
+        <v>43.92</v>
       </c>
       <c r="I31" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -1501,19 +1507,19 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F32">
-        <v>28.6</v>
+        <v>4.22</v>
       </c>
       <c r="G32">
-        <v>33.5</v>
+        <v>15.26</v>
       </c>
       <c r="H32">
-        <v>39.52</v>
+        <v>29.54</v>
       </c>
       <c r="I32" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -1530,19 +1536,19 @@
         <v>47</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="F33">
-        <v>33.08</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="G33">
-        <v>33.08</v>
+        <v>12.4</v>
       </c>
       <c r="H33">
-        <v>33.08</v>
+        <v>27.83</v>
       </c>
       <c r="I33" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1550,7 +1556,7 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C34" t="s">
         <v>46</v>
@@ -1559,19 +1565,19 @@
         <v>47</v>
       </c>
       <c r="E34">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F34">
-        <v>17.9</v>
+        <v>9.56</v>
       </c>
       <c r="G34">
-        <v>24.88</v>
+        <v>11.11</v>
       </c>
       <c r="H34">
-        <v>34.21</v>
+        <v>15.63</v>
       </c>
       <c r="I34" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -1591,7 +1597,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -1611,7 +1617,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="52">
   <si>
     <t>نام منطقه</t>
   </si>
@@ -46,105 +46,105 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دالان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع کوه دراء</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع دالان</t>
+    <t>منطقه شکار ممنوع شیکوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بناب</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع کوه هوا و</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بناب</t>
+    <t>منطقه شکار ممنوع مزايجان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
   </si>
   <si>
     <t>منطقه حفاظت شده بهرام گور</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع پادنا</t>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
   </si>
   <si>
     <t>پارک ملي قطرويه</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع شیکوه</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع مهارلو</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
     <t>منطقه حفاظت شده هرمود</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع کوهستان</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
     <t>منطقه حفاظت شده میانجنگل فسا</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده برم فیروز</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بصيران</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع توت سياه</t>
   </si>
   <si>
     <t>پناهگاه حيات وحش دره باغ</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بصيران</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع چاه نفت</t>
   </si>
   <si>
@@ -157,10 +157,10 @@
     <t>مناطق ممنوعه شکار</t>
   </si>
   <si>
-    <t>1405-08-06</t>
-  </si>
-  <si>
-    <t>2026-10-28</t>
+    <t>1405-08-07</t>
+  </si>
+  <si>
+    <t>2026-10-29</t>
   </si>
   <si>
     <t>شدید</t>
@@ -170,12 +170,6 @@
   </si>
   <si>
     <t>زیاد</t>
-  </si>
-  <si>
-    <t>متوسط</t>
-  </si>
-  <si>
-    <t>کم</t>
   </si>
   <si>
     <t>بدون داده</t>
@@ -637,16 +631,16 @@
         <v>47</v>
       </c>
       <c r="E2">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>49.57</v>
+        <v>48.47</v>
       </c>
       <c r="G2">
-        <v>55.86</v>
+        <v>58.53</v>
       </c>
       <c r="H2">
-        <v>64.86</v>
+        <v>63.4</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -669,13 +663,13 @@
         <v>8</v>
       </c>
       <c r="F3">
-        <v>51.95</v>
+        <v>51.86</v>
       </c>
       <c r="G3">
-        <v>52.78</v>
+        <v>55.97</v>
       </c>
       <c r="H3">
-        <v>54.56</v>
+        <v>58.12</v>
       </c>
       <c r="I3" t="s">
         <v>48</v>
@@ -695,19 +689,19 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>44.67</v>
+        <v>50.62</v>
       </c>
       <c r="G4">
-        <v>49.42</v>
+        <v>52.1</v>
       </c>
       <c r="H4">
-        <v>52.67</v>
+        <v>53.58</v>
       </c>
       <c r="I4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -715,7 +709,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
         <v>46</v>
@@ -724,16 +718,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F5">
-        <v>27.49</v>
+        <v>35.04</v>
       </c>
       <c r="G5">
-        <v>47.62</v>
+        <v>48.54</v>
       </c>
       <c r="H5">
-        <v>56.3</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="I5" t="s">
         <v>49</v>
@@ -753,16 +747,16 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>45.62</v>
+        <v>41.48</v>
       </c>
       <c r="G6">
-        <v>47.3</v>
+        <v>47.51</v>
       </c>
       <c r="H6">
-        <v>48.98</v>
+        <v>50.94</v>
       </c>
       <c r="I6" t="s">
         <v>49</v>
@@ -785,13 +779,13 @@
         <v>20</v>
       </c>
       <c r="F7">
-        <v>40.35</v>
+        <v>42.21</v>
       </c>
       <c r="G7">
-        <v>45.44</v>
+        <v>47.3</v>
       </c>
       <c r="H7">
-        <v>49.81</v>
+        <v>51.8</v>
       </c>
       <c r="I7" t="s">
         <v>49</v>
@@ -811,16 +805,16 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F8">
-        <v>39.58</v>
+        <v>33.23</v>
       </c>
       <c r="G8">
-        <v>43.26</v>
+        <v>47.29</v>
       </c>
       <c r="H8">
-        <v>49.7</v>
+        <v>57.3</v>
       </c>
       <c r="I8" t="s">
         <v>49</v>
@@ -840,16 +834,16 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F9">
-        <v>37.32</v>
+        <v>40</v>
       </c>
       <c r="G9">
-        <v>43.07</v>
+        <v>46.78</v>
       </c>
       <c r="H9">
-        <v>47.02</v>
+        <v>51.44</v>
       </c>
       <c r="I9" t="s">
         <v>49</v>
@@ -872,13 +866,13 @@
         <v>20</v>
       </c>
       <c r="F10">
-        <v>39.17</v>
+        <v>39.95</v>
       </c>
       <c r="G10">
-        <v>42.89</v>
+        <v>46.22</v>
       </c>
       <c r="H10">
-        <v>48.13</v>
+        <v>50.98</v>
       </c>
       <c r="I10" t="s">
         <v>49</v>
@@ -898,16 +892,16 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F11">
-        <v>31.35</v>
+        <v>38.62</v>
       </c>
       <c r="G11">
-        <v>41.61</v>
+        <v>45.78</v>
       </c>
       <c r="H11">
-        <v>47.31</v>
+        <v>53.05</v>
       </c>
       <c r="I11" t="s">
         <v>49</v>
@@ -918,7 +912,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
         <v>46</v>
@@ -927,16 +921,16 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F12">
-        <v>41.55</v>
+        <v>43.24</v>
       </c>
       <c r="G12">
-        <v>41.55</v>
+        <v>45.64</v>
       </c>
       <c r="H12">
-        <v>41.55</v>
+        <v>47.52</v>
       </c>
       <c r="I12" t="s">
         <v>49</v>
@@ -947,7 +941,7 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
         <v>46</v>
@@ -956,16 +950,16 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F13">
-        <v>37.97</v>
+        <v>28.72</v>
       </c>
       <c r="G13">
-        <v>41.2</v>
+        <v>43.79</v>
       </c>
       <c r="H13">
-        <v>43.91</v>
+        <v>57.3</v>
       </c>
       <c r="I13" t="s">
         <v>49</v>
@@ -985,16 +979,16 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="F14">
-        <v>20.44</v>
+        <v>37.63</v>
       </c>
       <c r="G14">
-        <v>40.96</v>
+        <v>43.67</v>
       </c>
       <c r="H14">
-        <v>54.87</v>
+        <v>51.33</v>
       </c>
       <c r="I14" t="s">
         <v>49</v>
@@ -1005,7 +999,7 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
         <v>46</v>
@@ -1014,16 +1008,16 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>65</v>
       </c>
       <c r="F15">
-        <v>36.55</v>
+        <v>33.45</v>
       </c>
       <c r="G15">
-        <v>39.88</v>
+        <v>43.17</v>
       </c>
       <c r="H15">
-        <v>45.29</v>
+        <v>51.71</v>
       </c>
       <c r="I15" t="s">
         <v>49</v>
@@ -1043,16 +1037,16 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>117</v>
+        <v>16</v>
       </c>
       <c r="F16">
-        <v>8.93</v>
+        <v>39.34</v>
       </c>
       <c r="G16">
-        <v>39.37</v>
+        <v>42.46</v>
       </c>
       <c r="H16">
-        <v>57.7</v>
+        <v>47.62</v>
       </c>
       <c r="I16" t="s">
         <v>49</v>
@@ -1063,7 +1057,7 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
         <v>46</v>
@@ -1072,19 +1066,19 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>10</v>
+        <v>117</v>
       </c>
       <c r="F17">
-        <v>27.64</v>
+        <v>30.57</v>
       </c>
       <c r="G17">
-        <v>36.84</v>
+        <v>42.39</v>
       </c>
       <c r="H17">
-        <v>42.48</v>
+        <v>51.71</v>
       </c>
       <c r="I17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1101,19 +1095,19 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="F18">
-        <v>32.52</v>
+        <v>34.2</v>
       </c>
       <c r="G18">
-        <v>36.66</v>
+        <v>42.04</v>
       </c>
       <c r="H18">
-        <v>43.42</v>
+        <v>50.27</v>
       </c>
       <c r="I18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1121,7 +1115,7 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
         <v>46</v>
@@ -1130,19 +1124,19 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F19">
-        <v>21.35</v>
+        <v>41.32</v>
       </c>
       <c r="G19">
-        <v>36.54</v>
+        <v>41.32</v>
       </c>
       <c r="H19">
-        <v>42.85</v>
+        <v>41.32</v>
       </c>
       <c r="I19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1150,7 +1144,7 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C20" t="s">
         <v>46</v>
@@ -1159,19 +1153,19 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F20">
-        <v>28.1</v>
+        <v>34.39</v>
       </c>
       <c r="G20">
-        <v>35.56</v>
+        <v>38.58</v>
       </c>
       <c r="H20">
-        <v>42.46</v>
+        <v>41.42</v>
       </c>
       <c r="I20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1188,16 +1182,16 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F21">
-        <v>29.75</v>
+        <v>34.54</v>
       </c>
       <c r="G21">
-        <v>29.75</v>
+        <v>37.77</v>
       </c>
       <c r="H21">
-        <v>29.75</v>
+        <v>44.16</v>
       </c>
       <c r="I21" t="s">
         <v>50</v>
@@ -1217,16 +1211,16 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F22">
-        <v>14.55</v>
+        <v>33.16</v>
       </c>
       <c r="G22">
-        <v>27.01</v>
+        <v>37.16</v>
       </c>
       <c r="H22">
-        <v>35.72</v>
+        <v>42.36</v>
       </c>
       <c r="I22" t="s">
         <v>50</v>
@@ -1237,7 +1231,7 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C23" t="s">
         <v>46</v>
@@ -1246,16 +1240,16 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F23">
-        <v>14.4</v>
+        <v>33.73</v>
       </c>
       <c r="G23">
-        <v>25.44</v>
+        <v>36.92</v>
       </c>
       <c r="H23">
-        <v>41.99</v>
+        <v>45.73</v>
       </c>
       <c r="I23" t="s">
         <v>50</v>
@@ -1278,13 +1272,13 @@
         <v>62</v>
       </c>
       <c r="F24">
-        <v>4.43</v>
+        <v>19.51</v>
       </c>
       <c r="G24">
-        <v>25.22</v>
+        <v>36.74</v>
       </c>
       <c r="H24">
-        <v>45.1</v>
+        <v>52.76</v>
       </c>
       <c r="I24" t="s">
         <v>50</v>
@@ -1307,13 +1301,13 @@
         <v>12</v>
       </c>
       <c r="F25">
-        <v>8.15</v>
+        <v>25.61</v>
       </c>
       <c r="G25">
-        <v>24.69</v>
+        <v>35.53</v>
       </c>
       <c r="H25">
-        <v>39.29</v>
+        <v>45.45</v>
       </c>
       <c r="I25" t="s">
         <v>50</v>
@@ -1324,7 +1318,7 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C26" t="s">
         <v>46</v>
@@ -1333,16 +1327,16 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F26">
-        <v>16.3</v>
+        <v>24.09</v>
       </c>
       <c r="G26">
-        <v>22.58</v>
+        <v>34.54</v>
       </c>
       <c r="H26">
-        <v>43.31</v>
+        <v>51.9</v>
       </c>
       <c r="I26" t="s">
         <v>50</v>
@@ -1365,13 +1359,13 @@
         <v>18</v>
       </c>
       <c r="F27">
-        <v>10.88</v>
+        <v>28.11</v>
       </c>
       <c r="G27">
-        <v>21.42</v>
+        <v>34.24</v>
       </c>
       <c r="H27">
-        <v>42.8</v>
+        <v>45.81</v>
       </c>
       <c r="I27" t="s">
         <v>50</v>
@@ -1382,7 +1376,7 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C28" t="s">
         <v>46</v>
@@ -1391,19 +1385,19 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F28">
-        <v>14.73</v>
+        <v>33.76</v>
       </c>
       <c r="G28">
-        <v>20.73</v>
+        <v>33.76</v>
       </c>
       <c r="H28">
-        <v>25.28</v>
+        <v>33.76</v>
       </c>
       <c r="I28" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -1411,7 +1405,7 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C29" t="s">
         <v>46</v>
@@ -1420,19 +1414,19 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F29">
-        <v>14.73</v>
+        <v>29.5</v>
       </c>
       <c r="G29">
-        <v>20.72</v>
+        <v>33.51</v>
       </c>
       <c r="H29">
-        <v>25.28</v>
+        <v>46.2</v>
       </c>
       <c r="I29" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -1440,7 +1434,7 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C30" t="s">
         <v>46</v>
@@ -1449,19 +1443,19 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F30">
-        <v>7.29</v>
+        <v>21.11</v>
       </c>
       <c r="G30">
-        <v>20.06</v>
+        <v>32.18</v>
       </c>
       <c r="H30">
-        <v>35.42</v>
+        <v>43.98</v>
       </c>
       <c r="I30" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -1478,19 +1472,19 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F31">
-        <v>6.82</v>
+        <v>15.47</v>
       </c>
       <c r="G31">
-        <v>17.17</v>
+        <v>29.34</v>
       </c>
       <c r="H31">
-        <v>43.92</v>
+        <v>43.8</v>
       </c>
       <c r="I31" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -1498,7 +1492,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C32" t="s">
         <v>46</v>
@@ -1507,19 +1501,19 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F32">
-        <v>4.22</v>
+        <v>24.33</v>
       </c>
       <c r="G32">
-        <v>15.26</v>
+        <v>29.31</v>
       </c>
       <c r="H32">
-        <v>29.54</v>
+        <v>39.16</v>
       </c>
       <c r="I32" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -1536,19 +1530,19 @@
         <v>47</v>
       </c>
       <c r="E33">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F33">
-        <v>8.539999999999999</v>
+        <v>28.07</v>
       </c>
       <c r="G33">
-        <v>12.4</v>
+        <v>29.23</v>
       </c>
       <c r="H33">
-        <v>27.83</v>
+        <v>32.46</v>
       </c>
       <c r="I33" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1556,7 +1550,7 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C34" t="s">
         <v>46</v>
@@ -1565,19 +1559,19 @@
         <v>47</v>
       </c>
       <c r="E34">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F34">
-        <v>9.56</v>
+        <v>26.24</v>
       </c>
       <c r="G34">
-        <v>11.11</v>
+        <v>29.04</v>
       </c>
       <c r="H34">
-        <v>15.63</v>
+        <v>31.27</v>
       </c>
       <c r="I34" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -1597,7 +1591,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -1617,7 +1611,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -46,105 +46,105 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع دالان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه دراء</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بناب</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده هرمود</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه هوا و</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع مل بلند</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع دالان</t>
-  </si>
-  <si>
     <t>منطقه شکار ممن.ع آق جلو</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه دراء</t>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مزايجان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مهارلو</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع شیکوه</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بناب</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه هوا و</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش دره باغ</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
   </si>
   <si>
     <t>منطقه حفاظت شده تنگ بستانک</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بصيران</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده برم فیروز</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
+  </si>
+  <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع توت سياه</t>
   </si>
   <si>
     <t>پارک ملي قطرويه</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده هرمود</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع کوهستان</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بصيران</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع توت سياه</t>
-  </si>
-  <si>
-    <t>پناهگاه حيات وحش دره باغ</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع چاه نفت</t>
   </si>
   <si>
@@ -157,10 +157,10 @@
     <t>مناطق ممنوعه شکار</t>
   </si>
   <si>
-    <t>1405-08-07</t>
-  </si>
-  <si>
-    <t>2026-10-29</t>
+    <t>1405-08-08</t>
+  </si>
+  <si>
+    <t>2026-10-30</t>
   </si>
   <si>
     <t>شدید</t>
@@ -631,16 +631,16 @@
         <v>47</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>48.47</v>
+        <v>50.23</v>
       </c>
       <c r="G2">
-        <v>58.53</v>
+        <v>52.69</v>
       </c>
       <c r="H2">
-        <v>63.4</v>
+        <v>56.38</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -660,19 +660,19 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F3">
-        <v>51.86</v>
+        <v>45.58</v>
       </c>
       <c r="G3">
-        <v>55.97</v>
+        <v>49.02</v>
       </c>
       <c r="H3">
-        <v>58.12</v>
+        <v>53.05</v>
       </c>
       <c r="I3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -689,19 +689,19 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="F4">
-        <v>50.62</v>
+        <v>42.58</v>
       </c>
       <c r="G4">
-        <v>52.1</v>
+        <v>48.11</v>
       </c>
       <c r="H4">
-        <v>53.58</v>
+        <v>50.71</v>
       </c>
       <c r="I4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -709,7 +709,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
         <v>46</v>
@@ -718,16 +718,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F5">
-        <v>35.04</v>
+        <v>36.82</v>
       </c>
       <c r="G5">
-        <v>48.54</v>
+        <v>45.05</v>
       </c>
       <c r="H5">
-        <v>65.01000000000001</v>
+        <v>52.91</v>
       </c>
       <c r="I5" t="s">
         <v>49</v>
@@ -738,7 +738,7 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s">
         <v>46</v>
@@ -747,16 +747,16 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F6">
-        <v>41.48</v>
+        <v>36.69</v>
       </c>
       <c r="G6">
-        <v>47.51</v>
+        <v>43.19</v>
       </c>
       <c r="H6">
-        <v>50.94</v>
+        <v>46.56</v>
       </c>
       <c r="I6" t="s">
         <v>49</v>
@@ -776,16 +776,16 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F7">
-        <v>42.21</v>
+        <v>30.71</v>
       </c>
       <c r="G7">
-        <v>47.3</v>
+        <v>43.12</v>
       </c>
       <c r="H7">
-        <v>51.8</v>
+        <v>47.26</v>
       </c>
       <c r="I7" t="s">
         <v>49</v>
@@ -796,7 +796,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C8" t="s">
         <v>46</v>
@@ -805,16 +805,16 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F8">
-        <v>33.23</v>
+        <v>40.1</v>
       </c>
       <c r="G8">
-        <v>47.29</v>
+        <v>42.88</v>
       </c>
       <c r="H8">
-        <v>57.3</v>
+        <v>44.85</v>
       </c>
       <c r="I8" t="s">
         <v>49</v>
@@ -834,16 +834,16 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F9">
-        <v>40</v>
+        <v>40.86</v>
       </c>
       <c r="G9">
-        <v>46.78</v>
+        <v>42.22</v>
       </c>
       <c r="H9">
-        <v>51.44</v>
+        <v>43.58</v>
       </c>
       <c r="I9" t="s">
         <v>49</v>
@@ -866,13 +866,13 @@
         <v>20</v>
       </c>
       <c r="F10">
-        <v>39.95</v>
+        <v>39.25</v>
       </c>
       <c r="G10">
-        <v>46.22</v>
+        <v>42.16</v>
       </c>
       <c r="H10">
-        <v>50.98</v>
+        <v>46.53</v>
       </c>
       <c r="I10" t="s">
         <v>49</v>
@@ -892,16 +892,16 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="F11">
-        <v>38.62</v>
+        <v>38.14</v>
       </c>
       <c r="G11">
-        <v>45.78</v>
+        <v>41.71</v>
       </c>
       <c r="H11">
-        <v>53.05</v>
+        <v>46.03</v>
       </c>
       <c r="I11" t="s">
         <v>49</v>
@@ -921,16 +921,16 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F12">
-        <v>43.24</v>
+        <v>37.28</v>
       </c>
       <c r="G12">
-        <v>45.64</v>
+        <v>41.64</v>
       </c>
       <c r="H12">
-        <v>47.52</v>
+        <v>48.18</v>
       </c>
       <c r="I12" t="s">
         <v>49</v>
@@ -950,16 +950,16 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F13">
-        <v>28.72</v>
+        <v>35.58</v>
       </c>
       <c r="G13">
-        <v>43.79</v>
+        <v>39.97</v>
       </c>
       <c r="H13">
-        <v>57.3</v>
+        <v>43.4</v>
       </c>
       <c r="I13" t="s">
         <v>49</v>
@@ -970,7 +970,7 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
         <v>46</v>
@@ -979,16 +979,16 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F14">
-        <v>37.63</v>
+        <v>34.61</v>
       </c>
       <c r="G14">
-        <v>43.67</v>
+        <v>38.01</v>
       </c>
       <c r="H14">
-        <v>51.33</v>
+        <v>40.99</v>
       </c>
       <c r="I14" t="s">
         <v>49</v>
@@ -1008,19 +1008,19 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>65</v>
+        <v>3</v>
       </c>
       <c r="F15">
-        <v>33.45</v>
+        <v>34.46</v>
       </c>
       <c r="G15">
-        <v>43.17</v>
+        <v>37.96</v>
       </c>
       <c r="H15">
-        <v>51.71</v>
+        <v>42.13</v>
       </c>
       <c r="I15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1028,7 +1028,7 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
         <v>46</v>
@@ -1037,19 +1037,19 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F16">
-        <v>39.34</v>
+        <v>32.5</v>
       </c>
       <c r="G16">
-        <v>42.46</v>
+        <v>37.84</v>
       </c>
       <c r="H16">
-        <v>47.62</v>
+        <v>45.78</v>
       </c>
       <c r="I16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1066,19 +1066,19 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="F17">
-        <v>30.57</v>
+        <v>29.12</v>
       </c>
       <c r="G17">
-        <v>42.39</v>
+        <v>37.24</v>
       </c>
       <c r="H17">
-        <v>51.71</v>
+        <v>41.81</v>
       </c>
       <c r="I17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1086,7 +1086,7 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C18" t="s">
         <v>46</v>
@@ -1098,16 +1098,16 @@
         <v>3</v>
       </c>
       <c r="F18">
-        <v>34.2</v>
+        <v>34.21</v>
       </c>
       <c r="G18">
-        <v>42.04</v>
+        <v>36.92</v>
       </c>
       <c r="H18">
-        <v>50.27</v>
+        <v>38.45</v>
       </c>
       <c r="I18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1124,19 +1124,19 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>4</v>
+        <v>65</v>
       </c>
       <c r="F19">
-        <v>41.32</v>
+        <v>28.98</v>
       </c>
       <c r="G19">
-        <v>41.32</v>
+        <v>36.39</v>
       </c>
       <c r="H19">
-        <v>41.32</v>
+        <v>41.92</v>
       </c>
       <c r="I19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1144,7 +1144,7 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C20" t="s">
         <v>46</v>
@@ -1153,19 +1153,19 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F20">
-        <v>34.39</v>
+        <v>32.55</v>
       </c>
       <c r="G20">
-        <v>38.58</v>
+        <v>35.95</v>
       </c>
       <c r="H20">
-        <v>41.42</v>
+        <v>38.61</v>
       </c>
       <c r="I20" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1173,7 +1173,7 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C21" t="s">
         <v>46</v>
@@ -1182,16 +1182,16 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>10</v>
+        <v>117</v>
       </c>
       <c r="F21">
-        <v>34.54</v>
+        <v>26.55</v>
       </c>
       <c r="G21">
-        <v>37.77</v>
+        <v>35.51</v>
       </c>
       <c r="H21">
-        <v>44.16</v>
+        <v>41.92</v>
       </c>
       <c r="I21" t="s">
         <v>50</v>
@@ -1211,16 +1211,16 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F22">
-        <v>33.16</v>
+        <v>33.11</v>
       </c>
       <c r="G22">
-        <v>37.16</v>
+        <v>35.44</v>
       </c>
       <c r="H22">
-        <v>42.36</v>
+        <v>42.31</v>
       </c>
       <c r="I22" t="s">
         <v>50</v>
@@ -1243,13 +1243,13 @@
         <v>13</v>
       </c>
       <c r="F23">
-        <v>33.73</v>
+        <v>32.66</v>
       </c>
       <c r="G23">
-        <v>36.92</v>
+        <v>35.33</v>
       </c>
       <c r="H23">
-        <v>45.73</v>
+        <v>39.26</v>
       </c>
       <c r="I23" t="s">
         <v>50</v>
@@ -1260,7 +1260,7 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C24" t="s">
         <v>46</v>
@@ -1269,16 +1269,16 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>62</v>
+        <v>5</v>
       </c>
       <c r="F24">
-        <v>19.51</v>
+        <v>29.31</v>
       </c>
       <c r="G24">
-        <v>36.74</v>
+        <v>35.2</v>
       </c>
       <c r="H24">
-        <v>52.76</v>
+        <v>37.59</v>
       </c>
       <c r="I24" t="s">
         <v>50</v>
@@ -1298,16 +1298,16 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="F25">
-        <v>25.61</v>
+        <v>28.68</v>
       </c>
       <c r="G25">
-        <v>35.53</v>
+        <v>35.05</v>
       </c>
       <c r="H25">
-        <v>45.45</v>
+        <v>45.32</v>
       </c>
       <c r="I25" t="s">
         <v>50</v>
@@ -1318,7 +1318,7 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s">
         <v>46</v>
@@ -1327,16 +1327,16 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F26">
-        <v>24.09</v>
+        <v>29.62</v>
       </c>
       <c r="G26">
-        <v>34.54</v>
+        <v>34.42</v>
       </c>
       <c r="H26">
-        <v>51.9</v>
+        <v>42</v>
       </c>
       <c r="I26" t="s">
         <v>50</v>
@@ -1359,13 +1359,13 @@
         <v>18</v>
       </c>
       <c r="F27">
-        <v>28.11</v>
+        <v>29.48</v>
       </c>
       <c r="G27">
-        <v>34.24</v>
+        <v>33.67</v>
       </c>
       <c r="H27">
-        <v>45.81</v>
+        <v>39.66</v>
       </c>
       <c r="I27" t="s">
         <v>50</v>
@@ -1376,7 +1376,7 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C28" t="s">
         <v>46</v>
@@ -1385,16 +1385,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F28">
-        <v>33.76</v>
+        <v>23.67</v>
       </c>
       <c r="G28">
-        <v>33.76</v>
+        <v>33</v>
       </c>
       <c r="H28">
-        <v>33.76</v>
+        <v>43.14</v>
       </c>
       <c r="I28" t="s">
         <v>50</v>
@@ -1405,7 +1405,7 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C29" t="s">
         <v>46</v>
@@ -1414,16 +1414,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F29">
-        <v>29.5</v>
+        <v>28.34</v>
       </c>
       <c r="G29">
-        <v>33.51</v>
+        <v>32.73</v>
       </c>
       <c r="H29">
-        <v>46.2</v>
+        <v>34.42</v>
       </c>
       <c r="I29" t="s">
         <v>50</v>
@@ -1434,7 +1434,7 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C30" t="s">
         <v>46</v>
@@ -1443,16 +1443,16 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F30">
-        <v>21.11</v>
+        <v>28.44</v>
       </c>
       <c r="G30">
-        <v>32.18</v>
+        <v>32.14</v>
       </c>
       <c r="H30">
-        <v>43.98</v>
+        <v>40.88</v>
       </c>
       <c r="I30" t="s">
         <v>50</v>
@@ -1463,7 +1463,7 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C31" t="s">
         <v>46</v>
@@ -1472,16 +1472,16 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F31">
-        <v>15.47</v>
+        <v>26</v>
       </c>
       <c r="G31">
-        <v>29.34</v>
+        <v>31.94</v>
       </c>
       <c r="H31">
-        <v>43.8</v>
+        <v>38.86</v>
       </c>
       <c r="I31" t="s">
         <v>50</v>
@@ -1501,16 +1501,16 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F32">
-        <v>24.33</v>
+        <v>28.45</v>
       </c>
       <c r="G32">
-        <v>29.31</v>
+        <v>30.16</v>
       </c>
       <c r="H32">
-        <v>39.16</v>
+        <v>34.16</v>
       </c>
       <c r="I32" t="s">
         <v>50</v>
@@ -1521,7 +1521,7 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C33" t="s">
         <v>46</v>
@@ -1533,13 +1533,13 @@
         <v>4</v>
       </c>
       <c r="F33">
-        <v>28.07</v>
+        <v>29.12</v>
       </c>
       <c r="G33">
-        <v>29.23</v>
+        <v>29.12</v>
       </c>
       <c r="H33">
-        <v>32.46</v>
+        <v>29.12</v>
       </c>
       <c r="I33" t="s">
         <v>50</v>
@@ -1550,7 +1550,7 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C34" t="s">
         <v>46</v>
@@ -1559,16 +1559,16 @@
         <v>47</v>
       </c>
       <c r="E34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F34">
-        <v>26.24</v>
+        <v>27.93</v>
       </c>
       <c r="G34">
-        <v>29.04</v>
+        <v>27.93</v>
       </c>
       <c r="H34">
-        <v>31.27</v>
+        <v>27.93</v>
       </c>
       <c r="I34" t="s">
         <v>50</v>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -46,102 +46,102 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع کوه دراء</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع دالان</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه دراء</t>
+    <t>منطقه حفاظت شده ارژن و پريشان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع پادنا</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع بناب</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده ارژن و پريشان</t>
+    <t>پارک ملي بختگان</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده ماله گاله</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده بهرام گور</t>
+  </si>
+  <si>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مهارلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع شیکوه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه هوا و</t>
+  </si>
+  <si>
+    <t>پارک ملي قطرويه</t>
   </si>
   <si>
     <t>منطقه حفاظت شده هرمود</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه هوا و</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده برم فیروز</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع مزايجان</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع پادنا</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده ماله گاله</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+    <t>منطقه شکار ممنوع بصيران</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>پارک ملی بمو</t>
   </si>
   <si>
     <t>منطقه شکار ممنوع دره باغ</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده بهرام گور</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع شیکوه</t>
-  </si>
-  <si>
-    <t>پارک ملي بختگان</t>
-  </si>
-  <si>
     <t>پناهگاه حيات وحش دره باغ</t>
   </si>
   <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بصيران</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع توت سياه</t>
   </si>
   <si>
-    <t>پارک ملي قطرويه</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع کوهستان</t>
   </si>
   <si>
@@ -157,10 +157,10 @@
     <t>مناطق ممنوعه شکار</t>
   </si>
   <si>
-    <t>1405-08-08</t>
-  </si>
-  <si>
-    <t>2026-10-30</t>
+    <t>1405-08-09</t>
+  </si>
+  <si>
+    <t>2026-10-31</t>
   </si>
   <si>
     <t>شدید</t>
@@ -631,16 +631,16 @@
         <v>47</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F2">
-        <v>50.23</v>
+        <v>53.59</v>
       </c>
       <c r="G2">
-        <v>52.69</v>
+        <v>56.56</v>
       </c>
       <c r="H2">
-        <v>56.38</v>
+        <v>60.2</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -660,16 +660,16 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>45.58</v>
+        <v>48.31</v>
       </c>
       <c r="G3">
-        <v>49.02</v>
+        <v>49.14</v>
       </c>
       <c r="H3">
-        <v>53.05</v>
+        <v>49.63</v>
       </c>
       <c r="I3" t="s">
         <v>49</v>
@@ -680,7 +680,7 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C4" t="s">
         <v>46</v>
@@ -692,13 +692,13 @@
         <v>20</v>
       </c>
       <c r="F4">
-        <v>42.58</v>
+        <v>41.53</v>
       </c>
       <c r="G4">
-        <v>48.11</v>
+        <v>48.87</v>
       </c>
       <c r="H4">
-        <v>50.71</v>
+        <v>53.88</v>
       </c>
       <c r="I4" t="s">
         <v>49</v>
@@ -709,7 +709,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
         <v>46</v>
@@ -718,16 +718,16 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>36.82</v>
+        <v>42.95</v>
       </c>
       <c r="G5">
-        <v>45.05</v>
+        <v>47.15</v>
       </c>
       <c r="H5">
-        <v>52.91</v>
+        <v>50.17</v>
       </c>
       <c r="I5" t="s">
         <v>49</v>
@@ -747,16 +747,16 @@
         <v>47</v>
       </c>
       <c r="E6">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>36.69</v>
+        <v>43.85</v>
       </c>
       <c r="G6">
-        <v>43.19</v>
+        <v>45.79</v>
       </c>
       <c r="H6">
-        <v>46.56</v>
+        <v>46.99</v>
       </c>
       <c r="I6" t="s">
         <v>49</v>
@@ -776,16 +776,16 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="F7">
-        <v>30.71</v>
+        <v>42.66</v>
       </c>
       <c r="G7">
-        <v>43.12</v>
+        <v>45.36</v>
       </c>
       <c r="H7">
-        <v>47.26</v>
+        <v>49.13</v>
       </c>
       <c r="I7" t="s">
         <v>49</v>
@@ -796,7 +796,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
         <v>46</v>
@@ -805,16 +805,16 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="F8">
-        <v>40.1</v>
+        <v>36.66</v>
       </c>
       <c r="G8">
-        <v>42.88</v>
+        <v>44.04</v>
       </c>
       <c r="H8">
-        <v>44.85</v>
+        <v>49.78</v>
       </c>
       <c r="I8" t="s">
         <v>49</v>
@@ -834,16 +834,16 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="F9">
-        <v>40.86</v>
+        <v>40.49</v>
       </c>
       <c r="G9">
-        <v>42.22</v>
+        <v>43.35</v>
       </c>
       <c r="H9">
-        <v>43.58</v>
+        <v>46.27</v>
       </c>
       <c r="I9" t="s">
         <v>49</v>
@@ -854,7 +854,7 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
         <v>46</v>
@@ -863,16 +863,16 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="F10">
-        <v>39.25</v>
+        <v>38.17</v>
       </c>
       <c r="G10">
-        <v>42.16</v>
+        <v>43.2</v>
       </c>
       <c r="H10">
-        <v>46.53</v>
+        <v>47.56</v>
       </c>
       <c r="I10" t="s">
         <v>49</v>
@@ -883,7 +883,7 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
         <v>46</v>
@@ -892,16 +892,16 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F11">
-        <v>38.14</v>
+        <v>39.52</v>
       </c>
       <c r="G11">
-        <v>41.71</v>
+        <v>43.15</v>
       </c>
       <c r="H11">
-        <v>46.03</v>
+        <v>48.09</v>
       </c>
       <c r="I11" t="s">
         <v>49</v>
@@ -912,7 +912,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
         <v>46</v>
@@ -921,16 +921,16 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F12">
-        <v>37.28</v>
+        <v>39.45</v>
       </c>
       <c r="G12">
-        <v>41.64</v>
+        <v>42.8</v>
       </c>
       <c r="H12">
-        <v>48.18</v>
+        <v>49.79</v>
       </c>
       <c r="I12" t="s">
         <v>49</v>
@@ -950,16 +950,16 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>16</v>
+        <v>117</v>
       </c>
       <c r="F13">
-        <v>35.58</v>
+        <v>33.38</v>
       </c>
       <c r="G13">
-        <v>39.97</v>
+        <v>42.63</v>
       </c>
       <c r="H13">
-        <v>43.4</v>
+        <v>48.59</v>
       </c>
       <c r="I13" t="s">
         <v>49</v>
@@ -982,13 +982,13 @@
         <v>10</v>
       </c>
       <c r="F14">
-        <v>34.61</v>
+        <v>37.62</v>
       </c>
       <c r="G14">
-        <v>38.01</v>
+        <v>42.44</v>
       </c>
       <c r="H14">
-        <v>40.99</v>
+        <v>45.43</v>
       </c>
       <c r="I14" t="s">
         <v>49</v>
@@ -999,7 +999,7 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s">
         <v>46</v>
@@ -1011,16 +1011,16 @@
         <v>3</v>
       </c>
       <c r="F15">
-        <v>34.46</v>
+        <v>37.74</v>
       </c>
       <c r="G15">
-        <v>37.96</v>
+        <v>42.34</v>
       </c>
       <c r="H15">
-        <v>42.13</v>
+        <v>45.72</v>
       </c>
       <c r="I15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1037,19 +1037,19 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F16">
-        <v>32.5</v>
+        <v>38.46</v>
       </c>
       <c r="G16">
-        <v>37.84</v>
+        <v>42</v>
       </c>
       <c r="H16">
-        <v>45.78</v>
+        <v>48.74</v>
       </c>
       <c r="I16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1057,7 +1057,7 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C17" t="s">
         <v>46</v>
@@ -1066,19 +1066,19 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="F17">
-        <v>29.12</v>
+        <v>39.01</v>
       </c>
       <c r="G17">
-        <v>37.24</v>
+        <v>41.04</v>
       </c>
       <c r="H17">
-        <v>41.81</v>
+        <v>43.07</v>
       </c>
       <c r="I17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1095,19 +1095,19 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="F18">
-        <v>34.21</v>
+        <v>34.02</v>
       </c>
       <c r="G18">
-        <v>36.92</v>
+        <v>39.73</v>
       </c>
       <c r="H18">
-        <v>38.45</v>
+        <v>43.14</v>
       </c>
       <c r="I18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1124,19 +1124,19 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>65</v>
+        <v>4</v>
       </c>
       <c r="F19">
-        <v>28.98</v>
+        <v>39.45</v>
       </c>
       <c r="G19">
-        <v>36.39</v>
+        <v>39.45</v>
       </c>
       <c r="H19">
-        <v>41.92</v>
+        <v>39.45</v>
       </c>
       <c r="I19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1153,19 +1153,19 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F20">
-        <v>32.55</v>
+        <v>37.79</v>
       </c>
       <c r="G20">
-        <v>35.95</v>
+        <v>39.03</v>
       </c>
       <c r="H20">
-        <v>38.61</v>
+        <v>39.67</v>
       </c>
       <c r="I20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1173,7 +1173,7 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C21" t="s">
         <v>46</v>
@@ -1182,19 +1182,19 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>117</v>
+        <v>13</v>
       </c>
       <c r="F21">
-        <v>26.55</v>
+        <v>34.91</v>
       </c>
       <c r="G21">
-        <v>35.51</v>
+        <v>38.98</v>
       </c>
       <c r="H21">
-        <v>41.92</v>
+        <v>43.29</v>
       </c>
       <c r="I21" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -1202,7 +1202,7 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C22" t="s">
         <v>46</v>
@@ -1211,19 +1211,19 @@
         <v>47</v>
       </c>
       <c r="E22">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="F22">
-        <v>33.11</v>
+        <v>35.32</v>
       </c>
       <c r="G22">
-        <v>35.44</v>
+        <v>38.95</v>
       </c>
       <c r="H22">
-        <v>42.31</v>
+        <v>45.55</v>
       </c>
       <c r="I22" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1240,19 +1240,19 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F23">
-        <v>32.66</v>
+        <v>33.29</v>
       </c>
       <c r="G23">
-        <v>35.33</v>
+        <v>38.28</v>
       </c>
       <c r="H23">
-        <v>39.26</v>
+        <v>45.68</v>
       </c>
       <c r="I23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -1272,13 +1272,13 @@
         <v>5</v>
       </c>
       <c r="F24">
-        <v>29.31</v>
+        <v>33.52</v>
       </c>
       <c r="G24">
-        <v>35.2</v>
+        <v>37.99</v>
       </c>
       <c r="H24">
-        <v>37.59</v>
+        <v>42.38</v>
       </c>
       <c r="I24" t="s">
         <v>50</v>
@@ -1289,7 +1289,7 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C25" t="s">
         <v>46</v>
@@ -1298,16 +1298,16 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="F25">
-        <v>28.68</v>
+        <v>29.33</v>
       </c>
       <c r="G25">
-        <v>35.05</v>
+        <v>37.99</v>
       </c>
       <c r="H25">
-        <v>45.32</v>
+        <v>47.59</v>
       </c>
       <c r="I25" t="s">
         <v>50</v>
@@ -1327,16 +1327,16 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="F26">
-        <v>29.62</v>
+        <v>32.76</v>
       </c>
       <c r="G26">
-        <v>34.42</v>
+        <v>37.71</v>
       </c>
       <c r="H26">
-        <v>42</v>
+        <v>42.76</v>
       </c>
       <c r="I26" t="s">
         <v>50</v>
@@ -1356,16 +1356,16 @@
         <v>47</v>
       </c>
       <c r="E27">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F27">
-        <v>29.48</v>
+        <v>33.91</v>
       </c>
       <c r="G27">
-        <v>33.67</v>
+        <v>37.58</v>
       </c>
       <c r="H27">
-        <v>39.66</v>
+        <v>42.37</v>
       </c>
       <c r="I27" t="s">
         <v>50</v>
@@ -1376,7 +1376,7 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C28" t="s">
         <v>46</v>
@@ -1385,16 +1385,16 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F28">
-        <v>23.67</v>
+        <v>29.52</v>
       </c>
       <c r="G28">
-        <v>33</v>
+        <v>37.14</v>
       </c>
       <c r="H28">
-        <v>43.14</v>
+        <v>44.18</v>
       </c>
       <c r="I28" t="s">
         <v>50</v>
@@ -1414,16 +1414,16 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F29">
-        <v>28.34</v>
+        <v>33.79</v>
       </c>
       <c r="G29">
-        <v>32.73</v>
+        <v>36.95</v>
       </c>
       <c r="H29">
-        <v>34.42</v>
+        <v>40.19</v>
       </c>
       <c r="I29" t="s">
         <v>50</v>
@@ -1446,13 +1446,13 @@
         <v>19</v>
       </c>
       <c r="F30">
-        <v>28.44</v>
+        <v>33.23</v>
       </c>
       <c r="G30">
-        <v>32.14</v>
+        <v>36.54</v>
       </c>
       <c r="H30">
-        <v>40.88</v>
+        <v>42.37</v>
       </c>
       <c r="I30" t="s">
         <v>50</v>
@@ -1475,13 +1475,13 @@
         <v>12</v>
       </c>
       <c r="F31">
-        <v>26</v>
+        <v>28.39</v>
       </c>
       <c r="G31">
-        <v>31.94</v>
+        <v>36.13</v>
       </c>
       <c r="H31">
-        <v>38.86</v>
+        <v>43.71</v>
       </c>
       <c r="I31" t="s">
         <v>50</v>
@@ -1492,7 +1492,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C32" t="s">
         <v>46</v>
@@ -1501,16 +1501,16 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F32">
-        <v>28.45</v>
+        <v>32.4</v>
       </c>
       <c r="G32">
-        <v>30.16</v>
+        <v>33.49</v>
       </c>
       <c r="H32">
-        <v>34.16</v>
+        <v>35.66</v>
       </c>
       <c r="I32" t="s">
         <v>50</v>
@@ -1521,7 +1521,7 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C33" t="s">
         <v>46</v>
@@ -1533,13 +1533,13 @@
         <v>4</v>
       </c>
       <c r="F33">
-        <v>29.12</v>
+        <v>28.84</v>
       </c>
       <c r="G33">
-        <v>29.12</v>
+        <v>31.18</v>
       </c>
       <c r="H33">
-        <v>29.12</v>
+        <v>34.33</v>
       </c>
       <c r="I33" t="s">
         <v>50</v>
@@ -1562,13 +1562,13 @@
         <v>2</v>
       </c>
       <c r="F34">
-        <v>27.93</v>
+        <v>30.69</v>
       </c>
       <c r="G34">
-        <v>27.93</v>
+        <v>30.69</v>
       </c>
       <c r="H34">
-        <v>27.93</v>
+        <v>30.69</v>
       </c>
       <c r="I34" t="s">
         <v>50</v>

--- a/data/FARS_FWI_GeoReport.xlsx
+++ b/data/FARS_FWI_GeoReport.xlsx
@@ -46,6 +46,9 @@
     <t>طبقه خطر</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع مل بلند</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع کوه دراء</t>
   </si>
   <si>
@@ -55,87 +58,84 @@
     <t>منطقه حفاظت شده ارژن و پريشان</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع مل بلند</t>
+    <t>منطقه شکار ممنوع شیکوه</t>
   </si>
   <si>
     <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
   </si>
   <si>
+    <t>منطقه حفاظت شده تنگ بستانک</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده میانجنگل فسا</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بناب</t>
+  </si>
+  <si>
     <t>منطقه شکار ممنوع پادنا</t>
   </si>
   <si>
-    <t>منطقه حفاظت شده میانجنگل فسا</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بناب</t>
+    <t>پناهگاه حيات وحش بختگان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممن.ع آق جلو</t>
   </si>
   <si>
     <t>پارک ملي بختگان</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع کوه گورم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه سياه</t>
+  </si>
+  <si>
     <t>منطقه حفاظت شده ماله گاله</t>
   </si>
   <si>
+    <t>پارک ملی بمو</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع خرمنکوه</t>
+  </si>
+  <si>
+    <t>منطقه حفاظت شده برم فیروز</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع بصيران</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع کوه خرسي</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مهارلو</t>
+  </si>
+  <si>
     <t>منطقه حفاظت شده بهرام گور</t>
   </si>
   <si>
-    <t>پناهگاه حيات وحش بختگان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مهارلو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع شیکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه گورم</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممن.ع آق جلو</t>
-  </si>
-  <si>
     <t>منطقه شکار ممنوع کوه هوا و</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع کوه خم</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع مزايجان</t>
+  </si>
+  <si>
+    <t>منطقه شکار ممنوع دره باغ</t>
+  </si>
+  <si>
     <t>پارک ملي قطرويه</t>
   </si>
   <si>
+    <t>منطقه شکار ممنوع روشن کوه</t>
+  </si>
+  <si>
     <t>منطقه حفاظت شده هرمود</t>
   </si>
   <si>
-    <t>منطقه شکار ممنوع کوه سياه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خرسي</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع روشن کوه</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده تنگ بستانک</t>
-  </si>
-  <si>
-    <t>منطقه حفاظت شده برم فیروز</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع خرمنکوه</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع مزايجان</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع بصيران</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع کوه خم</t>
-  </si>
-  <si>
-    <t>پارک ملی بمو</t>
-  </si>
-  <si>
-    <t>منطقه شکار ممنوع دره باغ</t>
-  </si>
-  <si>
     <t>پناهگاه حيات وحش دره باغ</t>
   </si>
   <si>
@@ -157,10 +157,10 @@
     <t>مناطق ممنوعه شکار</t>
   </si>
   <si>
-    <t>1405-08-09</t>
-  </si>
-  <si>
-    <t>2026-10-31</t>
+    <t>1405-08-10</t>
+  </si>
+  <si>
+    <t>2026-11-01</t>
   </si>
   <si>
     <t>شدید</t>
@@ -631,16 +631,16 @@
         <v>47</v>
       </c>
       <c r="E2">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>53.59</v>
+        <v>52.45</v>
       </c>
       <c r="G2">
-        <v>56.56</v>
+        <v>57.09</v>
       </c>
       <c r="H2">
-        <v>60.2</v>
+        <v>62.01</v>
       </c>
       <c r="I2" t="s">
         <v>48</v>
@@ -660,19 +660,19 @@
         <v>47</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F3">
-        <v>48.31</v>
+        <v>51.83</v>
       </c>
       <c r="G3">
-        <v>49.14</v>
+        <v>54.86</v>
       </c>
       <c r="H3">
-        <v>49.63</v>
+        <v>60.87</v>
       </c>
       <c r="I3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -680,7 +680,7 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C4" t="s">
         <v>46</v>
@@ -689,19 +689,19 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>41.53</v>
+        <v>53.1</v>
       </c>
       <c r="G4">
-        <v>48.87</v>
+        <v>54.27</v>
       </c>
       <c r="H4">
-        <v>53.88</v>
+        <v>55.23</v>
       </c>
       <c r="I4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -709,7 +709,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
         <v>46</v>
@@ -718,19 +718,19 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F5">
-        <v>42.95</v>
+        <v>44.58</v>
       </c>
       <c r="G5">
-        <v>47.15</v>
+        <v>51.61</v>
       </c>
       <c r="H5">
-        <v>50.17</v>
+        <v>56.52</v>
       </c>
       <c r="I5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -738,7 +738,7 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
         <v>46</v>
@@ -750,16 +750,16 @@
         <v>3</v>
       </c>
       <c r="F6">
-        <v>43.85</v>
+        <v>48.88</v>
       </c>
       <c r="G6">
-        <v>45.79</v>
+        <v>51.25</v>
       </c>
       <c r="H6">
-        <v>46.99</v>
+        <v>53.84</v>
       </c>
       <c r="I6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -767,7 +767,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
         <v>46</v>
@@ -776,19 +776,19 @@
         <v>47</v>
       </c>
       <c r="E7">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>42.66</v>
+        <v>49.85</v>
       </c>
       <c r="G7">
-        <v>45.36</v>
+        <v>50.95</v>
       </c>
       <c r="H7">
-        <v>49.13</v>
+        <v>52.3</v>
       </c>
       <c r="I7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -805,16 +805,16 @@
         <v>47</v>
       </c>
       <c r="E8">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F8">
-        <v>36.66</v>
+        <v>42.37</v>
       </c>
       <c r="G8">
-        <v>44.04</v>
+        <v>48.52</v>
       </c>
       <c r="H8">
-        <v>49.78</v>
+        <v>52.4</v>
       </c>
       <c r="I8" t="s">
         <v>49</v>
@@ -825,7 +825,7 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s">
         <v>46</v>
@@ -834,16 +834,16 @@
         <v>47</v>
       </c>
       <c r="E9">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F9">
-        <v>40.49</v>
+        <v>45.05</v>
       </c>
       <c r="G9">
-        <v>43.35</v>
+        <v>48.32</v>
       </c>
       <c r="H9">
-        <v>46.27</v>
+        <v>52.64</v>
       </c>
       <c r="I9" t="s">
         <v>49</v>
@@ -854,7 +854,7 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
         <v>46</v>
@@ -863,16 +863,16 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="F10">
-        <v>38.17</v>
+        <v>44.12</v>
       </c>
       <c r="G10">
-        <v>43.2</v>
+        <v>47.78</v>
       </c>
       <c r="H10">
-        <v>47.56</v>
+        <v>52.22</v>
       </c>
       <c r="I10" t="s">
         <v>49</v>
@@ -883,7 +883,7 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s">
         <v>46</v>
@@ -892,16 +892,16 @@
         <v>47</v>
       </c>
       <c r="E11">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F11">
-        <v>39.52</v>
+        <v>45.49</v>
       </c>
       <c r="G11">
-        <v>43.15</v>
+        <v>47.65</v>
       </c>
       <c r="H11">
-        <v>48.09</v>
+        <v>52.42</v>
       </c>
       <c r="I11" t="s">
         <v>49</v>
@@ -921,16 +921,16 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="F12">
-        <v>39.45</v>
+        <v>38</v>
       </c>
       <c r="G12">
-        <v>42.8</v>
+        <v>46.62</v>
       </c>
       <c r="H12">
-        <v>49.79</v>
+        <v>54.11</v>
       </c>
       <c r="I12" t="s">
         <v>49</v>
@@ -941,7 +941,7 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s">
         <v>46</v>
@@ -950,16 +950,16 @@
         <v>47</v>
       </c>
       <c r="E13">
-        <v>117</v>
+        <v>2</v>
       </c>
       <c r="F13">
-        <v>33.38</v>
+        <v>45.29</v>
       </c>
       <c r="G13">
-        <v>42.63</v>
+        <v>46.28</v>
       </c>
       <c r="H13">
-        <v>48.59</v>
+        <v>47.27</v>
       </c>
       <c r="I13" t="s">
         <v>49</v>
@@ -970,7 +970,7 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
         <v>46</v>
@@ -979,16 +979,16 @@
         <v>47</v>
       </c>
       <c r="E14">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="F14">
-        <v>37.62</v>
+        <v>38</v>
       </c>
       <c r="G14">
-        <v>42.44</v>
+        <v>46.15</v>
       </c>
       <c r="H14">
-        <v>45.43</v>
+        <v>53.7</v>
       </c>
       <c r="I14" t="s">
         <v>49</v>
@@ -1008,16 +1008,16 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="F15">
-        <v>37.74</v>
+        <v>41.45</v>
       </c>
       <c r="G15">
-        <v>42.34</v>
+        <v>46.12</v>
       </c>
       <c r="H15">
-        <v>45.72</v>
+        <v>53.95</v>
       </c>
       <c r="I15" t="s">
         <v>49</v>
@@ -1037,16 +1037,16 @@
         <v>47</v>
       </c>
       <c r="E16">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F16">
-        <v>38.46</v>
+        <v>42.47</v>
       </c>
       <c r="G16">
-        <v>42</v>
+        <v>46.06</v>
       </c>
       <c r="H16">
-        <v>48.74</v>
+        <v>49.48</v>
       </c>
       <c r="I16" t="s">
         <v>49</v>
@@ -1057,7 +1057,7 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
         <v>46</v>
@@ -1066,16 +1066,16 @@
         <v>47</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F17">
-        <v>39.01</v>
+        <v>44.4</v>
       </c>
       <c r="G17">
-        <v>41.04</v>
+        <v>46.01</v>
       </c>
       <c r="H17">
-        <v>43.07</v>
+        <v>48.83</v>
       </c>
       <c r="I17" t="s">
         <v>49</v>
@@ -1086,7 +1086,7 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
         <v>46</v>
@@ -1095,16 +1095,16 @@
         <v>47</v>
       </c>
       <c r="E18">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="F18">
-        <v>34.02</v>
+        <v>39.71</v>
       </c>
       <c r="G18">
-        <v>39.73</v>
+        <v>45.81</v>
       </c>
       <c r="H18">
-        <v>43.14</v>
+        <v>57.57</v>
       </c>
       <c r="I18" t="s">
         <v>49</v>
@@ -1115,7 +1115,7 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C19" t="s">
         <v>46</v>
@@ -1124,16 +1124,16 @@
         <v>47</v>
       </c>
       <c r="E19">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F19">
-        <v>39.45</v>
+        <v>42.09</v>
       </c>
       <c r="G19">
-        <v>39.45</v>
+        <v>43.65</v>
       </c>
       <c r="H19">
-        <v>39.45</v>
+        <v>45.76</v>
       </c>
       <c r="I19" t="s">
         <v>49</v>
@@ -1153,16 +1153,16 @@
         <v>47</v>
       </c>
       <c r="E20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F20">
-        <v>37.79</v>
+        <v>35.06</v>
       </c>
       <c r="G20">
-        <v>39.03</v>
+        <v>43.38</v>
       </c>
       <c r="H20">
-        <v>39.67</v>
+        <v>50.68</v>
       </c>
       <c r="I20" t="s">
         <v>49</v>
@@ -1182,16 +1182,16 @@
         <v>47</v>
       </c>
       <c r="E21">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F21">
-        <v>34.91</v>
+        <v>36.04</v>
       </c>
       <c r="G21">
-        <v>38.98</v>
+        <v>42.87</v>
       </c>
       <c r="H21">
-        <v>43.29</v>
+        <v>55.51</v>
       </c>
       <c r="I21" t="s">
         <v>49</v>
@@ -1214,13 +1214,13 @@
         <v>62</v>
       </c>
       <c r="F22">
-        <v>35.32</v>
+        <v>37.48</v>
       </c>
       <c r="G22">
-        <v>38.95</v>
+        <v>42.22</v>
       </c>
       <c r="H22">
-        <v>45.55</v>
+        <v>52.74</v>
       </c>
       <c r="I22" t="s">
         <v>49</v>
@@ -1240,16 +1240,16 @@
         <v>47</v>
       </c>
       <c r="E23">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F23">
-        <v>33.29</v>
+        <v>39.78</v>
       </c>
       <c r="G23">
-        <v>38.28</v>
+        <v>42.08</v>
       </c>
       <c r="H23">
-        <v>45.68</v>
+        <v>44.9</v>
       </c>
       <c r="I23" t="s">
         <v>49</v>
@@ -1269,19 +1269,19 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="F24">
-        <v>33.52</v>
+        <v>36.69</v>
       </c>
       <c r="G24">
-        <v>37.99</v>
+        <v>41.88</v>
       </c>
       <c r="H24">
-        <v>42.38</v>
+        <v>48.24</v>
       </c>
       <c r="I24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -1289,7 +1289,7 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C25" t="s">
         <v>46</v>
@@ -1298,19 +1298,19 @@
         <v>47</v>
       </c>
       <c r="E25">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="F25">
-        <v>29.33</v>
+        <v>36.29</v>
       </c>
       <c r="G25">
-        <v>37.99</v>
+        <v>41.7</v>
       </c>
       <c r="H25">
-        <v>47.59</v>
+        <v>48.04</v>
       </c>
       <c r="I25" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -1327,19 +1327,19 @@
         <v>47</v>
       </c>
       <c r="E26">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F26">
-        <v>32.76</v>
+        <v>37.07</v>
       </c>
       <c r="G26">
-        <v>37.71</v>
+        <v>41.21</v>
       </c>
       <c r="H26">
-        <v>42.76</v>
+        <v>44.36</v>
       </c>
       <c r="I26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -1359,16 +1359,16 @@
         <v>15</v>
       </c>
       <c r="F27">
-        <v>33.91</v>
+        <v>37.25</v>
       </c>
       <c r="G27">
-        <v>37.58</v>
+        <v>41</v>
       </c>
       <c r="H27">
-        <v>42.37</v>
+        <v>43.69</v>
       </c>
       <c r="I27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -1385,19 +1385,19 @@
         <v>47</v>
       </c>
       <c r="E28">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="F28">
-        <v>29.52</v>
+        <v>33.33</v>
       </c>
       <c r="G28">
-        <v>37.14</v>
+        <v>40.18</v>
       </c>
       <c r="H28">
-        <v>44.18</v>
+        <v>45.39</v>
       </c>
       <c r="I28" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -1405,7 +1405,7 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C29" t="s">
         <v>46</v>
@@ -1414,19 +1414,19 @@
         <v>47</v>
       </c>
       <c r="E29">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F29">
-        <v>33.79</v>
+        <v>39.83</v>
       </c>
       <c r="G29">
-        <v>36.95</v>
+        <v>39.83</v>
       </c>
       <c r="H29">
-        <v>40.19</v>
+        <v>39.83</v>
       </c>
       <c r="I29" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -1434,7 +1434,7 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C30" t="s">
         <v>46</v>
@@ -1443,19 +1443,19 @@
         <v>47</v>
       </c>
       <c r="E30">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F30">
-        <v>33.23</v>
+        <v>37.07</v>
       </c>
       <c r="G30">
-        <v>36.54</v>
+        <v>39.58</v>
       </c>
       <c r="H30">
-        <v>42.37</v>
+        <v>43.09</v>
       </c>
       <c r="I30" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -1463,7 +1463,7 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C31" t="s">
         <v>46</v>
@@ -1472,19 +1472,19 @@
         <v>47</v>
       </c>
       <c r="E31">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F31">
-        <v>28.39</v>
+        <v>37.31</v>
       </c>
       <c r="G31">
-        <v>36.13</v>
+        <v>39.36</v>
       </c>
       <c r="H31">
-        <v>43.71</v>
+        <v>41.97</v>
       </c>
       <c r="I31" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -1504,16 +1504,16 @@
         <v>3</v>
       </c>
       <c r="F32">
-        <v>32.4</v>
+        <v>36.47</v>
       </c>
       <c r="G32">
-        <v>33.49</v>
+        <v>38.9</v>
       </c>
       <c r="H32">
-        <v>35.66</v>
+        <v>43.1</v>
       </c>
       <c r="I32" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -1533,13 +1533,13 @@
         <v>4</v>
       </c>
       <c r="F33">
-        <v>28.84</v>
+        <v>33.43</v>
       </c>
       <c r="G33">
-        <v>31.18</v>
+        <v>34.94</v>
       </c>
       <c r="H33">
-        <v>34.33</v>
+        <v>38.61</v>
       </c>
       <c r="I33" t="s">
         <v>50</v>
@@ -1562,13 +1562,13 @@
         <v>2</v>
       </c>
       <c r="F34">
-        <v>30.69</v>
+        <v>32.3</v>
       </c>
       <c r="G34">
-        <v>30.69</v>
+        <v>32.3</v>
       </c>
       <c r="H34">
-        <v>30.69</v>
+        <v>32.3</v>
       </c>
       <c r="I34" t="s">
         <v>50</v>
